--- a/data/us_missile_range_data.xlsx
+++ b/data/us_missile_range_data.xlsx
@@ -2206,10 +2206,10 @@
         <v>27</v>
       </c>
       <c r="H2">
-        <v>32.3829</v>
+        <v>32.3831</v>
       </c>
       <c r="I2">
-        <v>-106.4783</v>
+        <v>-106.4781</v>
       </c>
       <c r="J2" t="s">
         <v>28</v>
@@ -2268,10 +2268,10 @@
         <v>42</v>
       </c>
       <c r="H3">
-        <v>34.742</v>
+        <v>34.7333</v>
       </c>
       <c r="I3">
-        <v>-120.5724</v>
+        <v>-120.5667</v>
       </c>
       <c r="J3" t="s">
         <v>28</v>
@@ -2392,10 +2392,10 @@
         <v>62</v>
       </c>
       <c r="H5">
-        <v>9.3948</v>
+        <v>8.7181</v>
       </c>
       <c r="I5">
-        <v>167.471</v>
+        <v>167.7328</v>
       </c>
       <c r="J5" t="s">
         <v>28</v>
@@ -2451,10 +2451,10 @@
         <v>70</v>
       </c>
       <c r="H6">
-        <v>22.0227</v>
+        <v>22.0394</v>
       </c>
       <c r="I6">
-        <v>-159.785</v>
+        <v>-159.7853</v>
       </c>
       <c r="J6" t="s">
         <v>28</v>
@@ -2513,10 +2513,10 @@
         <v>80</v>
       </c>
       <c r="H7">
-        <v>37.9402</v>
+        <v>37.94</v>
       </c>
       <c r="I7">
-        <v>-75.4664</v>
+        <v>-75.4661</v>
       </c>
       <c r="J7" t="s">
         <v>28</v>
@@ -2572,10 +2572,10 @@
         <v>52</v>
       </c>
       <c r="H8">
-        <v>30.4727</v>
+        <v>30.475</v>
       </c>
       <c r="I8">
-        <v>-86.5264</v>
+        <v>-86.5256</v>
       </c>
       <c r="J8" t="s">
         <v>28</v>
@@ -2631,7 +2631,7 @@
         <v>98</v>
       </c>
       <c r="H9">
-        <v>65.1296</v>
+        <v>65.1211</v>
       </c>
       <c r="I9">
         <v>-147.47</v>
@@ -2690,10 +2690,10 @@
         <v>107</v>
       </c>
       <c r="H10">
-        <v>37.7988</v>
+        <v>37.7981</v>
       </c>
       <c r="I10">
-        <v>-116.7809</v>
+        <v>-116.7806</v>
       </c>
       <c r="J10" t="s">
         <v>28</v>
@@ -2749,10 +2749,10 @@
         <v>98</v>
       </c>
       <c r="H11">
-        <v>57.4358</v>
+        <v>57.4333</v>
       </c>
       <c r="I11">
-        <v>-152.3378</v>
+        <v>-152.3333</v>
       </c>
       <c r="J11" t="s">
         <v>28</v>

--- a/data/us_missile_range_data.xlsx
+++ b/data/us_missile_range_data.xlsx
@@ -780,7 +780,9 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>A launch center used between 1975 and 1979 for testing German OTRAG rockets. The site achieved suborbital altitudes before operations were moved to Libya.</t>
+          <t>The **Shaba North, Kapani Tonneo OTRAG Launch Center** was a rocket launch facility located in Zaire (the modern-day Democratic Republic of the Congo) [SRC-0095]. Geographically situated at coordinates 7°55′33″S 28°31′40″E, the launch site was established and became operational in the mid-1970s [SRC-0095].
+The Kapani Tonneo facility was primarily utilized for the testing and launching of German OTRAG rockets [SRC-0095]. During its active operational period, which spanned from 1975 to 1979, the site hosted a total of three rocket launches [SRC-0095, SRC-0095]. These test flights were strictly suborbital, with the launched rockets achieving a maximum altitude of less than 50 kilometers above the launch site [SRC-0095]. 
+Following this initial phase of testing, the OTRAG launch site in Zaire was officially closed [SRC-0095]. Consequently, the testing of the German OTRAG rockets was relocated to a new facility in North Africa [SRC-0095]. Subsequent launch operations were moved to the Sabha, Tawiwa OTRAG Launch Center in Libya, which took over the rocket testing activities from 1981 to 1987 [SRC-0095]. Beyond these basic operational parameters and flight records, the provided sources do not contain further detailed information regarding the site's governing organization, specific radar and telemetry installations, or its ongoing physical status after its closure in the late 1970s [SRC-0095, SRC-0095, SRC-0095].</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -796,6 +798,11 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>SRC-0095</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1071,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>First Argentine launch site, operated from 1961 to 1962.</t>
+          <t>Pampa de Achala is a rocket launch site located in Argentina at the geographical coordinates of 31°35′00″S 64°50′00″W [SRC-0096]. It holds historical significance as the very first rocket launch site established in Argentina [SRC-0096]. The facility was operational for a brief period between 1961 and 1962 [SRC-0096]. During its active years, Pampa de Achala hosted a total of eight rocket launches [SRC-0096]. The rockets launched from this location were relatively small in scale; the heaviest rocket recorded had a total mass of 28 kilograms, and the highest altitude achieved by a launch from this site was 25 kilometers [SRC-0096]. While detailed records of the governing organization and broader history are not provided in the sources, its status as the nation's inaugural launch site marks its importance in Argentine aerospace history.</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1080,6 +1087,11 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1218,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Used in 1966 for Titus rocket launches during a solar eclipse.</t>
+          <t>Las Palmas is an Argentine rocket launch facility situated at the coordinates 27°05′43″S 58°45′13″W [SRC-0096]. The operational history of the site was extremely brief, with all known launch activities taking place entirely in the year 1966 [SRC-0096]. Las Palmas is notable for being used to conduct rocket launches specifically during a solar eclipse [SRC-0096]. During this time, the site hosted a total of two launches utilizing Titus rockets [SRC-0096]. These missions featured significantly larger vehicles than Argentina's earliest rocket tests, with the heaviest rocket launched from Las Palmas weighing 3,400 kilograms [SRC-0096]. The flights were successful in reaching the upper atmosphere, achieving a maximum altitude of 270 kilometers [SRC-0096].</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1222,6 +1234,11 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1272,7 +1289,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Hosted sounding rocket launches during a 1966 solar eclipse.</t>
+          <t>Tartagal is a rocket launch site located in Argentina at the geographical coordinates 22°45′42″S 63°49′26″W [SRC-0096]. Similar to the Las Palmas site, Tartagal's operational activities were strictly confined to the year 1966 [SRC-0096]. The facility was utilized to conduct launch operations specifically coinciding with a solar eclipse [SRC-0096]. The available sources do not provide further detailed information regarding the exact number of launches conducted, the types or mass of the rockets used, the specific governing organization, or the maximum altitude achieved by the missions launched from this location [SRC-0096].</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1288,6 +1305,11 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1360,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Rocket launch site active from 1968 to 1972.</t>
+          <t>Mar Chiquita served as a rocket launch facility in Argentina, positioned at the coordinates 37°43′27″S 57°24′18″W [SRC-0096]. The site maintained an operational status over a span of five years, from 1968 until 1972 [SRC-0096]. Throughout its period of activity, Mar Chiquita was the site of 11 rocket launches [SRC-0096]. The provided sources do not contain further detailed information such as the founding organization, the specific models or masses of the rockets launched, or the highest altitude reached by missions originating from this site [SRC-0096].</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1354,6 +1376,11 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1404,7 +1431,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Hosted a pair of rocket launches in 1973.</t>
+          <t>Villa Reynolds is a rocket launch site located in Argentina at the coordinates 33°43′29″S 65°22′38″W [SRC-0096]. The facility had a very short operational history, with its launch activity recorded solely in the year 1973 [SRC-0096]. During its operational window, the site hosted a total of two rocket launches [SRC-0096]. Additional detailed information, including the types of rockets tested, their payload mass, the apogees achieved during flight, or the specific governing organization overseeing the launches, is not available in the provided sources [SRC-0096].</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1420,6 +1447,11 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1502,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Conducted the Gradicom I military rocket test in 2009.</t>
+          <t>Serrezuela is an Argentine rocket launch site situated at the geographical coordinates 30°38′00″S 65°23′00″W [SRC-0096]. Unlike Argentina's older sounding rocket ranges from the 1960s and 1970s, Serrezuela was active in the 21st century, specifically in the year 2009 [SRC-0096]. The site was utilized to conduct a military test of the Gradicom I rocket, marking its sole recorded launch [SRC-0096]. The rocket fired from the Serrezuela facility had a mass of 500 kilograms and successfully reached an altitude of 40 kilometers [SRC-0096]. Further details regarding the site's ongoing status or additional facilities are not documented in the sources.</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1486,6 +1518,11 @@
       <c r="V14" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2171,9 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Saskatchewan launch site that hosted sounding rockets in 1980.</t>
+          <t>Southend is a Canadian rocket launch site located in the province of Saskatchewan, specifically positioned at the geographical coordinates of 56°12′N 103°08′W [SRC-0096]. While the provided sources do not offer a comprehensive history, specific founding year, or information regarding the governing organization that managed the facility, they do confirm that the Southend site was active and operational during the year 1980 [SRC-0096]. Over the course of its operational history, the site is recorded to have hosted a total of two rocket launches [SRC-0096].
+In terms of technical capabilities and launch milestones, the heaviest rocket launched from the Southend facility had a total lift-off mass of 1,200 kg [SRC-0096]. Furthermore, operations at the site were capable of reaching into the upper atmosphere and suborbital space, with the highest achieved altitude recorded at 156 kilometers above the launch site [SRC-0096]. The site is also documented in aerospace reference materials, such as Mark Wade's Encyclopedia Astronautica [SRC-0096]. 
+The available source material does not contain further detailed information regarding the presence of specific key facilities, tracking radars, ground support infrastructure, or notable mission designations. Additionally, the current operational status of the Southend launch site is not described in the provided texts.</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2150,6 +2189,11 @@
       <c r="V23" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2788,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Used as a fixed platform site for testing the Rayo tactical rocket in 1991.</t>
+          <t>Pampa de Tamarugal is a geographic region in Chile that has served as a critical testing ground for the country's military and aerospace developments, operating primarily under the auspices of the state-owned defense enterprise Fábricas y Maestranzas del Ejército (FAMAE) [SRC-0058], [SRC-0221]. Following the restoration of democratic governance in Chile in 1990, the site became instrumental in advancing the nation's indigenous missile and rocket capabilities [SRC-0058]. Notably, in 1991, Pampa de Tamarugal hosted the successful test-firing of the Proyecto Rayo tactical rocket [SRC-0058]. This unguided earth-to-earth multiple launch rocket system (MLRS), developed in a strategic partnership with the British firm Royal Ordnance, was launched from a fixed platform at the site [SRC-0058], [SRC-0058], [SRC-0221]. The Rayo rocket featured a 160 mm caliber and a maximum effective range exceeding 45 kilometers, originally designed to demonstrate the technological capabilities of the emerging Chilean arms industry and to appeal to export markets during the Cold War era [SRC-0058], [SRC-0058], [SRC-0059]. While the Rayo project was ultimately canceled from a commercial standpoint in 2002 due to shifts in global arms markets and a modern preference for precision-guided munitions, the tests conducted at Pampa de Tamarugal laid the foundational technology for future artillery systems [SRC-0059], [SRC-0059]. Today, the technological legacy of the test launches at Pampa de Tamarugal lives on in the modern FAMAE SLM (Sistema de Lanzamiento Múltiple) system, which adapted the subsystems and technologies proven at the site to create a highly versatile 160 mm and 306 mm rocket launcher platform [SRC-0059], [SRC-0059].</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -2760,6 +2804,11 @@
       <c r="V32" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>SRC-0058, SRC-0221, SRC-0059</t>
         </is>
       </c>
     </row>
@@ -2815,7 +2864,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Military field used since the 1970s for testing artillery, rockets, and munitions.</t>
+          <t>Peldehue is a prominent military field and weapons testing facility in Chile, utilized heavily by Fábricas y Maestranzas del Ejército (FAMAE) for the development and validation of national defense technologies [SRC-0058], [SRC-0058]. The site's historical significance is deeply tied to Chile's push for military self-sufficiency during the 1970s. Following the 1976 United States arms embargo imposed via the Kennedy Amendment, which restricted foreign military supplies due to human rights concerns under the military regime, FAMAE was forced to drastically intensify its domestic manufacturing efforts [SRC-0058], [SRC-0058]. In 1976, the Peldehue facility achieved a major milestone when it hosted the first successful test firing of a domestically produced 105 mm artillery projectile [SRC-0058], [SRC-0058]. This event marked Chile's transition toward a more comprehensive defense industrial base, significantly reducing its reliance on foreign imports for munitions and heavy weapons [SRC-0058]. In the modern era, Peldehue remains an active and vital proving ground for the Chilean Armed Forces. It is currently utilized for testing advanced artillery and rocket systems, most notably the FAMAE SLM (Sistema de Lanzamiento Múltiple) [SRC-0221]. The SLM is a highly capable multiple rocket launcher system mounted on a MAN 6x6 truck chassis, developed in collaboration with Israel Military Industries (IMI) and the Chilean firm DESA [SRC-0059], [SRC-0221]. At Peldehue, military engineers conduct tests on the SLM's ability to fire advanced munitions, including 160 mm Accular rockets and 306 mm EXTRA rockets, ensuring the operational readiness and technological sovereignty of Chile's modern artillery units [SRC-0059], [SRC-0059], [SRC-0221].</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -2831,6 +2880,11 @@
       <c r="V33" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>SRC-0058, SRC-0221, SRC-0059</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2940,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Testing location for the Oton MK40 70mm air-to-ground rocket.</t>
+          <t>Arica, located in northern Chile, serves as a strategic military testing site and operational area for the Chilean Armed Forces and the state-owned defense manufacturer Fábricas y Maestranzas del Ejército (FAMAE) [SRC-0039], [SRC-0221]. The military ranges in the area are utilized for conducting functional field tests and evaluating the performance of newly developed indigenous weaponry [SRC-0039], [SRC-0221]. Recently, Arica was the focal point for the testing of the Oton MK40, a new 70 mm air-to-ground rocket developed entirely in Chile [SRC-0039], [SRC-0039]. During these trials, the Chilean Army's Artillery Group No. 6 "Dolores," part of the 4th Motorized Brigade "Rancagua," provided essential logistical and operational support to FAMAE engineers [SRC-0039]. To thoroughly evaluate the weapon, the artillery group deployed a specialized observation patrol to monitor key performance parameters, including the rocket's range, dispersion, and overall reliability in realistic combat scenarios [SRC-0039]. The Oton MK40, which features a double-base extruded powder propellant and folding fins, is specifically designed for deployment from helicopters and low-speed aircraft to provide close air support and conduct armed reconnaissance [SRC-0039], [SRC-0039]. The successful execution of these tests at the Arica military ranges is a crucial step in validating the armament for active duty [SRC-0039]. By utilizing the Arica facilities for such evaluations, Chile continues to strengthen its strategic autonomy and technological independence, avoiding reliance on foreign suppliers and cementing FAMAE's position as a highly capable and advanced defense industry actor within the Latin American region [SRC-0039], [SRC-0039].</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -2902,6 +2956,11 @@
       <c r="V34" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>SRC-0039, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3671,9 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>Nerve center of Jiuquan's telemetry, tracking, and command network providing radar and optical tracking for launch vehicles.</t>
+          <t>The Dashuli Tracking Station is a crucial telemetry, tracking, and command (TT&amp;C) facility located 36 kilometers southwest of the South Launch Site at the Jiuquan Satellite Launch Centre in China [SRC-0084]. Originally constructed in 1968 to support early missile testing, the station has progressively evolved into the primary nerve center for Jiuquan's tracking and communication network, managing multiple optical and radar tracking posts distributed across the launch center [SRC-0084].
+The station plays a vital role during the initial phases of a rocket launch. It is responsible for tracking launch vehicles from the moment of take-off until approximately 500 seconds into the flight [SRC-0084]. To accomplish this, Dashuli utilizes an array of advanced equipment, including optical tracking telescopes, precision tracking radars, and telemetry antennas designed to receive critical measurement data from the launch vehicle's onboard systems [SRC-0084].
+Dashuli's infrastructure is comprehensive, comprising several integrated sub-systems dedicated to radar, optical tracking, communications, computer processing, meteorology, and technical and logistical support [SRC-0084]. The operational heart of the station is its control hall, which is equipped with over 30 control consoles [SRC-0084]. These consoles display 120 sets of real-time data that indicate the launch vehicle's trajectory and the live operational status of both the rocket and its payload [SRC-0084]. All gathered telemetry and tracking data are transmitted in real-time to the Mission Command and Control Centre (MCCC) at the Jiuquan headquarters to support critical decision-making during the launch process [SRC-0084].</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -3628,6 +3689,11 @@
       <c r="V44" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>SRC-0084</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3749,9 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>Central hub for China's satellite control network managing near-earth and geostationary orbital satellites.</t>
+          <t>The Xi'an Satellite Control Center (XSCC) is the primary command hub of China's satellite control network, managing the tracking, telemetry, control, and recovery of domestic and international spacecraft [SRC-0040, SRC-0040, SRC-0222]. Established as a cornerstone of China's aerospace capabilities, the XSCC is equipped to automatically develop real-time plans and simultaneously execute control over multiple satellites, with the historic capacity to handle up to six satellites at once [SRC-0040]. 
+The XSCC's technological infrastructure features a robust Central Computer System originally composed of NC12780 and VAX8700 computers interconnected via an Ethernet network known as the "Xin Xing He Qi" [SRC-0040]. This system provides high reliability and powerful processing capabilities to run multiple satellite control software programs simultaneously [SRC-0040]. A comprehensive monitoring display system provides operational staff with interactive tables and images detailing orbital flight information and crucial spacecraft engineering parameters [SRC-0040, SRC-0040].
+Software at the XSCC is divided into specialized categories for near-earth satellite tracking (including satellite recovery) and geostationary satellite tracking [SRC-0040, SRC-0040]. These systems manage telemetry processing, instruction generation, orbital determination and prediction, attitude control, and simulated maneuvers [SRC-0040]. The center also coordinates a network of five fixed near-earth tracking stations and specialized geostationary stations [SRC-0040, SRC-0040]. For geostationary missions, the XSCC operates in tandem with the Xiamen and Weinan control stations to manage spacecraft up to 40,000 kilometers in altitude [SRC-0040, SRC-0040]. In addition to its domestic operations, the XSCC houses an international satellite communication ground station that connects directly to the INTELSAT network, providing user-leased circuits to support the launch and control of overseas satellites [SRC-0040, SRC-0040].</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -3699,6 +3767,11 @@
       <c r="V45" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>SRC-0040, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -3754,7 +3827,9 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>Fixed near-earth satellite control station located in eastern China.</t>
+          <t>The Changchun Station is a tracking and telemetry facility that forms an integral part of China's near-earth satellite control network [SRC-0040]. Located in the eastern part of China, it operates as one of the country's five fixed near-earth satellite control stations, working in conjunction with sister stations located in Xiamen, Nanning, Weinan, and Kash [SRC-0040, SRC-0040].
+The primary operational mandate of the Changchun Station is to perform daily tracking, telemetry, and control over medium- and low-orbiting satellites [SRC-0040]. By cooperating seamlessly with the other fixed stations and the central Xi'an Satellite Control Center (XSCC), the Changchun facility helps ensure continuous monitoring and communication coverage for spacecraft passing through its designated geographic sector [SRC-0040, SRC-0040].
+Like other fixed stations in the network, the Changchun Station utilizes integrated systems to capture satellite telemetry, process tracking data, and transmit remote control instructions [SRC-0040, SRC-0040]. While specific equipment details for the Changchun site are limited in the available sources, stations within this near-earth network generally employ VHF/UHF control systems, precision tracking radars, and station computers that conduct preprocessing of orbit measurement data [SRC-0040, SRC-0040, SRC-0040]. This data is then exchanged with the Xi'an Satellite Control Center to facilitate real-time guidance, orbital analysis, and overall mission success [SRC-0040].</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -3770,6 +3845,11 @@
       <c r="V46" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -3825,7 +3905,9 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>Fixed station undertaking geostationary orbital satellite tracking, launch coverage, and daily control.</t>
+          <t>The Xiamen Station is a major dual-purpose telemetry, tracking, and control facility within the China Aerospace Control Network, operating out of eastern China [SRC-0040, SRC-0040]. It serves as one of the five fixed near-earth satellite control stations, conducting daily tracking and control for medium- and low-orbiting satellites [SRC-0040, SRC-0040]. Additionally, the Xiamen Station plays a vital role in China's Geostationary Orbital Satellite Control Network [SRC-0040].
+During launch operations, the Xiamen Station is responsible for tracking carrier rockets and managing perigee control missions for near-earth orbital satellites [SRC-0040]. For high-orbit missions, the station is equipped with unified C-band carrier wave control systems [SRC-0040]. Working in conjunction with onboard satellite transponders, this system enables the Xiamen Station to perform critical tracking orbit measurements (including distance, azimuth, and pitch angle), telemetry reception, and remote control over geostationary satellites operating at altitudes of up to 40,000 kilometers [SRC-0040, SRC-0040].
+To manage its complex responsibilities, the Xiamen Station utilizes a duplex computer operation system [SRC-0040]. This dual-computer setup allows the station to seamlessly process data, exchange information with the Xi'an Satellite Control Center, and execute attitude and orbit control over geostationary satellites [SRC-0040]. Furthermore, during mission preparation phases, the dual-computer architecture is utilized to conduct simulated satellite-to-earth reentry maneuvers, allowing one computer to simulate powered flight while the other operates as the live combat computer [SRC-0040, SRC-0040].</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -3841,6 +3923,11 @@
       <c r="V47" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -3896,7 +3983,8 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Fixed station providing carrier rocket flight coverage tracking and near-earth perigee control.</t>
+          <t>Nanning Station is a critical component of the China Aerospace Control Network, specifically operating as one of the five fixed near-earth satellite control stations deployed across the eastern, central, and western parts of China [SRC-0040]. As a primary tracking and control facility, Nanning Station is designed to cooperatively perform daily tracking and control operations for medium- and low-orbiting satellites [SRC-0040]. In addition to its standard near-earth responsibilities, the Nanning Station fulfills specialized roles during complex launch missions. It is specifically responsible for conducting carrier rocket flight coverage tracking measurements during the launch of geostationary satellites [SRC-0040]. Furthermore, the station is tasked with perigee control missions during near-earth orbital satellite launches [SRC-0040].
+To execute these missions, Nanning Station is equipped with a comprehensive suite of advanced tracking and communication technologies utilized across China's fixed network. This includes a VHF/UHF control system that features both dispersed and unified carrier-wave systems [SRC-0040]. The dispersed system utilizes a double-frequency velocimeter alongside a telemetry demodulation terminal to receive satellite telemetry signals, while independent remote control equipment manages ground-to-satellite instruction control and data insertion [SRC-0040], [SRC-0040]. The unified carrier-wave system employs a single antenna for both transmission and reception, adding essential distance and angle measurement capabilities [SRC-0040]. The station also relies on C-band monopulse precision tracking radars, which provide high precision and the ability to locate orbits with data, making them ideal for measuring satellite perigee periods and reentry orbits [SRC-0040], [SRC-0040]. Additionally, the facility utilizes integrated station computers and monitoring display systems to preprocess orbital measurement data, execute digital guidance, and conduct data exchange with the Xi'an Satellite Control Center [SRC-0040].</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -3912,6 +4000,11 @@
       <c r="V48" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -3967,7 +4060,8 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Fixed station conducting tracking and telemetry for both near-earth and high-orbiting geostationary satellites.</t>
+          <t>Weinan Station, located in central China, is a major fixed tracking and control facility within the China Aerospace Control Network [SRC-0040], [SRC-0040]. It serves a dual operational role, functioning both as a near-earth satellite control station and as a key node in the geostationary orbital satellite launch and control network [SRC-0040], [SRC-0040]. For its near-earth mission, Weinan cooperates with other fixed stations to perform daily tracking and control over medium- and low-orbiting satellites [SRC-0040]. However, its capabilities are notably expanded to undertake highly specialized missions involving geostationary orbital satellite launches and their long-term daily control [SRC-0040], [SRC-0040].
+As part of the geostationary control network, the Weinan Control Station is uniquely equipped with unified C-band carrier wave control systems [SRC-0040], [SRC-0040]. Working in conjunction with in-satellite transponders, this system performs tracking orbit measurements (including distance, azimuth, and pitch angle), telemetry (coding and simulation), and remote control (instruction and synchronous control) over high-orbiting satellites up to 40,000 kilometers in altitude [SRC-0040]. To manage these complex tasks, the Weinan station utilizes two computers operating in a duplex configuration [SRC-0040]. This dual-computer setup handles data processing, data exchange with the main satellite control center, attitude and orbit control, and the long-term supervision of geostationary satellites [SRC-0040]. During mission preparation periods, such as when carrying out satellite-to-earth reentry route simulating maneuver tests, one of these computers is dedicated to satellite powered simulation, while the other serves as the actual combat computer [SRC-0040], [SRC-0040].</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -3983,6 +4077,11 @@
       <c r="V49" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4038,7 +4137,8 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Fixed near-earth satellite control station located in western China.</t>
+          <t>Kashgar Station, referred to in operational documentation as Kash Station, is an aerospace tracking facility located in the western part of China [SRC-0040], [SRC-0040]. It operates as one of the five fixed near-earth satellite control stations within the broader China Aerospace Control Network, operating alongside other vital facilities like the Changchun, Xiamen, Nanning, and Weinan stations [SRC-0040]. The primary operational mission of the Kashgar Station is to perform daily tracking and control over medium- and low-orbiting satellites, working in close cooperation with the rest of the fixed station network to ensure continuous orbital coverage [SRC-0040].
+To fulfill its tracking and telemetry duties, the station relies on a standardized array of principal facilities deployed across China's fixed near-earth control stations. This includes sophisticated VHF/UHF control systems comprised of dispersed and unified carrier-wave architectures [SRC-0040]. These systems enable the station to measure distance-variation ratios, receive modulated satellite telemetry signals, and transmit remote control instructions and data insertions directly to spacecraft [SRC-0040], [SRC-0040]. Kashgar Station is also equipped with C-band monopulse precision tracking radars, which are essential for measuring satellite perigee periods and tracking reentry orbits due to their large number of measurement elements and high precision capabilities [SRC-0040], [SRC-0040]. Operations at the station are managed through integrated computers and monitoring display facilities that preprocess orbital measurement data and establish digital guidance for the control equipment [SRC-0040]. These computer systems also facilitate vital data exchange with the Xi'an Satellite Control Center, minimizing the reliance on standard communication voice channels [SRC-0040], [SRC-0040].</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4054,6 +4154,11 @@
       <c r="V50" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4214,9 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Command center for aerospace control and international satellite communications.</t>
+          <t>Beijing Command Center operates as a high-level strategic node within the China Aerospace Control Network, functioning directly under the authority of the National Defense Scientific and Engineering Committee [SRC-0040]. While primary satellite tracking, telemetry, and control (TT&amp;C) operations are executed by the Xi'an Satellite Control Center and its subordinate fixed and mobile stations, the Beijing Command Center serves a critical overarching command and communications role for the nation's spacefile operations [SRC-0040], [SRC-0040], [SRC-0040].
+The facility is heavily integrated into the network's long-distance communication infrastructure. Utilizing a combination of wire, wireless, and dedicated communication satellite lines, this network ensures reliable long-distance command communications, data transmission, and other essential service communications [SRC-0040]. This system connects the Beijing Command Center directly with the launch command control centers situated at various launch pads (such as Jiuquan, Xichang, and Taiyuan) and the main satellite control center [SRC-0040], [SRC-0040]. This robust connectivity ensures that the National Defense Scientific and Engineering Committee maintains continuous oversight and rapid coordination capabilities during complex aerospace missions.
+In addition to its domestic command responsibilities, the Beijing facility is a key hub for international space communications. International satellite communication ground stations have been established in Beijing, which can be directly connected to the global INTELSAT network [SRC-0040]. This capability allows the Beijing Command Center to provide user-leased circuits and facilitates international cooperation and data exchange, ensuring the synchronized execution of China's domestic and overseas satellite missions [SRC-0040], [SRC-0040].</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4125,6 +4232,11 @@
       <c r="V51" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4411,7 +4523,10 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>Safe and reliable launch facility in Balasore used for performance evaluation of rockets, missiles, and airborne weapons.</t>
+          <t>The Integrated Test Range (ITR) at Chandipur is a premier military test and evaluation center operated by the Defence Research and Development Organisation (DRDO) under India's Ministry of Defence [SRC-0075, SRC-0076]. Located in the Balasore district off the coast of Odisha, the facility provides safe and reliable launch infrastructure for the performance evaluation of rockets, ballistic missiles, and airborne weapon systems [SRC-0075, SRC-0073]. 
+While the exact founding year is not detailed in the provided sources, the ITR has long served as one of India's primary missile testing facilities for strategic and tactical development [SRC-0073]. The site is heavily equipped with high-performance range instrumentation designed to monitor flying objects from takeoff to impact [SRC-0075]. Key tracking facilities deployed along the coast include Electro-Optical Tracking Systems (EOTS), advanced radar networks, telemetry stations, and a real-time Central Computer System that captures precise location and vehicle health parameters throughout a missile's flight trajectory [SRC-0075, SRC-0076, SRC-0073].
+The ITR has hosted numerous notable activities, including developmental and user trials for the Prithvi, Akash, and Agni missile variants [SRC-0073]. Recently, the range facilitated the successful test-launch of the nuclear-capable Agni-1 short-range ballistic missile (SRBM) by the Strategic Forces Command (SFC) to validate operational parameters [SRC-0073, SRC-0057]. It has also hosted multiple successful flight-trials of the indigenous Very Short-Range Air Defence System (VSHORADS) against high-speed aerial targets [SRC-0050, SRC-0050]. 
+Currently, the Integrated Test Range remains fully active and is a crucial component of India's strategic defense modernization [SRC-0073]. The facility regularly conducts routine training and operational exercises, implementing strict safety protocols and temporary maritime restrictions in the Bay of Bengal during active launch operations [SRC-0073, SRC-0073].</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -4427,6 +4542,11 @@
       <c r="V55" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>SRC-0075, SRC-0076, SRC-0073, SRC-0057, SRC-0050</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4835,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Airbase that has operated transport and attack helicopters as well as UAV squadrons.</t>
+          <t>Tel Nof Airbase is an installation operated by the Israeli Air Force (IAF) [SRC-0139]. The facility has a long history as a critical hub for Israeli rotary-wing operations. In the 1950s, the 124 Squadron, known as the "Rolling Sword," was founded at Tel Nof as the very first helicopter squadron in the State of Israel [SRC-0139]. By 1962, Sikorsky S-58 helicopters belonging to this pioneering squadron were operating out of the base [SRC-0139]. The base later became home to Israel's attack helicopter fleet; in 1975, the 160 Squadron "First Cobra" was established at Tel Nof, equipped with the new AH-1 Cobra Tzefa attack helicopters [SRC-0139]. Eventually, both the 160 Squadron and the 124 Squadron were relocated from Tel Nof to Palmachim Airbase in 1979 and 1981, respectively [SRC-0139]. Tel Nof is also a primary operating location for Unit 669, the IAF's elite heliborne Combat Search and Rescue (CSAR) unit, which flies CH-53D Sea Stallion Yas'ur helicopters from the facility [SRC-0139, SRC-0139]. Furthermore, an IAI Searcher Hugla UAV was displayed at Tel Nof during Israel's Independence Day celebrations in April 2007 [SRC-0139]. Recently, since October 7, 2023, Tel Nof has played an active role in the Gaza war, with military drones operating around the clock from the base to gather intelligence and launch guided weapon attacks in support of advancing Israeli ground troops [SRC-0139].</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -4731,6 +4851,11 @@
       <c r="V59" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4911,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Israeli airbase that serves as a hub for UAV operations, including Heron 1 squadrons.</t>
+          <t>Hatzor Airbase is an operational military installation of the Israeli Air Force [SRC-0139]. While historical details regarding the facility's early years are limited in the available records, Hatzor has recently evolved into an important center for Israel's unmanned aerial vehicle (UAV) operations. In January 2023, the Israeli Air Force relocated the 200 Squadron, known as the "First UAV" squadron, from Palmachim Airbase to Hatzor Airbase [SRC-0139]. This squadron operates the Heron 1, also known as the Shoval, which is a key reconnaissance and surveillance drone [SRC-0139]. Following the outbreak of the Gaza war on October 7, 2023, Hatzor Airbase was utilized for continuous combat operations [SRC-0139]. Unmanned aerial vehicles stationed at Hatzor have been deployed in the airspace over the Gaza Strip around the clock [SRC-0139]. These drones perform a dual role: they collect vital battlefield intelligence and execute targeted strikes using guided weapons, working in close cooperation with Israeli ground troops to support their advances [SRC-0139].</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4802,6 +4927,11 @@
       <c r="V60" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4987,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Northern airbase operating drones for intelligence collection and aerial strikes.</t>
+          <t>Ramat David Airbase is a military installation operated by the Israeli Air Force [SRC-0139]. Historically, the base was the home of the 193 Squadron, named the "Defenders of the West," which provided critical aerial support for the Israeli Navy [SRC-0139]. The squadron operated a fleet of Eurocopter AS565 Panther Atalef helicopters specifically utilized for maritime patrol, maritime surveillance, and search and rescue (SAR) operations [SRC-0139]. The 193 Squadron was officially closed at Ramat David Airbase on August 31, 2025, prior to its planned reopening at Palmachim Airbase with newer SH-60 Seahawk helicopters [SRC-0139]. Following the start of the Gaza war on October 7, 2023, Ramat David Airbase was integrated into Israel's intense unmanned aerial vehicle (UAV) operations [SRC-0139]. Alongside other major Israeli bases, Ramat David serves as a launching point for military drones that operate continuously over the Gaza Strip [SRC-0139]. These continuous drone flights are dedicated to gathering real-time intelligence and launching guided weapons to support ground troop maneuvers [SRC-0139].</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -4873,6 +5003,11 @@
       <c r="V61" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5063,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Airbase forming part of the Israeli Air Force operational infrastructure.</t>
+          <t>Hatzerim Airbase is an installation of the Israeli Air Force situated in the southern region of the country [SRC-0139]. The airbase is prominently known for hosting the Israeli Air Force Museum, which preserves a variety of historical military aircraft and early unmanned aerial vehicles (UAVs) [SRC-0139, SRC-0139]. Among the artifacts preserved at the museum near Hatzerim are a 1950s-era Sikorsky S-55 helicopter, a Ryan Firebee Mabat UAV, and a Tadiran Mastiff UAV that originally belonged to the 200 Squadron [SRC-0139, SRC-0139]. In terms of active military operations, Hatzerim Airbase served as the home for the 123 Squadron, known as the "Desert Birds" [SRC-0139]. In 2002, this squadron was re-established at Hatzerim and equipped with a new fleet of UH-60 Black Hawk Yanshuf transport helicopters [SRC-0139]. The 123 Squadron operated out of Hatzerim Airbase for thirteen years, providing transport and logistical support, before the unit was relocated to Palmachim Airbase in 2015 [SRC-0139].</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -4944,6 +5079,11 @@
       <c r="V62" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5352,9 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>Forward-deployed AN/TPY-2 X-band radar site complementing Israel's multi-tier missile defense.</t>
+          <t>The AN/TPY-2 (Army/Navy Transportable Radar Surveillance) radar deployment in Israel serves as a critical component of the region's layered ballistic missile defense architecture [SRC-0012, SRC-0012]. The site is operated and supervised by the United States Army's 1st Space Brigade, specifically under the command of the 13th Missile Defence Battery [SRC-0012]. The United States agreed to provide this advanced radar system to Israel to complement the nation's existing domestic two-tier defense network, which includes the Arrow 2 and Patriot PAC-3 missile defense systems [SRC-0012].
+Manufactured by Raytheon, the AN/TPY-2 is an advanced, high-resolution X-band active electronically scanned array (AESA) radar [SRC-0011, SRC-0012]. It operates in the 8.55–10 GHz frequency range and features an antenna aperture of approximately 9.2 square meters [SRC-0012, SRC-0011]. Utilizing fully electronic beam steering, the radar provides near-instantaneous target updates and exceptional discrimination accuracy, distinguishing between lethal ballistic missile warheads and non-threats such as decoys or space clutter [SRC-0012, SRC-0011]. The system boasts a long-range detection capacity of 1,000 kilometers or more and can simultaneously track hundreds of targets during their midcourse and terminal flight phases [SRC-0011, SRC-0011]. 
+As a mobile, trailer-mounted system, the AN/TPY-2 integrates seamlessly with broader U.S. and allied missile defense networks, including the Command and Control, Battle Management, and Communications (C2BMC) architecture [SRC-0011, SRC-0011]. In its forward-based configuration in Israel, the radar detects ballistic missiles during their boost and early ascent phases, passing high-fidelity tracking and trajectory data downstream to fire control radars and interceptor systems [SRC-0012, SRC-0190]. This strategic deployment significantly extends the defense battlespace, providing vital early warning coverage against regional ballistic missile threats [SRC-0012, SRC-0011].</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -5228,6 +5370,11 @@
       <c r="V66" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>SRC-0012, SRC-0011, SRC-0190</t>
         </is>
       </c>
     </row>
@@ -5873,7 +6020,9 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>Site hosting an AN/TPY-2 early warning radar to collect intelligence on ballistic missile developments.</t>
+          <t>The Shariki Radar Site is a strategic military installation located in the Shariki region of Japan [SRC-0012]. The site plays a critical role in regional defense and early warning architectures through its operation of the AN/TPY-2 transportable radar [SRC-0012]. Developed by Raytheon, the AN/TPY-2 is a highly mobile, X-band active electronically scanned array (AESA) radar system that utilizes solid-state gallium arsenide (GaAs) transmit/receive modules to provide long-range surveillance and high-resolution target tracking capabilities [SRC-0183].
+The primary mission of the radar deployment at the Shariki site is to collect strategic-level intelligence on North Korean ballistic missile developments and to provide Japan with advanced early warning of incoming warheads [SRC-0012]. Due to its strategic placement and powerful tracking capabilities, the AN/TPY-2 radar at Shariki is also able to monitor and scan portions of Russian territory located near Japan [SRC-0012]. 
+The Shariki Radar Site functions as a key node within a broader, layered ballistic missile defense network in the region. The tracking data gathered by the radar complements Japan's existing air defense capabilities, including point defense systems like the PAC-3, as well as the upgraded Aegis combat systems on Japan's *Kongo*-class destroyers, which utilize the longer-range RIM-161 Standard Missile 3 (SM-3) for theater ballistic missile defense [SRC-0012]. While the AN/TPY-2 radar system itself was introduced in 2007 and is deployed by the United States and its allies globally [SRC-0183, SRC-0011], the provided sources do not detail the exact founding year of the Shariki site itself or its specific host governing organization.</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -5889,6 +6038,11 @@
       <c r="V75" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>SRC-0012, SRC-0183, SRC-0011</t>
         </is>
       </c>
     </row>
@@ -6101,7 +6255,9 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>Measuring complex and radar system at Baikonur used to track launch vehicle trajectories and receive telemetry.</t>
+          <t>The Saturn-MS Measuring Complex is a critical radar and tracking facility located at the Baikonur Cosmodrome in Kazakhstan [SRC-0173, SRC-0222]. Situated atop Murguduk hill, also known as "snake mountain," the complex serves as the first major landmark visible from the Kyzylorda-Aralsk highway when traveling to the cosmodrome [SRC-0173]. The foundation for the complex's first antenna was laid on January 25, 1967 [SRC-0173]. It successfully conducted its first communication tests in November 1970 with the Luna-16 automatic interplanetary station—which famously returned lunar soil to Earth—and officially commenced full-scale operations on November 3, 1971 [SRC-0173].
+Initially established as a strictly military facility operated by a dedicated military unit, Saturn-MS was designed to monitor rocket trajectories, telemetry, space communications, and satellite control [SRC-0173]. Over the decades, the complex expanded its capabilities to keep pace with technological advancements. It was equipped to support the joint Soyuz-Apollo program in 1975, integrated a squadron of four flying telemetry laboratory aircraft in 1976, and added a communications center in 1987 to facilitate operations for the Buran space shuttle [SRC-0173]. The facility's primary tracking hardware consists of two massive parabolic antennas, each measuring 25 meters in diameter and weighing 200 tons [SRC-0222, SRC-0173].
+Throughout its operational history, Saturn-MS has been instrumental in numerous high-profile space programs. It has tracked the launches of Soyuz, Soyuz-TM, Progress, and Progress-M spacecraft, while also maintaining deep-space communications with interplanetary stations exploring the Moon, Venus, Mars, and Halley's comet [SRC-0222, SRC-0173]. In 2006, the managing military unit was disbanded, and the site underwent a complete civilian transition under the administration of the Russian space agency, Roscosmos [SRC-0222, SRC-0173]. Today, the complex continues to undergo gradual modernization, functioning as the vital "eyes" of the Baikonur Cosmodrome [SRC-0173].</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -6117,6 +6273,11 @@
       <c r="V78" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>SRC-0173, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -6461,7 +6622,10 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>Launch pad used for testing Taepo Dong 1 and 2 missiles.</t>
+          <t>The Nodong Launch Pad is a rocket launching site situated in North Korea, specifically located in the area historically known as Tae Po Dong (Taep'o-dong) [SRC-0162, SRC-0205]. The broader facility encompassing this pad is formally known as the Tonghae Satellite Launching Ground, or Musudan-ri, which lies in southern Hwadae County, North Hamgyong Province, near the cape of Musu Dan [SRC-0205, SRC-0205]. 
+The development of the launching infrastructure in this area began in the early 1980s [SRC-0205]. At the time, North Korea required a new flight-test facility to reverse-engineer and produce copies of the Soviet Scud-B missile; their previous test site at Hwajin-ri had insufficient range and risked sending missiles into Chinese territorial waters [SRC-0205]. Construction of the original launch pad was completed in 1985 by the 117th Regiment of the Ministry of People's Armed Forces' Air Force Construction Bureau [SRC-0205]. During the early 1990s, the site underwent significant expansion, adding a missile assembly facility, fuel storage buildings, a range control center, and advanced tracking facilities [SRC-0205].
+The Nodong Launch Pad and its surrounding complex have supported the testing of various military rockets, including the Hwasong, Rodong, and the Taepodong-1 and Taepodong-2 missiles, which take their name from the local area [SRC-0162, SRC-0205, SRC-0205]. A highly notable launch occurred in 1998, when North Korea launched a Paektusan-1 vehicle from this site, claiming to have successfully placed the Kwangmyŏngsŏng-1 satellite into orbit—a claim that remains unverified by independent sources [SRC-0205].
+The facility features a disused launch pad equipped with a 30-meter umbilical tower, a top-mounted gantry crane, a flame blast bucket, and a blockhouse with an access tunnel [SRC-0205, SRC-0205]. Nearby infrastructure includes an engine test stand, a missile assembly building, and a ground tracking facility [SRC-0205, SRC-0205]. Since 2014, the site has reportedly been reduced to a caretaker status [SRC-0205].</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -6477,6 +6641,11 @@
       <c r="V83" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>SRC-0162, SRC-0205</t>
         </is>
       </c>
     </row>
@@ -6972,7 +7141,10 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>A planned spaceport positioned for rocket development, training, and open-water experimental launches.</t>
+          <t>The **Philippine Spaceport** is a proposed rocket launch facility planned to be established in the Cagayan Special Economic Zone (CEZA) in the Philippines [SRC-0221]. Currently in its early planning and development stages as of 2026, the spaceport aims to position the Philippines as a prominent gateway to space and a hub for satellite launches in Southeast Asia [SRC-0066, SRC-0146]. 
+The initiative gained significant momentum on March 4, 2026, when a historic Memorandum of Understanding (MOU) was signed during the Philippines–Korea Business Forum in Manila [SRC-0066, SRC-0145]. The agreement brought together key governing and partner organizations, including the Philippine Space Agency (PhilSA), the Department of Information and Communications Technology (DICT), the Cagayan Economic Zone Authority (CEZA), the South Korean rocket firm Perigee Aerospace, and Ascend International Gateway, Inc. [SRC-0066, SRC-0145]. This collaborative framework is designed to facilitate rocket development training, localized assembly, and experimental launches that will serve as a proof of concept for the permanent spaceport [SRC-0066, SRC-0145, SRC-0145].
+The foundation for this project stems from a technology transfer program conducted in late 2025, during which PhilSA engineers trained with Perigee Aerospace in South Korea to gain hands-on experience in launch vehicle systems and testing [SRC-0066, SRC-0145]. The choice of the Philippines for a spaceport is highly strategic; its geographic proximity to the equator reduces the fuel required to reach orbit, while its eastern seaboard facing the open Pacific Ocean ensures safe rocket launch trajectories and recovery operations over open waters [SRC-0221, SRC-0146, SRC-0066, SRC-0145]. 
+While specific launch pads and radar facilities have yet to be constructed, the spaceport is envisioned to support both domestic space ambitions and international commercial space operators [SRC-0145, SRC-0145]. As of mid-2026, the Philippine Spaceport remains a planned project, representing a pivotal step in advancing the country's space industry, driving foreign investments, and enhancing national digital connectivity [SRC-0146, SRC-0066].</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -6988,6 +7160,11 @@
       <c r="V90" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC-0221, SRC-0066, SRC-0146, SRC-0145</t>
         </is>
       </c>
     </row>
@@ -7265,7 +7442,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>A planned civilian launch site for vertical rocket launches in Chonburi province.</t>
+          <t>While the sources specifically refer to this location as the "Ko Juang–Ko Jan" site in Chonburi, it is identified as the most suitable candidate for Thailand's future spaceport project [SRC-0199]. Evaluated by the Geo-Informatics and Space Technology Development Agency (GISTDA) in collaboration with KPMG Phoomchai Business Advisory, the site was chosen over other potential locations due to its highly favorable physical and geographical characteristics [SRC-0199, SRC-0199, SRC-0199]. The Ko Juang-Ko Jan site stands out because it is situated on government-owned land, which significantly reduces the costs associated with land acquisition and area modification [SRC-0199]. Consequently, it requires the lowest initial investment among the surveyed sites, estimated at 376 million baht [SRC-0199]. Geographically and operationally, the site is particularly well-suited for vertical rocket launches [SRC-0223]. A major advantage of this location is its minimal impact on surrounding populated areas and local communities, fulfilling crucial safety and environmental requirements for spaceflight operations [SRC-0223, SRC-0199]. Economically, the Ko Juang-Ko Jan spaceport is projected to be highly beneficial, as it is the only evaluated site with a positive economic net present value (NPV) [SRC-0199]. Furthermore, it boasts an impressive social return on investment (SROI) of 1.79, meaning every baht invested generates approximately 1.79 baht in social value through human capital development, high-tech employment, and STEM training [SRC-0199, SRC-0199]. The phased development of the site will initially focus on suborbital rocket testing and launch capabilities over the first two to five years, serving as a foundational step before progressing to orbital missions and a fully-fledged space hub [SRC-0199, SRC-0199].</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -7281,6 +7458,11 @@
       <c r="V94" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>SRC-0199, SRC-0223</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7518,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>An advanced hub in Si Racha housing the National Assembly Integrated and Test Centre for satellite development.</t>
+          <t>The Space Krenovation Park (SKP) is a high-level aerospace research and satellite development facility located in Si Racha, Thailand [SRC-0198]. Operated under the auspices of the Geo-Informatics and Space Technology Development Agency (GISTDA), the park serves as the kingdom's most advanced hub for space technology and satellite operations [SRC-0198, SRC-0068]. The facility is integral to Thailand's strategic goal of transitioning from a mere consumer of space technology to a key creator within the global space supply chain [SRC-0198, SRC-0198]. Key facilities located within the Space Krenovation Park include the National Assembly Integrated and Test Centre (NAIT) and the Space Technology Research Centre (S-TREC) [SRC-0198]. These centers are dedicated to advanced satellite development, testing, and high-level aerospace research [SRC-0198]. The Si Racha location also functions as the primary spaceport and control center for GISTDA's THEOS (Thailand Earth Observation Satellite) program, officially serving as the GISTDA THEOS Control &amp; Receiving Station [SRC-0068]. Recently, the Space Krenovation Park was visited by delegations from Thailand's Ministry of Higher Education, Science, Research and Innovation (MHESI) and Japan's Ministry of Economy, Trade and Industry (METI) [SRC-0198, SRC-0198]. This visit was part of a strategic partnership aiming to establish a domestic spaceport and a national satellite constellation in the Eastern Economic Corridor (EEC) [SRC-0198, SRC-0198]. This international collaboration highlights the park's critical role in advancing Thailand's national space industry, attracting investment, and stimulating the New S-Curve economy through knowledge transfer and high-skilled employment [SRC-0198].</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -7352,6 +7534,11 @@
       <c r="V95" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC-0198, SRC-0068</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7594,9 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Testing ground used for the launch of the UAE's first homegrown hybrid rocket.</t>
+          <t>The Abu Dhabi Testing Ground, situated in a desert area of Abu Dhabi, United Arab Emirates, serves as a launch location for the nation's expanding aerospace and space exploration programs [SRC-0207, SRC-0221]. While specific details regarding the exact coordinates, founding year, and permanent radar or support facilities of the testing ground are not detailed in the provided sources, the site is notably utilized by the Technology Innovation Institute (TII), which operates as the applied research division of the Advanced Technology Research Council (ATRC) [SRC-0207].
+The testing ground gained historical prominence in February 2026 when it hosted the successful launch of the UAE's first locally designed and manufactured hybrid rocket [SRC-0207, SRC-0221]. This landmark mission was conducted by a team of researchers led by Dr. Najwa Aaraj and Dr. Elias Tsotsanis to test cutting-edge propulsion systems [SRC-0221, SRC-0207]. The rocket launched from this desert site utilized a hybrid propulsion system, combining a solid fuel component with nitrous oxide acting as the oxidizer, which is considered safer and more cost-effective than fully liquid-fueled engines [SRC-0207].
+During its flight from the Abu Dhabi site, the hybrid sounding rocket reached an altitude of approximately three kilometers before safely descending using a parachute recovery system [SRC-0207, SRC-0221]. The mission successfully validated the rocket's structural durability, flight stability, and propulsion efficiency [SRC-0207]. Engineers at the site collected extensive performance data during the flight to improve future designs [SRC-0207]. All essential components of the rocket, including avionics, structural frameworks, and control mechanisms, were developed and tested locally, demonstrating the UAE's growing sovereign capabilities in aerospace engineering [SRC-0207, SRC-0207]. The site currently acts as a critical test bed for proving new technologies before they are scaled up for larger launchers and orbital flights, aligning with the UAE's broader national space strategy [SRC-0207, SRC-0207].</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -7423,6 +7612,11 @@
       <c r="V96" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC-0207, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -7478,7 +7672,9 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Forward-based X-band active electronically scanned array radar deployed for missile warning.</t>
+          <t>The AN/TPY-2 Radar Site in the United Arab Emirates (UAE) is a forward-based early warning and missile defense installation equipped with the Army/Navy Transportable Radar Surveillance (AN/TPY-2) system [SRC-0183]. While the exact location, founding year, and internal governing structure of the specific UAE site are not fully detailed in the provided sources, it forms a critical node in the broader United States and allied ballistic missile defense architecture deployed across the Middle East [SRC-0183, SRC-0011].
+The key facility at this site is the AN/TPY-2 radar, a highly mobile, high-resolution, X-band active electronically scanned array (AESA) radar originally manufactured by Raytheon [SRC-0183, SRC-0011, SRC-0011]. Operating in the 8.55 to 10 GHz frequency range, the radar utilizes over 25,000 gallium arsenide (and increasingly Gallium Nitride) transmit/receive modules across an approximate 9.2-square-meter aperture [SRC-0183, SRC-0011, SRC-0011, SRC-0190]. The system is capable of electronically steering its radar beams to detect, classify, and track hundreds of ballistic missile threats simultaneously at ranges of 1,000 kilometers or more [SRC-0011, SRC-0011, SRC-0011]. In the UAE, this radar integrates with Terminal High Altitude Area Defense (THAAD) batteries to provide a rapid response capability against regional theater ballistic threats [SRC-0183, SRC-0011, SRC-0190].
+The site has seen notable operational activity during periods of heightened regional tensions. During the 2026 Iran war, the UAE Ministry of Defense reported that national air defenses were actively intercepting missiles and drones launched from Iran [SRC-0078]. Concurrently, satellite imagery and news reports indicated that radar bases housing key U.S. missile interceptors, including locations in the UAE, were targeted and hit during these retaliatory strikes [SRC-0012, SRC-0012, SRC-0184, SRC-0184]. Despite these attacks, the AN/TPY-2 network remains a cornerstone of the layered defense strategy for the UAE and allied forces in the Persian Gulf region [SRC-0183, SRC-0011].</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -7494,6 +7690,11 @@
       <c r="V97" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>SRC-0183, SRC-0011, SRC-0190, SRC-0078, SRC-0012, SRC-0184</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7745,9 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Former sounding rocket launch site operated from 1984 to 1990.</t>
+          <t>Ahtopol is a former rocket launch site located in Bulgaria [SRC-0095, SRC-0096]. Geographically situated at coordinates 42°05′09″N 27°57′18″E, the facility was utilized for aerospace and rocket launch activities during the 1980s [SRC-0095, SRC-0096]. The site officially became operational in the year 1984 and maintained active operations until it was closed in 1990 [SRC-0095, SRC-0096]. 
+During its six years of operational history, the Ahtopol launch site was utilized for a total of 28 rocket launches [SRC-0095, SRC-0096]. The aerospace operations conducted at this location involved suborbital flights, with the highest achieved altitude recorded at 90 kilometers, reaching the upper limits of the atmosphere just below the official edge of space [SRC-0095, SRC-0096]. Additionally, the heaviest rocket launched from the Ahtopol facility weighed 475 kilograms [SRC-0095, SRC-0096]. 
+While the fundamental operational statistics and geographical location of the site are documented, the available sources do not provide further detailed information concerning the specific governing organization, military branch, or space agency that managed the facility [SRC-0095, SRC-0096]. Furthermore, the provided texts do not contain details regarding the site's key infrastructure, specific radar systems, or its current status and preservation following the cessation of launch activities in 1990 [SRC-0095, SRC-0096].</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -7560,6 +7763,11 @@
       <c r="V98" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC-0095, SRC-0096</t>
         </is>
       </c>
     </row>
@@ -7615,7 +7823,8 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>Permanent location for the Estonian Air Defence Wing and its IRIS-T medium-range air defense systems.</t>
+          <t>**Ämari Air Base** is a key military installation located in Estonia, serving as a central hub for both national and international air defense operations. The base operates as the permanent garrison and headquarters for the Air Defence Wing (Õhukaitsedivisjon) of the Estonian Air Force, an active unit established in 2023 [SRC-0014, SRC-0014]. The Air Defence Wing's primary mission at the base is to ensure the integrity of Estonian airspace through the planning and execution of active air defense operations [SRC-0014]. To support this mission, Ämari Air Base is slated to be equipped with newly purchased IRIS-T medium-range air defense systems [SRC-0014].
+Beyond its national significance, Ämari Air Base is a critical component of the North Atlantic Treaty Organization's (NATO) defense architecture on its Eastern Flank [SRC-0119]. Following Russia's illegal annexation of Crimea in 2014, NATO expanded its Baltic Air Policing Mission, deploying allied fighter detachments to Ämari to help secure the region's airspace [SRC-0119]. The base has since become integral to NATO's evolving Rotational Air Defense Model, which aims to provide continuous protection against airborne threats by deploying ground-based long-range air defenses alongside traditional air patrols [SRC-0119, SRC-0119]. Estonia provides crucial host nation support for the various allied air defense contingents that operate out of Ämari Air Base [SRC-0119]. Through these joint and multinational efforts, the base actively facilitates the strengthening of NATO's Integrated Air and Missile Defense System (IAMD), effectively contributing to the collective security, military mobility, and deterrence measures of the Baltic region [SRC-0119, SRC-0119].</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -7631,6 +7840,11 @@
       <c r="V99" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC-0014, SRC-0119</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7900,9 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>Major firing range used for national and multinational ground-based air defense and live-fire exercises.</t>
+          <t>The **Lohtaja Firing Range and Training Area** is a prominent military installation located in Finland, noted by geopolitical analyses to be associated with the Lapland region [SRC-0221], and specifically encompassing the coastal areas around Lohtaja and Houraati [SRC-0017]. As a central hub for the Finnish Defence Forces, the range is utilized jointly by the Finnish Army, Navy, Air Force, and the Border Guard to maintain and enhance national and regional security [SRC-0017, SRC-0191]. 
+The facility is best known for hosting "Mallet Strike," a major biannual ground-based air defence exercise that stands as the most critical live-firing training event for Finnish conscripts, reservists, and active personnel [SRC-0017, SRC-0007]. Since 2023, the site has regularly integrated allied NATO forces into its operations, featuring troops and equipment from countries such as the United Kingdom, Sweden, Norway, and Germany [SRC-0221, SRC-0017, SRC-0007, SRC-0007]. Exercises at the site frequently involve up to 1,900 personnel [SRC-0017, SRC-0191].
+Lohtaja provides a highly challenging and realistic training environment, further enhanced by harsh Finnish weather conditions and complex aerial threat simulations [SRC-0007, SRC-0191]. The range supports live-fire operations for a diverse array of anti-aircraft weaponry, including 35ITK88 and 23ITK61/95 anti-aircraft guns, as well as numerous surface-to-air missile systems like the ITO90M, ITO05, ITO05M, NASAMS, British Starstreak, and German Patriot batteries [SRC-0221, SRC-0007]. Recent exercises at the site have also introduced Counter-Unmanned Aerial System (C-UAS) measures and force protection equipment to address modern battlefield threats [SRC-0191, SRC-0017]. The airspace and grounds routinely accommodate large-scale maneuvers involving hundreds of vehicles, drones, helicopters, and fighter aircraft, maintaining Lohtaja's status as a critical asset for both Finnish and NATO integrated air and missile defence capabilities [SRC-0017, SRC-0191, SRC-0007].</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -7702,6 +7918,11 @@
       <c r="V100" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC-0221, SRC-0017, SRC-0191, SRC-0007</t>
         </is>
       </c>
     </row>
@@ -8845,7 +9066,9 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>New military training range spanning over 15,000 hectares for brigade-level exercises and firing.</t>
+          <t>The Sēlija Military Training Range is a new, large-scale military testing and training zone located in Latvia, governed by the Latvian Ministry of Defence and utilized by the National Armed Forces and its allies [SRC-0063, SRC-0221]. The development of the facility was significantly accelerated following the 2022 NATO summit in Madrid, which called for an increased presence of allied forces in the Baltic States in response to regional security threats stemming from Russia's invasion of Ukraine [SRC-0063, SRC-0221]. The range covers a vast total area of 15,590 hectares, acquired through the combination of 15,430 hectares of state-owned properties and the expropriation of 160 hectares of private land [SRC-0221, SRC-0063].
+The project's first phase was developed between 2022 and 2025 with an estimated cost of 36.5 million euros, establishing its initial operational capabilities [SRC-0063, SRC-0063]. The live-fire training area was officially opened in February 2026, with key Latvian officials, including President Edgars Rinkēvičs and Minister of Defence Andris Sprūds, in attendance [SRC-0063, SRC-0063, SRC-0221]. Key facilities at the site currently include a logistics support area for company-level units, an ammunition storage area, a 300-metre shooting range, a tactical shooting range for infantry platoons, specialized ranges for machine guns and snipers, and an unexploded ordnance zone [SRC-0063]. 
+Currently active, the range hosts a variety of training operations, including tactical and engineering drills, armored vehicle maneuvers, aircraft overflights, and unmanned aerial vehicle (UAV) training [SRC-0221, SRC-0063]. Soldiers from the Latvian National Armed Forces, the National Guard, the State Defence Service, and allied NATO countries regularly utilize the facility [SRC-0063]. A second phase of development is planned for 2026 to 2029, aiming to expand the site's collective training infrastructure to accommodate larger-scale, brigade-level exercises [SRC-0221, SRC-0063].</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -8861,6 +9084,11 @@
       <c r="V116" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>SRC-0063, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -8916,7 +9144,9 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Coastal military drill site where HIMARS live-fire exercises were conducted against simulated naval targets.</t>
+          <t>Šķēde is a veteran air defense military training range located on the Baltic coast of Latvia [SRC-0221]. Serving as a key operational site for both the Latvian National Armed Forces and allied international troops, the active facility plays a critical role in regional defense integration and military readiness [SRC-0221, SRC-0221, SRC-0109]. Unlike the newly developed Sēlija range, Šķēde has functioned as an established air defense range for years, hosting various live-fire exercises and providing essential training infrastructure for Baltic security [SRC-0221]. Furthermore, because neighboring Lithuania currently lacks its own active rocket firing range, Lithuanian military forces regularly utilize the Šķēde facility to conduct their training exercises [SRC-0221].
+The site is notable for accommodating advanced weapon systems and large-scale international military drills. During the "Defender 23" exercise in May 2023, the Michigan National Guard’s 1st Battalion, 182nd Field Artillery Regiment deployed to the Šķēde range to conduct a "Baltic Raid" drill [SRC-0109, SRC-0109]. This event marked a significant regional milestone, as it was the first time an M142 High Mobility Artillery Rocket System (HIMARS) was fired from Latvia into the Baltic Sea, successfully targeting simulated naval threats [SRC-0221, SRC-0109]. This exercise aimed to enhance interoperability between United States, NATO, and partner forces [SRC-0109]. 
+In addition to HIMARS rocket tests, Šķēde has hosted live-fire tests for the Avenger air defense system [SRC-0221]. Today, the range remains highly active and continues to serve as a strategic location for military training, air defense operations, and maritime target engagements along the Baltic coastline [SRC-0221].</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -8932,6 +9162,11 @@
       <c r="V117" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>SRC-0221, SRC-0109</t>
         </is>
       </c>
     </row>
@@ -9362,7 +9597,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>A World War II era rocket launch site used by Nazi Germany.</t>
+          <t>**Leba in Pommern** is a former rocket launch facility situated at geographical coordinates 54°46′09″N 17°35′37″E [SRC-0095]. Historically located in the region of Pommern (Pomerania), the site was under the jurisdiction of Nazi Germany during its operational years [SRC-0095]. The facility was active during World War II, specifically functioning between 1941 and 1945 [SRC-0095]. During this period, the governing military organization utilized the Leba installation primarily for the testing and launching of Nazi-German rockets [SRC-0095]. Following the end of the Second World War and the subsequent redrawing of national borders in 1945, the territory encompassing the Leba in Pommern launch site was incorporated into Poland [SRC-0095]. Today, the site remains a historical footnote of wartime rocket development. Detailed information regarding specific facilities, radars, or other notable activities at this location is not available in the provided sources.</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -9378,6 +9613,11 @@
       <c r="V123" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>SRC-0095</t>
         </is>
       </c>
     </row>
@@ -9428,7 +9668,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>A former site used for launching Polish rockets in the 1960s and 1970s.</t>
+          <t>**Łeba-Rąbka** is a deactivated rocket launch site located at coordinates 54°45′16″N 17°31′05″E in Poland [SRC-0095, SRC-0221]. Established during the Cold War era, the facility was operational for a decade, spanning from 1963 to 1973 [SRC-0095, SRC-0221]. Unlike the military-focused installations from earlier periods in the region, Łeba-Rąbka was governed by Polish authorities and dedicated strictly to scientific research [SRC-0221, SRC-0221]. The site's primary activity involved the launching of Polish meteorological research rockets into the atmosphere [SRC-0221, SRC-0221]. Over the course of its ten-year operational history, a total of 36 rocket launches were successfully conducted from this location [SRC-0095]. The site does not currently host any active aerospace or military operations and is officially classified as inactive [SRC-0221]. Detailed information regarding the specific types of radar, infrastructure, or technical facilities present at Łeba-Rąbka is not available in the provided sources.</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -9444,6 +9684,11 @@
       <c r="V124" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>SRC-0095, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -9499,7 +9744,8 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>A Nazi German V-2 rocket testing site established in the Tuchola Forest.</t>
+          <t>**SS-Proving Ground Westpreussen** (also known as SS-Proving Ground Westpreußen) is a historical World War II military reservation and rocket launch facility located in the Tuchola Forest [SRC-0095]. The site is positioned at geographical coordinates 53°37′11″N 17°59′06″E [SRC-0095]. While the Tuchola Forest is located in present-day Poland, during the facility's active period in 1944 and 1945, it was part of Nazi-occupied Poland and governed directly by Nazi Germany's military apparatus [SRC-0095]. 
+The proving ground gained strategic prominence in the latter stages of the war. In late July 1944, the rapid advance of the Soviet Red Army forced German forces to evacuate their primary missile testing base at Blizna [SRC-0025]. Consequently, launch activities and testing personnel were immediately relocated to the Tuchola Forest [SRC-0025]. At this new location, the SS-Proving Ground Westpreussen was utilized heavily for the deployment and testing of Nazi-German V-2 ballistic missiles [SRC-0095, SRC-0025, SRC-0031]. The site operated briefly before the war's conclusion in 1945 [SRC-0095]. Detailed specifications concerning the internal facilities, radars, or physical remnants of the site are not provided in the sources.</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -9515,6 +9761,11 @@
       <c r="V125" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>SRC-0095, SRC-0025, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -9570,7 +9821,8 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>A firing range in Poland used for NATO live-fire air defense exercises such as Ramstein Legacy.</t>
+          <t>**Ustka Training Range** is an active military testing and exercise facility located in Ustka, Poland [SRC-0124, SRC-0221]. Governed by Polish defense authorities, the site is extensively utilized by the North Atlantic Treaty Organization (NATO) and allied partner nations for multinational defense drills [SRC-0124, SRC-0221]. The training range serves as a critical hub for conducting live-fire exercises specifically focused on surface-to-air defense systems, ensuring allied interoperability and operational readiness [SRC-0124, SRC-0221]. 
+One of the most notable activities hosted at the Ustka Training Range was its participation in Ramstein Legacy 22, a large-scale NATO live-fire air and missile defense exercise [SRC-0221, SRC-0124]. During this event, military personnel from several allied nations—including the Czech Republic, France, Poland, Slovakia, and the United Kingdom—converged at the site to integrate and test a variety of advanced weapon systems in live-fire scenarios [SRC-0124]. The demonstrations prominently featured systems such as the British Starstreak air defense system [SRC-0124]. The site continues to play a vital role in maintaining the strategic defense posture of European airspace [SRC-0124, SRC-0221].</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -9586,6 +9838,11 @@
       <c r="V126" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>SRC-0124, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -9641,7 +9898,11 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>An artillery and bombing range facility operating since 1904.</t>
+          <t>The **Field Firing Range of Alcochete** is a military proving ground and training facility located in the Lisbon and Tagus Valley region, approximately 30 kilometers east of Lisbon, Portugal [SRC-0149]. Covering an expansive surface area of 7,539 hectares, the installation has historically served as a critical testing and training area for the nation's armed forces [SRC-0149].
+**History and Operations**
+The facility was originally established and opened in 1904, functioning primarily as an artillery and bombing range [SRC-0149]. Over the decades, it has supported various military operations, tests, and exercises. In 1993, the control and administration of the proving ground were officially transferred to the Portuguese Air Force [SRC-0149]. Despite being under Air Force jurisdiction, the firing range remains a joint-use facility. It is actively utilized by other branches of the Portuguese military, as well as various law enforcement agencies, to conduct vital training exercises and weapons testing [SRC-0149]. 
+**Current Status and Future Relocation**
+The current status of the Field Firing Range of Alcochete is transitional. The historic proving ground is scheduled to be closed and relocated to accommodate major civilian infrastructure development in the region [SRC-0149]. Specifically, the site is slated to be replaced by the new Luís de Camões Airport, a major aviation project that is currently projected to open in 2034 [SRC-0149]. As a result of this development, the Portuguese Air Force is planning to relocate the military proving ground operations, with the municipality of Mértola in the Alentejo region being considered as a possible new location for the facility [SRC-0149, SRC-0149].</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -9657,6 +9918,11 @@
       <c r="V127" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>SRC-0149</t>
         </is>
       </c>
     </row>
@@ -9857,7 +10123,9 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>A strategic ballistic missile defense installation supporting NATO's European Phased Adaptive Approach.</t>
+          <t>Aegis Ashore Romania is an operational land-based missile defense installation deployed in Romania to support the integrated defense of NATO’s European territory and allied military forces [SRC-0093, SRC-0134]. The facility serves as a critical strategic component aimed at countering ballistic missile threats that originate from outside the Euro-Atlantic region [SRC-0093]. The establishment and operationalization of this site represent a key milestone and contribution by the United States Missile Defense Agency (MDA) to Phase 3 of the European Phased Adaptive Approach (EPAA) [SRC-0093]. 
+Technologically, the Aegis Ashore system in Romania is specifically designed and equipped to launch advanced Standard Missile-3 (SM-3) interceptors, which notably includes both the SM-3 Block IBTU and the SM-3 Block IIA missile variants [SRC-0093]. The development of the Aegis Ashore architecture leverages decades of United States investment in advanced radar technologies and missile defense systems, building heavily upon the proven capabilities of the maritime Aegis Combat System [SRC-0101]. 
+To ensure the operational success, safety, and reliability of the Romanian deployment, extensive research, development, and live-fire testing were conducted at the Aegis Ashore Missile Defense Test Complex (AAMDTC) [SRC-0134]. This test complex is located at the Pacific Missile Range Facility (PMRF) in Kauai, Hawaii [SRC-0134]. The PMRF testing facility, which was established specifically for research and evaluation purposes, has been instrumental in rigorously evaluating the Aegis Ashore systems before their active operational deployment in Romania and other international locations [SRC-0134]. Currently, the Aegis Ashore Romania site remains fully operational, functioning as a cornerstone of NATO's ballistic missile defense shield in Europe [SRC-0093, SRC-0134].</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -9873,6 +10141,11 @@
       <c r="V130" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>SRC-0093, SRC-0134, SRC-0101</t>
         </is>
       </c>
     </row>
@@ -10631,7 +10904,9 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>A missile testing and rocket range in Wales historically used for Skylark rockets.</t>
+          <t>The Aberporth Range is a rocket launch and aerospace testing facility located in Wales, near the town of Aberystwyth [SRC-0162]. Situated at the geographical coordinates of 52.1°N, 4.3°W, the site is operated and governed by the Defence Evaluation and Research Agency (DERA) [SRC-0162]. 
+Historically, the Aberporth Range has functioned as a suborbital launch site, contributing to regional aerospace testing and evaluation efforts [SRC-0162]. The range is most notably associated with the launch of the Skylark, a British sounding rocket utilized heavily during the mid-to-late 20th century for various scientific, atmospheric, and technological missions [SRC-0162]. 
+While the site is recognized in global registries of rocket launch facilities, the provided sources do not contain further detailed information regarding its exact founding year, an extensive operational history, specific radar and tracking infrastructure, or its current active status. Due to this limitation of available source data, a more comprehensive description of the facility's day-to-day operations and modern capabilities cannot be generated.</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -10647,6 +10922,11 @@
       <c r="V141" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>SRC-0162</t>
         </is>
       </c>
     </row>
@@ -10780,7 +11060,8 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>A spaceport in England intended for horizontal rocket launches.</t>
+          <t>Spaceport Cornwall is an aerospace facility located in Newquay, Cornwall, England, UK, and operates in association with the United Kingdom Space Agency (UKSA) [SRC-0031, SRC-0096]. The site was developed as a key component of the UK government's LaunchUK programme, which aimed to establish a domestic network of spaceports to capture a share of the growing commercial spaceflight market [SRC-0096, SRC-0174, SRC-0174]. Capitalizing on the UK's geography for accessing low Earth orbit, Spaceport Cornwall was distinctively designed to support horizontal launch operations rather than traditional vertical rocket launches [SRC-0174, SRC-0221].
+The spaceport's most notable operational activity occurred when it hosted its first and only attempted space launch [SRC-0174, SRC-0221]. This historic mission was conducted by Virgin Orbit, a private aerospace company that utilized a modified Boeing 747 aircraft to air-launch small satellites into orbit [SRC-0174, SRC-0221]. However, the highly anticipated horizontal launch attempt ultimately ended in failure [SRC-0221]. Following this unsuccessful mission, Virgin Orbit suffered severe financial difficulties and eventually declared bankruptcy [SRC-0174, SRC-0221]. Due to the complete collapse of its primary commercial launch partner, Spaceport Cornwall is currently inactive for space launch operations [SRC-0221]. The provided sources do not detail the spaceport's specific radar facilities, precise founding date, or internal administrative structure beyond its UKSA affiliation [SRC-0031, SRC-0221].</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -10796,6 +11077,11 @@
       <c r="V143" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>SRC-0031, SRC-0096, SRC-0174, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -10846,7 +11132,9 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>A planned vertical launch spaceport in the Scottish Highlands.</t>
+          <t>Sutherland Spaceport is a proposed rocket launch facility located on the Scottish mainland in the Scottish Highlands, near the settlement of Tongue [SRC-0221, SRC-0161, SRC-0176]. The site was initially conceived as part of the UK government's strategic initiative to establish a domestic commercial space industry, specifically targeting the launch of small satellites into polar and sun-synchronous orbits [SRC-0174, SRC-0161]. The ambitious project officially received formal planning approval from the Scotland Highland Council in August 2020 [SRC-0096].
+The primary commercial operator slated to use the Sutherland facility was the UK-based rocket manufacturer Orbex [SRC-0221, SRC-0176]. However, the development of the spaceport encountered critical and ultimately fatal obstacles. In October 2024, Orbex announced a major strategic shift, declaring its intention to completely mothball the proposed Sutherland spaceport project [SRC-0176]. The company decided to relocate its planned launch operations to the SaxaVord Spaceport on the Shetland Islands, citing that SaxaVord was in a significantly more advanced state of development and operational readiness [SRC-0176]. 
+The viability of the Sutherland project collapsed completely shortly thereafter. Orbex faced severe financial difficulties, ultimately becoming insolvent and permanently ceasing all operations in February 2026 [SRC-0221, SRC-0176]. Consequently, following the bankruptcy of its anchor tenant and main launch provider, the Sutherland Spaceport project remains frozen and mothballed, with no active space launches occurring at the site [SRC-0221, SRC-0176].</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -10862,6 +11150,11 @@
       <c r="V144" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>SRC-0221, SRC-0161, SRC-0176, SRC-0174, SRC-0096</t>
         </is>
       </c>
     </row>
@@ -10978,7 +11271,9 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>A British overseas territory utilized as a tracking station and historical launch site for the Eastern Range.</t>
+          <t>Ascension Island is a remote Atlantic island located at geographical coordinates 7°58′29″S 14°24′53″W [SRC-0096]. Although it is a British territory, the island plays a highly strategic role as a major down-range tracking station for the United States' Eastern Range (ER), a vast space and missile tracking network managed by the 45th Space Wing stationed at Patrick Air Force Base [SRC-0118, SRC-0189]. The Eastern Range infrastructure extends from Newfoundland across the Atlantic, terminating at Ascension Island [SRC-0189].
+The island is outfitted with an array of sophisticated tracking, radar, and telemetry facilities to monitor ballistic missiles and orbital space launches continuously from liftoff [SRC-0069, SRC-0106]. Its key infrastructure includes precision metric tracking radars that use both beacon and echo tracking to supply real-time flight data to central command computers [SRC-0106]. Ascension also features advanced metric optics capabilities, housing precision theodolites, ballistic cameras, and long-range large-aperture telescopes [SRC-0106].
+To support crucial data acquisition, Ascension Island relies on post-detect telemetry systems and land-based stations that transmit real-time telemetry back to the mainland via satellite communications (SATCOM) [SRC-0189, SRC-0106, SRC-0118]. However, unlike several other down-range stations, Ascension Island does not possess telemetry doppler data capabilities for metric measurements [SRC-0106]. Additionally, the site supports the Missile Impact Location System (MILS), utilizing a target array of bottom-mounted hydrophones located near the island to record impact data from reentry vehicles [SRC-0106]. Historically, during the late 1950s, the U.S. military deployed modified radar and telemetry ships between Antigua and Ascension Island to recover launch reentry vehicles and collect vital weather data [SRC-0192]. Today, Ascension Island remains a critical node in global space domain tracking.</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -10994,6 +11289,11 @@
       <c r="V146" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>SRC-0096, SRC-0118, SRC-0189, SRC-0069, SRC-0106, SRC-0192</t>
         </is>
       </c>
     </row>
@@ -11643,7 +11943,9 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Secondary launch site known for its close equatorial launch access in the Asia Pacific region.</t>
+          <t>Utingu, commonly known as Punsand Bay, is a geographical location in Australia that has been associated with the development of aerospace and rocket launch infrastructure [SRC-0096]. Situated in Bamaga, the area operates under the local government jurisdiction of the council of the Torres Strait Island Region [SRC-0096]. 
+Historically, the site was identified as a secondary launch facility for Space Centre Australia, intended to complement the organization's primary site facilities located further south near RAAF Scherger on the Cape York Peninsula [SRC-0096]. A key strategic and geographical advantage of Utingu Punsand Bay is its extreme northern latitude. It is noted as being one of the closest facilities to equatorial launch access in the entire Asia Pacific region [SRC-0096]. Proximity to the equator is a highly desirable trait for spaceports, as it provides launch vehicles with an equatorial velocity boost, increasing payload capacity and launch efficiency.
+Despite these geographic benefits and its formal designation as a secondary site for Space Centre Australia, the facility is currently categorized strictly under "past and/or planned only" spaceports [SRC-0096]. While the overarching Space Centre Australia project has been active in securing land for its main site, the provided sources do not detail a specific founding year, the presence of key facilities, tracking radars, or any notable launch activities that have actually taken place at the Utingu Punsand Bay site [SRC-0096]. Its current status remains that of a planned or historical concept rather than an active, operational orbital spaceport [SRC-0096].</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -11659,6 +11961,11 @@
       <c r="V155" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -11714,7 +12021,9 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Planned launch site and location of a 2002 High Speed Flight Demonstration by Japan.</t>
+          <t>Christmas Island is an Australian external territory located in the Indian Ocean that has a notable history of planned and executed aerospace testing and rocket launch activities [SRC-0096]. The island's formal involvement in the space industry began taking shape in the late 1990s. In 1997, a major commercial project was planned by the Asia Pacific Space Centre to establish a dedicated launch site on the island [SRC-0096]. This proposed spaceport was part of a collaborative aerospace plan involving both Australia and Japan [SRC-0094]. However, despite the initial planning and international interest, the spaceport project ultimately did not proceed due to insufficient financial backing [SRC-0096].
+Although the 1997 commercial spaceport did not materialize into a permanent governing organization, Christmas Island later served as a successful testing ground for international aerospace research. In 2002, the Japan Aerospace Exploration Agency (JAXA) successfully utilized the island for Phase I of its High Speed Flight Demonstration (HSFD) program [SRC-0096]. These notable flight tests and demonstrations were conducted at Aeon Field, an existing airfield located on Christmas Island [SRC-0096].
+Today, Christmas Island is classified among past and/or planned rocket launch sites [SRC-0096]. The provided sources do not contain further detailed information regarding a specific founding year for a permanent spaceport, the installation of permanent tracking radars, or any subsequent spaceflight activities beyond the 2002 JAXA demonstration [SRC-0096]. Its current status is inactive regarding ongoing orbital rocket launches.</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -11730,6 +12039,11 @@
       <c r="V156" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>SRC-0096, SRC-0094</t>
         </is>
       </c>
     </row>
@@ -11932,7 +12246,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>ARPA Long-Range Tracking and Instrumentation Radar utilized for deep-space tracking and tracking space launches.</t>
+          <t>The ARPA Long-Range Tracking and Instrumentation Radar (ALTAIR) is a highly sensitive tracking radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island in the Kwajalein Atoll, Marshall Islands [SRC-0071, SRC-0071, SRC-0150]. Conceived in the early 1960s to study U.S. strategic weapon performance against large Soviet radars, ALTAIR became operational in 1970 [SRC-0071, SRC-0071]. The facility is governed under the Ronald Reagan Ballistic Missile Defense Test Site by the U.S. Army Space and Missile Defense Command [SRC-0150, SRC-0151]. ALTAIR operates at both VHF and UHF frequencies and features a massive 150-foot diameter antenna that rotates on a 110-foot circular track [SRC-0071, SRC-0071]. Despite its rotating portion weighing almost a million pounds, the system is exceptionally agile and capable of tracking deep reentry vehicles [SRC-0071]. ALTAIR is notable for its immense power-aperture product, which allows it to consistently acquire ballistic missile targets launched from Vandenberg Space Force Base over 3500 kilometers away [SRC-0071, SRC-0071]. In 1977, ALTAIR's mission expanded into space surveillance; it now serves as a central node for detecting new foreign space launches and tracking deep-space satellites for the U.S. Space Command [SRC-0071, SRC-0071]. Additionally, ALTAIR supports complex scientific research, such as NASA's sounding rocket tests and the generation of highly precise, GPS-driven vertical ionospheric models [SRC-0071, SRC-0151]. ALTAIR remains an actively modernized, heavily utilized asset at the range [SRC-0071, SRC-0071].</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -11948,6 +12262,11 @@
       <c r="V159" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12322,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>Target Resolution and Discrimination Experiment radar used for missile tracking.</t>
+          <t>The Target Resolution and Discrimination Experiment (TRADEX) is a precision instrumentation radar situated at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, Kwajalein Atoll, within the Marshall Islands [SRC-0071, SRC-0071]. It holds the distinction of being the first radar fielded at KREMS, becoming fully operational and accepted by the Advanced Research Projects Agency in December 1962 [SRC-0071, SRC-0071]. The facility falls under the governance of the U.S. Army Space and Missile Defense Command as part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0150, SRC-0151]. Initially designed with an 84-foot antenna operating as a UHF tracker and L-band illuminator, TRADEX was an early pioneer of pulse compression waveforms for high sensitivity and precise range resolution [SRC-0071, SRC-0071]. In 1970, the radar was shut down for a major redesign that removed its UHF tracking capability and replaced it with a dual-frequency L-band and S-band system [SRC-0071]. TRADEX has played a pivotal role in ballistic missile defense development, acting as the primary testbed for discrimination techniques and algorithms for systems like Nike-X, Safeguard, and Site Defense [SRC-0071, SRC-0071]. In its current status, TRADEX operates as a dedicated contributing sensor for the Space Surveillance Network, providing deep-space tracking while also continuing its mission of gathering signature data on ballistic missiles and validating modern naval Aegis BMD waveforms [SRC-0071, SRC-0071].</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -12019,6 +12338,11 @@
       <c r="V160" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12074,7 +12398,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>ARPA Lincoln C-Band Observables Radar providing high-resolution imaging capabilities.</t>
+          <t>The ARPA-Lincoln C-band Observables Radar (ALCOR) is a high-power tracking and imaging radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island in the Kwajalein Atoll [SRC-0071, SRC-0071]. Managed by the U.S. Army Space and Missile Defense Command under the Reagan Test Site, ALCOR was authorized for development in 1965 and became operational in January 1970 [SRC-0150, SRC-0071, SRC-0071]. ALCOR operates in the C-band and is enclosed within a prominent radome [SRC-0071, SRC-0071]. It was historically significant as the United States' first high-power, long-range, wideband radar [SRC-0071]. ALCOR originally utilized 500 MHz chirped pulses to achieve extraordinary range resolution, allowing researchers to measure the exact length of threat objects and discern individual scattering centers on reentry vehicles [SRC-0071, SRC-0071]. This capability was instrumental in proving the value of wideband radars for ballistic missile discrimination [SRC-0071]. Furthermore, ALCOR achieved a major technological milestone in 1971 when it became the first radar to successfully apply inverse synthetic aperture radar (ISAR) imaging techniques to orbiting satellites, profoundly advancing the field of space-object identification [SRC-0071]. Today, ALCOR maintains an active and critical operational status at the Reagan Test Site [SRC-0071, SRC-0071]. Following a 1999 modernization to the Radar Open System Architecture, it continues to track main rocket bodies, identify space debris, and capture real-time wideband signatures [SRC-0071, SRC-0071, SRC-0151].</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
@@ -12090,6 +12414,11 @@
       <c r="V161" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12474,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>Millimeter-Wave imaging radar used for space surveillance and detailed intelligence data collection.</t>
+          <t>The Millimeter-Wave (MMW) radar is a highly advanced imaging and tracking system located on Roi-Namur island in the Kwajalein Atoll, Marshall Islands [SRC-0071, SRC-0071]. Operated under the Ronald Reagan Ballistic Missile Defense Test Site by the U.S. Army Space and Missile Defense Command, the MMW radar was developed to meet the growing need for high-resolution target data and became operational in 1983 [SRC-0150, SRC-0071, SRC-0071]. Operating in the Ka-band, the MMW radar is enclosed in a protective radome and features a specialized optical beam waveguide system designed to reduce microwave losses [SRC-0071, SRC-0071]. The radar's very short wavelength significantly increases the number of visible scattering centers on a target, allowing it to produce incredibly detailed images [SRC-0071]. Because of this, it quickly became the premier imaging system at the Kiernan Reentry Measurements Site (KREMS) for space-object identification [SRC-0071]. MMW's precision also makes it an essential asset for Ballistic Missile Defense testing, as it can accurately measure the miss distance and impact point of kinetic interceptors [SRC-0071]. In 1987, it was integrated with the Kwajalein Discrimination System to provide real-time imaging of reentry vehicles [SRC-0071]. Upgraded in 2000 under the Radar Open System Architecture program, the MMW radar remains fully operational today, continuously supporting U.S. Strategic Command space missions and missile test operations [SRC-0150, SRC-0071].</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -12161,6 +12490,11 @@
       <c r="V162" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0150</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12682,9 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Pacific Proving Grounds site formerly used for launches in conjunction with nuclear bomb tests.</t>
+          <t>Bikini Atoll is a geographic feature and former weapons testing site located in the Ralik (Sunset) Chain of the Marshall Islands in the Pacific Ocean [SRC-0163]. The atoll is situated at the coordinates 11°36′54″N 165°33′11″E [SRC-0096]. Historically, Bikini Atoll served as a primary location for the Pacific Proving Grounds, an extensive reservation established by the United States Atomic Energy Commission in the year 1946 [SRC-0149]. The governing organization for these proving grounds was the United States Department of Energy [SRC-0149].
+The most notable activities conducted at Bikini Atoll centered around the United States' nuclear weapons testing program [SRC-0149, SRC-0163]. In addition to nuclear detonations, the atoll was utilized as a rocket launch site; these rocket launches were conducted specifically in conjunction with the nuclear bomb tests to support the testing program's objectives [SRC-0096]. While detailed information on specific key facilities or radars at the atoll is not provided in the available sources, its primary function was fully dedicated to these explosive and rocket testing operations.
+Operating alongside Enewetak Atoll and the surrounding areas, Bikini Atoll played a significant role in the testing of advanced weapons technologies until the Pacific Proving Grounds were officially deactivated in 1963 [SRC-0149]. Regarding its current status, the testing facilities at Bikini Atoll are inactive, and the site remains an inactive U.S. Department of Energy area [SRC-0149].</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
@@ -12364,6 +12700,11 @@
       <c r="V165" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>SRC-0163, SRC-0096, SRC-0149</t>
         </is>
       </c>
     </row>
@@ -12414,7 +12755,9 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Pacific Proving Grounds site formerly used for launches in conjunction with nuclear bomb tests.</t>
+          <t>Eniwetok (also spelled Enewetak) is an atoll located in the western Ralik (Sunset) Chain of the Marshall Islands in the Pacific Ocean [SRC-0163]. Positioned at the exact coordinates of 11°20′24″N 162°19′30″E, it served as a significant site for mid-twentieth-century military experimentation [SRC-0096]. Along with Bikini Atoll, Eniwetok was one of the primary components of the Pacific Proving Grounds, a designated testing area established in 1946 by the United States Atomic Energy Commission [SRC-0149]. The site fell under the jurisdiction and governing organization of the United States Department of Energy [SRC-0149].
+During its operational years, Eniwetok was primarily utilized for nuclear weapons testing [SRC-0149]. As part of these operations, the atoll functioned as a rocket launch site, with various rocket launches executed in direct conjunction with the nuclear bomb tests taking place at the facility [SRC-0096]. While the sources do not detail specific key facilities, buildings, or radar installations located on the atoll, its infrastructure was fully dedicated to supporting these nuclear and rocket test missions.
+The testing installations at Eniwetok were heavily utilized until the broader Pacific Proving Grounds were deactivated in 1963 [SRC-0149]. Regarding its current status, the Eniwetok testing site is classified as an inactive U.S. Department of Energy area [SRC-0149].</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -12430,6 +12773,11 @@
       <c r="V166" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC-0163, SRC-0096, SRC-0149</t>
         </is>
       </c>
     </row>
@@ -12711,7 +13059,9 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>Florida space launch range for polar and geostationary orbits.</t>
+          <t>The Eastern Range (ER) is a massive United States launch range extending from Argentia in Newfoundland to Ascension Island in the South Atlantic Ocean [SRC-0189]. The range operates primarily out of the Cape Canaveral Space Force Station and the Kennedy Space Center in Florida [SRC-0189, SRC-0118]. Constructed in the 1950s and early 1960s to serve as research and development facilities for early missile programs [SRC-0189], the ER is currently governed by the United States Space Force (USSF) and managed by Space Launch Delta 45 (formerly the 45th Space Wing), headquartered at Patrick Space Force Base [SRC-0189, SRC-0202].
+The primary mission of the Eastern Range is to support safe and secure space and ballistic missile launches, aeronautical operations, and space surveillance for the Department of Defense, NASA, and commercial entities [SRC-0202, SRC-0189]. To accomplish this, the range utilizes a vast array of key facilities and instrumentation, including precision tracking radars, telemetry processing systems, optic tracking systems, and the Flight Termination System (FTS) [SRC-0118, SRC-0202]. The ER incorporates the Network CORE communication backbone and downrange tracking sites in Antigua and Ascension Island [SRC-0118, SRC-0118]. Furthermore, support ships such as the USNS Howard O. Lorenzen and USNS Invincible provide critical radar tracking data in broad ocean areas where ground stations cannot reach [SRC-0192, SRC-0192, SRC-0192].
+In recent years, the Eastern Range has experienced a massive increase in operations. After a "Drive for 48" initiative aimed at supporting 48 launches a year [SRC-0203], the range supported a record-breaking 109 orbital flights in 2025 [SRC-0203, SRC-0202]. Currently active and expanding under a "Spaceport of the Future" infrastructure initiative, the ER aims to accommodate 500 or more launches annually by 2030, remaining the dominant space launch hub in the United States [SRC-0203].</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -12727,6 +13077,11 @@
       <c r="V170" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>SRC-0189, SRC-0118, SRC-0202, SRC-0192, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -12782,7 +13137,9 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Launch and testing site located on the Eastern Range.</t>
+          <t>Cape Canaveral Space Force Station (CCSFS) is a premier military space launch facility located on Cape Canaveral in Brevard County, Florida, situated south-southeast of NASA's Kennedy Space Center on Merritt Island [SRC-0031]. The site was established in 1949 by President Harry S. Truman as the Joint Long Range Proving Ground [SRC-0031]. Following a transfer of land from the Navy to the Air Force, it was designated the Long Range Proving Ground Base in 1950 [SRC-0031]. Over the decades, the site underwent several name changes, including Cape Kennedy Air Force Station, before officially becoming Cape Canaveral Space Force Station in December 2020 [SRC-0031].
+Governed by the United States Space Force and operated by Space Launch Delta 45, CCSFS acts as the primary launch site for the Eastern Range [SRC-0031]. The station’s key facilities include four highly active space launch complexes (SLC-36, SLC-40, SLC-41, and SLC-46), Landing Zone 40, and a 10,000-foot Skid Strip runway used by heavy military airlift aircraft to transport satellite payloads [SRC-0031, SRC-0031, SRC-0031]. Additionally, the site hosts the Naval Ordnance Test Unit (NOTU), which tests sea-based weapons and Fleet Ballistic Missiles [SRC-0031, SRC-0031].
+Cape Canaveral has an exceptionally notable history in spaceflight. It was the launch site for the first U.S. Earth satellite in 1958, the first U.S. astronaut in orbit in 1962, and early spacecraft to orbit Mars, Saturn, and Mercury [SRC-0031]. During the Cold War, the facility tested major missile systems including the Redstone, Jupiter, Polaris, Atlas, and Titan [SRC-0031]. Today, the station remains highly active, partnering heavily with commercial space industry leaders. Private companies such as SpaceX, United Launch Alliance, and Blue Origin lease and operate launch pads at the site, launching Falcon 9, Vulcan Centaur, and New Glenn rockets into orbit [SRC-0031].</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -12798,6 +13155,11 @@
       <c r="V171" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>SRC-0031</t>
         </is>
       </c>
     </row>
@@ -13005,7 +13367,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>The Ronald Reagan Ballistic Missile Defense Test Site (RTS), historically known as the Kwajalein Missile Range, is a premier United States military test range located on the Kwajalein Atoll in the Republic of the Marshall Islands, approximately 2,200 miles southwest of Hawaii [SRC-0106, SRC-0159]. Founded over 50 years ago, the site's technical operations began around 1962 when the TRADEX radar became operational, with the facility being officially renamed the Reagan Test Site in 1999 [SRC-0071, SRC-0071, SRC-0071]. The RTS is governed by the U.S. Army Space and Missile Defense Command (USASMDC), with technical leadership and scientific advisement provided by MIT Lincoln Laboratory [SRC-0159, SRC-0071, SRC-0164]. The site's primary mission includes testing intercontinental ballistic missiles (ICBMs), evaluating ballistic missile defense systems, and conducting space domain awareness [SRC-0164]. Key facilities are largely centered at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, which hosts four of the world's most sophisticated high-power instrumentation radars: ALTAIR (VHF/UHF), TRADEX (L/S band), ALCOR (C-band), and MMW (Ka-band) [SRC-0071, SRC-0071]. These systems provide unparalleled radar measurements, space-object tracking, and deep-space intelligence collection [SRC-0164, SRC-0106]. Additionally, the range relies on extensive telemetry sites, optical tracking systems like SRADOT, and underwater acoustic impact location systems [SRC-0164]. Currently, RTS operates as a government-managed, contractor-operated (GMCO) installation, with operations run remotely from the RTS Operation Center in Huntsville, Alabama (ROC-H) [SRC-0164, SRC-0150]. The facility routinely supports high-profile Department of Defense operations, such as the Air Force's "Glory Trip" Minuteman III tests, hypersonic boost-glide developmental tests, and NASA scientific missions, cementing its status as a critical node in U.S. national security and space surveillance networks [SRC-0164, SRC-0150, SRC-0151].</t>
+          <t>The Ronald Reagan Ballistic Missile Defense Test Site (RTS), formerly known as Kwajalein Missile Range, is located in the Kwajalein Atoll of the Republic of the Marshall Islands, situated in the central Pacific Ocean [SRC-0071, SRC-0150]. Established in 1959 when the atoll was chosen to test the Nike-Zeus antiballistic missile system, the site has grown into a premier Department of Defense Major Range and Test Facility Base [SRC-0071, SRC-0071, SRC-0150]. It is governed by the U.S. Army Space and Missile Defense Command (USASMDC) [SRC-0150]. Operations are controlled remotely from the RTS Operation Center in Huntsville, Alabama (ROC-H) [SRC-0150]. The installation's key facilities include the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, which hosts four world-class instrumentation radars: ALTAIR, TRADEX, ALCOR, and MMW [SRC-0071, SRC-0071]. RTS also features extensive telemetry sites, optical tracking mounts like the Super RADOT, and a ship-based mobile range safety system [SRC-0071, SRC-0071, SRC-0071]. Notable activities at the site include developmental and operational flight tests for Air Force Minuteman III intercontinental ballistic missiles (Glory Trip missions), Army and Navy hypersonic boost-glide tests, and intercept demonstrations for Missile Defense Agency systems like THAAD, Patriot, and Aegis [SRC-0150, SRC-0150, SRC-0164]. Furthermore, RTS provides vital space domain awareness for U.S. Strategic Command and supports NASA scientific research, such as the SEED sounding rocket mission for ionospheric studies [SRC-0164, SRC-0151]. Today, RTS remains in active operational status, continuously modernized through distributed net-centric architecture [SRC-0071, SRC-0164].</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -13025,7 +13387,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>SRC-0106, SRC-0159, SRC-0071, SRC-0164, SRC-0150, SRC-0151</t>
+          <t>SRC-0071, SRC-0150, SRC-0164, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -13157,7 +13519,9 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>Vast overland military testing area and proving ground in New Mexico.</t>
+          <t>White Sands Missile Range (WSMR) is a vast military testing area and firing range located in the Tularosa Basin of southern New Mexico [SRC-0218]. Covering approximately 3,200 square miles across Doña Ana, Otero, Socorro, Sierra, and Lincoln counties, it is the largest military installation in the United States [SRC-0218]. The installation was originally established in 1941 as the Alamogordo Bombing and Gunnery Range [SRC-0218]. It was officially designated as the White Sands Proving Ground on July 9, 1945, and later renamed White Sands Missile Range in May 1958 [SRC-0218, SRC-0218].
+Governed by the United States Army Test and Evaluation Command (ATEC), WSMR provides an overland range to support research and development testing for the Army, Navy, Air Force, NASA, and commercial partners [SRC-0218, SRC-0106]. Key facilities include multiple launch complexes (such as LC-33, LC-36, and LC-38), the White Sands Test Center, the High-Energy Laser Test Facility (HELSTF), and the Radar Target Backscatter Facility (RATSCAT) [SRC-0106, SRC-0106, SRC-0218, SRC-0218]. The range is also equipped with over 2,000 monumented instrumentation points and rare Multiple Object Tracking Radars (MOTR) used for flight safety operations [SRC-0106, SRC-0157].
+WSMR is famous for several historically significant events, most notably the Trinity test on July 16, 1945, the world's first atomic bomb detonation [SRC-0218]. Following World War II, the range hosted the testing of 67 captured German V-2 rockets [SRC-0218]. It was also the site of the only space shuttle landing outside of California or Florida, when Columbia landed on the Northrop Strip in 1982 [SRC-0218]. Currently active, WSMR conducts ongoing developmental testing of air defense systems, ballistic missiles, and electromagnetic countermeasures, while also housing protected natural areas like White Sands National Park [SRC-0106, SRC-0218, SRC-0218].</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -13173,6 +13537,11 @@
       <c r="V176" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>SRC-0218, SRC-0106, SRC-0157</t>
         </is>
       </c>
     </row>
@@ -13304,7 +13673,9 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>Army proving ground in Utah for biological and chemical defense testing.</t>
+          <t>Dugway Proving Ground is an active and specialized military installation situated in the Great Salt Lake Desert of Utah [SRC-0149]. While its exact founding year is not specified in the provided records, the facility operates as a critical component of the Department of Defense's Major Range and Test Facility Base (MRTFB), which is a national asset maintained to support the DoD acquisition system [SRC-0085, SRC-0105]. The proving ground is governed and managed by the United States Army Test and Evaluation Command [SRC-0149].
+The primary mission and notable activities at Dugway Proving Ground revolve around the testing and evaluation of United States and Allied biological and chemical weapon defense systems [SRC-0149]. Unlike ranges focused heavily on ballistic missile or space launches, Dugway specializes in environmental testing, evaluating chemical and biological defense systems, and validating passive defense systems [SRC-0222]. The remote and harsh geography of the Utah desert provides a secure, isolated, and controlled environment necessary for these highly sensitive and hazardous evaluations. 
+As a core testing site, the proving ground relies on specific infrastructure to safely test these defensive capabilities, though exact radar or launch complex specifications are not heavily detailed in the sources [SRC-0149, SRC-0105]. Currently, Dugway Proving Ground remains an active and vital military testing location. Historically, the Department of Defense has recognized its ongoing importance by allocating millions of dollars in future infrastructure and range improvements to ensure its capabilities can meet the future needs of the military and the Army Test and Evaluation Command [SRC-0105, SRC-0105].</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -13320,6 +13691,11 @@
       <c r="V178" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>SRC-0149, SRC-0085, SRC-0105, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -13451,7 +13827,9 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>Army proving ground and testing center in Maryland.</t>
+          <t>Aberdeen Test Center is located at the Aberdeen Proving Ground on the western shore of the Chesapeake Bay, approximately 30 miles northeast of Baltimore, Maryland [SRC-0149, SRC-0106]. Established on October 20, 1917, just six months after the United States entered World War I, it holds the distinction of being the United States Army's oldest active proving ground [SRC-0149]. It was originally constructed to ensure that the design and testing of ordnance materiel could be conducted in close proximity to the nation's industrial and shipping hubs [SRC-0149]. The facility is governed and operated by the United States Army [SRC-0149, SRC-0222].
+The testing center boasts expansive facilities, including 79,000 acres of land and water dedicated to firing and explosive testing, as well as 3,000 acres strictly for automotive system evaluations [SRC-0106]. Key facilities include ten major automotive test areas covering 39 miles of severe terrain courses, such as the Munson Test Course, Perryman Test Course, and Churchville Test Area, which feature steep hills, mud, and staggered bumps to test vehicle endurance [SRC-0106]. For weaponry, the Main Front Area provides 28 firing positions and restricted airspace for range firings out to 34,000 meters [SRC-0106].
+Notable activities at the Aberdeen Test Center involve the developmental testing of artillery weapon systems, mortars, recoilless rifles, armored vehicles, and air defense systems [SRC-0106]. The site also conducts rigorous environmental and vulnerability tests, assessing live ammunition and warheads against vibration, temperature extremes, fungus, salt fog, and electromagnetic interference [SRC-0222, SRC-0106]. Today, the Aberdeen Test Center remains a fully active proving ground, continuing its century-long legacy of evaluating the durability, ballistic vulnerability, and overall performance of military vehicles and ordnance for the U.S. Armed Forces [SRC-0149, SRC-0222, SRC-0106].</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -13467,6 +13845,11 @@
       <c r="V180" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>SRC-0149, SRC-0106, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -13522,7 +13905,9 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>Air Force training and testing range in Nevada.</t>
+          <t>The Nevada Test and Training Range (NTTR) is a massive military testing and training installation located within the Nellis Air Force Base Complex in southern Nevada [SRC-0149, SRC-0222]. Originally associated with the adjacent Nevada National Security Site (formerly the Nevada Proving Grounds) [SRC-0149], the NTTR is governed and operated by the United States Air Force [SRC-0222]. It serves as a major component of the Department of Defense's Major Range and Test Facility Base (MRTFB) [SRC-0085].
+The NTTR encompasses specialized air and ground sectors designed for rigorous combat simulations. Key facilities include the North Ranges, which feature the Tonopah and Tolicha Peak Electronic Combat (EC) areas [SRC-0106]. These areas provide highly realistic enemy radar environments for aircrew training [SRC-0106]. The tactical ranges, such as Range 71, are equipped with simulated missile sites, airfields, convoys, and nuclear bombing circles where live and inert ordnance can be deployed [SRC-0106]. The South Ranges similarly offer realistic ground target simulations, including ICBM sites and targets in and around Dogbone Lake [SRC-0106]. 
+Notable activities at the NTTR focus on advanced tactical warfare training, including air-to-air and air-to-ground munitions delivery, and air combat maneuvering [SRC-0222, SRC-0106]. The range is essential for conducting Operational Test and Evaluation (OT&amp;E) and hosting major large-force exercises like Red Flag and Gallant Eagle [SRC-0106]. Currently, the Nevada Test and Training Range remains a fully active and premier training hub for the Air Force. Recognizing its critical role in national security and pilot readiness, the military has planned significant investments for the NTTR, including over $450 million in infrastructure and test asset improvements to support future weapon systems testing and advanced electronic warfare simulations [SRC-0222, SRC-0105].</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -13538,6 +13923,11 @@
       <c r="V181" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>SRC-0149, SRC-0222, SRC-0085, SRC-0106, SRC-0105</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13983,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>Air Force range in Utah supporting missile and guided weapons testing.</t>
+          <t>The Utah Test and Training Range (UTTR) is located in the Great Salt Lake Desert, approximately 70 miles west of Salt Lake City, Utah [SRC-0106]. The range encompasses 2,136 square nautical miles of Department of Defense-owned landspace [SRC-0106], split into two primary restricted areas: the North Range and the South Range, bounded by military operating areas with restricted airspace extending from the surface up to 58,000 feet [SRC-0106]. UTTR is managed by the 6501st Range Squadron out of Hill Air Force Base, which operates under the 6545th Test Group and the Air Force Flight Test Center (AFFTC) [SRC-0106]. The installation provides extensive range facilities for the test and evaluation of manned and unmanned aircraft systems, as well as tactical training for air-to-air and air-to-ground weapon delivery [SRC-0106]. Its sophisticated instrumentation network includes the High Accuracy Multiple Object Tracking System (HAMOTS), which collects time-space-position information, alongside precision tracking radars, surveillance radars, and cinetheodolites [SRC-0106], [SRC-0106]. Operations are overseen from the Mission Control Center at Hill AFB, which is equipped for real-time data collection and display [SRC-0106]. UTTR houses numerous specialized target facilities, such as the Eagle Range for air-to-ground scoring, the Kitty Cat Range for live ordnance drops, and the Wildcat and Baker's Strongpoint Ranges, which feature simulated industrial complexes, convoys, and surface-to-air missile sites [SRC-0106]. Notable activities conducted at the range include the testing of cruise missiles (such as the ALCM and GLCM), Maverick missiles, conventional munitions shelf-life testing, and full-spectrum joint training exercises [SRC-0106].</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -13609,6 +13999,11 @@
       <c r="V182" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
         </is>
       </c>
     </row>
@@ -13664,7 +14059,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>Air Force complex in Tennessee focused on aerodynamic and propulsion testing.</t>
+          <t>The Arnold Engineering Development Complex (AEDC), historically referred to as the Arnold Engineering Development Center, is situated in middle Tennessee, roughly 72 miles southeast of Nashville and 61 miles northwest of Chattanooga [SRC-0106]. It occupies a 40,000-acre reservation, allowing it to operate with minimal environmental impact while accommodating advanced test facilities [SRC-0106]. AEDC manages, develops, and operates critical ground environmental test facilities dedicated to the research and development of aerospace systems [SRC-0106]. The complex simulates aerodynamic, propulsion, and space flight environments to support a wide range of government and commercial users [SRC-0106]. AEDC is equipped with uniquely advanced testing infrastructure. It houses nine wind tunnels covering Mach 0.2 to 10, including the nation's only 16-foot transonic and supersonic wind tunnels capable of airframe and propulsion integration testing under controlled altitude conditions [SRC-0106]. Other key facilities include arc heater test units like the Dust Erosion Tunnel and High Enthalpy Ablation Test Facility, aeroballistic and impact ranges capable of accelerating models to 23,500 feet per second, and multiple turbojet and turbofan test cells [SRC-0106]. These robust capabilities enable AEDC to support testing for an extensive array of notable military programs. Historical and ongoing projects supported at the complex include the B-1 and F-15/16 aircraft, various air-launched cruise missiles, the Peacekeeper and Minuteman ICBMs, the Trident missile, and the Space Shuttle [SRC-0106].</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -13680,6 +14075,11 @@
       <c r="V183" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
         </is>
       </c>
     </row>
@@ -13811,7 +14211,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>Major naval testing facility in California's Mojave Desert.</t>
+          <t>The Naval Air Warfare Center Weapons Division (NAWCWD) operates extensive test and evaluation facilities at China Lake, located in the upper Mojave Desert about 150 miles northeast of Los Angeles, California [SRC-0106]. As a premier military proving ground and testing facility [SRC-0149], [SRC-0195], the China Lake complex spans 1.1 million acres of land and incorporates 17,000 square miles of the R-2508 restricted military airspace [SRC-0195]. NAWCWD China Lake is responsible for the development, testing, and evaluation of air- and surface-launched weapons, electronic warfare systems, missiles, and parachute systems [SRC-0106]. The installation features specialized testing zones, including Air Operation Ranges (Air Weapons Range, Air Tactics Range, and Military Target Range) for evaluating fire-control systems and guided weapons against fixed and moving targets [SRC-0106]. It also houses Guided Missile Ranges for testing tactical air-defense systems, heavily instrumented Supersonic Test Tracks, and Explosive and Propulsion Test Ranges [SRC-0106], [SRC-0106]. The Electronic Warfare Threat Environment Simulation (EWTES) Facility, also known as the Electronic Combat Range, provides a simulated hostile defense environment for electronic countermeasures testing and tactics development [SRC-0106], [SRC-0195]. China Lake has supported a vast array of high-profile defense projects, including the integration and testing of TOMAHAWK and cruise missiles, HARM, SPARROW, SIDEWINDER, MAVERICK, and various Navy conventional ordnance systems [SRC-0106].</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -13827,6 +14227,11 @@
       <c r="V185" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>SRC-0106, SRC-0149, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -13960,7 +14365,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>Naval test center in Maryland for aircraft and integrated systems.</t>
+          <t>The Naval Air Warfare Center Aircraft Division (NAWCAD) Patuxent River, historically known as the Naval Air Test Center, is situated in Lexington Park, Maryland, on the shores of the Chesapeake Bay approximately 45 miles southeast of Washington, D.C. [SRC-0106]. As a major component of the Department of Defense's test infrastructure, NAWCAD provides comprehensive technical and engineering support for the life cycle testing and evaluation of aircraft weapon systems [SRC-0106], [SRC-0195]. The installation features extensive airfield and flight test ranges, controlling 50,000 square miles of airspace, 39,375 square miles of sea space, and 7,950 acres of land space to support its research and development missions [SRC-0195]. NAWCAD Patuxent River encompasses state-of-the-art infrastructure, including the Air Combat Environment Test and Evaluation Facility (ACETEF) and Electromagnetic Environmental Effects Facilities, which allow for the thorough evaluation of electromagnetic interference, radiation hazards, and vulnerability [SRC-0106], [SRC-0195]. Its capabilities also include full-scale aircraft testing with operating engines and systems under normal power [SRC-0106], as well as air-breathing propulsion system test facilities [SRC-0195]. The site primarily performs developmental and operational testing of both manned and unmanned air vehicles, covering mission systems, carrier suitability certification, modeling, and simulation support [SRC-0195]. It supports over 160 aircraft representing all Navy and Marine Corps platforms, functioning as a critical hub for evaluating aircraft flight characteristics, maintenance logistics, and weapon separation envelopes [SRC-0106], [SRC-0106].</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -13976,6 +14381,11 @@
       <c r="V187" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>SRC-0106, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14441,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>Navy acoustic and underwater test facility.</t>
+          <t>The Atlantic Undersea Test and Evaluation Center (AUTEC) is a detachment of the Naval Undersea Warfare Center (NUWC) Division Newport, with its primary deep-water test facilities located on Andros Island and the Berry Islands in the Bahamas [SRC-0106], [SRC-0195]. AUTEC’s administrative and flight operations are headquartered in West Palm Beach, Florida [SRC-0195]. Located in the Tongue of the Ocean—a sheltered, 800-fathom-deep, and quiet body of water—AUTEC provides the U.S. Navy with full-spectrum test and evaluation capabilities for undersea warfare systems, sonar calibration, and fleet readiness [SRC-0106], [SRC-0195]. The center is composed of three main ranges: the AUTEC Weapons Range, an instrumented tracking range for assessing sensors, weapons, and platforms; the Acoustic Measurement Range, the East Coast's only permanent underwater noise-measuring facility for recording hydroacoustic emissions from submarines and surface ships; and the Fleet Operational Readiness Accuracy Check Site (FORACS V), which measures the accuracy of ASW and navigational sensors [SRC-0106]. The main base at Andros Island's Site 1 hosts the Command Control Building for real-time tracking and data processing, a precision machine shop, dive lockers, and torpedo Intermediate Maintenance Activities (IMA) for both lightweight and heavyweight torpedoes [SRC-0195]. AUTEC supports high-profile Navy projects, including Mk 46 and Mk 48 torpedo certifications, DD-963 and FFG-7 ship acceptance trials, advanced magnetics silencing, and various anti-submarine warfare tactics development [SRC-0106], [SRC-0195].</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -14047,6 +14457,11 @@
       <c r="V188" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W188" t="inlineStr">
+        <is>
+          <t>SRC-0106, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14517,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>Upgraded Early Warning Radar in California supporting missile defense.</t>
+          <t>The Upgraded Early Warning Radar (UEWR) at Beale Air Force Base in California is a critical ground-based strategic radar site operated by the United States Space Force [SRC-0190], [SRC-0212]. Managed by the 7th Space Warning Squadron (7 SWS) under the Space Operations Command, the installation forms a vital node in the United States' early warning and space domain awareness network [SRC-0190]. The Beale radar operates using an AN/FPS-132 Solid-State Phased Array system transmitting in the UHF band [SRC-0190]. Designed with two active array faces, the facility provides 240-degree azimuth coverage [SRC-0190], [SRC-0212]. The Beale radar was originally built in 1979 as a PAVE PAWS (Perimeter Acquisition Vehicle Entry Phased-Array Weapons System) installation [SRC-0190]. It underwent a significant upgrade to the UEWR configuration in 2005 and received further system enhancements in 2019 [SRC-0190]. Today, the radar feeds directly into the Missile Defense Agency's Ground-based Midcourse Defense (GMD) system, alongside sister UEWR sites in Thule, Greenland, and Fylingdales, United Kingdom [SRC-0187], [SRC-0212]. It provides essential detection, tracking, and classification data to identify incoming ballistic missile threats [SRC-0212]. The Beale UEWR is currently slated for the Ground Based Radar Digitization (GBRD) program's Phase 1 prototyping, with an Initial Operational Capability (IOC) targeted for Fiscal Year 2030, ensuring the continued modernization of its strategic missile warning and space surveillance missions [SRC-0190].</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -14118,6 +14533,11 @@
       <c r="V189" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W189" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0212, SRC-0187</t>
         </is>
       </c>
     </row>
@@ -14173,7 +14593,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>Upgraded Early Warning Radar in Massachusetts supporting missile defense.</t>
+          <t>Cape Cod Space Force Station, located atop Flat Rock Hill within the Massachusetts Military Reservation, hosts a vital strategic radar installation [SRC-0133]. The site was established and activated in 1980 as a PAVE Phased Array Warning System (PAVE PAWS) installation, originally using the AN/FPS-115 radar to guard the East Coast against sea-launched and intercontinental ballistic missiles [SRC-0190]. The facility is currently operated by the 6th Space Warning Squadron (6 SWS), a unit functioning under the United States Space Force's Space Operations Command [SRC-0190]. The key facility at this station is the AN/FPS-132 Upgraded Early Warning Radar (UEWR) [SRC-0190]. Upgraded from its original configuration under a 2013 contract, the current solid-state phased-array radar operates in the UHF frequency band and features two active faces [SRC-0190]. Each radar face provides 120 degrees of azimuth coverage, yielding a combined 240-degree coverage arc across the Atlantic Ocean [SRC-0190]. Using electronic beam steering instead of a rotating mechanical dish, the system can rapidly scan the horizon [SRC-0133]. The radar's primary mission includes missile warning and space surveillance [SRC-0133]. It actively tracks low-Earth orbit satellites, space debris, and other objects deviating from known orbits [SRC-0190]. Notably, the Cape Cod UEWR is the only radar in the United States capable of confirming a detected missile launch directed toward the US or Canada from the east [SRC-0133]. The radar completed its UEWR modernization between 2016 and 2017, successfully integrating into the Ballistic Missile Defense System [SRC-0190]. Currently, the radar is fully operational and is scheduled for front-end digitization under the Space Force's accelerated Ground Based Radar Digitization (GBRD) program [SRC-0190].</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -14189,6 +14609,11 @@
       <c r="V190" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W190" t="inlineStr">
+        <is>
+          <t>SRC-0133, SRC-0190</t>
         </is>
       </c>
     </row>
@@ -14244,7 +14669,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>Upgraded Early Warning Radar located in Alaska.</t>
+          <t>Clear Space Force Station, located in central Alaska, operates as a critical sensor hub for the Pacific theater [SRC-0190]. The site was originally established in September 1961 as one of the three original Ballistic Missile Early Warning System (BMEWS) installations, which initially relied on mechanical radars [SRC-0190]. Today, the early warning mission at the site is governed and executed by the 13th Space Warning Squadron (13 SWS) under the United States Space Force Space Operations Command [SRC-0190]. The primary facility at the site is the AN/FPS-132 Upgraded Early Warning Radar (UEWR) [SRC-0190]. The system was upgraded from its 1981 AN/FPS-123 Solid-State Phased Array Radar System (SSPARS) configuration by Raytheon under a $125.3 million contract awarded in 2012 [SRC-0190]. Housed within the original scanner building, the modern UEWR features a two-panel solid-state phased array operating in the UHF band [SRC-0190], [SRC-0190]. This dual-face design provides a 240-degree coverage arc across the Arctic and Pacific regions [SRC-0190]. Clear SFS serves a vital role by conducting overlapping early warning, precision tracking, and space surveillance missions [SRC-0190]. The UEWR upgrade was officially completed in Fiscal Year 2016, adding crucial Ground-based Midcourse Defense communication capabilities to the site [SRC-0190]. Currently, the UEWR radar is fully operational and continues its continuous missile warning mission [SRC-0190]. To ensure its long-term viability, the Clear UEWR has been selected for phase one prototyping under the Space Force's Ground Based Radar Digitization (GBRD) program, an initiative designed to transition legacy radar infrastructure from analog to digital operations by upgrading both front-end antennas and back-end data processors by 2030 [SRC-0186], [SRC-0190].</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -14260,6 +14685,11 @@
       <c r="V191" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W191" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0186</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14745,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Long Range Discrimination Radar located in Alaska for missile defense.</t>
+          <t>Located at Clear Space Force Station in Alaska, the Long Range Discrimination Radar (LRDR) is a cutting-edge sensor designed to defend the US homeland against complex ballistic missile threats [SRC-0190]. The Missile Defense Agency (MDA) initiated the LRDR program in March 2014, driven by a congressional mandate to deploy a radar optimized against threats from North Korea [SRC-0190]. Lockheed Martin was awarded the $784 million development contract in October 2015, and the radar achieved initial fielding on December 6, 2021 [SRC-0190]. The LRDR is jointly managed by the MDA and the United States Space Force Combat Forces Command [SRC-0190]. It is maintained locally by the 13th Space Warning Squadron, while daily operations are executed remotely by the 7th Space Warning Squadron [SRC-0190]. The key facility, the AN/FPS-138 LRDR, is a multi-face active electronically scanned array (AESA) radar utilizing Gallium Nitride (GaN) solid-state semiconductor technology [SRC-0190]. It features dual monostatic arrays operating in the S-band, with each radar face measuring 60 feet high and 60 feet wide [SRC-0190]. The radar is specifically designed for high-resolution midcourse target discrimination [SRC-0190]. It can simultaneously track and distinguish lethal ballistic missile warheads from decoys, spent rocket bodies, and space debris, preserving the limited inventory of Ground-Based Interceptors [SRC-0045], [SRC-0190]. The system is capable of continuous threat monitoring, ensuring operational readiness even during maintenance cycles [SRC-0045]. Lockheed Martin completed final acceptance and handed the radar over to the MDA in April 2024 [SRC-0190]. The system transitioned to fully operational status under the Combat Forces Command on December 8, 2025, and was declared fully operational for homeland defense in early 2026 [SRC-0190].</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -14331,6 +14761,11 @@
       <c r="V192" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W192" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0045</t>
         </is>
       </c>
     </row>
@@ -14386,7 +14821,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Perimeter Acquisition Radar Attack Characterization System in North Dakota.</t>
+          <t>Cavalier Space Force Station is situated in North Dakota, approximately 15 miles south of the Canadian border [SRC-0143]. The radar facility was originally designed and built by General Electric in the early 1970s as the Perimeter Acquisition Radar (PAR), serving as a central component of the US Army's Safeguard anti-ballistic missile system [SRC-0190]. After the Safeguard system was decommissioned in 1976 shortly after activation, the radar was transferred to the Air Force [SRC-0190]. The base was renamed Cavalier Air Force Station in 1983 and officially became Cavalier Space Force Station in 2021 [SRC-0190]. The site is currently governed by the 10th Space Warning Squadron (10 SWS) under the Space Force's Space Operations Command, with maintenance and sustainment support provided by contractors such as InDyne [SRC-0190], [SRC-0210]. The station houses the AN/FPQ-16 Perimeter Acquisition Radar Attack Characterization System (PARCS) [SRC-0190]. PARCS is a massive, single-faced passive electronically scanned array (PESA) radar housed in a reinforced concrete structure [SRC-0190]. Operating in the UHF band between 420 and 450 MHz, the radar utilizes an output of approximately 14.3 megawatts of peak power [SRC-0190]. The radar's single face provides 140 degrees of azimuth coverage with a detection range extending up to 2,000 miles [SRC-0190]. PARCS provides early warning detection of sea-launched and intercontinental ballistic missiles targeting North America [SRC-0190]. Operating as a collateral sensor for the Space Surveillance Network, it continuously monitors and tracks more than half of all Earth-orbiting space objects [SRC-0190]. PARCS remains fully operational today and is scheduled for a comprehensive overhaul to digitize its 1970s-era front-end antenna under the Ground Based Radar Digitization (GBRD) program [SRC-0190].</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -14402,6 +14837,11 @@
       <c r="V193" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC-0143, SRC-0190, SRC-0210</t>
         </is>
       </c>
     </row>
@@ -14614,7 +15054,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>Mobile semi-submersible early warning and discrimination radar system.</t>
+          <t>The Sea-Based X-Band Radar (SBX-1) is a mobile, ocean-going early warning and tracking radar platform typically deployed in the Pacific Ocean [SRC-0129], [SRC-0190]. Introduced in 2006, the radar was uniquely developed to serve as a highly relocatable, precision midcourse sensor for the US ballistic missile defense system [SRC-0093], [SRC-0190]. The platform is operated and governed jointly by the Military Sealift Command (MSC) and the Missile Defense Agency (MDA) [SRC-0190]. The SBX consists of an advanced X-band phased-array radar mounted on a modified semi-submersible oil rig platform [SRC-0129], [SRC-0190]. The massive radar array is protected from the maritime environment by a pressurized white radome measuring 103 feet high and 120 feet in diameter [SRC-0190]. The system utilizes approximately 45,000 active transmit/receive modules and 69,632 multi-sectional circuits to electronically shape, steer, and amplify the radar beam [SRC-0190]. The radar provides high-precision tracking, object classification, and midcourse discrimination of threat missiles and countermeasures [SRC-0093], [SRC-0129]. It is incredibly sensitive, capable of identifying baseball-sized objects at a range of up to 2,500 miles [SRC-0190]. In 2012, the SBX was placed in a limited test and operations status, allowing it to be recalled to active duty for contingency operations and testing [SRC-0181]. The platform remains an active and critical defense asset today. After 20 years of maritime service, the vessel recently underwent major maintenance to replace its distinctive golf ball-like radome dome in December 2025 [SRC-0129], [SRC-0190]. The recent deployment of new ground-based radars in Alaska may provide the MDA with the geographic flexibility to permanently relocate the SBX to the East Coast or Hawaii [SRC-0181].</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -14630,6 +15070,11 @@
       <c r="V196" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W196" t="inlineStr">
+        <is>
+          <t>SRC-0129, SRC-0190, SRC-0093, SRC-0181</t>
         </is>
       </c>
     </row>
@@ -14685,7 +15130,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>Trailer-mounted X-band radar system used for missile defense.</t>
+          <t>The Army/Navy Transportable Radar Surveillance (AN/TPY-2) system is a mobile, high-resolution radar platform designed for rapid global deployment [SRC-0183]. Introduced in 2007, these transportable systems have been forward-deployed to strategic locations worldwide, including Japan, South Korea, Turkey, and the United Arab Emirates, to counter regional ballistic missile threats [SRC-0183], [SRC-0190]. The radar system is operated and governed jointly by the US Army and the Missile Defense Agency (MDA) [SRC-0190]. The primary facility is the AN/TPY-2 trailer-mounted, single-faced active electronically scanned array (AESA) radar operating in the X-band, specifically between 8.55 and 10 GHz [SRC-0190]. It utilizes over 25,000 transmit/receive modules across a 9.2-square-meter aperture to provide 120 degrees of sector coverage with a detection range exceeding 1,000 kilometers [SRC-0183], [SRC-0190]. The radar can operate in two distinct modes: a forward-based mode for long-range surveillance and early warning, or a terminal mode where it serves as the fire control element for the Terminal High Altitude Area Defense (THAAD) system [SRC-0183]. Currently, five forward-based AN/TPY-2 sites augment US homeland defense by detecting, tracking, and discriminating inbound targets much earlier in their flight paths [SRC-0093], [SRC-0093]. The radar can be transported by C-17 aircraft to austere locations, enabling highly responsive sensor coverage [SRC-0183]. The system remains fully operational globally. The radar fleet recently completed a comprehensive modernization program between 2024 and 2025 to transition its modules to advanced Gallium Nitride (GaN) solid-state technology, significantly enhancing its reliability and performance [SRC-0190]. Additionally, defense contractor Raytheon was recently awarded a $966 million contract modification to continue supporting the radar [SRC-0086].</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -14701,6 +15146,11 @@
       <c r="V197" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC-0183, SRC-0190, SRC-0093, SRC-0086</t>
         </is>
       </c>
     </row>
@@ -14883,7 +15333,9 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>FAA-licensed commercial spaceport in Florida.</t>
+          <t>Located in **Jacksonville, Florida**, **Cecil Airport Spaceport** (also referred to as Cecil Spaceport or Cecil Field Spaceport) is a commercial horizontal launch site co-located at Cecil Airport, a public joint civil-military aviation facility [SRC-0110, SRC-0110, SRC-0154]. Formerly known as Naval Air Station Cecil Field, the site transitioned to commercial and civilian use and is now governed and operated by the **Jackson Aviation Authority** [SRC-0110, SRC-0031]. The facility achieved a significant historical milestone when it was officially licensed in **January 2010**, becoming the **first commercial Air and Space Port on the East Coast of the United States** [SRC-0110]. Because of its unique capabilities, the State of Florida legally considers the facility a designated "spaceport territory" [SRC-0110].
+The spaceport's primary launch infrastructure centers around its massive **horizontal launch runway, which measures 12,503 feet in length and 200 feet in width** [SRC-0110]. Currently, Cecil Spaceport is licensed by the FAA strictly to support **suborbital commercial space launches**; however, its close proximity to the Atlantic Ocean makes it highly suitable to potentially support orbital launch operations in the future [SRC-0110]. 
+Beyond its spaceflight launch capabilities, Cecil Airport remains a highly active multi-purpose aviation hub that regularly supports general aviation (GA) and ongoing military operations [SRC-0110]. Additionally, the site functions as a major **Maintenance, Repair, and Overhaul (MRO) facility**, providing critical services for large aerospace entities and defense contractors, including Boeing, Flightstar, Pratt &amp; Whitney, and the United States Navy [SRC-0110]. By successfully combining commercial space operations with traditional aviation and MRO services, Cecil Spaceport maintains a highly active current status within the United States' expanding horizontal spaceport network [SRC-0110, SRC-0110].</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -14899,6 +15351,11 @@
       <c r="V200" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W200" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0154, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -16097,7 +16554,9 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>Military testing area in Nevada.</t>
+          <t>The Tonopah Test Range, located in Nevada, United States (coordinates 37°47′47″N 116°46′46″W), is a significant military testing, training, and launch facility [SRC-0096, SRC-0095]. Historically, the site at Tonopah functioned as a Continental United States (CONUS) radar station under the Aerospace Defense Command's Semi-Automatic Ground Environment (SAGE) network [SRC-0016].
+Today, Tonopah is deeply integrated into the operations of the Tactical Fighter Weapons Center (TFWC), which is headquartered at Nellis Air Force Base [SRC-0106]. The TFWC manages approximately 6,000 square miles of desert terrain, characterized by valleys, dry lakebeds, and mountain ranges with elevations between 2,500 and 10,000 feet above sea level [SRC-0106]. Within this vast restricted airspace, the Tonopah Electronic Combat (EC) Range serves as one of the two primary "North Ranges" (the other being Tolicha Peak) [SRC-0106].
+The primary operational purpose of the Tonopah EC Range is to simulate a realistic enemy radar and threat environment for tactical aircrew training [SRC-0106]. The facility provides an operationally oriented, combat-like setting where multiple air and ground units can conduct integrated air-to-air and air-to-ground training, as well as test and evaluation (T&amp;E) missions [SRC-0106]. The region's dry climate ensures excellent flight conditions year-round, allowing the facility to accommodate everything from single-aircraft sorties to massive joint exercises involving hundreds of military aircraft [SRC-0106]. Additionally, Tonopah is formally classified as a rocket launch site within the United States [SRC-0096, SRC-0095].</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -16113,6 +16572,11 @@
       <c r="V217" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W217" t="inlineStr">
+        <is>
+          <t>SRC-0096, SRC-0095, SRC-0016, SRC-0106</t>
         </is>
       </c>
     </row>
@@ -16305,7 +16769,9 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>Proposed spaceport site in Michigan previously used as an Air Force radar facility.</t>
+          <t>The former Mount Horace Greeley Calumet Air Force Station (AFS) is a deactivated military installation located in Keweenaw County, Michigan [SRC-0110]. The property encompasses a total of approximately 2,964 acres of land, composed of five separate but contiguous parcels that include both the footprint of the historical military facility and surrounding forested wilderness [SRC-0110].
+Historically, the site was established and utilized as a United States Air Force radar tracking and surveillance facility [SRC-0016, SRC-0110]. As part of the Continental United States (CONUS) air defense network, the Calumet station operated under the Aerospace Defense Command [SRC-0016]. The military continued to operate the radar facility until its official closure in 1988 [SRC-0110]. A decade after its decommission as a military installation, the infrastructure was repurposed as a youth correctional facility, which remained active from 1998 until 2004 [SRC-0110]. Since 2004, the property has been entirely vacant and inactive [SRC-0110].
+Environmental assessments of the former Calumet Air Force Station indicate that portions of the site were previously used as a landfill, resulting in documented contamination issues across the premises [SRC-0110]. Recently, the former Calumet AFS was evaluated as "Site 1" in a site selection and feasibility study conducted by the Michigan Aerospace Manufacturing Association [SRC-0110]. The Michigan Launch Initiative assessed the location to determine its viability for hosting a commercial vertical launch complex to support small-class orbital rockets [SRC-0110, SRC-0110]. However, the existing environmental contamination and past usage as a landfill present significant development challenges for future aerospace infrastructure [SRC-0110].</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
@@ -16321,6 +16787,11 @@
       <c r="V220" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W220" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0016</t>
         </is>
       </c>
     </row>
@@ -16371,7 +16842,9 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>Former NASA sounding rocket launch site in Michigan proposed as a spaceport.</t>
+          <t>The former Keweenaw Rocket Range is located in Keweenaw County, Michigan, situated along the shore of Lake Superior at the easternmost point of the Keweenaw Peninsula [SRC-0110]. The site spans approximately 474 acres and comprises four contiguous parcels of state-owned land [SRC-0110]. While a designated portion of this property was historically developed as the Keweenaw Rocket Range, the remainder of the site consists of pristine forested wilderness that is currently utilized for outdoor recreation [SRC-0110].
+Historically, the site operated as an active sounding rocket launch facility between 1964 and 1971 [SRC-0096, SRC-0095]. During this operational period, the launch complex was primarily utilized by NASA and the University of Michigan to conduct suborbital sounding rocket missions [SRC-0110]. Records show that more than 50 rocket launches were successfully executed at the Keweenaw site [SRC-0096, SRC-0095]. These suborbital flights supported payload capacities of up to 770 kilograms and reached maximum altitudes of less than 160 kilometers [SRC-0096, SRC-0095].
+Following the conclusion of its launch programs in 1971, the Keweenaw Rocket Range was deactivated and remains inactive today [SRC-0096, SRC-0095]. Recently, the historic launch site was evaluated as "Site 2" under the Michigan Launch Initiative's site selection and feasibility study for a new commercial spaceport [SRC-0110]. An assessment of the property's environmental conditions noted that, unlike some other candidate sites, there is no known contamination present at the former rocket range [SRC-0110]. The study considered the area's strategic geographic benefits, particularly its coastal Lake Superior location, for potentially supporting future small-class vertical launch vehicles and modern spaceport operations [SRC-0110, SRC-0110].</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -16387,6 +16860,11 @@
       <c r="V221" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W221" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0096, SRC-0095</t>
         </is>
       </c>
     </row>
@@ -16509,7 +16987,8 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>Former Army airfield in Michigan proposed as a launch site.</t>
+          <t>The Raco Army Airfield, currently known as the Smithers Winter Test Center, is a facility located in the state of Michigan [SRC-0110]. The site encompasses approximately 800 acres and consists of a single contiguous parcel of land that is presently owned and governed by the United States Forest Service [SRC-0110]. Historically, the installation was designated as the Raco Army Airfield (AAF), during which time it served primarily as a refueling stop for military aircraft [SRC-0110]. The airfield's structural layout is distinct, featuring three runways of equal length that are arranged in a geometric triangular pattern [SRC-0110].
+In its current status, the facility has been repurposed from its original military aviation mission. It is now officially known as the Smithers Winter Test Center and is utilized primarily as a specialized testing location for evaluating vehicles under harsh winter conditions [SRC-0110]. Environmental assessments of the property indicate that there is no known contamination present at the site, which distinguishes it from other historical military facilities in the region [SRC-0110]. The site was recently evaluated as a potential candidate (designated as Site 6) for a vertical launch complex under the Michigan Spaceport Site Selection and Feasibility Study, owing to its extensive acreage and existing runway footprint [SRC-0110]. While its primary current use remains vehicular winter testing, its legacy infrastructure continues to make it a point of interest for future aerospace or testing developments [SRC-0110].</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
@@ -16525,6 +17004,11 @@
       <c r="V223" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W223" t="inlineStr">
+        <is>
+          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -16575,7 +17059,9 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>Proposed spaceport launch location on a former Air Force base in Michigan.</t>
+          <t>The Oscoda-Wurtsmith Alert Apron is a designated parcel of land located at the Oscoda-Wurtsmith Airport (OSC) in Michigan [SRC-0110, SRC-0110]. Encompassing approximately 125 acres, this specific site includes the historical Alert Apron and its immediate surrounding areas [SRC-0110]. The property is governed by the Oscoda-Wurtsmith Airport Authority, which assumed control of the broader airport facility after it transitioned to public use in December 1993 [SRC-0110, SRC-0110].
+Historically, the site was an integral component of the Wurtsmith Air Force Base, a military installation that was originally established in 1923 as a soft-surface landing site for the Army Air Corps and later operated by the United States Air Force [SRC-0110]. Following the end of the Cold War and the fall of the Soviet Union, the base was deemed no longer necessary and officially closed in 1993 [SRC-0110]. Since the base's closure, the Alert Apron site has remained largely vacant [SRC-0110].
+In recent years, the Alert Apron was evaluated as "Site 11" during the Michigan Spaceport Site Selection and Feasibility Study for potential development as a vertical launch complex [SRC-0110]. However, development at this site faces several notable constraints. Because it is located directly on an active airfield, any new facilities or structures built on the apron are strictly subject to height restrictions governed by Federal Aviation Administration Part 77 imaginary surfaces, which ensure that new constructions do not interfere with aircraft operations [SRC-0110, SRC-0110]. Furthermore, environmental assessments indicate that the site has known contamination issues, as it was previously utilized by the military for the use and storage of hazardous substances and waste materials [SRC-0110].</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -16591,6 +17077,11 @@
       <c r="V224" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W224" t="inlineStr">
+        <is>
+          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -24288,7 +24779,8 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in Texas.</t>
+          <t>Licensed in June 2015, the Houston Spaceport is a horizontal commercial spaceport co-located at Ellington Airport, an airport owned by the City of Houston and operated by the Houston Airport System [SRC-0110, SRC-0110]. Located approximately 5.5 miles northwest of the National Aeronautics and Space Administration's (NASA) Johnson Space Center, the facility accommodates general aviation, military, NASA, and suborbital commercial space operations [SRC-0110]. Notably, the Houston Spaceport was the very first commercial spaceport in the United States to construct a new control tower equipped with dedicated mission-control facilities designed specifically for commercial space operations [SRC-0110].
+The spaceport features a primary runway measuring 9,001 feet long by 150 feet wide, well above the 8,000-foot recommendation for Horizontal Takeoff Horizontal Landing (HTHL) operations [SRC-0110, SRC-0110]. Like other air and space ports, it uses conventional runway infrastructure to support these HTHL vehicles, which rely on aerodynamic control through a combination of jet-power, rocket power, or controlled glide [SRC-0110, SRC-0110]. As an active hub for aerospace activity, the spaceport had secured commitments from tenants including Intuitive Machines, San Jacinto College, and FlightSafety International as of January 2020 [SRC-0110]. The spaceport's development and planning involved conceptual terminal designs focused on integrating aerospace commercial activities into the existing airfield [SRC-0110]. Overall, it functions not only as a licensed launch and reentry site but also as an emerging center for aerospace testing, development, manufacturing, and research opportunities [SRC-0110].</t>
         </is>
       </c>
       <c r="T325" t="inlineStr">
@@ -24304,6 +24796,11 @@
       <c r="V325" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -24354,7 +24851,9 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in California.</t>
+          <t>Licensed in June 2004, the Mojave Air and Space Port holds the distinction of being the first commercially licensed spaceport in the United States [SRC-0110, SRC-0110]. Operated by the East Kern Airport District, the facility is located in the Mojave Desert of California [SRC-0110]. As a prominent horizontal air and space port, it is equipped with a massive primary runway measuring 12,503 feet long by 200 feet wide, making it highly capable of supporting various Horizontal Takeoff Horizontal Landing (HTHL) vehicles [SRC-0110, SRC-0110].
+The spaceport is a leading air launch facility for private spaceflight and aerospace research [SRC-0161]. It is licensed to support suborbital commercial launches while concurrently functioning as a general aviation airport [SRC-0110]. The site has attracted significant aerospace investment and is home to over 60 tenants [SRC-0110]. Prominent companies operating out of the facility include Interorbital Systems, Masten Space Systems, Northrop Grumman, Stratolaunch Systems, The Spaceship Company, and Virgin Orbit [SRC-0110]. Prior to moving its operations to Spaceport America in 2019, Virgin Galactic also based its spaceflight activities at Mojave [SRC-0188].
+Beyond serving as a launch site, the spaceport operates as a dynamic hub for aerospace business. The diverse companies stationed at the Mojave Air and Space Port conduct a wide range of activities, including advanced vehicle development, cutting-edge aerospace design, and extensive flight testing and research [SRC-0110, SRC-0110]. This blend of capabilities allows the spaceport to generate revenue from testing, manufacturing, and research that often exceeds the revenue tied strictly to licensed launches [SRC-0110].</t>
         </is>
       </c>
       <c r="T326" t="inlineStr">
@@ -24370,6 +24869,11 @@
       <c r="V326" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0161, SRC-0188</t>
         </is>
       </c>
     </row>
@@ -24420,7 +24924,9 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in Oklahoma.</t>
+          <t>Licensed by the FAA in June 2006, the Oklahoma Air and Space Port holds the unique distinction of being the first licensed commercial spaceport located in a land-locked state in the United States [SRC-0110]. Situated in Burns Flat, Oklahoma, the spaceport is co-located with the Clinton-Sherman Industrial Airpark and is managed by the Oklahoma Industry Development Authority (OSIDA) [SRC-0110, SRC-0096]. It features a massive primary runway measuring 13,503 feet long by 150 feet wide, which provides substantial infrastructure for Horizontal Takeoff Horizontal Landing (HTHL) spaceplanes [SRC-0110].
+The facility is currently licensed to support suborbital commercial space launches and simultaneously serves as an active airport accommodating both military and general aviation operations [SRC-0110]. Uniquely, the Oklahoma Air and Space Port was the first commercially licensed spaceport in the country to establish an FAA-approved spaceflight corridor that was not situated within Special Use Airspace (SUA) [SRC-0110].
+In addition to its launch capabilities, the spaceport features existing infrastructure dedicated to aerospace testing, research and development, and flight operations [SRC-0110]. These facilities position the site to attract emerging aerospace ventures. For example, it was announced that Dawn Aerospace's Aurora Mark 2 suborbital spaceplane would begin flying from the Burns Flat spaceport [SRC-0203]. By utilizing its existing runway and aerospace infrastructure, the Oklahoma Spaceport continues to function as a vital hub for commercial spaceflight research and horizontal launch operations [SRC-0110, SRC-0203].</t>
         </is>
       </c>
       <c r="T327" t="inlineStr">
@@ -24436,6 +24942,11 @@
       <c r="V327" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0096, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -24491,7 +25002,9 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in Kodiak Island, Alaska.</t>
+          <t>The Pacific Spaceport Complex – Alaska, formerly known as the Kodiak Launch Complex, is a commercial and military spaceport located on Kodiak Island, Alaska [SRC-0161, SRC-0110]. Owned and operated by the Alaska Aerospace Corporation, the facility was officially awarded its commercial spaceport license in September 2003 [SRC-0110]. Notably, the Pacific Spaceport Complex – Alaska became the first commercial spaceport in the United States that was not co-located on a preexisting federal range [SRC-0110].
+Operating as a vertical launch site, the complex is capable of supporting launch azimuths ranging from 110 degrees to 220 degrees, making it highly suitable for missions requiring high inclination and polar orbits [SRC-0110]. Since 1998, the facility has supported various orbital and sub-orbital launch operations for both commercial and military customers [SRC-0161]. Historical records indicate that the spaceport has hosted at least 9 launches over its operational history [SRC-0161].
+The site’s remote location in Alaska provides a unique geographic advantage for vertical rocket launches, ensuring safe trajectories over the Pacific Ocean [SRC-0110]. By providing access to specialized launch corridors, the Pacific Spaceport Complex – Alaska remains an important asset within the United States' vertical commercial spaceport network, directly supporting the testing and deployment of advanced aerospace technologies away from traditional mainland federal ranges [SRC-0110, SRC-0110].</t>
         </is>
       </c>
       <c r="T328" t="inlineStr">
@@ -24507,6 +25020,11 @@
       <c r="V328" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W328" t="inlineStr">
+        <is>
+          <t>SRC-0161, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -24557,7 +25075,9 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in New Mexico.</t>
+          <t>Spaceport America, formerly known as the Southwest Regional Spaceport, is an FAA-licensed commercial spaceport located on 18,000 acres of State Trust Land in the Jornada del Muerto desert basin, 45 miles north of Las Cruces, New Mexico [SRC-0188]. Owned and operated by the State of New Mexico through the New Mexico Spaceport Authority, it bills itself as the world's first purpose-built commercial spaceport [SRC-0188]. Unlike many other sites, Spaceport America was constructed to accommodate both vertical and horizontal launch aerospace vehicles, featuring a 12,000-foot concrete runway [SRC-0188, SRC-0188].
+The spaceport's inception dates back to 1990, with initial funding secured via congressional earmarks [SRC-0188]. The site broke ground in 2009 and was officially declared open on October 18, 2011 [SRC-0188, SRC-0188]. Virgin Galactic signed a 20-year lease as the anchor tenant, and on May 22, 2021, launched the VSS Unity with three people aboard, making New Mexico the third US state to launch humans into space [SRC-0188, SRC-0188]. The terminal hangar facility, designed by Foster+Partners, achieved LEED-Gold certification and incorporates sustainable features like "Earth Tubes" for cooling [SRC-0188, SRC-0188].
+Spaceport America hosts several tenants and operators, including UP Aerospace, SpinLaunch, HAPSMobile Aerovironment, EXOS Aerospace, and Boeing [SRC-0188, SRC-0188]. UP Aerospace has launched numerous SpaceLoft XL sounding rockets from the site since its first rocket launch on September 25, 2006 [SRC-0188, SRC-0188]. The spaceport also serves as an educational and non-aerospace hub, hosting the Spaceport America Cup for intercollegiate rocket engineering (from 2017 to 2024) and providing test tracks for automotive companies like Infiniti [SRC-0188, SRC-0188].</t>
         </is>
       </c>
       <c r="T329" t="inlineStr">
@@ -24573,6 +25093,11 @@
       <c r="V329" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC-0188</t>
         </is>
       </c>
     </row>
@@ -24623,7 +25148,9 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in Virginia.</t>
+          <t>The Mid-Atlantic Regional Spaceport (MARS) is an FAA-licensed vertical launch commercial spaceport located at Wallops Island, Virginia [SRC-0110, SRC-0161]. The facility is owned and operated by the Virginia Commercial Space Flight Authority (VCSFA) and was officially awarded a Launch Site Operator License in December 2002 [SRC-0110]. As a critical component of the United States' vertical launch network, MARS shares geography with NASA's Wallops Flight Facility, leveraging the location's extensive history in rocket launches and scientific exploration [SRC-0110, SRC-0161].
+The spaceport maintains multiple active launch complexes to accommodate a variety of rocket classes. Launch Pad 0A has historically supported medium-to-large lift launch vehicles, most notably the Antares rocket used for resupply missions to the International Space Station [SRC-0110, SRC-0110]. Launch Pad 0B is designated for small lift launch vehicles, such as the Minotaur I [SRC-0110]. Additionally, commercial aerospace company Rocket Lab USA constructed a new launch facility at MARS, known as Launch Pad 2, which was designed to support its launch operations beginning in 2020 [SRC-0110].
+By 2025, the Mid-Atlantic Regional Spaceport stood out as a significant contributor to orbital spaceflight. Outside of the traditional federal ranges at Cape Canaveral and Vandenberg, MARS was the only other spaceport in the United States to host an orbital launch that year, specifically a Rocket Lab Electron mission [SRC-0203]. The site provides crucial infrastructure and launch capabilities for commercial, government, and military payloads [SRC-0110].</t>
         </is>
       </c>
       <c r="T330" t="inlineStr">
@@ -24639,6 +25166,11 @@
       <c r="V330" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W330" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0161, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -24694,7 +25226,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>Rocket launch site in Alaska.</t>
+          <t>The Kodiak Launch Complex, currently known as the Pacific Spaceport Complex – Alaska (PSCA), is a commercial and military spaceport located on Kodiak Island, Alaska [SRC-0092, SRC-0096, SRC-0110]. Owned and operated by the Alaska Aerospace Corporation (formerly the Alaska Aerospace Development Corporation), the facility was created by the State of Alaska to develop aerospace-related economic and technical opportunities [SRC-0110, SRC-0092]. It officially became a commercially licensed spaceport in September 2003, making it the first commercial spaceport in the United States that was not co-located on a preexisting federal range [SRC-0110]. Operational since 1991, the complex has supported a mix of orbital and suborbital missions [SRC-0096, SRC-0161]. The site's geographic location is highly advantageous, capable of supporting launch azimuths ranging from 110° to 220°, which is ideal for placing payloads into high-inclination and polar orbits [SRC-0110]. Over its history, the facility has hosted at least 26 launches, accommodating launch vehicles with a lift-off mass of up to 86,000 kilograms [SRC-0096]. Its launch operations encompass ballistic missile interceptor tests as well as commercial and government satellite launches [SRC-0096]. Among the launch vehicles supported at the complex are the Athena and Minuteman/AIT rockets [SRC-0162]. Today, the spaceport remains an active asset for sub-orbital and orbital launches, catering to both military and civilian aerospace customers [SRC-0096, SRC-0161].</t>
         </is>
       </c>
       <c r="T331" t="inlineStr">
@@ -24710,6 +25242,11 @@
       <c r="V331" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC-0092, SRC-0096, SRC-0110, SRC-0161, SRC-0162</t>
         </is>
       </c>
     </row>
@@ -24765,7 +25302,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>Private launch site located in Texas.</t>
+          <t>The SpaceX Launch Site, formally known as the SpaceX Starbase Spaceport, is a private rocket production facility, test site, and spaceport located at Boca Chica, Texas [SRC-0096, SRC-0094]. Situated near the Gulf of Mexico, the site was originally planned to accommodate commercial launches of the Falcon family of rockets [SRC-0096]. However, it has since evolved to be used exclusively by SpaceX for the development, testing, and launching of the massive Starship spacecraft and its Super Heavy booster [SRC-0096]. Operations at the Texas facility began around 2018, and it has since supported numerous prototype test flights and orbital launch attempts [SRC-0096]. Starbase has accommodated rockets with a lift-off mass of approximately 5,000,000 kilograms, making it the primary hub for the company's interplanetary ambitions [SRC-0096]. The launch site has hosted around 21 launches as of recent tracking data [SRC-0161]. In addition to its dedicated Starbase facility, SpaceX conducts the vast majority of its commercial, civil, and military launches from leased pads at federal and military ranges. This includes Space Launch Complex 40 (SLC-40) and Launch Complex 39A (LC-39A) at the Kennedy Space Center and Cape Canaveral Space Force Station in Florida, as well as Space Launch Complex 4E (SLC-4E) and Space Launch Complex 6 (SLC-6) at Vandenberg Space Force Base in California [SRC-0031, SRC-0031, SRC-0214, SRC-0214]. These distributed sites allow SpaceX to maintain a high launch cadence across the country.</t>
         </is>
       </c>
       <c r="T332" t="inlineStr">
@@ -24781,6 +25318,11 @@
       <c r="V332" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W332" t="inlineStr">
+        <is>
+          <t>SRC-0096, SRC-0094, SRC-0161, SRC-0031, SRC-0214</t>
         </is>
       </c>
     </row>
@@ -24836,7 +25378,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>Private launch site located in Texas.</t>
+          <t>The Blue Origin Launch Site, known operationally as Corn Ranch, is a private spaceport and rocket testing facility located near Van Horn, Texas [SRC-0096]. Operational since 2006, the West Texas facility is owned and operated entirely by Blue Origin, the aerospace manufacturer founded by Jeff Bezos [SRC-0096]. Corn Ranch is predominantly utilized for suborbital spaceflight launches and rocket engine testing, specifically serving as the exclusive launch site for the company's New Shepard reusable suborbital launch vehicle [SRC-0096, SRC-0161]. The site has hosted numerous uncrewed and crewed flights, with historical launch counts reported between 20 and 38 missions depending on the operational timeframe [SRC-0096, SRC-0161]. Rockets launched from this Texas facility have achieved altitudes of approximately 105 kilometers, successfully crossing the Kármán line into space before vertically landing [SRC-0096]. Beyond its private Texas launch site, Blue Origin has significantly expanded its orbital launch capabilities by leasing Launch Complex 36 (LC-36) at the Cape Canaveral Space Force Station in Florida [SRC-0031]. In September 2015, NASA announced that Blue Origin had leased LC-36 and would modify the historic pad as a launch site for their next-generation launch vehicles [SRC-0031]. At LC-36, the company is actively developing facilities to support its heavy-lift New Glenn rocket, marking a transition from purely suborbital operations in Texas to heavy-lift orbital missions from the Florida coast [SRC-0031, SRC-0031].</t>
         </is>
       </c>
       <c r="T333" t="inlineStr">
@@ -24852,6 +25394,11 @@
       <c r="V333" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>SRC-0096, SRC-0161, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -24973,7 +25520,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in California.</t>
+          <t>The California Spaceport is a commercial space launch facility located within the boundaries of Vandenberg Space Force Base (formerly Vandenberg Air Force Base) on the central coast of California [SRC-0092, SRC-0110]. It holds a significant historical distinction as the first commercially licensed spaceport in the United States, having received its Launch Site Operator License from the Federal Aviation Administration (FAA) on September 19, 1996 [SRC-0092, SRC-0110]. The spaceport's launch infrastructure is situated at Space Launch Complex 8 (SLC-8) [SRC-0110]. Initially, the site was operated and managed by Spaceport Systems International, L.P. (SSI) in a strategic partnership with ITT Federal Services Corporation (ITT FSC), a major technical and support services contractor [SRC-0092]. Today, the site is operated by L3Harris Spaceport Systems [SRC-0110]. The facility was established to provide flexible and cost-effective commercial launch operations by directly leveraging the existing launch infrastructure, airspace coordination, and range safety services of the federal Western Range [SRC-0092, SRC-0092]. California Spaceport has supported commercial vertical launch activities, with early reports noting at least two launches from the facility [SRC-0092]. While the 2018 Annual Compendium of Commercial Space Transportation indicated that its active license was set to expire in September 2021 [SRC-0110], the spaceport represents a critical early milestone in the development of the commercial spaceflight industry in the United States, demonstrating the viability of hosting commercial spaceports on existing federal military ranges [SRC-0092].</t>
         </is>
       </c>
       <c r="T335" t="inlineStr">
@@ -24989,6 +25536,11 @@
       <c r="V335" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>SRC-0092, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25039,7 +25591,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>Commercial spaceport located in Florida.</t>
+          <t>Spaceport Florida is a commercial space launch facility located within the federal Eastern Range at Cape Canaveral Space Force Station (formerly Cape Canaveral Air Station) in Florida [SRC-0092, SRC-0092]. The site was initially established and managed by the Spaceport Florida Authority (SFA), an entity created by the Governor and Legislature of Florida as the United States' first state government space agency [SRC-0092]. The SFA was designed to foster space-related enterprises, commercial launch activities, and educational projects to stimulate the state's economy [SRC-0092]. To facilitate these launches, the spaceport operates Launch Complex 46 (LC-46), for which it originally received a Launch Site Operator License from the Federal Aviation Administration (FAA) [SRC-0092]. Operations at the site directly benefit from the existing tracking infrastructure and robust range safety services provided by the Department of Defense at the federal launch range [SRC-0092]. Currently, the facility is part of the broader Cape Canaveral Spaceport (CCS) network operated by Space Florida, which encompasses multiple launch facilities including the Shuttle Landing Facility, SLC-36, SLC-37, SLC-40, SLC-41, and SLC-46 [SRC-0110]. LC-46 was officially licensed for vertical launches in July 2010 and remains the only licensed spaceport on CCS that supports vertical launch [SRC-0110]. The facility has successfully supported both commercial and government vertical launch operations over its history, including at least two early launches [SRC-0092, SRC-0110].</t>
         </is>
       </c>
       <c r="T336" t="inlineStr">
@@ -25055,6 +25607,11 @@
       <c r="V336" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W336" t="inlineStr">
+        <is>
+          <t>SRC-0092, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25110,7 +25667,9 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>Major NASA space launch facility in Florida.</t>
+          <t>The John F. Kennedy Space Center (KSC) is a major United States spaceport located on Merritt Island, Florida, situated west and north of Cape Canaveral and linked to it by bridges and causeways [SRC-0031, SRC-0031]. Governed and operated by the National Aeronautics and Space Administration (NASA), KSC was originally established to support the Apollo program. The sheer size of the Saturn V rocket, which was necessary to achieve the goal of landing a man on the Moon, required a much larger launch facility than the adjacent Cape Canaveral could provide [SRC-0031]. Following the assassination of President John F. Kennedy, his successor, President Lyndon B. Johnson, issued Executive Order 11129 on November 29, 1963, officially renaming the Merritt Island Launch Operations Center to the John F. Kennedy Space Center [SRC-0031].
+KSC boasts extensive infrastructure to support human and robotic spaceflight. Key facilities include Launch Complex 39 (specifically pads LC-39A and LC-39B), the iconic Vehicle Assembly Building, the Launch Control Center, the Crawlerway, and multiple Orbiter Processing Facilities [SRC-0031, SRC-0031, SRC-0031]. Additionally, the site hosts the Shuttle Landing Facility (SLF), a runway historically used for Space Shuttle Orbiter landings [SRC-0110]. Today, the SLF is operated by Space Florida under a property agreement with NASA and supports horizontal suborbital and orbital commercial launches [SRC-0110].
+Historically notable for launching the Apollo Saturn V rockets and the Space Shuttle fleet [SRC-0031, SRC-0110], KSC currently operates in conjunction with the adjacent Cape Canaveral Space Force Station as part of the Eastern Range [SRC-0054, SRC-0202]. The Eastern Range, overseen by the U.S. Space Force's Space Launch Delta 45, provides essential safety, tracking, and control infrastructure for all KSC launches [SRC-0202, SRC-0202]. KSC continues to be a bustling hub for NASA, military, and commercial aerospace endeavors [SRC-0202, SRC-0202].</t>
         </is>
       </c>
       <c r="T337" t="inlineStr">
@@ -25126,6 +25685,11 @@
       <c r="V337" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W337" t="inlineStr">
+        <is>
+          <t>SRC-0031, SRC-0110, SRC-0054, SRC-0202</t>
         </is>
       </c>
     </row>
@@ -25181,7 +25745,9 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>NASA launch and testing site in Virginia.</t>
+          <t>Wallops Flight Facility is a United States spaceport and rocket launch site located on Wallops Island, Virginia [SRC-0154, SRC-0162]. Governed and operated by the National Aeronautics and Space Administration (NASA), the site has historically grown from a small test range for guided missile research into the agency's premier location for suborbital and small orbital activities [SRC-0185].
+The facility supports NASA's Science Mission Directorate, with its strategic vision and goals encompassing Earth Science, Heliophysics, and Astrophysics [SRC-0185]. To achieve these goals, Wallops is heavily utilized for launching sounding rockets, scientific balloons, and small orbital aerospace vehicles that aid in worldwide science exploration and technology development [SRC-0185]. Wallops is equipped with a tracking radar that integrates with broader monitoring networks, such as the Eastern Test Range [SRC-0106]. Furthermore, launches from Wallops Island have been used to test and demonstrate the tracking capabilities of other advanced military systems, such as the Long Range Discrimination Radar (LRDR) [SRC-0100].
+In addition to NASA's own operations, Wallops Flight Facility hosts the Mid-Atlantic Regional Spaceport (MARS), facilitating commercial and military spaceflight [SRC-0031]. As commercial space industry capabilities have expanded, Wallops has accommodated private aerospace companies. Notably, Rocket Lab constructed its Launch Complex 2 at the facility, which was slated to debut with a mission for the U.S. Air Force [SRC-0110, SRC-0110, SRC-0110]. By providing robust infrastructure for both government research and commercial enterprises, Wallops Flight Facility remains a critical component of the United States' national space launch architecture and scientific testing capabilities [SRC-0185, SRC-0154].</t>
         </is>
       </c>
       <c r="T338" t="inlineStr">
@@ -25197,6 +25763,11 @@
       <c r="V338" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W338" t="inlineStr">
+        <is>
+          <t>SRC-0154, SRC-0162, SRC-0185, SRC-0106, SRC-0100, SRC-0031, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25521,7 +26092,9 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>Former military launch complex in Utah.</t>
+          <t>The Green River Launch Complex is a United States military rocket launch site and weapons test facility located in the state of Utah [SRC-0036, SRC-0037, SRC-0095, SRC-0218]. Classified as a proving ground and launch complex, the site was utilized by the United States Air Force to support suborbital sounding rocket flights and experimental missile testing during the Cold War era [SRC-0037, SRC-0218].
+One of the most notable activities associated with the Green River Launch Complex occurred on July 11, 1970 [SRC-0218]. On this date, the U.S. Air Force launched an Athena sounding rocket equipped with a V-123-D re-entry vehicle [SRC-0218]. The test's intended target was located within the White Sands Missile Range (WSMR) in New Mexico [SRC-0218]. However, the rocket suffered a significant anomaly and veered off its planned trajectory [SRC-0218]. Instead of landing in New Mexico, the Athena rocket flew over the international border and impacted approximately 180 to 200 miles south of the United States-Mexico border, crashing in the Mapimi Desert in the northeastern corner of the Mexican state of Durango [SRC-0218]. 
+Beyond its use for the Athena program and its categorization alongside other national aerospace test facilities, detailed operational history, establishing dates, and current status of the Green River Launch Complex are not extensively documented in the available records [SRC-0036, SRC-0037, SRC-0218].</t>
         </is>
       </c>
       <c r="T343" t="inlineStr">
@@ -25537,6 +26110,11 @@
       <c r="V343" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W343" t="inlineStr">
+        <is>
+          <t>SRC-0036, SRC-0037, SRC-0095, SRC-0218</t>
         </is>
       </c>
     </row>
@@ -26203,7 +26781,8 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>Aegis Ashore missile defense site in northern Poland with SPY-1D radar and SM-3 interceptors.</t>
+          <t>**Aegis Ashore Poland**, located in Redzikowo, is a modern missile defense installation that represents a critical contribution by the United States Missile Defense Agency (MDA) to Phase 3 of the European Phased Adaptive Approach [SRC-0093]. The site is specifically designed to launch advanced interceptors, including the SM-3 Block IBTU and Block IIA missiles, providing a defensive shield for NATO's European territory and forces against ballistic missile threats originating from outside the Euro-Atlantic region [SRC-0093, SRC-0093]. 
+The facility reached a significant milestone in December 2023 when it was officially accepted by the U.S. Chief of Naval Operations [SRC-0093]. Currently, Aegis Ashore Poland is funded, maintained, and operated by the United States Navy [SRC-0093]. As part of its integration process, the installation was scheduled for a planned maintenance period focused on upgrading its computer networks and communications systems [SRC-0093]. Upon completion of these technical upgrades, the facility will be formally accepted by the U.S. European Command [SRC-0093, SRC-0093]. Following this acceptance, the governing authority and operational control of the Redzikowo site will be transferred from the U.S. European Command directly to NATO [SRC-0093, SRC-0093].</t>
         </is>
       </c>
       <c r="T352" t="inlineStr">
@@ -26219,6 +26798,11 @@
       <c r="V352" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W352" t="inlineStr">
+        <is>
+          <t>SRC-0093</t>
         </is>
       </c>
     </row>
@@ -26345,7 +26929,9 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>Aleutian Island station historically supporting Cobra Judy and now Sea-Based X-band Radar (SBX-1) home port.</t>
+          <t>Adak Island, located in the Aleutian Islands of Alaska, serves as a nominal strategic location for the United States Department of Defense's Ballistic Missile Defense System [SRC-0178, SRC-0178, SRC-0179, SRC-0179]. Although often referred to as a base of operations, its most prominent modern role is designated as the homeport for the Sea-Based X-Band Radar (SBX-1) [SRC-0178, SRC-0178, SRC-0179].
+The SBX-1 is a massive, floating active electronically scanned array radar mounted on a fifth-generation CS-50 twin-hulled semi-submersible platform [SRC-0178, SRC-0179]. Developed by the Missile Defense Agency (MDA), the radar is designed to operate in severe weather and heavy seas to detect, track, and discriminate incoming ballistic missiles targeting the United States from adversaries like North Korea and China [SRC-0178, SRC-0178, SRC-0179]. To accommodate this specialized vessel, the military invested $26 million in 2007 to construct a custom eight-point mooring chain system in Adak's Kuluk Bay [SRC-0178, SRC-0179].
+Despite being officially slated to be based at Adak Island, the SBX-1 has never actually moored there or put into port at the facility [SRC-0178, SRC-0178, SRC-0179, SRC-0179]. Instead, the radar station has spent its operational life either roaming the Pacific Ocean, including the waters off the coast of Alaska, or returning to Pearl Harbor, Hawaii, for extensive maintenance, repairs, and testing [SRC-0178, SRC-0179, SRC-0178, SRC-0179]. As a result, while Adak Island features the dedicated infrastructure to support the SBX-1, it remains an unused deployment site for the vessel [SRC-0178, SRC-0179, SRC-0179]. Additional details regarding the site's other historical uses or facilities are not provided in the source material.</t>
         </is>
       </c>
       <c r="T354" t="inlineStr">
@@ -26361,6 +26947,11 @@
       <c r="V354" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W354" t="inlineStr">
+        <is>
+          <t>SRC-0178, SRC-0179</t>
         </is>
       </c>
     </row>
@@ -26416,7 +27007,9 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>Major Hawaiian naval base; home port for Aegis BMD-capable ships and Sea-Based X-band Radar (SBX-1).</t>
+          <t>Pearl Harbor Naval Base, part of Joint Base Pearl Harbor-Hickam, is a premier United States Navy installation located on the island of Oahu, Hawaii [SRC-0074, SRC-0136]. Managed under the Commander, Navy Region Hawaii, the base hosts the Pearl Harbor Naval Shipyard and provides critical operational, maintenance, and logistics support for the U.S. Pacific Fleet [SRC-0136, SRC-0134].
+In the 21st century, Pearl Harbor has become a vital hub for the Missile Defense Agency's (MDA) Ballistic Missile Defense System, primarily due to its ongoing support of the Sea-Based X-band Radar (SBX-1) [SRC-0178, SRC-0179, SRC-0178]. The SBX-1 is a self-propelled, floating radar station mounted on a semi-submersible platform, designed to track and discriminate incoming ballistic missile threats [SRC-0178, SRC-0179]. Although nominally assigned to a homeport in Adak, Alaska, the SBX-1 spends a significant portion of its time moored at Pearl Harbor for testing, maintenance, and upgrades [SRC-0179, SRC-0178, SRC-0179].
+Historical records indicate the SBX-1 was stationed at Pearl Harbor for repairs for 170 days in 2006, 63 days in 2007, 63 days in 2008, 177 days in 2009, and 51 days in 2010 [SRC-0178, SRC-0179]. The vessel also returned in late 2015 for testing and underwent a $24 million upgrade before departing again in 2017 [SRC-0179, SRC-0179]. After 20 years of service, the SBX-1 recently received a new protective radome while undergoing maintenance at the base [SRC-0129]. Because of the radar's distinct, spherical white dome and its frequent, highly visible presence at the installation, local residents have colloquially dubbed the vessel the "Golf Ball" or the "Pearl of Pearl Harbor" [SRC-0179].</t>
         </is>
       </c>
       <c r="T355" t="inlineStr">
@@ -26432,6 +27025,11 @@
       <c r="V355" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W355" t="inlineStr">
+        <is>
+          <t>SRC-0074, SRC-0136, SRC-0134, SRC-0178, SRC-0179, SRC-0129</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27625,9 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>Forward-based AN/TPY-2 X-band radar in Aomori, Japan for missile defense.</t>
+          <t>The Shariki Communications Site is a military installation located in the Shariki region of Japan [SRC-0012]. It functions as a critical forward-deployed sensor node for the United States Department of Defense's layered ballistic missile defense architecture in the Pacific theater [SRC-0012].
+The primary asset at the Shariki site is the AN/TPY-2 radar system [SRC-0012]. The AN/TPY-2 is a transportable, high-resolution X-band active electronically scanned array (AESA) radar designed to detect, track, and discriminate short-, medium-, and intermediate-range ballistic missiles [SRC-0012, SRC-0011]. At the Shariki installation, the radar's specific operational mandate is to collect strategic-level intelligence and metric data on North Korean missile developments [SRC-0012]. Additionally, due to its geographic position and high-powered sensors, the AN/TPY-2 radar at Shariki is capable of scanning into Russian territory situated near Japan [SRC-0012].
+The intelligence and tracking data generated by the Shariki site provide vital early warning of incoming warheads for Japan [SRC-0012]. This capability seamlessly integrates with and complements the broader Japanese missile defense network, which utilizes Patriot PAC-3 systems for terminal point defense and Aegis-equipped Kongo-class destroyers armed with RIM-161 Standard Missile 3 (SM-3) interceptors for theater-wide ballistic missile defense [SRC-0012]. While the site is a critical component of regional security and U.S.-Japanese military cooperation, further extensive details regarding its establishment date, facility footprint, or managing personnel are not covered in the available source material.</t>
         </is>
       </c>
       <c r="T363" t="inlineStr">
@@ -27043,6 +27643,11 @@
       <c r="V363" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="W363" t="inlineStr">
+        <is>
+          <t>SRC-0012, SRC-0011</t>
         </is>
       </c>
     </row>
@@ -27491,7 +28096,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T131"/>
+  <dimension ref="A1:T186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -27723,7 +28328,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Nerve center for the telemetry, tracking, and command network at Jiuquan. Transmits real-time trajectory data to the control headquarters.</t>
+          <t>The Dashuli Tracking Station, originally constructed in 1968 to support missile testing, currently serves as the nerve center for the telemetry, tracking, and command network at the Jiuquan Satellite Launch Centre [SRC-0084]. Among its primary instrumentation is a tracking radar system, which operates in conjunction with optical tracking telescopes to monitor launch vehicles [SRC-0084]. While the specific manufacturer, frequency band, and exact year of the radar's construction are not explicitly detailed in the provided sources, the radar's core purpose is to track launch vehicles from lift-off until approximately 500 seconds into the flight [SRC-0084]. The radar system is part of a broader tracking network that includes optical, communication, computer, and meteorology sub-systems [SRC-0084]. The data gathered by this tracking radar, along with telemetry measurements, is fed into the station's control hall [SRC-0084, SRC-0084]. This hall features over 30 control consoles that display 120 sets of real-time data regarding the trajectory of the launch vehicle and the live status of the rocket and its payload [SRC-0084]. This tracking information is then transmitted in real-time to the Mission Command and Control Centre at the headquarters to facilitate crucial decision-making during the launch process [SRC-0084]. Currently, the radar remains an operational and integral component of China's space launch infrastructure at Jiuquan [SRC-0084, SRC-0084].</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -27744,6 +28349,11 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>SRC-0084</t>
         </is>
       </c>
     </row>
@@ -28041,7 +28651,8 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Scans neighboring territories to monitor missile developments. Integrates with existing missile defense architectures.</t>
+          <t>The AN/TPY-2 is a highly advanced, trailer-mounted active electronically scanned array (AESA) missile defense radar [SRC-0011, SRC-0012]. Manufactured by Raytheon Technologies and introduced in 2007, this ruggedized, all-weather system operates in the X-band frequency range (8.55–10 GHz) [SRC-0011, SRC-0011, SRC-0011, SRC-0012]. Operating in the X-band, combined with electronic beam steering, provides exceptional target resolution, allowing the radar to precisely track small objects and accurately discriminate between actual ballistic missile warheads and decoys [SRC-0012, SRC-0011, SRC-0012].
+The AN/TPY-2 boasts a detection range exceeding 1,000 kilometers, reaching up to 3,000 kilometers depending on the target and operating mode [SRC-0011, SRC-0012, SRC-0011]. It is capable of tracking hundreds of targets simultaneously and integrates seamlessly with defense networks like THAAD, Aegis BMD, and C2BMC [SRC-0011, SRC-0011, SRC-0011, SRC-0011]. The system's primary purpose is long-range detection, tracking, and discrimination of ballistic missile threats, serving as both a forward-based early warning radar and a terminal defense radar [SRC-0012, SRC-0011, SRC-0011]. Currently operational and in active deployment globally, the radar stationed in the Shariki region of Japan is specifically tasked with collecting strategic intelligence on North Korean missile developments and providing early warning of incoming warheads [SRC-0011, SRC-0012]. Additionally, from its position at Shariki, the AN/TPY-2 has the capability to scan Russian territory near Japan [SRC-0012].</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -28062,6 +28673,11 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>SRC-0011, SRC-0012</t>
         </is>
       </c>
     </row>
@@ -29927,7 +30543,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Capable of tracking up to 40 airborne objects simultaneously, ensuring systems under test fly safely.</t>
+          <t>The Multiple Object Tracking Radar (MOTR) is an extremely rare, phased-array tracking radar utilized at the White Sands Missile Range (WSMR) [SRC-0114, SRC-0157]. Built in the mid-1980s, the original procurement cost for each MOTR unit was approximately $36 million [SRC-0114]. While the specific manufacturer and frequency band are not explicitly named in the provided sources, the MOTR operates by transmitting a pulse of energy through phase-shifting elements, delaying the pulse by a fraction of a wavelength to steer the beam off boresight [SRC-0114]. This advanced technology enables the radar to cover a 60-degree area and provides the capability to track the exact location of up to 40 airborne objects simultaneously with extreme precision [SRC-0157, SRC-0114]. The energy is received and processed by any of three channel receivers [SRC-0114]. The primary purpose of the radar is to support flight safety operations, carefully tracking airborne systems under test to ensure they remain on their designated paths [SRC-0157]. As for its current status, WSMR owns three of the five MOTR systems ever produced worldwide (MOTR-1, MOTR-3, and MOTR-4) [SRC-0114, SRC-0114]. MOTR-4 was recently saved from an Air Force scrap yard at Vandenberg Air Force Base and transferred to WSMR to replace aging infrastructure [SRC-0157, SRC-0157]. Recreating such a system today would cost upward of $70 billion [SRC-0114].</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -29948,6 +30564,11 @@
       <c r="S33" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>SRC-0114, SRC-0157</t>
         </is>
       </c>
     </row>
@@ -29994,7 +30615,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Used to track targets and missiles, though being partially supplemented by newer MOTR systems.</t>
+          <t>The AN/FPS-16 is a precision instrumentation tracking radar manufactured by RCA that has been historically utilized at the White Sands Missile Range (WSMR) for trajectory tracking and data collection [SRC-0217]. The exact frequency band is not specified in the sources, but the radar was integrated into the range well before 1972, a time when WSMR maintained three AN/FPS-16 units in active operation [SRC-0217]. During the 1963 to 1964 testing season, the AN/FPS-16 was employed to track superpressure balloons carrying spherical targets, successfully recording position data in X, Y, and Z coordinates on magnetic tape at a rate of one data point per second [SRC-0103]. Unlike newer phased-array systems, the AN/FPS-16 operates on a single-track basis and lacks the capability to provide precision measurements for multiple objects simultaneously [SRC-0114, SRC-0114]. On average, the radar's purpose supports about 25 tracks during a single mission [SRC-0114]. Regarding its current status, the AN/FPS-16 system at WSMR is being phased out of service due to aging technology and high maintenance costs. Upgrading the existing AN/FPS-16 radars to modern standards would have cost the installation approximately $7.5 million, while purchasing new equivalents would cost $9 million [SRC-0114]. To improve data quality and reduce associated costs by 70 percent, WSMR is replacing two of its AN/FPS-16 radars with the newly acquired Multiple Object Tracking Radar 4 (MOTR-4) [SRC-0114, SRC-0114].</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -30015,6 +30636,11 @@
       <c r="S34" t="inlineStr">
         <is>
           <t>Published</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>SRC-0217, SRC-0103, SRC-0114</t>
         </is>
       </c>
     </row>
@@ -30610,7 +31236,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled, mobile active electronically scanned array radar station that operates as a critical part of the Ground-Based Midcourse Defense (GMD) system [SRC-0178, SRC-0179, SRC-0179]. While nominally based at Adak Island, Alaska, it has spent significant time in Pearl Harbor for maintenance and upgrades [SRC-0178, SRC-0179]. Designed by Raytheon for Boeing and deployed in 2006, the $900 million system operates in the X-band to provide high-resolution target discrimination, differentiating enemy warheads from decoys and conducting precision tracking [SRC-0179, SRC-0178, SRC-0178, SRC-0178]. The radar is mounted on a converted fifth-generation CS-50 twin-hulled semi-submersible platform that displaces 50,000 tons and measures 389 feet in length [SRC-0178, SRC-0179, SRC-0179]. The 4,130-square-foot phased-array antenna weighs 4,000,000 pounds and utilizes tens of thousands of solid-state transmit-receive modules mounted on an octagonal base capable of moving ±270 degrees in azimuth [SRC-0178, SRC-0178, SRC-0179]. The radar is protected by a flexible, positive-air-pressure central dome [SRC-0178, SRC-0179]. Capable of detecting baseball-sized objects from 2,500 to 2,900 miles away, the SBX-1 has undergone numerous maintenance periods at Pearl Harbor, most notably replacing its massive protective radome in December 2025 to ensure its continued viability for decades of future homeland missile defense missions [SRC-0178, SRC-0179, SRC-0190, SRC-0190].</t>
+          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled, mobile active electronically scanned array (AESA) early-warning radar system [SRC-0179, SRC-0178, SRC-0179]. Operating in the X-band, it provides finer target resolution than lower-frequency radars [SRC-0178, SRC-0179]. The radar was developed by Raytheon, with Boeing serving as the prime contractor, and was deployed in 2006 as a critical midcourse sensor for the U.S. Ballistic Missile Defense System [SRC-0178, SRC-0178, SRC-0178]. The radar antenna itself spans 384 square meters and is protected by a flexible, positively pressurized central dome [SRC-0178, SRC-0179, SRC-0178]. The array is built to accommodate 45,000 solid-state transmit-receive modules, and currently operates with approximately 22,000 installed modules focused toward the center to minimize grating lobes [SRC-0179, SRC-0179]. The primary purpose of the SBX-1 is to detect, precision-track, and discriminate enemy ballistic missile warheads from decoys, boasting the capability to track an object the size of a baseball from 2,900 miles away [SRC-0179, SRC-0178, SRC-0178]. While the vessel is nominally homeported at Adak Island in Alaska, it has never actually been moored there [SRC-0179, SRC-0179, SRC-0179, SRC-0178]. Instead, the SBX-1 has spent significant time at Pearl Harbor, Hawaii, for extensive maintenance, testing, and repairs—such as a 170-day stay in 2006—and actively deploys from there into the Pacific Ocean to monitor foreign missile launches [SRC-0179, SRC-0179, SRC-0178].</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -30635,7 +31261,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>SRC-0178, SRC-0179, SRC-0190</t>
+          <t>SRC-0179, SRC-0178</t>
         </is>
       </c>
     </row>
@@ -37657,6 +38283,3147 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>SRC-0086, SRC-0013, SRC-0016</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>RAD-0131</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SITE-0138</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Tracking, Telemetry And Flight Termination System</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>The tracking radar infrastructure at SaxaVord Spaceport is a newly established, bespoke rocket tracking, telemetry, and flight termination system located on the Lamba Ness peninsula on the island of Unst in Shetland, Scotland [SRC-0130, SRC-0176]. While specific technical parameters such as the system's exact frequency band, manufacturer, power output, and physical dimensions are not explicitly detailed in the provided sources, the radar network is an essential part of the first fully licensed vertical launch spaceport in Western Europe [SRC-0175, SRC-0176]. 
+The primary purpose of this tracking equipment is to monitor the ascent of rockets launching small satellites into polar and sun-synchronous orbits [SRC-0175]. In modern spaceflight operations, such tracking systems are mandated by range authorities to follow the vehicle's flight path continuously and relay data to a Range Control Centre, which is proposed to be located at the former RAF SaxaVord radar complex [SRC-0176, SRC-0202]. If a rocket veers off its designated trajectory, the integrated flight termination system can be activated to safely destroy the vehicle [SRC-0202]. The tracking and telemetry systems have already been installed on the site to support the first operational launch complex [SRC-0130]. Following the UK Civil Aviation Authority's issuance of a range licence in April 2024, which allows the spaceport to control the sea and airspace along its launch trajectories, this tracking infrastructure is primed to eventually support up to 30 launches per year [SRC-0176, SRC-0130, SRC-0176].</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>SRC-0130</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr">
+        <is>
+          <t>SRC-0130, SRC-0176, SRC-0175, SRC-0202</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>RAD-0132</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SITE-0352</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Aegis Ashore</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>The Aegis Ashore system in Romania is a critical land-based ballistic missile defense (BMD) installation designed to defeat short- to intermediate-range ballistic missile threats [SRC-0134]. While the exact dimensions, power output, year built, and specific site manufacturing details of the Romanian facility are not explicitly detailed in the provided sources, the Aegis system fundamentally relies on S-band radar frequencies for its operations [SRC-0178]. The primary purpose of this system is to provide robust defense for NATO's European territories and deployed forces against ballistic missile threats originating from outside the Euro-Atlantic region [SRC-0093]. To achieve this defensive mission, the Aegis Ashore site is highly capable and specifically equipped to launch advanced Standard Missile-3 (SM-3) Block IBTU and Block IIA interceptors [SRC-0093]. Regarding its current status, the Aegis Ashore system in Romania is fully operational [SRC-0134, SRC-0093]. It currently serves as a cornerstone of the Missile Defense Agency's contribution to Phase 3 of the European Phased Adaptive Approach (EPAA) [SRC-0093]. Notable operational development and rigorous testing for the Aegis Ashore architecture were extensively conducted at the Pacific Missile Range Facility in Hawaii beginning in 2002; these tests were critical to ensuring the reliability and success of the active operational system that is now deployed in Romania [SRC-0134].</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>SRC-0134</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr">
+        <is>
+          <t>SRC-0134, SRC-0178, SRC-0093</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>RAD-0133</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SITE-0357</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Early Warning Radar</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>The provided sources contain very limited technical information regarding the surveillance radar at Rovaniemi Air Base. Specific details such as the radar's exact type, frequency band, manufacturer, year of construction, physical dimensions, power output, current operational status, and any recent modernizations or upgrades are not mentioned in the available documents. What is known from the sources is that an early warning radar was active at Rovaniemi in the mid-1980s. Its capabilities were notably demonstrated during the Lake Inari incident on December 28, 1984 [SRC-0165]. During this event, a Soviet Navy SS-N-3 missile, which had been modified with MiG avionics for use as a remote-controlled target, lost radio contact with its operator, strayed across the Finnish border, and eventually crashed through the ice into Lake Inari [SRC-0165]. The early warning radar at Rovaniemi successfully detected the incoming missile, which prompted the dispatch of two Saab 35 Draken fighter jets to investigate the airspace incursion [SRC-0165]. Although the fighters were unable to locate the missile in the air before it crashed, the radar's early warning detection successfully fulfilled its purpose of monitoring Finnish airspace for unauthorized border crossings during a tense period [SRC-0165].</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>SRC-0165</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>SRC-0165</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>RAD-0134</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SITE-0356</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Close-Range Radar</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Similar to the Rovaniemi system, the provided sources lack detailed technical specifications for the surveillance radar located at the Kaamanen Radar Site. There is no information available in the text regarding the system's frequency band, manufacturer, exact year it was built, power capabilities, physical dimensions, or current operational status. However, the sources describe it as a close-range radar system [SRC-0165]. The primary notable operation involving this radar also occurred during the December 1984 Lake Inari incident [SRC-0165]. While the Rovaniemi early warning radar provided the initial warning, the close-range radar at Kaamanen also successfully picked up the unauthorized entry of the Soviet SS-N-3 cruise missile into Finnish airspace [SRC-0165]. The missile, which was being used as a target drone by the Soviet Navy, had strayed off course due to a presumed loss of radio contact with its operator [SRC-0165]. The combined tracking data from the Kaamanen close-range radar and the Rovaniemi early warning radar alerted the Finnish military to the threat [SRC-0165]. While the specific technical parameters of the Kaamanen radar remain unstated in the provided documents, its capability to detect and track stray cruise missiles over the remote northern territories of Finland was clearly demonstrated during this historical event [SRC-0165].</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>SRC-0165</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>SRC-0165</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>RAD-0135</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SITE-0113</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Air And Sea Surveillance Radar System</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>The NATO Missile Firing Installation (NAMFI), located at Souda Bay on the island of Crete, Greece, relies on an Air and Sea surveillance radar system to safely support its extensive operations [SRC-0122, SRC-0122, SRC-0122]. Established in 1967 as a premier NATO training facility for air defense systems, the range takes advantage of the region's clear atmospheric conditions year-round [SRC-0122]. Because the firing range's operational trajectories frequently intersect with busy commercial and military air and maritime traffic routes, the primary purpose of the surveillance radar system is to monitor the surrounding environment and resolve any possible tracking conflicts to ensure safety during live-fire exercises [SRC-0122]. The radar provides critical situational awareness for a variety of complex missile tests, most notably supporting launches of the MIM-104 Patriot and MIM-23 Hawk surface-to-air missile systems, as well as occasionally tracking other air-to-surface weapons [SRC-0122]. While specific technical specifications—such as the radar's exact designation, frequency band, manufacturer, dimensions, peak power output, and precise year of installation—are not detailed in the provided sources, the radar system remains in highly active operational status [SRC-0122]. It currently supports the armed forces of Greece, Germany, the Netherlands, and the United States during regular, multinational integrated air and missile defense training operations [SRC-0122, SRC-0122].</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>SRC-0122</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>SRC-0122</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>RAD-0136</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SITE-0194</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Cobra Dane (An/Fps-108)</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>The COBRA DANE (AN/FPS-108) is a single-faced, ground-based, L-band (1175–1375 MHz) large phased-array radar (LPAR) located at Eareckson Air Station on Shemya Island, Alaska [SRC-0001, SRC-0043, SRC-0190]. Developed in the mid-1970s and achieving operational status in 1977, the radar was initially built for the United States Air Force to collect intelligence data on Soviet ballistic missile tests and verify the SALT II arms limitation treaty [SRC-0043, SRC-0001, SRC-0190]. Today, it is operated by the U.S. Space Force [SRC-0043, SRC-0190]. COBRA DANE features a massive 95-foot diameter array face containing 15,360 active radiating elements and generates a peak RF power of approximately 15.4 megawatts using 96 Traveling Wave Tube (TWT) amplifiers [SRC-0190, SRC-0001, SRC-0043]. Its primary capabilities include providing midcourse coverage for the Ballistic Missile Defense System (detecting and classifying ICBMs and SLBMs to cue interceptors) and conducting space domain awareness by tracking satellites and orbital debris [SRC-0043, SRC-0027, SRC-0044]. It can detect objects as small as a basketball at distances of 2,000 miles [SRC-0043, SRC-0043]. Having undergone significant modernizations, such as the 1990 System Modernization and recent TWT redesigns, COBRA DANE is currently slated for comprehensive back-end digitization under the Ground Based Radar Digitization (GBRD) program [SRC-0001, SRC-0186, SRC-0190, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>SRC-0001</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>SRC-0001, SRC-0043, SRC-0190, SRC-0027, SRC-0044, SRC-0186</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>RAD-0137</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SITE-0344</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Long Range Discrimination Radar (Lrdr) (An/Fps-138)</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>The Long Range Discrimination Radar (LRDR), designated as AN/FPS-138, is a state-of-the-art solid-state Active Electronically Scanned Array (AESA) radar located at Clear Space Force Station in Alaska [SRC-0045, SRC-0045, SRC-0190]. Developed by Lockheed Martin, the contract was awarded in 2015, leading to its initial fielding in December 2021 [SRC-0100, SRC-0190]. The LRDR operates in the S-band and utilizes highly efficient Gallium Nitride (GaN) semiconductor technology [SRC-0100, SRC-0190]. Physically, it features dual monostatic arrays, each measuring 60 feet high by 60 feet wide, providing an extensive field of view for its multi-mission requirements [SRC-0100, SRC-0190, SRC-0003]. The radar's primary purpose is homeland missile defense, specifically designed to simultaneously search, track, and discriminate multiple long-range ballistic missile threats [SRC-0045, SRC-0045]. Its high-resolution S-band capabilities allow it to distinguish lethal warheads from non-lethal decoys and debris, preserving the inventory of Ground-Based Interceptors [SRC-0190, SRC-0045, SRC-0100]. Additionally, it supports space domain awareness by monitoring active and inactive satellites [SRC-0100, SRC-0190]. The system achieved operational acceptance by the USSF Combat Forces Command in December 2025 and is fully operational for homeland defense, featuring an adaptable open architecture designed to counter emerging hypersonic threats [SRC-0045, SRC-0190, SRC-0045].</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>SRC-0045</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>SRC-0045, SRC-0190, SRC-0100, SRC-0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>RAD-0138</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SITE-0345</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Perimeter Acquisition Radar Attack Characterization System (Parcs) (An/Fpq-16)</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>The Perimeter Acquisition Radar Attack Characterization System (PARCS), designated AN/FPQ-16, is a massive, single-faced passive electronically scanned array (PESA) radar situated at Cavalier Space Force Station in North Dakota [SRC-0008, SRC-0143, SRC-0190]. Built by General Electric in the early 1970s, it originally served as the Perimeter Acquisition Radar (PAR) for the U.S. Army's Safeguard anti-ballistic missile program before being transferred to the Air Force in 1976 and 1977 [SRC-0190, SRC-0008, SRC-0008]. Operating in the UHF band (420–450 MHz), the radar boasts a peak power output of roughly 14.3 megawatts [SRC-0132, SRC-0190]. Its single fixed antenna face provides a 140-degree azimuth and 93-degree elevation coverage, capable of detecting and tracking targets up to 2,000 miles away [SRC-0132, SRC-0190]. The primary mission of PARCS is early warning, keeping watch for sea-launched and intercontinental ballistic missiles aimed at North America, while its secondary role involves monitoring over half of all Earth-orbiting objects for the Space Surveillance Network [SRC-0143, SRC-0190, SRC-0008]. Maintained by the 10th Space Warning Squadron and sustained by contractors such as InDyne, this legacy Cold War asset remains operational today [SRC-0190, SRC-0190]. To address hardware obsolescence, PARCS is scheduled to receive a modernized, digitized front-end antenna array under the Space Force's Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>SRC-0008</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>SRC-0008, SRC-0143, SRC-0190, SRC-0132, SRC-0186</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>RAD-0139</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SITE-0366</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Multiple Object Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>The Multiple Object Tracking Radar (MOTR) is a highly specialized phased-array tracking system located at White Sands Missile Range (WSMR) [SRC-0114, SRC-0157]. Built in the mid-1980s at an original cost of $36 million each, the MOTR is an exceptionally rare asset, with only five units ever constructed worldwide [SRC-0114, SRC-0157]. The radar transmits pulses of energy through phase-shifting elements, allowing it to electronically steer its beam off-boresight to cover a 60-degree area and simultaneously track up to 40 airborne objects [SRC-0157, SRC-0114]. Its primary purpose at WSMR is to support flight safety operations and test evaluations by providing precise Time-Space-Position-Information (TSPI) data, ensuring that airborne systems follow their intended flight paths safely [SRC-0157, SRC-0114]. 
+Currently, WSMR is the only installation globally to house three MOTR systems [SRC-0114]. Most notably, MOTR-4 was rescued from an Air Force scrap yard at Vandenberg Air Force Base in 2011 [SRC-0157, SRC-0157]. An internal team at WSMR successfully disassembled, transported, and reassembled the radar, achieving operational status in 2015 [SRC-0157, SRC-0114]. This acquisition replaced older AN/FPS-16 radars, delivering vastly improved data quality and realizing significant cost savings for the installation [SRC-0114, SRC-0114, SRC-0114].</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>SRC-0114</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>SRC-0114, SRC-0157</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>RAD-0140</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>SITE-0366</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>An/Fps-16 (An/Fps-16)</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Historically, White Sands Missile Range (WSMR) operated multiple RCA-manufactured AN/FPS-16 instrumentation radars to provide precise metric tracking and flight safety data [SRC-0008], [SRC-0217]. These single-object tracking radar systems were crucial for observing test vehicles, sounding rockets, and tracking superpressure weather balloons while recording position data at a rate of one point per second [SRC-0103], [SRC-0153]. Over the decades, WSMR utilized at least three of these legacy tracking systems across its expansive range [SRC-0217]. While highly accurate, the AN/FPS-16 radars were limited by their ability to track only a single object at a time and required significant personnel and financial resources to maintain [SRC-0114]. Rather than spending approximately $7.5 million to upgrade the aging FPS-16s to modern standards, or $9 million for new equivalent units, WSMR strategically replaced them with a rare Multiple Object Tracking Radar (MOTR-4) acquired from Vandenberg [SRC-0114], [SRC-0114], [SRC-0114]. The transportable MOTR system maintained the high tracking accuracy of the AN/FPS-16 while offering multiple-track capabilities, effectively replacing two FPS-16 units and saving the equivalent of eight employees' annual workloads [SRC-0114], [SRC-0114].</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>SRC-0008</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>SRC-0008, SRC-0217, SRC-0103, SRC-0153, SRC-0114</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>RAD-0141</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SITE-0347</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Upgraded Early Warning Radar (Uewr) (An/Fps-132)</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Cape Cod Space Force Station, Massachusetts, provides critical early warning coverage over the United States East Coast and the Atlantic Ocean [SRC-0133], [SRC-0190]. Operated by the 6th Space Warning Squadron, the radar is the only facility in the nation capable of confirming a detected intercontinental or sea-launched ballistic missile attack from the east [SRC-0133]. Housed in a 32-meter (105-foot) high building, the solid-state phased-array radar utilizes two flat faces tilted back 20 degrees, each measuring 31 meters (102 feet) wide [SRC-0133]. The system operates in the UHF band (420 to 450 MHz) and features 1,792 active antenna elements per face, capable of producing approximately 582.4 kW of peak power and 152.5 kW of average power [SRC-0133], [SRC-0133]. The radar electronically steers a narrow 2.2-degree main beam to provide a 240-degree sweep [SRC-0133], [SRC-0133]. Originally activated in 1980 as a PAVE PAWS installation, it was upgraded to the AN/FPS-132 UEWR configuration by Raytheon between 2013 and 2017 [SRC-0190], [SRC-0190]. This modification integrated the radar into the Ballistic Missile Defense System without requiring major structural changes [SRC-0190]. It also continues its secondary mission of space surveillance and is targeted for the Space Force's upcoming GBRD modernization by 2030 [SRC-0186], [SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>SRC-0133</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>SRC-0133, SRC-0190, SRC-0186</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>RAD-0142</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SITE-0344</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Upgraded Early Warning Radar (Uewr) (An/Fps-132)</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Clear Space Force Station, Alaska, is a vital strategic sensor hub in the Pacific theater, operated by the 13th Space Warning Squadron [SRC-0190], [SRC-0190]. Originally established in September 1961 as a mechanical Ballistic Missile Early Warning System (BMEWS) site, the facility was upgraded in 1981 to an AN/FPS-123 Solid-State Phased Array Radar System (SSPARS) [SRC-0190]. To meet modern threats, the Air Force and the Missile Defense Agency awarded Raytheon a $125.3 million contract in 2012 to upgrade the system to the AN/FPS-132 UEWR configuration [SRC-0190]. Completed in Fiscal Year 2016 within the existing scanner building, this upgrade integrated critical Ground-based Midcourse Defense (GMD) communication capabilities [SRC-0190]. Operating in the UHF band, the radar’s two-panel phased-array configuration provides a 240-degree coverage arc stretching across the Arctic and Pacific regions [SRC-0190], [SRC-0190]. Its primary purpose is to provide early warning of ballistic missile attacks and overlapping space domain awareness alongside the newly constructed Long Range Discrimination Radar (LRDR) also located at Clear [SRC-0190], [SRC-0190]. To counter future advanced digital threats, the Clear UEWR is scheduled for front-end antenna digitization and integration into a common virtual software stack under the Space Force's Ground Based Radar Digitization (GBRD) Phase 1 prototyping program, expected to achieve initial operational capability by FY 2030 [SRC-0190], [SRC-0190], [SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>RAD-0143</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SITE-0290</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Arsr-4 (Arsr-4) At Gibbsboro J-51 Jss</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>The ARSR-4 (Air Route Surveillance Radar-4) at the Gibbsboro J-51 Joint Surveillance System (JSS) site is a three-dimensional, long-range surveillance radar located at 39°49′29″N 074°57′15″W in New Jersey [SRC-0086, SRC-0086]. Manufactured by the Northrop Grumman Corporation in the 1990s, the ARSR-4 was designed to replace obsolete 1960s-vintage AN/FPS-20 and ARSR-1/2 radars [SRC-0086, SRC-0086, SRC-0086]. It operates in the L-band frequency range of 1.215 to 1.4 GHz, utilizing dual-channel frequency hopping technology to provide robust long-range detection and anti-jamming defense [SRC-0086, SRC-0086]. This solid-state radar system features an impressive effective detection range of 250 nautical miles and can detect small, low-flying objects by minimizing clutter and weather effects through its "look down" capability [SRC-0086, SRC-0086]. The ARSR-4 emits a peak power of 65 kW and an average power of 3.5 kW [SRC-0086]. The Gibbsboro site, formerly known as the Aerospace Defense Command (ADCOM) Gibbsboro Air Force Station (Z-63), saw its USAF operations close in 1984 before it transitioned into a joint-use FAA/USAF JSS facility [SRC-0086]. During the change-out to the new ARSR-4 system, the nearby Trevose J-61 site served as a temporary data-tie to maintain coverage until Gibbsboro officially reopened with its upgraded ARSR-4 [SRC-0086]. Today, it functions as a critical, largely unattended asset for both national airspace defense and civil air traffic control [SRC-0086, SRC-0086].</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>RAD-0144</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SITE-0291</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Arsr-2 (Arsr-2) At Gallup Gal Jss</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>The ARSR-2 at the Gallup GAL JSS site is a long-range Air Route Surveillance Radar located at 36°04′33″N 108°51′37″W, above Washington Pass, north of Gallup, New Mexico [SRC-0086]. It is also historically known as the Farmington site and the former Aerospace Defense Command (ADCOM) SAGE site Z-221 [SRC-0086]. Opened by the Federal Aviation Administration (FAA) in 1963, the system forms a vital part of the Joint Surveillance System (JSS), providing atmospheric air defense and air traffic control data for both the FAA and the United States Air Force [SRC-0086, SRC-0086]. The ARSR-2 was originally developed by Raytheon in the 1960s to operate in the L-band frequency range of 1215 to 1350 MHz, functioning identically to its ARSR-1 predecessor but with redesigned components for improved reliability [SRC-0086, SRC-0086]. Initially, the radar provided a detection range of approximately 200 nautical miles and relied on nationwide vacuum tube technology [SRC-0086, SRC-0086]. However, to maintain its operational viability and extend its service life, the Gallup ARSR-2, alongside all other ARSR-1 and ARSR-2 systems, was upgraded to the modern Common ARSR (CARSR) configuration by the end of 2015 [SRC-0086, SRC-0086]. This substantial upgrade replaced legacy parts with completely solid-state transmitter components and software shared with the FAA's newer ASR-11 airport surveillance radars, maintaining its 200-nautical-mile range while vastly improving its operational efficiency [SRC-0086].</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>RAD-0145</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SITE-0292</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Arsr-1E (Arsr-1E) At Mesa Rica Qwc Jss</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>The ARSR-1E at the Mesa Rica QWC JSS site is a long-range Air Route Surveillance Radar situated at 35°14′15″N 104°12′16″W in New Mexico [SRC-0086]. Originally part of the Semi Automatic Ground Environment (SAGE) network, it operated as the former Aerospace Defense Command (ADCOM) SAGE site Z-234 [SRC-0086, SRC-0086]. Manufactured by Raytheon and initially introduced in 1958, the ARSR-1 series operates in the adjacent L-band frequency range between 1215 and 1350 MHz [SRC-0086, SRC-0086]. Built to support both civilian air traffic control and military air defense, the system originally achieved a maximum detection range of around 170 to 200 nautical miles [SRC-0086, SRC-0086]. Like many older radar installations in the Joint Surveillance System, the Mesa Rica facility initially relied on outdated vacuum tube technology [SRC-0086]. Over time, these legacy systems required significant overhauls to remain reliable and effective for the Federal Aviation Administration (FAA) and the U.S. Air Force [SRC-0086, SRC-0086]. By the end of 2015, the Mesa Rica ARSR-1E was fully modernized under the Common ARSR (CARSR) upgrade program [SRC-0086]. This crucial retrofit replaced the aging hardware with a completely solid-state architecture, integrating new transmitter components and modern software shared with the FAA's ASR-11 radars [SRC-0086]. Through this modernization, the Mesa Rica site continues its dual-purpose mission, sustaining a reliable 200-nautical-mile surveillance range to monitor internal and border airspace [SRC-0086, SRC-0086].</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>RAD-0146</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>SITE-0293</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Surveillance Radar At Silver City J-28 Jss</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>The surveillance radar at the Silver City J-28 JSS site was a long-range radar installation located atop Brushy Mountain at 32°59′21″N 108°57′38″W in New Mexico [SRC-0086]. Originally established as part of the 1972 Southern Air Defense System, the Silver City facility operated as the former Aerospace Defense Command (ADCOM) site Z-245 [SRC-0086]. Like other legacy radar facilities integrated into the Joint Surveillance System (JSS), it was designed to provide crucial atmospheric air defense tracking and civil air traffic control data for both the Federal Aviation Administration and the United States Air Force [SRC-0086]. While specific dimensions and power outputs for the original Silver City radar are not explicitly detailed in the provided sources, the site historically utilized legacy long-range search radar equipment characteristic of the early Cold War and SAGE network eras [SRC-0086, SRC-0086]. Ultimately, the Silver City J-28 site was closed in the 1990s as the U.S. military and the FAA sought to modernize the JSS network with more advanced, reliable, and standardized radar technology [SRC-0086]. The surveillance coverage formerly provided by the Silver City facility was subsequently replaced by the newly constructed J-28A site in Deming, New Mexico [SRC-0086]. The Deming site took over the sector's operational responsibilities by utilizing the highly capable ARSR-4 three-dimensional solid-state radar system, effectively ending the operational history of the Silver City J-28 site [SRC-0086, SRC-0086].</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>RAD-0147</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>SITE-0225</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Arsr-4 (Arsr-4) At Deming Tars</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>The Deming area in New Mexico hosts two distinct yet complementary radar surveillance capabilities: the ARSR-4 at the J-28A Joint Surveillance System (JSS) site and the Tethered Aerostat Radar System (TARS). The ARSR-4 radar, located at 32°29′30″N 107°09′59″W, is a state-of-the-art, three-dimensional, solid-state long-range surveillance radar manufactured by Northrop Grumman [SRC-0086, SRC-0086]. Operating in the L-band (1.215–1.4 GHz), the ARSR-4 outputs 65 kW of peak power and provides a 250-nautical-mile detection range [SRC-0086]. It features a "look down" capability and frequency-hopping technology to track low-flying targets while minimizing clutter [SRC-0086, SRC-0086]. The J-28A site was established to replace the older Silver City J-28 installation, providing enhanced air defense and air traffic control data [SRC-0086]. In addition to the fixed ARSR-4, Deming operates a TARS site at 32°01′36″N 107°51′51″W [SRC-0197]. The TARS platform uses a 420,000-cubic-foot helium-filled aerostat that ascends to 15,000 feet, carrying a Lockheed Martin L-88(V)3 L-band radar [SRC-0098, SRC-0197]. The TARS radar features a 29-foot rotating antenna inside a fabric windscreen, providing 360-degree, downward-looking coverage out to 200 nautical miles [SRC-0098, SRC-0197]. Modernized in 1999 to the standard 420K/L-88 configuration, the Deming TARS plays a critical role in supporting U.S. Customs and Border Protection by detecting low-flying drug smugglers and airborne incursions along the southern border [SRC-0098, SRC-0098].</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>SRC-0086, SRC-0197, SRC-0098</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>RAD-0148</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SITE-0295</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Arsr-2 (Arsr-2) At Battle Mountain Btm Jss</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>The ARSR-2 at the Battle Mountain BTM JSS site is a long-range Air Route Surveillance Radar positioned on top of Mount Lewis, south of Battle Mountain, Nevada, at coordinates 40°24′11″N 116°52′04″W [SRC-0086]. Historically referred to as the Elko site and designated as the former Aerospace Defense Command (ADCOM) site Z-214, the facility is a key component of the Joint Surveillance System (JSS) [SRC-0086]. Operating in the L-band frequency range (1215–1350 MHz), the ARSR-2 was developed by Raytheon in the 1960s to serve the dual purposes of North American atmospheric air defense and civilian air traffic control [SRC-0086, SRC-0086, SRC-0086]. Originally reliant on vacuum tube electronics, the system provided reliable detection out to a range of 200 nautical miles [SRC-0086, SRC-0086]. Over the decades, maintaining these legacy components became increasingly difficult [SRC-0086]. To ensure continued operational viability, the Federal Aviation Administration and the U.S. Air Force upgraded the Battle Mountain installation under the Common ARSR (CARSR) program, which was completed for all ARSR-1/2 systems by the end of 2015 [SRC-0086]. This critical modernization replaced the outdated hardware with a completely solid-state architecture, sharing modern software and transmitter components with the newer ASR-11 airport surveillance radars [SRC-0086]. Today, the upgraded Battle Mountain radar remains an essential, unmanned asset that provides continuous, highly reliable airspace monitoring capabilities for the western United States [SRC-0086, SRC-0086].</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>SRC-0086</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>RAD-0149</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>SITE-0045</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>C-Band Monopulse Precision Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Changchun Station is part of China's network of five fixed near-Earth satellite control stations, deployed to perform daily tracking and control over medium and low-orbiting satellites [SRC-0040, SRC-0040]. To fulfill its tracking and control responsibilities, the station is equipped with a C-band monopulse precision tracking radar [SRC-0040, SRC-0040]. Although the sources do not specify the manufacturer or the exact year this radar was built, they detail its capabilities and operational purpose. The radar operates in the C-band frequency and is specifically designed for the precise measurement of a satellite's perigee period and its reentry orbit [SRC-0040, SRC-0040]. It possesses a high capability for locating orbits with data, which is attributed to its large number of measurement elements and overall high measurement precision [SRC-0040, SRC-0040]. In conjunction with other station facilities like VHF/UHF control systems, station computers, and monitoring display equipment, the radar's data undergoes preprocessing to support digital guidance, acquisition, and remote control instruction delivery [SRC-0040, SRC-0040, SRC-0040]. The station exchanges this processed radar data with the Xi'an Satellite Control Center to conserve communication voice channels and integrate into the broader China Aerospace Control Network [SRC-0040, SRC-0040]. The current status of the radar system involves active participation in China's near-Earth satellite tracking, telemetry, control, and recovery operations [SRC-0040, SRC-0040].</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>RAD-0150</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>SITE-0046</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>C-Band Monopulse Precision Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Xiamen Station is a critical node in the China Aerospace Control Network, functioning both as one of the five fixed near-Earth satellite control stations and as a key facility for geostationary orbital satellite launches [SRC-0040, SRC-0040]. Among its primary tracking instrumentation is a C-band monopulse precision tracking radar [SRC-0040, SRC-0040]. While the specific manufacturer and exact year of construction are not provided in the sources, the radar operates within the C-band frequency [SRC-0040, SRC-0040]. This radar system is utilized for highly precise measurements of satellite perigee periods and reentry orbits, a capability made possible by its large number of measurement elements and high overall measurement precision [SRC-0040, SRC-0040]. Alongside the station's unified C-band carrier wave control systems, the radar provides vital data for tracking orbit measurements, including distance, azimuth, and pitch angle [SRC-0040]. Data from the radar is processed by the station's dual computers and exchanged with the Xi'an Satellite Control Center, ensuring robust attitude and orbit control during long-term satellite supervision and geostationary satellite launches [SRC-0040, SRC-0040, SRC-0040]. Today, the radar remains in an active operational status, continuing to support the daily tracking, control, and launch missions of China's expanding aerospace and satellite network [SRC-0040, SRC-0040].</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>RAD-0151</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>SITE-0047</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>C-Band Monopulse Precision Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>The Nanning Station operates as one of China's five fixed near-earth satellite control stations within the national aerospace network [SRC-0040], [SRC-0040]. As part of this network, several control stations are outfitted with a C-band monopulse precision tracking radar, which serves as a core component of the site's telemetry and tracking capabilities [SRC-0040], [SRC-0040]. The provided sources do not disclose the manufacturer or the exact year this radar was built, but they highlight its operational characteristics and strategic importance [SRC-0040], [SRC-0040]. Operating within the C-band frequency range, the radar is designed with a large number of measurement elements that provide high measurement precision [SRC-0040], [SRC-0040]. Its primary purpose is to locate orbits using recorded data, making it particularly suitable for measuring a satellite's perigee period and its reentry orbit [SRC-0040], [SRC-0040]. The Nanning Station itself leverages these tracking radar capabilities to perform daily control over medium- and low-orbiting satellites [SRC-0040]. Additionally, the station conducts carrier rocket flight coverage tracking measurements during geostationary satellite launches and perigee control missions for near-earth orbital satellites [SRC-0040]. The radar system remains operational as an integral part of China's tracking and control network, which effectively manages both domestic and overseas satellite missions [SRC-0040], [SRC-0040].</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>RAD-0152</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>SITE-0048</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Unified C-Band Carrier Wave Control System</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>The Weinan Station is a critical dual-purpose facility within China's aerospace control network, supporting both near-earth and geostationary orbital satellite operations [SRC-0040], [SRC-0040], [SRC-0040]. A primary system at this site is the unified C-band carrier wave control system, which acts as a tracking radar and telemetry unit [SRC-0040]. Operating in the C-band frequency range, this system functions cooperatively with in-satellite transponders to execute precise tracking orbit measurements, telemetry reception, and remote control for high-orbiting satellites up to 40,000 kilometers in altitude [SRC-0040]. Its tracking radar capabilities specifically cover distance, azimuth, and pitch angle measurements [SRC-0040]. The sources do not document the system's manufacturer or the year it was built, but its operational purpose is clearly defined: it is essential for the launch and daily control of geostationary satellites [SRC-0040], [SRC-0040]. The Weinan Station utilizes a duplex computer architecture to process the radar's station data, exchange data with the Xi'an Control Center, and manage satellite attitude and long-term orbit control [SRC-0040]. Additionally, the system supports simulated maneuver tests for satellite-to-earth reentry routes [SRC-0040]. The system is currently operational, playing a foundational role in managing China's geostationary communication satellites and broader space domain activities [SRC-0040], [SRC-0040].</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>RAD-0153</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>SITE-0049</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>C-Band Monopulse Precision Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>The Kashgar Station (referred to as Kash Station in the sources) is deployed in the western part of China as one of the five fixed near-earth satellite control stations [SRC-0040], [SRC-0040]. Like other stations in this network, it is supported by a C-band monopulse precision tracking radar, although the specific manufacturer and year of construction are not provided in the source documents [SRC-0040], [SRC-0040]. Operating on the C-band frequency, this radar system is engineered with a high number of measurement elements, which ensures exceptionally high measurement precision [SRC-0040], [SRC-0040]. The primary purpose of this radar is the accurate measurement of a satellite's perigee period and its reentry orbit, leveraging its strong capability to locate orbits using precise tracking data [SRC-0040], [SRC-0040]. At the Kashgar Station, this radar facilitates the cooperative daily tracking and control of medium- and low-orbiting satellites [SRC-0040]. Working in tandem with other regional stations, the facility ensures continuous orbital monitoring and trajectory tracking, which are critical for both satellite maintenance and the safe recovery of reentry compartments [SRC-0040], [SRC-0040], [SRC-0040]. The radar remains an operational asset within China's broader aerospace control network, actively contributing to the nation's space surveillance and satellite tracking missions [SRC-0040], [SRC-0040].</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>SRC-0040</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>RAD-0154</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>SITE-0054</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Radar System</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>The Integrated Test Range (ITR) located at Chandipur in the Balasore district of Odisha, India, operates a variety of high-performance range instrumentation systems, which prominently include tracking radars [SRC-0073, SRC-0073, SRC-0076]. These local radar arrays are specifically deployed to track the flight trajectories of rockets, ballistic missiles, and airborne weapon systems from their initial take-off through to the point of impact [SRC-0076, SRC-0222]. The primary purpose of this radar system is to precisely locate flying objects, capture real-time flight data, and work in conjunction with Electro-Optical Tracking Systems (EOTS), telemetry stations, and central computer systems to evaluate overall weapon performance [SRC-0076, SRC-0050]. 
+Recently, these radars have been actively utilized in major strategic tests, such as the successful flight-trials of the Very Short-Range Air Defence System (VSHORADS) and the Agni-1 short-range ballistic missile, where they successfully monitored the missiles' flight paths and validated their effectiveness against aerial targets [SRC-0073, SRC-0073, SRC-0050]. The systems remain in active operational status under the management of the Defence Research and Development Organisation (DRDO) [SRC-0076, SRC-0050]. While the sources confirm their critical operational role, they do not disclose specific technical details regarding the radars' exact type, frequency bands, manufacturers, or the years they were built [SRC-0073, SRC-0076, SRC-0222, SRC-0050].</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>SRC-0073</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>SRC-0073, SRC-0076, SRC-0222, SRC-0050</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>RAD-0155</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>SITE-0065</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>An/Tpy-2</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>The AN/TPY-2 (Army Navy/Transportable Radar Surveillance) is an advanced, transportable Active Electronically Scanned Array (AESA) radar system manufactured by Raytheon Technologies [SRC-0011], [SRC-0011], [SRC-0012]. Introduced to the military in 2007, the radar operates in the high-frequency X-band (8.55–10 GHz), which provides exceptional target resolution, precise discrimination between warheads and non-threats like decoys, and highly accurate target tracking [SRC-0011], [SRC-0011], [SRC-0012]. The radar features an antenna aperture of approximately 9.2 square meters and utilizes fully electronic beam steering [SRC-0011], [SRC-0011]. Built for a strategic missile-defense purpose, the system is designed to detect, track, and classify ballistic missile threats during their midcourse and terminal phases at ranges exceeding 1,000 kilometers [SRC-0011], [SRC-0011], [SRC-0012]. The AN/TPY-2 boasts the capability to track hundreds of targets simultaneously with rapid, sub-second update rates, integrating seamlessly with allied and U.S. missile-defense architectures such as THAAD, Aegis BMD, and the Command and Control, Battle Management, and Communications (C2BMC) network [SRC-0011], [SRC-0011], [SRC-0011]. The radar is currently fully operational and actively deployed across the globe [SRC-0011]. In Israel, the system was provided by the United States to act as a critical early warning sensor, complementing the country's existing Arrow 2 and Patriot PAC-3 air defense systems [SRC-0012]. The Israeli deployment of the AN/TPY-2 radar is supervised by the U.S. Army's 1st Space Brigade, specifically operating as the 13th Missile Defence Battery [SRC-0012].</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>SRC-0011</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>SRC-0011, SRC-0012</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>RAD-0156</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>SITE-0077</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Saturn-Ms</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>The Saturn-MS measuring complex is a strategic tracking and telemetry radar system located at the Baikonur Cosmodrome in Kazakhstan [SRC-0173]. The facility is visually defined by its two massive parabolic antennas, each measuring 25 meters in diameter and weighing 200 tons, situated atop Murguduk hill [SRC-0173]. Construction of the Saturn-MS complex began on January 25, 1967, and following initial communication tests with the Luna-16 interplanetary station in November 1970, the system entered full-scale operational service on November 3, 1971 [SRC-0173]. While the specific manufacturer and frequency bands are not detailed in the available sources, its capabilities are extensive. The complex is designed to monitor rocket trajectories, gather telemetry, manage space communications, and execute satellite control during the critical phases of a launch [SRC-0173]. Historically operated as an exclusively military facility, the complex tracked various high-profile missions, including the Soyuz-Apollo program, the Buran shuttle, and interplanetary probes to the Moon, Mars, and Venus [SRC-0173, SRC-0173]. In 2006, the military unit managing the site was disbanded, and Saturn-MS transitioned into a fully civilian tracking facility [SRC-0173]. Today, it continues to undergo gradual modernization to serve as the primary monitoring "eyes" for Baikonur Cosmodrome launches well into the future [SRC-0173].</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>SRC-0173</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr">
+        <is>
+          <t>SRC-0173</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>RAD-0157</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>SITE-0096</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>An/Tpy-2</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>The AN/TPY-2 (Army Navy/Transportable Radar Surveillance) is a highly mobile, transportable active electronically scanned array (AESA) radar system developed and manufactured by Raytheon Technologies [SRC-0011, SRC-0012, SRC-0012, SRC-0183]. Introduced into service in 2007, this advanced sensor operates in the X-band frequency range (8.55–10 GHz), which provides exceptional target resolution and tracking fidelity [SRC-0012, SRC-0183, SRC-0011, SRC-0190]. The system is designed to detect, classify, track, and discriminate between ballistic missiles, lethal warheads, and non-threats such as decoys at extraordinary ranges exceeding 1,000 kilometers [SRC-0011, SRC-0011, SRC-0011, SRC-0012]. It is capable of tracking hundreds of high-speed targets simultaneously and uses electronic beam steering for near-instantaneous updates [SRC-0011, SRC-0011]. Recently, Raytheon upgraded the AN/TPY-2 with gallium nitride (GaN) semiconductor components, significantly improving its overall sensitivity, search volume, and detection range over legacy models [SRC-0190, SRC-0012, SRC-0158]. The primary purpose of the AN/TPY-2 is to serve as the cornerstone sensor for the Terminal High Altitude Area Defense (THAAD) system, while also cueing other defense networks such as the MIM-104 Patriot PAC-3, Aegis BMD, and C2BMC systems [SRC-0012, SRC-0190, SRC-0011, SRC-0011, SRC-0011]. It can be deployed in a forward-based mode for strategic early warning or a terminal mode for fire control [SRC-0183]. Currently, the AN/TPY-2 remains fully operational and is actively deployed in the United Arab Emirates (UAE), where it is integrated with THAAD batteries to provide regional missile defense and rapid response capabilities against theater ballistic threats [SRC-0183, SRC-0183].</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>SRC-0012</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>SRC-0011, SRC-0012, SRC-0183, SRC-0190, SRC-0158</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>RAD-0158</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>SITE-0098</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Iris-T Radar</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>The IRIS-T radar is an integral component of the IRIS-T SLM medium-range air defense system, which is slated to be permanently stationed at the Ämari Air Base in Estonia [SRC-0014, SRC-0014]. Originating from Germany, the system was part of a joint procurement decision made by Estonia and Latvia in May 2023 to significantly enhance their ground-based air defense capabilities [SRC-0014]. Currently, the radar and its associated systems are on order, with three batteries expected to become fully operational within the Estonian Air Force's newly established Air Defence Wing by the year 2026 [SRC-0014, SRC-0014]. The radar is highly mobile and is designed to be mounted on the German-manufactured MAN SX44 platform truck, which also serves as the transport vehicle for the system's operations center and missile launcher [SRC-0014]. The primary purpose of the IRIS-T radar is to support active air defense operations and ensure the integrity of Estonia's airspace [SRC-0014]. While specific technical specifications such as the exact frequency band and the original year built are not detailed in the provided sources, the radar will function as the primary sensor for the IRIS-T SLM batteries [SRC-0014, SRC-0014]. Once fielded, it will work in tandem with NATO allied fighter detachments that are also deployed to Ämari Air Base for the Baltic Air Policing Mission, thereby providing a critical medium-range tracking and targeting capability against regional aerial threats [SRC-0119].</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>SRC-0014</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>SRC-0014, SRC-0119</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>RAD-0159</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>SITE-0125</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Czech Radar Systems</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>During the NATO large-scale live-fire air defense exercise Ramstein Legacy 22, which took place from June 6 to 10, 2022, Czech radar systems were deployed on a beach at the Ustka Training Range in Poland [SRC-0124], [SRC-0124]. While specific details regarding the exact radar type, frequency band, manufacturer, and year built are not provided in the available sources, these radar systems were part of a broader integration of 17 surface-based air and missile defense systems tested in live-fire scenarios [SRC-0124]. The primary purpose of deploying these systems at Ustka was to participate in multinational demonstrations alongside French, Polish, Slovak, and United Kingdom troops, focusing on enhancing allied interoperability and demonstrating various weapons platforms, including the Starstreak air defense system [SRC-0124], [SRC-0124]. The exercise aimed to strengthen the NATO alliance's defensive posture in response to conventional threats, highlighting a unified coalition effort across the European theater [SRC-0124]. The current status of these Czech radar systems at the Ustka site is not active, as they were deployed temporarily as part of a rotational exercise involving around 50 aircraft and multiple international contingents [SRC-0124], [SRC-0124]. This event served to reinforce the integrated air defense capabilities and the cooperative bond among NATO allies [SRC-0124].</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>SRC-0124</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>SRC-0124</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>RAD-0160</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>SITE-0351</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>An/Spy-1</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>The AN/SPY-1 radar is a critical sensor component integrated into the Aegis Ashore Poland installation, representing a key element of the United States Missile Defense Agency’s (MDA) Phase 3 contribution to the European Phased Adaptive Approach [SRC-0093]. Accepted by the Chief of Naval Operations in December 2023, this site is funded and operated by the U.S. Navy to protect NATO's European territory against ballistic missile threats [SRC-0093]. While the exact manufacturer and year built are not detailed in the provided sources, the AN/SPY-1 serves as a primary sensor for the Aegis Combat System and the broader Aegis Ballistic Missile Defense System [SRC-0055], [SRC-0055], [SRC-0179], [SRC-0179]. The Aegis system is known to operate in the S-band frequency, differentiating it from X-band and C-band defense radars [SRC-0178]. The AN/SPY-1 radar's capabilities are vast, supporting full Aegis missile defense warfighting operations while also participating in the Space Force Space Domain Awareness (SDA) mission [SRC-0093]. Following its operational acceptance, the Poland site entered a maintenance period to upgrade its computer networks and communications systems [SRC-0093]. The radar's SDA capability has been fully transitioned to the Navy, maintaining complete compatibility with deployed naval operations and incorporating appropriate safeguards for its dual-mission profile [SRC-0093]. The system remains in active operational status, continuously supporting defense requirements and future capability demonstrations in the region [SRC-0093], [SRC-0093].</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>SRC-0093</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>SRC-0093, SRC-0055, SRC-0179, SRC-0178</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>RAD-0161</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>SITE-0145</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Precision Tracking Radar</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Ascension Island, situated in the Atlantic Ocean, serves as a crucial downrange station within the Eastern Test Range (ETR) network, hosting precision tracking radars to support space and missile operations [SRC-0095, SRC-0106]. While the provided sources do not specify the radar's exact manufacturer, operating frequency band, or the year it was originally built, they identify the system as a metric radar capable of performing both beacon and echo tracking [SRC-0106, SRC-0106]. The primary purpose of this radar installation is to provide comprehensive launch, midcourse, and terminal phase coverage for ballistic missiles [SRC-0106]. In terms of capabilities, the precision tracking radar acquires and transmits real-time trajectory data directly to the computer center at Cape Canaveral Air Force Station (CCAFS) [SRC-0106]. The radar operates alongside a broader suite of instrumentation on the island, including target arrays of bottom-mounted hydrophones for the Missile Impact Location System (MILS) and terrestrial telemetry stations [SRC-0106, SRC-0106, SRC-0106]. Notably, while other ETR downrange sites possess telemetry doppler data capabilities for metric measurements, Ascension Island does not [SRC-0106]. In its current status, Ascension Island remains an active and vital post-detect telemetry site for the ETR, utilizing advanced digital satellite communication (SATCOM) links to transport telemetry and radar management data back to the Range Operations Control Center [SRC-0118, SRC-0118].</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>SRC-0095</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>SRC-0095, SRC-0106, SRC-0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>RAD-0162</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>SITE-0173</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Altair</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>The ARPA Long-Range Tracking and Instrumentation Radar (ALTAIR) is a highly agile tracking and instrumentation radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur, part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Designed and developed under the direction of ARPA and Lincoln Laboratory, it began operations in 1970 [SRC-0071], [SRC-0071], [SRC-0071]. ALTAIR operates in the VHF (0.162 GHz) and UHF (0.422 GHz) frequency bands and is equipped with a massive 150-foot diameter antenna that rotates on a 110-foot circular track [SRC-0071], [SRC-0071], [SRC-0071]. It produces a peak transmit power of 6 megawatts at both frequencies, with a range resolution of 32 meters at VHF and 15 meters at UHF [SRC-0071], [SRC-0071], [SRC-0071]. Originally built to evaluate U.S. strategic weapons against Soviet-style large VHF and UHF radars, ALTAIR is capable of acquiring targets over 3500 kilometers away [SRC-0071], [SRC-0071]. Over time, its purpose expanded to include tracking new foreign space launches, conducting space surveillance, performing deep-space tracking, and supporting ionospheric modeling [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0151]. ALTAIR was upgraded in 1984 with an array of traveling-wave tubes to double its UHF average power, and further upgraded in 1995 to 300 kW, greatly enhancing its deep-space capabilities [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. In 2002, the radar's electronics were modernized under the Radar Open System Architecture (ROSA) project, allowing remote operations [SRC-0071], [SRC-0071], [SRC-0071]. Today, ALTAIR remains an active and heavily utilized sensor, supporting space activities for 128 hours per week while serving as a critical asset for the U.S. Space Surveillance Network [SRC-0071], [SRC-0071], [SRC-0071].</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0151</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>RAD-0163</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>SITE-0173</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tradex</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>The Target Resolution and Discrimination Experiment (TRADEX) is a high-power instrumentation and tracking radar situated at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur within the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0071]. Built by the RCA Corporation under the direction of ARPA, TRADEX was the first radar installed at the site and began operations in 1962 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. It originally operated as a UHF tracker and L-band illuminator, but in 1970, the radar was extensively modified to operate in the L-band (1.320 GHz) and S-band (2.95 GHz) [SRC-0071], [SRC-0071], [SRC-0071]. The radar features an 84-foot diameter antenna and utilizes pulse compression to achieve a range resolution of approximately 15 meters [SRC-0071], [SRC-0071], [SRC-0071]. It delivers a peak transmit power of 2.0 megawatts in both its L-band and S-band frequencies [SRC-0071]. TRADEX was historically a workhorse for developing ballistic missile discrimination techniques, evaluating reentry vehicle wakes, and collecting signature data for systems like Safeguard [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Its capabilities were steadily upgraded with features like multi-static measurements, S-band pseudo-random noise waveforms to emulate Soviet radars, and a real-time multi-target tracker [SRC-0071], [SRC-0071], [SRC-0071]. In 2002, the radar received a Radar Open System Architecture (ROSA) modernization, equipping it with commercial off-the-shelf hardware and enabling remote operations [SRC-0071], [SRC-0071], [SRC-0071]. Currently, TRADEX remains fully operational, serving as an official contributing sensor to the Air Force Space Surveillance Network and dedicating at least 10 hours a week to deep-space tracking [SRC-0071], [SRC-0071].</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>RAD-0164</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>SITE-0173</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Alcor</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>The ARPA-Lincoln C-band Observables Radar (ALCOR) is a wideband instrumentation and imaging radar located at the Reagan Test Site on Roi-Namur [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Lincoln Laboratory served as the prime contractor for the radar, with assistance from RCA, Westinghouse, Hughes, and Honeywell [SRC-0071], [SRC-0071]. ALCOR became operational in January 1970, marking a milestone as the United States' first high-power, long-range, wideband radar [SRC-0071], [SRC-0071], [SRC-0071]. The system operates in the C-band (5.664 GHz narrowband and 5.672 GHz wideband) utilizing a 40-foot diameter antenna with a peak transmit power of 2.25 megawatts and a very narrow 0.3-degree beamwidth [SRC-0071]. ALCOR's extremely wide 500 MHz bandwidth allows it to provide fine range resolution, which is essential for measuring the length of objects and examining individual scattering centers [SRC-0071], [SRC-0071], [SRC-0071]. Because of this, its primary purpose involves ballistic missile discrimination and space-object identification [SRC-0071], [SRC-0071]. Notably, in 1971, ALCOR became the first radar to successfully use inverse synthetic aperture radar (ISAR) imaging techniques on orbiting satellites [SRC-0071], [SRC-0071]. The radar has seen multiple upgrades over its lifetime, including the installation of an extended-interaction klystron high-power amplifier in 1994, which increased its pulse-repetition frequency and enabled real-time coherent integration [SRC-0071], [SRC-0071]. In 1999, ALCOR was the first radar at the site to receive the Radar Open System Architecture (ROSA) modernization, which replaced legacy components with modern modular systems [SRC-0071]. ALCOR remains an active, state-of-the-art sensor today [SRC-0071].</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>RAD-0165</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>SITE-0173</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Mmw</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>The Millimeter-Wave (MMW) radar is an extremely high-resolution imaging radar located at the Reagan Test Site on Roi-Namur [SRC-0071], [SRC-0071], [SRC-0071]. Developed with Lincoln Laboratory acting as the prime contractor, the MMW radar began operations in 1983 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Originally designed as a dual-frequency system operating at 35 GHz (Ka-band) and 95.5 GHz (W-band), the 95.5 GHz capability was removed in the 1990s due to high atmospheric absorption and transmission losses [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Today, it operates strictly in the Ka-band using a 45-foot diameter antenna and generates 0.060 megawatts of peak transmit power [SRC-0071]. A standout feature is its exceptionally narrow beamwidth of 0.0435 degrees and its wide 4 GHz bandwidth, which provides a highly precise range resolution of approximately six centimeters [SRC-0071], [SRC-0113], [SRC-0113]. The primary purpose of the MMW radar is to collect high-fidelity signature databases on ballistic missiles, measure interceptor miss distances, and conduct detailed space-object identification [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. It is currently the highest-resolution imaging radar in the Space Surveillance Network and serves as the primary satellite-imaging sensor at the Reagan Test Site [SRC-0071], [SRC-0071], [SRC-0113]. The radar has undergone continuous technological improvements, including the adoption of an advanced quasi-optical beam-waveguide system, a new radome, and the Radar Open System Architecture (ROSA) upgrade in October 2000 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. In 2011, it became the first radar to utilize the new ROSA II technology, and it remains fully operational today [SRC-0071], [SRC-0071], [SRC-0071].</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0113</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>RAD-0166</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>SITE-0173</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Mps-36</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>The MPS-36 radars are a pair of skin and beacon-tracking radars located on Kwajalein Island, which is part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0151]. While the provided sources do not explicitly detail their original manufacturer, exact frequency band, or initial year built, they have long played a vital supporting role during test launches and space missions at the site [SRC-0071], [SRC-0151], [SRC-0151]. Their primary purpose is to provide highly accurate trajectory tracking of test vehicles, main rocket bodies, and scientific payloads [SRC-0071], [SRC-0151]. During missions such as the NASA Sporadic-E Electro Dynamics (SEED) sounding rocket launch, the two MPS-36 radars are utilized to track the rocket body and payload to measure and predict their trajectory from launch to impact in the broad ocean area, which is especially critical in the event of a loss of downlinked telemetry data [SRC-0151], [SRC-0151]. Like the larger KREMS radars located on Roi-Namur, the MPS-36 systems have undergone significant modernization to maintain their effectiveness and integration with the rest of the range. In 2004, the two MPS-36 radars received an upgrade utilizing the Radar Open System Architecture (ROSA) back-end technology, which automated the systems and integrated them into the centralized Kwajalein Mission Control Center [SRC-0071], [SRC-0071], [SRC-0071]. Today, both MPS-36 radars remain operational and continue to support critical data collection for Department of Defense and NASA missions [SRC-0071], [SRC-0151].</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>SRC-0071</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>SRC-0071, SRC-0151</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>RAD-0167</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>SITE-0170</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Multiple Object Tracking Radar 2 (Motr-2)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>The Multiple Object Tracking Radar 2 (MOTR-2) is a highly sophisticated phased-array tracking radar stationed at Cape Canaveral Space Force Station [SRC-0157, SRC-0114]. Manufactured in the mid-1980s at an initial cost of $36 million per unit, the MOTR system is exceedingly rare, with only five units ever built globally [SRC-0114, SRC-0114]. While the exact frequency band and manufacturer are not detailed in the sources, the system's design is well documented. Initially, the White Sands Missile Range was slated to receive the first three systems; however, following the tragic accident that claimed the Space Shuttle Challenger, the MOTR-2 unit was permanently diverted to Cape Canaveral [SRC-0157, SRC-0114]. The radar is engineered to transmit energy pulses through phase-shifting elements, using fractional wavelength delays to steer its beam off boresight [SRC-0114]. This allows the radar to effectively scan a 60-degree area and track the precise location of up to 40 airborne objects simultaneously, a significant capability upgrade over single-track legacy systems [SRC-0157, SRC-0114]. Returning signals are processed via a three-channel receiver architecture to produce highly accurate measurement data [SRC-0114]. The primary purpose of the MOTR-2 is to provide critical tracking and flight safety operations for launch vehicles and airborne systems on the range [SRC-0157, SRC-0114]. In its current status, it remains an active and invaluable tracking asset, with estimates suggesting that recreating a radar of this caliber today would cost $70 billion [SRC-0114].</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>SRC-0157</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>SRC-0157, SRC-0114</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>RAD-0168</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>SITE-0181</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>An-Gpn12 Surveillance Radar</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>At the Utah Test and Training Range (UTTR), the radar network includes the AN-GPN12 surveillance radar system, which is a critical component for monitoring the expansive airspace over the Great Salt Lake Desert [SRC-0106, SRC-0106]. The UTTR itself provides major range facilities for the test and evaluation of manned and unmanned aircraft systems, as well as tactical training for air-to-air and air-to-ground weapon delivery [SRC-0106]. The AN-GPN12 is integrated into the range's broader tracking network and is operated alongside two precision tracking radars [SRC-0106]. This surveillance radar is specifically provided, maintained, and operated by the 299th Communication Squadron, also known as Clover Control, which is a unit of the Utah Air National Guard [SRC-0106]. Radar information and time-space-position information from the UTTR network are linked via microwave to the Mission Control Center located at Hill Air Force Base, where the data is displayed on plotboards in real-time for test managers [SRC-0106, SRC-0106]. Additionally, the radar tracking data can be transmitted by microwave through the data acquisition and transmission system directly to Edwards Air Force Base to support joint testing and evaluation efforts [SRC-0106]. While the specific manufacturer, installation year, and frequency band of the AN-GPN12 are not detailed in the available sources, its primary capability and purpose are to provide robust airspace surveillance to ensure range safety and coordinate complex operational testing within the UTTR's restricted airspace [SRC-0106, SRC-0106]. The system is currently operational [SRC-0106].</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>RAD-0169</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>SITE-0181</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Precision Tracking Radars</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>In addition to surveillance capabilities, the Utah Test and Training Range (UTTR) operates a network featuring two precision tracking radars [SRC-0106]. These radars are essential for supporting the primary mission of the UTTR, which involves the comprehensive test and evaluation of manned and unmanned aerospace systems, cruise missiles, and conventional munitions [SRC-0106, SRC-0106]. Positioned to cover the vast airspace of the North and South Ranges, these tracking radars capture critical time-space-position information (TSPI) during flight tests [SRC-0106, SRC-0106]. The data collected by both precision tracking radars is transmitted in real-time via a dedicated microwave link to the Mission Control Center (MCC) situated at Hill Air Force Base [SRC-0106, SRC-0106]. At the MCC, the radar telemetry and TSPI data are displayed on large plotboards to allow range control personnel to monitor test vehicles dynamically [SRC-0106, SRC-0106]. Furthermore, the radar network is integrated with the broader Department of Defense test infrastructure, possessing the capability to send radar tracking information by microwave through a data acquisition and transmission system to Edwards Air Force Base [SRC-0106]. The available sources do not specify the exact manufacturer, operating frequency band, or year of installation for these two precision tracking radars [SRC-0106]. However, their current status is operational, and their main purpose is to function alongside the High Accuracy Multiple Object Tracking System (HAMOTS), cinetheodolites, and the AN-GPN12 surveillance radar to deliver highly accurate, real-time tracking data for tactical training and weapon delivery evaluations [SRC-0106, SRC-0106, SRC-0106].</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>RAD-0170</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>SITE-0188</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>An/Fps-132 Upgraded Early Warning Radar (Uewr)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Beale Air Force Base in California is a solid-state phased-array radar system operating in the Ultra High Frequency (UHF) band [SRC-0183, SRC-0190, SRC-0212]. Originally established in 1979 as an AN/FPS-115 PAVE Phased Array Warning System (PAVE PAWS), the radar was subsequently upgraded to the AN/FPS-123 Early Warning Radar, and finally modernized to the Raytheon-manufactured AN/FPS-132 UEWR configuration in 2005 [SRC-0190, SRC-0184, SRC-0184, SRC-0190, SRC-0212]. The radar features a two-panel configuration housed in a 10-story scanner building, with each fixed-orientation face providing 120 degrees of azimuth coverage, yielding a total 240-degree coverage arc oriented toward the Pacific Ocean [SRC-0190, SRC-0212, SRC-0190, SRC-0190]. The primary purpose of the Beale UEWR is to provide early warning of land-launched and sea-launched ballistic missile attacks, conduct target classification, and supply midcourse missile tracking data to cue other sensors and interceptors within the Ground-based Midcourse Defense (GMD) system [SRC-0190, SRC-0212]. It also performs a secondary space domain awareness mission, tracking satellites and space debris for the Space Surveillance Network [SRC-0183, SRC-0190, SRC-0212]. Because of its proximity to the Vandenberg Space Force Base interceptor site, the Beale UEWR serves as a primary demonstration platform for GMD test events [SRC-0212, SRC-0190]. Currently, the radar is fully operational under the 7th Space Warning Squadron of the U.S. Space Force and is scheduled for front-end and back-end digitization under the Ground Based Radar Digitization (GBRD) program, with Initial Operational Capability targeted for fiscal year 2030 [SRC-0190, SRC-0190, SRC-0190, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>SRC-0183</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>SRC-0183, SRC-0190, SRC-0212, SRC-0184</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>RAD-0171</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>SITE-0347</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>An/Fps-132 Uewr</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Cape Cod Space Force Station, Massachusetts, is a solid-state phased array radar system operating in the UHF band (420 to 450 MHz) [SRC-0133, SRC-0133, SRC-0190]. Originally built by Raytheon and activated in 1980 as a PAVE PAWS installation (AN/FPS-115), it received significant electronics and signal processor upgrades from Raytheon between 2013 and 2016 to reach its current UEWR configuration [SRC-0190, SRC-0184, SRC-0190]. The radar consists of two active array faces tilted at a 20-degree angle, with each face containing 1,792 active antenna elements out of a total 5,354 [SRC-0133, SRC-0133]. Together, the panels provide a 240-degree azimuth coverage across the Atlantic Ocean [SRC-0190, SRC-0133]. It operates at an average power of 152.5 kW and a peak output of 340 watts per active element [SRC-0133, SRC-0133]. The radar’s purpose is to provide early warning of intercontinental and sea-launched ballistic missile (ICBM and SLBM) attacks against North America, while its secondary mission involves tracking low-Earth orbit satellites and space debris for space domain awareness [SRC-0190, SRC-0133, SRC-0190]. Currently, the radar is fully operational under the 6th Space Warning Squadron and is scheduled to undergo front-end digitization as part of the Ground Based Radar Digitization (GBRD) program’s initial prototyping phase [SRC-0190, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>SRC-0133</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>SRC-0133, SRC-0190, SRC-0184</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>RAD-0172</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>SITE-0344</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>An/Fps-132 Uewr</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) located at Clear Space Force Station in Alaska is a solid-state phased array radar operating in the UHF frequency band [SRC-0001, SRC-0190, SRC-0190]. The site was originally established in 1961 as a Ballistic Missile Early Warning System (BMEWS) facility with mechanical radars before transitioning to a solid-state system in 1981 [SRC-0001, SRC-0190]. In 2012, Raytheon was contracted to upgrade the system to the AN/FPS-132 UEWR configuration, a modernization effort completed in Fiscal Year 2016 [SRC-0001, SRC-0190]. The system utilizes a two-panel array configuration housed in a specialized scanner building, providing a 240-degree coverage arc across the Arctic and Pacific regions [SRC-0190, SRC-0190, SRC-0008]. Its primary purpose is to deliver long-range early warning, precision tracking, and target classification of ballistic missile threats, as well as to support space surveillance operations for the Space Surveillance Network [SRC-0190, SRC-0093, SRC-0093]. Currently, the UEWR is fully operational and maintained by the 13th Space Warning Squadron [SRC-0190]. Looking forward, the radar is slated to receive comprehensive hardware and software upgrades, including aperture digitization, under the Space Force's Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>SRC-0001</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>SRC-0001, SRC-0190, SRC-0008, SRC-0093, SRC-0186</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>RAD-0173</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>SITE-0344</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Long Range Discrimination Radar (Lrdr / An/Fps-138)</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>The Long Range Discrimination Radar (LRDR), designated AN/FPS-138, at Clear Space Force Station is an advanced multi-face Active Electronically Scanned Array (AESA) radar operating in the S-band [SRC-0190, SRC-0005, SRC-0100, SRC-0190]. Manufactured by Lockheed Martin under a $784 million contract awarded in 2015, the radar achieved initial fielding in late 2021 and was officially accepted for operational use in December 2025 [SRC-0045, SRC-0181, SRC-0190]. The LRDR incorporates scalable Gallium Nitride (GaN) solid-state technology, featuring dual monostatic arrays that each measure 60 feet high by 60 feet wide [SRC-0190, SRC-0003, SRC-0100]. It was specifically designed to provide persistent, long-range midcourse discrimination, capable of simultaneously tracking multiple small objects and distinguishing lethal ballistic missile warheads from decoys, spent rocket bodies, and debris [SRC-0190, SRC-0045, SRC-0100]. By accurately filtering out non-lethal objects, it conserves the inventory of Ground-Based Interceptors [SRC-0190, SRC-0100]. The radar features an open systems architecture and a unique "maintain-while-operate" capability ensuring continuous 24/7 coverage [SRC-0100, SRC-0045]. Currently, the LRDR is fully operational for homeland defense and space domain awareness missions under the command of the U.S. Space Force Combat Forces Command, integrated directly with the Command and Control, Battle Management and Communications (C2BMC) network [SRC-0100, SRC-0190, SRC-0045, SRC-0045].</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0005, SRC-0100, SRC-0045, SRC-0181, SRC-0003</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>RAD-0174</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>SITE-0345</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>An/Fpq-16 Parcs</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>The AN/FPQ-16 Perimeter Acquisition Radar Attack Characterization System (PARCS) is a massive, single-faced, passive electronically scanned array (PESA) radar located at Cavalier Space Force Station in North Dakota [SRC-0008, SRC-0143, SRC-0190]. Operating in the UHF band (420–450 MHz), PARCS was manufactured by General Electric in the early 1970s as part of the U.S. Army's Safeguard anti-ballistic missile system [SRC-0008, SRC-0190, SRC-0132]. Following the decommissioning of the Safeguard program, the radar was transferred to the Air Force in 1976 [SRC-0008, SRC-0190]. The massive concrete installation generates a peak output of approximately 14.3 megawatts, directing a single north-facing beam that provides 140 degrees of azimuth coverage and 93 degrees of elevation coverage [SRC-0132, SRC-0190]. With a detection range of roughly 2,000 miles, its primary purpose is to detect and track incoming intercontinental and sea-launched ballistic missiles targeting North America [SRC-0008, SRC-0190, SRC-0132]. Its secondary mission is space surveillance, where it tracks more than half of all Earth-orbiting objects for the Space Surveillance Network [SRC-0143, SRC-0190, SRC-0008]. Currently, PARCS is fully operational under the 10th Space Warning Squadron, sustained by a multi-year contract with InDyne Inc., and is scheduled for a comprehensive front-end digitization overhaul under the Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>SRC-0008</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>SRC-0008, SRC-0143, SRC-0190, SRC-0132, SRC-0186</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>RAD-0175</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>SITE-0195</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Sea-Based X-Band Radar (Sbx-1)</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled Active Electronically Scanned Array (AESA) radar platform operating in the X-band frequency [SRC-0178, SRC-0178, SRC-0178]. Developed by Raytheon (radar) and Boeing (prime contractor) and deployed in 2006, the radar is mounted on a heavily modified fifth-generation CS-50 twin-hulled semi-submersible drilling rig [SRC-0178, SRC-0178, SRC-0178, SRC-0190]. The radar antenna weighs 1,800 tonnes and is protected by a flexible, positive-air-pressure radome measuring 103 feet high and 120 feet in diameter [SRC-0178, SRC-0179, SRC-0190]. It contains approximately 45,000 solid-state transmit-receive modules that can mechanically move ±270 degrees in azimuth and up to 85 degrees in elevation [SRC-0190, SRC-0178, SRC-0179]. The system's primary purpose is ballistic missile defense, specifically midcourse discrimination—identifying lethal enemy warheads from decoys—and providing precision tracking data to the Ground-Based Midcourse Defense (GMD) system [SRC-0190, SRC-0178, SRC-0179]. Its X-band wavelength provides extreme resolution, capable of tracking an object the size of a baseball from 2,500 to 2,900 miles away [SRC-0178, SRC-0190, SRC-0179]. Currently, SBX-1 is an active, operational asset managed by the Military Sealift Command; it received a new radome in December 2025 and routinely deploys in the Pacific Ocean to monitor missile threats [SRC-0129, SRC-0129, SRC-0190].</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>SRC-0178</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>SRC-0178, SRC-0190, SRC-0179, SRC-0129</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>RAD-0176</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>SITE-0196</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>An/Tpy-2</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>The AN/TPY-2 is a high-resolution, mobile Active Electronically Scanned Array (AESA) radar operating in the X-band (8.55–10 GHz) [SRC-0190, SRC-0011, SRC-0012]. Manufactured by Raytheon and initially introduced in 2007, the system consists of a trailer-mounted 9.2-square-meter antenna array utilizing thousands of solid-state transmit/receive modules [SRC-0011, SRC-0011, SRC-0183, SRC-0190]. Recently, Raytheon completed upgrades equipping the radar with Gallium Nitride (GaN) semiconductor technology, which significantly enhanced its search volume, sensitivity, and detection range [SRC-0190, SRC-0012, SRC-0158]. The AN/TPY-2 has a detection range exceeding 1,000 kilometers and provides 120-degree sector coverage while tracking hundreds of targets simultaneously [SRC-0190, SRC-0011, SRC-0011]. The radar serves a dual-purpose mission: in "Terminal Mode," it acts as the primary fire control radar for the Terminal High Altitude Area Defense (THAAD) system, guiding interceptors against descending warheads; in "Forward-Based Mode," it acts as a strategic early warning sensor deployed globally to detect ballistic missiles in their boost and early ascent phases [SRC-0190, SRC-0012]. Currently, the system is fully operational with deployments in regions such as Japan, South Korea, Israel, and the Middle East, and receives ongoing modernization and sustainment support under a recent $966 million contract modification [SRC-0011, SRC-0183, SRC-0190, SRC-0158].</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0011, SRC-0012, SRC-0183, SRC-0158</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>RAD-0177</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>SITE-0219</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Air Route Surveillance Radar (Arsr)</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>The former Calumet Air Force Station, located in Michigan, was historically utilized as a United States Air Force radar facility until its closure in 1988 [SRC-0110]. During its operational tenure, the facility served as a Continental United States (CONUS) station for the Air Route Surveillance Radar (ARSR) network, a system jointly operated by the Air Force and the Federal Aviation Administration to monitor internal and border airspace [SRC-0016], [SRC-0016]. While the exact ARSR variant stationed at Calumet is not detailed in the sources, the ARSR family consists of long-range 3D surveillance radars that operate in the L-band frequency (1.215–1.4 GHz) [SRC-0013], [SRC-0016]. These systems were manufactured by defense contractors such as Raytheon, Westinghouse, and Northrop Grumman, with the earliest models introduced in 1958 [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. They were designed with a look-down capability to detect low-flying aircraft attempting to elude detection, advanced clutter reduction processing, and an effective tracking range of 200 to 250 nautical miles [SRC-0013], [SRC-0016], [SRC-0016]. Following the end of its mission as a military radar facility, the Calumet site was repurposed as a youth correctional facility from 1998 to 2004, and the land has remained vacant and unused since 2004 [SRC-0110].</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>SRC-0110</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>SRC-0110, SRC-0016, SRC-0013</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>RAD-0178</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>SITE-0216</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Air Route Surveillance Radar (Arsr)</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>The Tonopah Test Range in Nevada operates as a Continental United States (CONUS) station within the Air Route Surveillance Radar (ARSR) network, a long-range radar system utilized jointly by the United States Air Force and the Federal Aviation Administration to control and monitor airspace within and around U.S. borders [SRC-0016], [SRC-0016]. Although the exact ARSR model installed at Tonopah is unspecified in the provided documentation, ARSR systems universally operate in the L-band frequency range (1.215–1.4 GHz) as long-range, three-dimensional air surveillance radars [SRC-0013], [SRC-0016]. Primary manufacturers of the ARSR series include Raytheon, Westinghouse, and Northrop Grumman, with the system's first generation introduced in 1958 [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. The radars generally provide an effective target detection range between 200 and 250 nautical miles, utilizing hardware and software post-processing to reduce clutter and detect low-flying targets [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. In addition to its role in the ARSR network, the Tonopah Test Range features a dedicated Electronic Combat (EC) Range [SRC-0106]. This EC range is specifically designed to provide a realistic, simulated enemy radar environment to support the training of aircrews in electronic warfare, although the exact designations of the hostile threat radars simulated at this location are not detailed [SRC-0106].</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>SRC-0016</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>SRC-0016, SRC-0013, SRC-0106</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>RAD-0179</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>SITE-0224</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>L-88(V)3 Radar</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>The L-88(V)3 radar is an airborne ground surveillance radar operating as the primary payload for the Tethered Aerostat Radar System (TARS) at Cudjoe Key, Florida [SRC-0190, SRC-0197]. Manufactured by Lockheed Martin, the L-88(V)3 is a lightweight derivative of the standard L-88 radar, specifically operating in the L-band frequency [SRC-0190, SRC-0197]. The first aerostats were assigned to the United States Air Force at Cudjoe Key in December 1980, though Lockheed Martin was awarded subsequent contracts (such as in 2002) to provide the upgraded L-88(V)3 radar systems for the TARS network [SRC-0197, SRC-0098]. The radar is mounted beneath a 275,000-cubic-foot (275K) Lockheed Martin blimp tethered at high altitudes (up to 15,000 feet) and enclosed by a fabric windscreen [SRC-0197, SRC-0197]. The radar utilizes a rotating antenna to provide 360-degree coverage at maximum detection ranges of up to 200 nautical miles (370 kilometers) [SRC-0190, SRC-0098, SRC-0197]. The primary purpose of the radar is to conduct low-level surveillance across the Straits of Florida and the Caribbean, functioning as an anti-drug smuggling and air sovereignty asset capable of tracking low-flying aircraft and surface vessels [SRC-0196, SRC-0197]. Currently, the system remains in active service and is operated by the U.S. Customs and Border Protection (CBP) agency, continuously feeding track data to the Air and Marine Operations Center [SRC-0197, SRC-0196, SRC-0197].</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>SRC-0190</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>SRC-0190, SRC-0197, SRC-0098, SRC-0196</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>RAD-0180</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>SITE-0225</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>L-88 Radar</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>The L-88 radar is a downward-looking, airborne ground surveillance system deployed at the Tethered Aerostat Radar System (TARS) site in Deming, New Mexico [SRC-0197, SRC-0098, SRC-0197]. Built and integrated by Lockheed Martin, the radar operates in the L-band frequency and features a 29-foot rotating antenna enclosed in a protective aerodynamic radome windscreen [SRC-0190, SRC-0098]. Following a 1999 modernization contract from the U.S. Air Force, the Deming TARS installation was successfully upgraded and transitioned to the standard 420K/L-88 configuration [SRC-0098]. Designed to be lofted to an operational altitude of 15,000 feet by a massive 420,000-cubic-foot helium-filled aerostat, the radar provides uninterrupted, 360-degree coverage over a 200-nautical-mile radius [SRC-0190, SRC-0197, SRC-0098]. The L-88's core purpose is to support North American Aerospace Defense Command (NORAD) and federal law enforcement by detecting and tracking low-altitude, low-observable threats such as drug-smuggling aircraft, ultra-lights, and drones crossing the United States-Mexico border [SRC-0196, SRC-0197]. Despite its robust design and capability to withstand severe weather, the current operational status of the Deming aerostat radar site is listed as "Not Flying" [SRC-0197]. The broader TARS program, however, remains actively funded and operated under the jurisdiction of U.S. Customs and Border Protection (CBP) [SRC-0197].</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>SRC-0197</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>SRC-0197, SRC-0098, SRC-0190, SRC-0196</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>RAD-0181</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>SITE-0336</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Metric Tracking Radars</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>The Kennedy Space Center (KSC) in Florida, operating in conjunction with the Cape Canaveral Air Force Station and Patrick Air Force Base as part of the Eastern Space and Missile Center, utilizes a network of metric tracking radars [SRC-0106], [SRC-0106], [SRC-0189]. While the exact manufacturer, operating frequency bands, and specific years of construction for the individual radar units physically situated at KSC are not fully detailed in the provided sources, these precision tracking systems are fundamental to the Eastern Range's launch operations [SRC-0106], [SRC-0106]. The primary purpose of these metric radars is to provide highly accurate, real-time trajectory and positioning data to central computer systems during the prelaunch, launch, and postlaunch phases of test vehicles [SRC-0106], [SRC-0106].
+These radar systems are highly capable, configured for either beacon tracking or echo tracking, which allows them to reliably monitor rockets, space boosters, and space shuttles as they ascend [SRC-0106], [SRC-0162]. The data generated by these radars is critical for range safety, enabling flight safety officers to monitor the vehicle's flight path, predict impact points, and ensure the launch remains within safe operational corridors [SRC-0118], [SRC-0118]. Currently, these metric tracking radars remain an active, integral component of the Eastern Range's instrumentation, working alongside telemetry and optical systems to support military, civilian, and commercial missions [SRC-0106], [SRC-0189], [SRC-0189].</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>SRC-0106, SRC-0189, SRC-0162, SRC-0118</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>RAD-0182</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SITE-0337</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Wallops Island (Nasa) Radar</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>The Wallops Flight Facility, operated by NASA in Virginia, features an on-site radar system dedicated to supporting the facility's aerospace testing missions [SRC-0106], [SRC-0154], [SRC-0154]. While the specific technical parameters of this radar—such as its exact hardware type, frequency band, manufacturer, and year of construction—are not detailed in the provided sources, its presence is documented as part of the Eastern Test Range's broader tracking and instrumentation network [SRC-0106]. The primary purpose of the radar infrastructure at Wallops Island is to provide crucial flight tracking and range safety data for the rockets, sounding rockets, and suborbital missions launched from the site [SRC-0106]. 
+Although the on-site radar's specific capabilities are not exhaustively described, the launch activities at Wallops Flight Facility are frequently supported and monitored by highly advanced external radar systems. For instance, the Long Range Discrimination Radar (LRDR) and its scaled Solid State Radar Integration Site (SSRIS) prototype in Moorestown, New Jersey, have actively tracked space launches originating from NASA's Wallops Island to test and verify their own tracking software [SRC-0003], [SRC-0100]. During these exercises, the external phased-array systems successfully demonstrated their ability to acquire and track Wallops-launched rockets, highlighting the facility's active, ongoing status as a key launch site within the United States' space testing infrastructure [SRC-0100].</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>SRC-0106</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>SRC-0106, SRC-0154, SRC-0003, SRC-0100</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>RAD-0183</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>SITE-0340</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Mobile Multi-Sensor Tspi System (Mmts) Radar</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>The Mobile Multi-Sensor Time-Space-Position-Information-System (MMTS) is a specialized tracking system delivered to and integrated into Redstone Arsenal via the TENA network architecture [SRC-0085]. Manufactured by Photo-Sonics, Inc., under a contract awarded by the U.S. Army Program Executive Office for Simulation, Training, and Instrumentation (PEO STRI), this mobile platform incorporates both high-performance optical tracking pedestals and a radar unit that functions as a comprehensive single-station solution [SRC-0085]. While the specific frequency band and exact year of construction for the radar component are not detailed in the sources, the system's primary purpose is to track and provide highly accurate Time-Space-Position-Information (TSPI) for high-speed weapons, including hyper-velocity projectiles [SRC-0085].
+The MMTS radar system boasts advanced capabilities such as a high-speed auto tracker capable of capturing 250 frames per second, high dynamics, and fully integrated pedestal and sensor control software [SRC-0085]. It also features automated stellar and turn-and-dump calibration, alongside a simulation system and a range interface computer designed to calculate real-time three-dimensional data [SRC-0085]. Integrated data-reduction software further enables six degrees of freedom calculations [SRC-0085]. Before its final delivery to the Redstone facility, the MMTS successfully completed functional testing and its Final Site Acceptance Test at the White Sands Missile Range, proving its current operational readiness [SRC-0085].</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>SRC-0085</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>SRC-0085</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>RAD-0184</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>SITE-0353</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Sea-Based X-Band Radar (Sbx-1)</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>The Sea-Based X-Band Radar (SBX-1) is nominally assigned to Adak Island, Alaska, as its official homeport, although the radar has never actually moored or deployed there despite the installation of a $26 million mooring chain system [SRC-0179, SRC-0179, SRC-0179, SRC-0179]. Developed by Raytheon and Boeing, the SBX-1 was deployed in 2006 as a floating, mobile active electronically scanned array (AESA) early-warning radar [SRC-0179, SRC-0178, SRC-0178]. It operates in the X-band, providing high-resolution tracking capabilities that allow it to differentiate lethal warheads from decoys during the midcourse phase of a ballistic missile's flight [SRC-0178, SRC-0179]. The massive 384-square-meter antenna is mounted on a semi-submersible platform and currently houses 22,000 solid-state transmit-receive modules, though it has the capacity for 45,000 [SRC-0179, SRC-0179, SRC-0179]. The radar is incredibly powerful, with the ability to track baseball-sized objects from 2,900 miles away [SRC-0179]. Its primary purpose at its intended Adak base was to track missile threats launched toward the United States from North Korea and China [SRC-0179]. However, in practice, the SBX-1 roams the Pacific Ocean to monitor missile tests and relies on Pearl Harbor, Hawaii, for its maintenance and port stays [SRC-0179, SRC-0179, SRC-0179].</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>SRC-0179</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>SRC-0179, SRC-0178</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>RAD-0185</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>SITE-0362</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>An/Tpy-2</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>See description</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>The AN/TPY-2 is a transportable, high-resolution, X-band active electronically scanned array (AESA) radar manufactured by Raytheon [SRC-0011, SRC-0012]. Introduced in 2007, this system is a primary component of the U.S. military's layered ballistic missile defense network, notably serving as the radar for the THAAD system [SRC-0012, SRC-0011, SRC-0011]. It operates in the X-band frequency (8.55–10 GHz), which provides a shorter wavelength and finer resolution necessary to differentiate between hostile warheads, clutter, and decoys during the midcourse and terminal phases of a ballistic missile's flight [SRC-0011, SRC-0012]. The radar has a detection range of over 1,000 kilometers and is capable of simultaneously tracking hundreds of targets [SRC-0011, SRC-0011, SRC-0011]. Featuring electronic beam steering, the AN/TPY-2 provides exceptional target discrimination and near-instantaneous updates [SRC-0011, SRC-0011]. The system is highly mobile and trailer-mounted, requiring only a small crew to operate [SRC-0011]. An AN/TPY-2 radar has been deployed to the Shariki region in Japan. Its primary purpose at this forward-based location is to collect strategic-level early warning information on North Korean missile developments, warn Japan of incoming warheads, and scan Russian territory near Japan [SRC-0012]. The radar seamlessly integrates with U.S. and allied missile defense networks, passing critical trajectory data to downstream fire control systems [SRC-0011, SRC-0012].</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>SRC-0011</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>SRC-0011, SRC-0012</t>
         </is>
       </c>
     </row>

--- a/data/us_missile_range_data.xlsx
+++ b/data/us_missile_range_data.xlsx
@@ -780,9 +780,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>The **Shaba North, Kapani Tonneo OTRAG Launch Center** was a rocket launch facility located in Zaire (the modern-day Democratic Republic of the Congo) [SRC-0095]. Geographically situated at coordinates 7°55′33″S 28°31′40″E, the launch site was established and became operational in the mid-1970s [SRC-0095].
-The Kapani Tonneo facility was primarily utilized for the testing and launching of German OTRAG rockets [SRC-0095]. During its active operational period, which spanned from 1975 to 1979, the site hosted a total of three rocket launches [SRC-0095, SRC-0095]. These test flights were strictly suborbital, with the launched rockets achieving a maximum altitude of less than 50 kilometers above the launch site [SRC-0095]. 
-Following this initial phase of testing, the OTRAG launch site in Zaire was officially closed [SRC-0095]. Consequently, the testing of the German OTRAG rockets was relocated to a new facility in North Africa [SRC-0095]. Subsequent launch operations were moved to the Sabha, Tawiwa OTRAG Launch Center in Libya, which took over the rocket testing activities from 1981 to 1987 [SRC-0095]. Beyond these basic operational parameters and flight records, the provided sources do not contain further detailed information regarding the site's governing organization, specific radar and telemetry installations, or its ongoing physical status after its closure in the late 1970s [SRC-0095, SRC-0095, SRC-0095].</t>
+          <t>A launch center used between 1975 and 1979 for testing German OTRAG rockets. The site achieved suborbital altitudes before operations were moved to Libya.</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -798,11 +796,6 @@
       <c r="V4" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>SRC-0095</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1064,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Pampa de Achala is a rocket launch site located in Argentina at the geographical coordinates of 31°35′00″S 64°50′00″W [SRC-0096]. It holds historical significance as the very first rocket launch site established in Argentina [SRC-0096]. The facility was operational for a brief period between 1961 and 1962 [SRC-0096]. During its active years, Pampa de Achala hosted a total of eight rocket launches [SRC-0096]. The rockets launched from this location were relatively small in scale; the heaviest rocket recorded had a total mass of 28 kilograms, and the highest altitude achieved by a launch from this site was 25 kilometers [SRC-0096]. While detailed records of the governing organization and broader history are not provided in the sources, its status as the nation's inaugural launch site marks its importance in Argentine aerospace history.</t>
+          <t>First Argentine launch site, operated from 1961 to 1962.</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1087,11 +1080,6 @@
       <c r="V8" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1206,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>Las Palmas is an Argentine rocket launch facility situated at the coordinates 27°05′43″S 58°45′13″W [SRC-0096]. The operational history of the site was extremely brief, with all known launch activities taking place entirely in the year 1966 [SRC-0096]. Las Palmas is notable for being used to conduct rocket launches specifically during a solar eclipse [SRC-0096]. During this time, the site hosted a total of two launches utilizing Titus rockets [SRC-0096]. These missions featured significantly larger vehicles than Argentina's earliest rocket tests, with the heaviest rocket launched from Las Palmas weighing 3,400 kilograms [SRC-0096]. The flights were successful in reaching the upper atmosphere, achieving a maximum altitude of 270 kilometers [SRC-0096].</t>
+          <t>Used in 1966 for Titus rocket launches during a solar eclipse.</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1234,11 +1222,6 @@
       <c r="V10" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1272,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>Tartagal is a rocket launch site located in Argentina at the geographical coordinates 22°45′42″S 63°49′26″W [SRC-0096]. Similar to the Las Palmas site, Tartagal's operational activities were strictly confined to the year 1966 [SRC-0096]. The facility was utilized to conduct launch operations specifically coinciding with a solar eclipse [SRC-0096]. The available sources do not provide further detailed information regarding the exact number of launches conducted, the types or mass of the rockets used, the specific governing organization, or the maximum altitude achieved by the missions launched from this location [SRC-0096].</t>
+          <t>Hosted sounding rocket launches during a 1966 solar eclipse.</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1305,11 +1288,6 @@
       <c r="V11" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1338,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>Mar Chiquita served as a rocket launch facility in Argentina, positioned at the coordinates 37°43′27″S 57°24′18″W [SRC-0096]. The site maintained an operational status over a span of five years, from 1968 until 1972 [SRC-0096]. Throughout its period of activity, Mar Chiquita was the site of 11 rocket launches [SRC-0096]. The provided sources do not contain further detailed information such as the founding organization, the specific models or masses of the rockets launched, or the highest altitude reached by missions originating from this site [SRC-0096].</t>
+          <t>Rocket launch site active from 1968 to 1972.</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1376,11 +1354,6 @@
       <c r="V12" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1431,7 +1404,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>Villa Reynolds is a rocket launch site located in Argentina at the coordinates 33°43′29″S 65°22′38″W [SRC-0096]. The facility had a very short operational history, with its launch activity recorded solely in the year 1973 [SRC-0096]. During its operational window, the site hosted a total of two rocket launches [SRC-0096]. Additional detailed information, including the types of rockets tested, their payload mass, the apogees achieved during flight, or the specific governing organization overseeing the launches, is not available in the provided sources [SRC-0096].</t>
+          <t>Hosted a pair of rocket launches in 1973.</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1447,11 +1420,6 @@
       <c r="V13" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1470,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>Serrezuela is an Argentine rocket launch site situated at the geographical coordinates 30°38′00″S 65°23′00″W [SRC-0096]. Unlike Argentina's older sounding rocket ranges from the 1960s and 1970s, Serrezuela was active in the 21st century, specifically in the year 2009 [SRC-0096]. The site was utilized to conduct a military test of the Gradicom I rocket, marking its sole recorded launch [SRC-0096]. The rocket fired from the Serrezuela facility had a mass of 500 kilograms and successfully reached an altitude of 40 kilometers [SRC-0096]. Further details regarding the site's ongoing status or additional facilities are not documented in the sources.</t>
+          <t>Conducted the Gradicom I military rocket test in 2009.</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1518,11 +1486,6 @@
       <c r="V14" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -2171,9 +2134,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>Southend is a Canadian rocket launch site located in the province of Saskatchewan, specifically positioned at the geographical coordinates of 56°12′N 103°08′W [SRC-0096]. While the provided sources do not offer a comprehensive history, specific founding year, or information regarding the governing organization that managed the facility, they do confirm that the Southend site was active and operational during the year 1980 [SRC-0096]. Over the course of its operational history, the site is recorded to have hosted a total of two rocket launches [SRC-0096].
-In terms of technical capabilities and launch milestones, the heaviest rocket launched from the Southend facility had a total lift-off mass of 1,200 kg [SRC-0096]. Furthermore, operations at the site were capable of reaching into the upper atmosphere and suborbital space, with the highest achieved altitude recorded at 156 kilometers above the launch site [SRC-0096]. The site is also documented in aerospace reference materials, such as Mark Wade's Encyclopedia Astronautica [SRC-0096]. 
-The available source material does not contain further detailed information regarding the presence of specific key facilities, tracking radars, ground support infrastructure, or notable mission designations. Additionally, the current operational status of the Southend launch site is not described in the provided texts.</t>
+          <t>Saskatchewan launch site that hosted sounding rockets in 1980.</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2189,11 +2150,6 @@
       <c r="V23" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2744,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>Pampa de Tamarugal is a geographic region in Chile that has served as a critical testing ground for the country's military and aerospace developments, operating primarily under the auspices of the state-owned defense enterprise Fábricas y Maestranzas del Ejército (FAMAE) [SRC-0058], [SRC-0221]. Following the restoration of democratic governance in Chile in 1990, the site became instrumental in advancing the nation's indigenous missile and rocket capabilities [SRC-0058]. Notably, in 1991, Pampa de Tamarugal hosted the successful test-firing of the Proyecto Rayo tactical rocket [SRC-0058]. This unguided earth-to-earth multiple launch rocket system (MLRS), developed in a strategic partnership with the British firm Royal Ordnance, was launched from a fixed platform at the site [SRC-0058], [SRC-0058], [SRC-0221]. The Rayo rocket featured a 160 mm caliber and a maximum effective range exceeding 45 kilometers, originally designed to demonstrate the technological capabilities of the emerging Chilean arms industry and to appeal to export markets during the Cold War era [SRC-0058], [SRC-0058], [SRC-0059]. While the Rayo project was ultimately canceled from a commercial standpoint in 2002 due to shifts in global arms markets and a modern preference for precision-guided munitions, the tests conducted at Pampa de Tamarugal laid the foundational technology for future artillery systems [SRC-0059], [SRC-0059]. Today, the technological legacy of the test launches at Pampa de Tamarugal lives on in the modern FAMAE SLM (Sistema de Lanzamiento Múltiple) system, which adapted the subsystems and technologies proven at the site to create a highly versatile 160 mm and 306 mm rocket launcher platform [SRC-0059], [SRC-0059].</t>
+          <t>Used as a fixed platform site for testing the Rayo tactical rocket in 1991.</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -2804,11 +2760,6 @@
       <c r="V32" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>SRC-0058, SRC-0221, SRC-0059</t>
         </is>
       </c>
     </row>
@@ -2864,7 +2815,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>Peldehue is a prominent military field and weapons testing facility in Chile, utilized heavily by Fábricas y Maestranzas del Ejército (FAMAE) for the development and validation of national defense technologies [SRC-0058], [SRC-0058]. The site's historical significance is deeply tied to Chile's push for military self-sufficiency during the 1970s. Following the 1976 United States arms embargo imposed via the Kennedy Amendment, which restricted foreign military supplies due to human rights concerns under the military regime, FAMAE was forced to drastically intensify its domestic manufacturing efforts [SRC-0058], [SRC-0058]. In 1976, the Peldehue facility achieved a major milestone when it hosted the first successful test firing of a domestically produced 105 mm artillery projectile [SRC-0058], [SRC-0058]. This event marked Chile's transition toward a more comprehensive defense industrial base, significantly reducing its reliance on foreign imports for munitions and heavy weapons [SRC-0058]. In the modern era, Peldehue remains an active and vital proving ground for the Chilean Armed Forces. It is currently utilized for testing advanced artillery and rocket systems, most notably the FAMAE SLM (Sistema de Lanzamiento Múltiple) [SRC-0221]. The SLM is a highly capable multiple rocket launcher system mounted on a MAN 6x6 truck chassis, developed in collaboration with Israel Military Industries (IMI) and the Chilean firm DESA [SRC-0059], [SRC-0221]. At Peldehue, military engineers conduct tests on the SLM's ability to fire advanced munitions, including 160 mm Accular rockets and 306 mm EXTRA rockets, ensuring the operational readiness and technological sovereignty of Chile's modern artillery units [SRC-0059], [SRC-0059], [SRC-0221].</t>
+          <t>Military field used since the 1970s for testing artillery, rockets, and munitions.</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -2880,11 +2831,6 @@
       <c r="V33" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>SRC-0058, SRC-0221, SRC-0059</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2886,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>Arica, located in northern Chile, serves as a strategic military testing site and operational area for the Chilean Armed Forces and the state-owned defense manufacturer Fábricas y Maestranzas del Ejército (FAMAE) [SRC-0039], [SRC-0221]. The military ranges in the area are utilized for conducting functional field tests and evaluating the performance of newly developed indigenous weaponry [SRC-0039], [SRC-0221]. Recently, Arica was the focal point for the testing of the Oton MK40, a new 70 mm air-to-ground rocket developed entirely in Chile [SRC-0039], [SRC-0039]. During these trials, the Chilean Army's Artillery Group No. 6 "Dolores," part of the 4th Motorized Brigade "Rancagua," provided essential logistical and operational support to FAMAE engineers [SRC-0039]. To thoroughly evaluate the weapon, the artillery group deployed a specialized observation patrol to monitor key performance parameters, including the rocket's range, dispersion, and overall reliability in realistic combat scenarios [SRC-0039]. The Oton MK40, which features a double-base extruded powder propellant and folding fins, is specifically designed for deployment from helicopters and low-speed aircraft to provide close air support and conduct armed reconnaissance [SRC-0039], [SRC-0039]. The successful execution of these tests at the Arica military ranges is a crucial step in validating the armament for active duty [SRC-0039]. By utilizing the Arica facilities for such evaluations, Chile continues to strengthen its strategic autonomy and technological independence, avoiding reliance on foreign suppliers and cementing FAMAE's position as a highly capable and advanced defense industry actor within the Latin American region [SRC-0039], [SRC-0039].</t>
+          <t>Testing location for the Oton MK40 70mm air-to-ground rocket.</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -2956,11 +2902,6 @@
       <c r="V34" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>SRC-0039, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -3671,9 +3612,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>The Dashuli Tracking Station is a crucial telemetry, tracking, and command (TT&amp;C) facility located 36 kilometers southwest of the South Launch Site at the Jiuquan Satellite Launch Centre in China [SRC-0084]. Originally constructed in 1968 to support early missile testing, the station has progressively evolved into the primary nerve center for Jiuquan's tracking and communication network, managing multiple optical and radar tracking posts distributed across the launch center [SRC-0084].
-The station plays a vital role during the initial phases of a rocket launch. It is responsible for tracking launch vehicles from the moment of take-off until approximately 500 seconds into the flight [SRC-0084]. To accomplish this, Dashuli utilizes an array of advanced equipment, including optical tracking telescopes, precision tracking radars, and telemetry antennas designed to receive critical measurement data from the launch vehicle's onboard systems [SRC-0084].
-Dashuli's infrastructure is comprehensive, comprising several integrated sub-systems dedicated to radar, optical tracking, communications, computer processing, meteorology, and technical and logistical support [SRC-0084]. The operational heart of the station is its control hall, which is equipped with over 30 control consoles [SRC-0084]. These consoles display 120 sets of real-time data that indicate the launch vehicle's trajectory and the live operational status of both the rocket and its payload [SRC-0084]. All gathered telemetry and tracking data are transmitted in real-time to the Mission Command and Control Centre (MCCC) at the Jiuquan headquarters to support critical decision-making during the launch process [SRC-0084].</t>
+          <t>Nerve center of Jiuquan's telemetry, tracking, and command network providing radar and optical tracking for launch vehicles.</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
@@ -3689,11 +3628,6 @@
       <c r="V44" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>SRC-0084</t>
         </is>
       </c>
     </row>
@@ -3749,9 +3683,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>The Xi'an Satellite Control Center (XSCC) is the primary command hub of China's satellite control network, managing the tracking, telemetry, control, and recovery of domestic and international spacecraft [SRC-0040, SRC-0040, SRC-0222]. Established as a cornerstone of China's aerospace capabilities, the XSCC is equipped to automatically develop real-time plans and simultaneously execute control over multiple satellites, with the historic capacity to handle up to six satellites at once [SRC-0040]. 
-The XSCC's technological infrastructure features a robust Central Computer System originally composed of NC12780 and VAX8700 computers interconnected via an Ethernet network known as the "Xin Xing He Qi" [SRC-0040]. This system provides high reliability and powerful processing capabilities to run multiple satellite control software programs simultaneously [SRC-0040]. A comprehensive monitoring display system provides operational staff with interactive tables and images detailing orbital flight information and crucial spacecraft engineering parameters [SRC-0040, SRC-0040].
-Software at the XSCC is divided into specialized categories for near-earth satellite tracking (including satellite recovery) and geostationary satellite tracking [SRC-0040, SRC-0040]. These systems manage telemetry processing, instruction generation, orbital determination and prediction, attitude control, and simulated maneuvers [SRC-0040]. The center also coordinates a network of five fixed near-earth tracking stations and specialized geostationary stations [SRC-0040, SRC-0040]. For geostationary missions, the XSCC operates in tandem with the Xiamen and Weinan control stations to manage spacecraft up to 40,000 kilometers in altitude [SRC-0040, SRC-0040]. In addition to its domestic operations, the XSCC houses an international satellite communication ground station that connects directly to the INTELSAT network, providing user-leased circuits to support the launch and control of overseas satellites [SRC-0040, SRC-0040].</t>
+          <t>Central hub for China's satellite control network managing near-earth and geostationary orbital satellites.</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -3767,11 +3699,6 @@
       <c r="V45" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>SRC-0040, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -3827,9 +3754,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>The Changchun Station is a tracking and telemetry facility that forms an integral part of China's near-earth satellite control network [SRC-0040]. Located in the eastern part of China, it operates as one of the country's five fixed near-earth satellite control stations, working in conjunction with sister stations located in Xiamen, Nanning, Weinan, and Kash [SRC-0040, SRC-0040].
-The primary operational mandate of the Changchun Station is to perform daily tracking, telemetry, and control over medium- and low-orbiting satellites [SRC-0040]. By cooperating seamlessly with the other fixed stations and the central Xi'an Satellite Control Center (XSCC), the Changchun facility helps ensure continuous monitoring and communication coverage for spacecraft passing through its designated geographic sector [SRC-0040, SRC-0040].
-Like other fixed stations in the network, the Changchun Station utilizes integrated systems to capture satellite telemetry, process tracking data, and transmit remote control instructions [SRC-0040, SRC-0040]. While specific equipment details for the Changchun site are limited in the available sources, stations within this near-earth network generally employ VHF/UHF control systems, precision tracking radars, and station computers that conduct preprocessing of orbit measurement data [SRC-0040, SRC-0040, SRC-0040]. This data is then exchanged with the Xi'an Satellite Control Center to facilitate real-time guidance, orbital analysis, and overall mission success [SRC-0040].</t>
+          <t>Fixed near-earth satellite control station located in eastern China.</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -3845,11 +3770,6 @@
       <c r="V46" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -3905,9 +3825,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>The Xiamen Station is a major dual-purpose telemetry, tracking, and control facility within the China Aerospace Control Network, operating out of eastern China [SRC-0040, SRC-0040]. It serves as one of the five fixed near-earth satellite control stations, conducting daily tracking and control for medium- and low-orbiting satellites [SRC-0040, SRC-0040]. Additionally, the Xiamen Station plays a vital role in China's Geostationary Orbital Satellite Control Network [SRC-0040].
-During launch operations, the Xiamen Station is responsible for tracking carrier rockets and managing perigee control missions for near-earth orbital satellites [SRC-0040]. For high-orbit missions, the station is equipped with unified C-band carrier wave control systems [SRC-0040]. Working in conjunction with onboard satellite transponders, this system enables the Xiamen Station to perform critical tracking orbit measurements (including distance, azimuth, and pitch angle), telemetry reception, and remote control over geostationary satellites operating at altitudes of up to 40,000 kilometers [SRC-0040, SRC-0040].
-To manage its complex responsibilities, the Xiamen Station utilizes a duplex computer operation system [SRC-0040]. This dual-computer setup allows the station to seamlessly process data, exchange information with the Xi'an Satellite Control Center, and execute attitude and orbit control over geostationary satellites [SRC-0040]. Furthermore, during mission preparation phases, the dual-computer architecture is utilized to conduct simulated satellite-to-earth reentry maneuvers, allowing one computer to simulate powered flight while the other operates as the live combat computer [SRC-0040, SRC-0040].</t>
+          <t>Fixed station undertaking geostationary orbital satellite tracking, launch coverage, and daily control.</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
@@ -3923,11 +3841,6 @@
       <c r="V47" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -3983,8 +3896,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>Nanning Station is a critical component of the China Aerospace Control Network, specifically operating as one of the five fixed near-earth satellite control stations deployed across the eastern, central, and western parts of China [SRC-0040]. As a primary tracking and control facility, Nanning Station is designed to cooperatively perform daily tracking and control operations for medium- and low-orbiting satellites [SRC-0040]. In addition to its standard near-earth responsibilities, the Nanning Station fulfills specialized roles during complex launch missions. It is specifically responsible for conducting carrier rocket flight coverage tracking measurements during the launch of geostationary satellites [SRC-0040]. Furthermore, the station is tasked with perigee control missions during near-earth orbital satellite launches [SRC-0040].
-To execute these missions, Nanning Station is equipped with a comprehensive suite of advanced tracking and communication technologies utilized across China's fixed network. This includes a VHF/UHF control system that features both dispersed and unified carrier-wave systems [SRC-0040]. The dispersed system utilizes a double-frequency velocimeter alongside a telemetry demodulation terminal to receive satellite telemetry signals, while independent remote control equipment manages ground-to-satellite instruction control and data insertion [SRC-0040], [SRC-0040]. The unified carrier-wave system employs a single antenna for both transmission and reception, adding essential distance and angle measurement capabilities [SRC-0040]. The station also relies on C-band monopulse precision tracking radars, which provide high precision and the ability to locate orbits with data, making them ideal for measuring satellite perigee periods and reentry orbits [SRC-0040], [SRC-0040]. Additionally, the facility utilizes integrated station computers and monitoring display systems to preprocess orbital measurement data, execute digital guidance, and conduct data exchange with the Xi'an Satellite Control Center [SRC-0040].</t>
+          <t>Fixed station providing carrier rocket flight coverage tracking and near-earth perigee control.</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
@@ -4000,11 +3912,6 @@
       <c r="V48" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4060,8 +3967,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>Weinan Station, located in central China, is a major fixed tracking and control facility within the China Aerospace Control Network [SRC-0040], [SRC-0040]. It serves a dual operational role, functioning both as a near-earth satellite control station and as a key node in the geostationary orbital satellite launch and control network [SRC-0040], [SRC-0040]. For its near-earth mission, Weinan cooperates with other fixed stations to perform daily tracking and control over medium- and low-orbiting satellites [SRC-0040]. However, its capabilities are notably expanded to undertake highly specialized missions involving geostationary orbital satellite launches and their long-term daily control [SRC-0040], [SRC-0040].
-As part of the geostationary control network, the Weinan Control Station is uniquely equipped with unified C-band carrier wave control systems [SRC-0040], [SRC-0040]. Working in conjunction with in-satellite transponders, this system performs tracking orbit measurements (including distance, azimuth, and pitch angle), telemetry (coding and simulation), and remote control (instruction and synchronous control) over high-orbiting satellites up to 40,000 kilometers in altitude [SRC-0040]. To manage these complex tasks, the Weinan station utilizes two computers operating in a duplex configuration [SRC-0040]. This dual-computer setup handles data processing, data exchange with the main satellite control center, attitude and orbit control, and the long-term supervision of geostationary satellites [SRC-0040]. During mission preparation periods, such as when carrying out satellite-to-earth reentry route simulating maneuver tests, one of these computers is dedicated to satellite powered simulation, while the other serves as the actual combat computer [SRC-0040], [SRC-0040].</t>
+          <t>Fixed station conducting tracking and telemetry for both near-earth and high-orbiting geostationary satellites.</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
@@ -4077,11 +3983,6 @@
       <c r="V49" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4137,8 +4038,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>Kashgar Station, referred to in operational documentation as Kash Station, is an aerospace tracking facility located in the western part of China [SRC-0040], [SRC-0040]. It operates as one of the five fixed near-earth satellite control stations within the broader China Aerospace Control Network, operating alongside other vital facilities like the Changchun, Xiamen, Nanning, and Weinan stations [SRC-0040]. The primary operational mission of the Kashgar Station is to perform daily tracking and control over medium- and low-orbiting satellites, working in close cooperation with the rest of the fixed station network to ensure continuous orbital coverage [SRC-0040].
-To fulfill its tracking and telemetry duties, the station relies on a standardized array of principal facilities deployed across China's fixed near-earth control stations. This includes sophisticated VHF/UHF control systems comprised of dispersed and unified carrier-wave architectures [SRC-0040]. These systems enable the station to measure distance-variation ratios, receive modulated satellite telemetry signals, and transmit remote control instructions and data insertions directly to spacecraft [SRC-0040], [SRC-0040]. Kashgar Station is also equipped with C-band monopulse precision tracking radars, which are essential for measuring satellite perigee periods and tracking reentry orbits due to their large number of measurement elements and high precision capabilities [SRC-0040], [SRC-0040]. Operations at the station are managed through integrated computers and monitoring display facilities that preprocess orbital measurement data and establish digital guidance for the control equipment [SRC-0040]. These computer systems also facilitate vital data exchange with the Xi'an Satellite Control Center, minimizing the reliance on standard communication voice channels [SRC-0040], [SRC-0040].</t>
+          <t>Fixed near-earth satellite control station located in western China.</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
@@ -4154,11 +4054,6 @@
       <c r="V50" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4214,9 +4109,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>Beijing Command Center operates as a high-level strategic node within the China Aerospace Control Network, functioning directly under the authority of the National Defense Scientific and Engineering Committee [SRC-0040]. While primary satellite tracking, telemetry, and control (TT&amp;C) operations are executed by the Xi'an Satellite Control Center and its subordinate fixed and mobile stations, the Beijing Command Center serves a critical overarching command and communications role for the nation's spacefile operations [SRC-0040], [SRC-0040], [SRC-0040].
-The facility is heavily integrated into the network's long-distance communication infrastructure. Utilizing a combination of wire, wireless, and dedicated communication satellite lines, this network ensures reliable long-distance command communications, data transmission, and other essential service communications [SRC-0040]. This system connects the Beijing Command Center directly with the launch command control centers situated at various launch pads (such as Jiuquan, Xichang, and Taiyuan) and the main satellite control center [SRC-0040], [SRC-0040]. This robust connectivity ensures that the National Defense Scientific and Engineering Committee maintains continuous oversight and rapid coordination capabilities during complex aerospace missions.
-In addition to its domestic command responsibilities, the Beijing facility is a key hub for international space communications. International satellite communication ground stations have been established in Beijing, which can be directly connected to the global INTELSAT network [SRC-0040]. This capability allows the Beijing Command Center to provide user-leased circuits and facilitates international cooperation and data exchange, ensuring the synchronized execution of China's domestic and overseas satellite missions [SRC-0040], [SRC-0040].</t>
+          <t>Command center for aerospace control and international satellite communications.</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
@@ -4232,11 +4125,6 @@
       <c r="V51" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
         </is>
       </c>
     </row>
@@ -4523,10 +4411,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>The Integrated Test Range (ITR) at Chandipur is a premier military test and evaluation center operated by the Defence Research and Development Organisation (DRDO) under India's Ministry of Defence [SRC-0075, SRC-0076]. Located in the Balasore district off the coast of Odisha, the facility provides safe and reliable launch infrastructure for the performance evaluation of rockets, ballistic missiles, and airborne weapon systems [SRC-0075, SRC-0073]. 
-While the exact founding year is not detailed in the provided sources, the ITR has long served as one of India's primary missile testing facilities for strategic and tactical development [SRC-0073]. The site is heavily equipped with high-performance range instrumentation designed to monitor flying objects from takeoff to impact [SRC-0075]. Key tracking facilities deployed along the coast include Electro-Optical Tracking Systems (EOTS), advanced radar networks, telemetry stations, and a real-time Central Computer System that captures precise location and vehicle health parameters throughout a missile's flight trajectory [SRC-0075, SRC-0076, SRC-0073].
-The ITR has hosted numerous notable activities, including developmental and user trials for the Prithvi, Akash, and Agni missile variants [SRC-0073]. Recently, the range facilitated the successful test-launch of the nuclear-capable Agni-1 short-range ballistic missile (SRBM) by the Strategic Forces Command (SFC) to validate operational parameters [SRC-0073, SRC-0057]. It has also hosted multiple successful flight-trials of the indigenous Very Short-Range Air Defence System (VSHORADS) against high-speed aerial targets [SRC-0050, SRC-0050]. 
-Currently, the Integrated Test Range remains fully active and is a crucial component of India's strategic defense modernization [SRC-0073]. The facility regularly conducts routine training and operational exercises, implementing strict safety protocols and temporary maritime restrictions in the Bay of Bengal during active launch operations [SRC-0073, SRC-0073].</t>
+          <t>Safe and reliable launch facility in Balasore used for performance evaluation of rockets, missiles, and airborne weapons.</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
@@ -4542,11 +4427,6 @@
       <c r="V55" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>SRC-0075, SRC-0076, SRC-0073, SRC-0057, SRC-0050</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4715,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>Tel Nof Airbase is an installation operated by the Israeli Air Force (IAF) [SRC-0139]. The facility has a long history as a critical hub for Israeli rotary-wing operations. In the 1950s, the 124 Squadron, known as the "Rolling Sword," was founded at Tel Nof as the very first helicopter squadron in the State of Israel [SRC-0139]. By 1962, Sikorsky S-58 helicopters belonging to this pioneering squadron were operating out of the base [SRC-0139]. The base later became home to Israel's attack helicopter fleet; in 1975, the 160 Squadron "First Cobra" was established at Tel Nof, equipped with the new AH-1 Cobra Tzefa attack helicopters [SRC-0139]. Eventually, both the 160 Squadron and the 124 Squadron were relocated from Tel Nof to Palmachim Airbase in 1979 and 1981, respectively [SRC-0139]. Tel Nof is also a primary operating location for Unit 669, the IAF's elite heliborne Combat Search and Rescue (CSAR) unit, which flies CH-53D Sea Stallion Yas'ur helicopters from the facility [SRC-0139, SRC-0139]. Furthermore, an IAI Searcher Hugla UAV was displayed at Tel Nof during Israel's Independence Day celebrations in April 2007 [SRC-0139]. Recently, since October 7, 2023, Tel Nof has played an active role in the Gaza war, with military drones operating around the clock from the base to gather intelligence and launch guided weapon attacks in support of advancing Israeli ground troops [SRC-0139].</t>
+          <t>Airbase that has operated transport and attack helicopters as well as UAV squadrons.</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
@@ -4851,11 +4731,6 @@
       <c r="V59" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -4911,7 +4786,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>Hatzor Airbase is an operational military installation of the Israeli Air Force [SRC-0139]. While historical details regarding the facility's early years are limited in the available records, Hatzor has recently evolved into an important center for Israel's unmanned aerial vehicle (UAV) operations. In January 2023, the Israeli Air Force relocated the 200 Squadron, known as the "First UAV" squadron, from Palmachim Airbase to Hatzor Airbase [SRC-0139]. This squadron operates the Heron 1, also known as the Shoval, which is a key reconnaissance and surveillance drone [SRC-0139]. Following the outbreak of the Gaza war on October 7, 2023, Hatzor Airbase was utilized for continuous combat operations [SRC-0139]. Unmanned aerial vehicles stationed at Hatzor have been deployed in the airspace over the Gaza Strip around the clock [SRC-0139]. These drones perform a dual role: they collect vital battlefield intelligence and execute targeted strikes using guided weapons, working in close cooperation with Israeli ground troops to support their advances [SRC-0139].</t>
+          <t>Israeli airbase that serves as a hub for UAV operations, including Heron 1 squadrons.</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
@@ -4927,11 +4802,6 @@
       <c r="V60" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -4987,7 +4857,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>Ramat David Airbase is a military installation operated by the Israeli Air Force [SRC-0139]. Historically, the base was the home of the 193 Squadron, named the "Defenders of the West," which provided critical aerial support for the Israeli Navy [SRC-0139]. The squadron operated a fleet of Eurocopter AS565 Panther Atalef helicopters specifically utilized for maritime patrol, maritime surveillance, and search and rescue (SAR) operations [SRC-0139]. The 193 Squadron was officially closed at Ramat David Airbase on August 31, 2025, prior to its planned reopening at Palmachim Airbase with newer SH-60 Seahawk helicopters [SRC-0139]. Following the start of the Gaza war on October 7, 2023, Ramat David Airbase was integrated into Israel's intense unmanned aerial vehicle (UAV) operations [SRC-0139]. Alongside other major Israeli bases, Ramat David serves as a launching point for military drones that operate continuously over the Gaza Strip [SRC-0139]. These continuous drone flights are dedicated to gathering real-time intelligence and launching guided weapons to support ground troop maneuvers [SRC-0139].</t>
+          <t>Northern airbase operating drones for intelligence collection and aerial strikes.</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
@@ -5003,11 +4873,6 @@
       <c r="V61" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -5063,7 +4928,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>Hatzerim Airbase is an installation of the Israeli Air Force situated in the southern region of the country [SRC-0139]. The airbase is prominently known for hosting the Israeli Air Force Museum, which preserves a variety of historical military aircraft and early unmanned aerial vehicles (UAVs) [SRC-0139, SRC-0139]. Among the artifacts preserved at the museum near Hatzerim are a 1950s-era Sikorsky S-55 helicopter, a Ryan Firebee Mabat UAV, and a Tadiran Mastiff UAV that originally belonged to the 200 Squadron [SRC-0139, SRC-0139]. In terms of active military operations, Hatzerim Airbase served as the home for the 123 Squadron, known as the "Desert Birds" [SRC-0139]. In 2002, this squadron was re-established at Hatzerim and equipped with a new fleet of UH-60 Black Hawk Yanshuf transport helicopters [SRC-0139]. The 123 Squadron operated out of Hatzerim Airbase for thirteen years, providing transport and logistical support, before the unit was relocated to Palmachim Airbase in 2015 [SRC-0139].</t>
+          <t>Airbase forming part of the Israeli Air Force operational infrastructure.</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
@@ -5079,11 +4944,6 @@
       <c r="V62" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>SRC-0139</t>
         </is>
       </c>
     </row>
@@ -5352,9 +5212,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>The AN/TPY-2 (Army/Navy Transportable Radar Surveillance) radar deployment in Israel serves as a critical component of the region's layered ballistic missile defense architecture [SRC-0012, SRC-0012]. The site is operated and supervised by the United States Army's 1st Space Brigade, specifically under the command of the 13th Missile Defence Battery [SRC-0012]. The United States agreed to provide this advanced radar system to Israel to complement the nation's existing domestic two-tier defense network, which includes the Arrow 2 and Patriot PAC-3 missile defense systems [SRC-0012].
-Manufactured by Raytheon, the AN/TPY-2 is an advanced, high-resolution X-band active electronically scanned array (AESA) radar [SRC-0011, SRC-0012]. It operates in the 8.55–10 GHz frequency range and features an antenna aperture of approximately 9.2 square meters [SRC-0012, SRC-0011]. Utilizing fully electronic beam steering, the radar provides near-instantaneous target updates and exceptional discrimination accuracy, distinguishing between lethal ballistic missile warheads and non-threats such as decoys or space clutter [SRC-0012, SRC-0011]. The system boasts a long-range detection capacity of 1,000 kilometers or more and can simultaneously track hundreds of targets during their midcourse and terminal flight phases [SRC-0011, SRC-0011]. 
-As a mobile, trailer-mounted system, the AN/TPY-2 integrates seamlessly with broader U.S. and allied missile defense networks, including the Command and Control, Battle Management, and Communications (C2BMC) architecture [SRC-0011, SRC-0011]. In its forward-based configuration in Israel, the radar detects ballistic missiles during their boost and early ascent phases, passing high-fidelity tracking and trajectory data downstream to fire control radars and interceptor systems [SRC-0012, SRC-0190]. This strategic deployment significantly extends the defense battlespace, providing vital early warning coverage against regional ballistic missile threats [SRC-0012, SRC-0011].</t>
+          <t>Forward-deployed AN/TPY-2 X-band radar site complementing Israel's multi-tier missile defense.</t>
         </is>
       </c>
       <c r="T66" t="inlineStr">
@@ -5370,11 +5228,6 @@
       <c r="V66" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>SRC-0012, SRC-0011, SRC-0190</t>
         </is>
       </c>
     </row>
@@ -6020,9 +5873,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>The Shariki Radar Site is a strategic military installation located in the Shariki region of Japan [SRC-0012]. The site plays a critical role in regional defense and early warning architectures through its operation of the AN/TPY-2 transportable radar [SRC-0012]. Developed by Raytheon, the AN/TPY-2 is a highly mobile, X-band active electronically scanned array (AESA) radar system that utilizes solid-state gallium arsenide (GaAs) transmit/receive modules to provide long-range surveillance and high-resolution target tracking capabilities [SRC-0183].
-The primary mission of the radar deployment at the Shariki site is to collect strategic-level intelligence on North Korean ballistic missile developments and to provide Japan with advanced early warning of incoming warheads [SRC-0012]. Due to its strategic placement and powerful tracking capabilities, the AN/TPY-2 radar at Shariki is also able to monitor and scan portions of Russian territory located near Japan [SRC-0012]. 
-The Shariki Radar Site functions as a key node within a broader, layered ballistic missile defense network in the region. The tracking data gathered by the radar complements Japan's existing air defense capabilities, including point defense systems like the PAC-3, as well as the upgraded Aegis combat systems on Japan's *Kongo*-class destroyers, which utilize the longer-range RIM-161 Standard Missile 3 (SM-3) for theater ballistic missile defense [SRC-0012]. While the AN/TPY-2 radar system itself was introduced in 2007 and is deployed by the United States and its allies globally [SRC-0183, SRC-0011], the provided sources do not detail the exact founding year of the Shariki site itself or its specific host governing organization.</t>
+          <t>Site hosting an AN/TPY-2 early warning radar to collect intelligence on ballistic missile developments.</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
@@ -6038,11 +5889,6 @@
       <c r="V75" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W75" t="inlineStr">
-        <is>
-          <t>SRC-0012, SRC-0183, SRC-0011</t>
         </is>
       </c>
     </row>
@@ -6255,9 +6101,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>The Saturn-MS Measuring Complex is a critical radar and tracking facility located at the Baikonur Cosmodrome in Kazakhstan [SRC-0173, SRC-0222]. Situated atop Murguduk hill, also known as "snake mountain," the complex serves as the first major landmark visible from the Kyzylorda-Aralsk highway when traveling to the cosmodrome [SRC-0173]. The foundation for the complex's first antenna was laid on January 25, 1967 [SRC-0173]. It successfully conducted its first communication tests in November 1970 with the Luna-16 automatic interplanetary station—which famously returned lunar soil to Earth—and officially commenced full-scale operations on November 3, 1971 [SRC-0173].
-Initially established as a strictly military facility operated by a dedicated military unit, Saturn-MS was designed to monitor rocket trajectories, telemetry, space communications, and satellite control [SRC-0173]. Over the decades, the complex expanded its capabilities to keep pace with technological advancements. It was equipped to support the joint Soyuz-Apollo program in 1975, integrated a squadron of four flying telemetry laboratory aircraft in 1976, and added a communications center in 1987 to facilitate operations for the Buran space shuttle [SRC-0173]. The facility's primary tracking hardware consists of two massive parabolic antennas, each measuring 25 meters in diameter and weighing 200 tons [SRC-0222, SRC-0173].
-Throughout its operational history, Saturn-MS has been instrumental in numerous high-profile space programs. It has tracked the launches of Soyuz, Soyuz-TM, Progress, and Progress-M spacecraft, while also maintaining deep-space communications with interplanetary stations exploring the Moon, Venus, Mars, and Halley's comet [SRC-0222, SRC-0173]. In 2006, the managing military unit was disbanded, and the site underwent a complete civilian transition under the administration of the Russian space agency, Roscosmos [SRC-0222, SRC-0173]. Today, the complex continues to undergo gradual modernization, functioning as the vital "eyes" of the Baikonur Cosmodrome [SRC-0173].</t>
+          <t>Measuring complex and radar system at Baikonur used to track launch vehicle trajectories and receive telemetry.</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -6273,11 +6117,6 @@
       <c r="V78" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W78" t="inlineStr">
-        <is>
-          <t>SRC-0173, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -6622,10 +6461,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>The Nodong Launch Pad is a rocket launching site situated in North Korea, specifically located in the area historically known as Tae Po Dong (Taep'o-dong) [SRC-0162, SRC-0205]. The broader facility encompassing this pad is formally known as the Tonghae Satellite Launching Ground, or Musudan-ri, which lies in southern Hwadae County, North Hamgyong Province, near the cape of Musu Dan [SRC-0205, SRC-0205]. 
-The development of the launching infrastructure in this area began in the early 1980s [SRC-0205]. At the time, North Korea required a new flight-test facility to reverse-engineer and produce copies of the Soviet Scud-B missile; their previous test site at Hwajin-ri had insufficient range and risked sending missiles into Chinese territorial waters [SRC-0205]. Construction of the original launch pad was completed in 1985 by the 117th Regiment of the Ministry of People's Armed Forces' Air Force Construction Bureau [SRC-0205]. During the early 1990s, the site underwent significant expansion, adding a missile assembly facility, fuel storage buildings, a range control center, and advanced tracking facilities [SRC-0205].
-The Nodong Launch Pad and its surrounding complex have supported the testing of various military rockets, including the Hwasong, Rodong, and the Taepodong-1 and Taepodong-2 missiles, which take their name from the local area [SRC-0162, SRC-0205, SRC-0205]. A highly notable launch occurred in 1998, when North Korea launched a Paektusan-1 vehicle from this site, claiming to have successfully placed the Kwangmyŏngsŏng-1 satellite into orbit—a claim that remains unverified by independent sources [SRC-0205].
-The facility features a disused launch pad equipped with a 30-meter umbilical tower, a top-mounted gantry crane, a flame blast bucket, and a blockhouse with an access tunnel [SRC-0205, SRC-0205]. Nearby infrastructure includes an engine test stand, a missile assembly building, and a ground tracking facility [SRC-0205, SRC-0205]. Since 2014, the site has reportedly been reduced to a caretaker status [SRC-0205].</t>
+          <t>Launch pad used for testing Taepo Dong 1 and 2 missiles.</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -6641,11 +6477,6 @@
       <c r="V83" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W83" t="inlineStr">
-        <is>
-          <t>SRC-0162, SRC-0205</t>
         </is>
       </c>
     </row>
@@ -7141,10 +6972,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>The **Philippine Spaceport** is a proposed rocket launch facility planned to be established in the Cagayan Special Economic Zone (CEZA) in the Philippines [SRC-0221]. Currently in its early planning and development stages as of 2026, the spaceport aims to position the Philippines as a prominent gateway to space and a hub for satellite launches in Southeast Asia [SRC-0066, SRC-0146]. 
-The initiative gained significant momentum on March 4, 2026, when a historic Memorandum of Understanding (MOU) was signed during the Philippines–Korea Business Forum in Manila [SRC-0066, SRC-0145]. The agreement brought together key governing and partner organizations, including the Philippine Space Agency (PhilSA), the Department of Information and Communications Technology (DICT), the Cagayan Economic Zone Authority (CEZA), the South Korean rocket firm Perigee Aerospace, and Ascend International Gateway, Inc. [SRC-0066, SRC-0145]. This collaborative framework is designed to facilitate rocket development training, localized assembly, and experimental launches that will serve as a proof of concept for the permanent spaceport [SRC-0066, SRC-0145, SRC-0145].
-The foundation for this project stems from a technology transfer program conducted in late 2025, during which PhilSA engineers trained with Perigee Aerospace in South Korea to gain hands-on experience in launch vehicle systems and testing [SRC-0066, SRC-0145]. The choice of the Philippines for a spaceport is highly strategic; its geographic proximity to the equator reduces the fuel required to reach orbit, while its eastern seaboard facing the open Pacific Ocean ensures safe rocket launch trajectories and recovery operations over open waters [SRC-0221, SRC-0146, SRC-0066, SRC-0145]. 
-While specific launch pads and radar facilities have yet to be constructed, the spaceport is envisioned to support both domestic space ambitions and international commercial space operators [SRC-0145, SRC-0145]. As of mid-2026, the Philippine Spaceport remains a planned project, representing a pivotal step in advancing the country's space industry, driving foreign investments, and enhancing national digital connectivity [SRC-0146, SRC-0066].</t>
+          <t>A planned spaceport positioned for rocket development, training, and open-water experimental launches.</t>
         </is>
       </c>
       <c r="T90" t="inlineStr">
@@ -7160,11 +6988,6 @@
       <c r="V90" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC-0221, SRC-0066, SRC-0146, SRC-0145</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7265,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>While the sources specifically refer to this location as the "Ko Juang–Ko Jan" site in Chonburi, it is identified as the most suitable candidate for Thailand's future spaceport project [SRC-0199]. Evaluated by the Geo-Informatics and Space Technology Development Agency (GISTDA) in collaboration with KPMG Phoomchai Business Advisory, the site was chosen over other potential locations due to its highly favorable physical and geographical characteristics [SRC-0199, SRC-0199, SRC-0199]. The Ko Juang-Ko Jan site stands out because it is situated on government-owned land, which significantly reduces the costs associated with land acquisition and area modification [SRC-0199]. Consequently, it requires the lowest initial investment among the surveyed sites, estimated at 376 million baht [SRC-0199]. Geographically and operationally, the site is particularly well-suited for vertical rocket launches [SRC-0223]. A major advantage of this location is its minimal impact on surrounding populated areas and local communities, fulfilling crucial safety and environmental requirements for spaceflight operations [SRC-0223, SRC-0199]. Economically, the Ko Juang-Ko Jan spaceport is projected to be highly beneficial, as it is the only evaluated site with a positive economic net present value (NPV) [SRC-0199]. Furthermore, it boasts an impressive social return on investment (SROI) of 1.79, meaning every baht invested generates approximately 1.79 baht in social value through human capital development, high-tech employment, and STEM training [SRC-0199, SRC-0199]. The phased development of the site will initially focus on suborbital rocket testing and launch capabilities over the first two to five years, serving as a foundational step before progressing to orbital missions and a fully-fledged space hub [SRC-0199, SRC-0199].</t>
+          <t>A planned civilian launch site for vertical rocket launches in Chonburi province.</t>
         </is>
       </c>
       <c r="T94" t="inlineStr">
@@ -7458,11 +7281,6 @@
       <c r="V94" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>SRC-0199, SRC-0223</t>
         </is>
       </c>
     </row>
@@ -7518,7 +7336,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>The Space Krenovation Park (SKP) is a high-level aerospace research and satellite development facility located in Si Racha, Thailand [SRC-0198]. Operated under the auspices of the Geo-Informatics and Space Technology Development Agency (GISTDA), the park serves as the kingdom's most advanced hub for space technology and satellite operations [SRC-0198, SRC-0068]. The facility is integral to Thailand's strategic goal of transitioning from a mere consumer of space technology to a key creator within the global space supply chain [SRC-0198, SRC-0198]. Key facilities located within the Space Krenovation Park include the National Assembly Integrated and Test Centre (NAIT) and the Space Technology Research Centre (S-TREC) [SRC-0198]. These centers are dedicated to advanced satellite development, testing, and high-level aerospace research [SRC-0198]. The Si Racha location also functions as the primary spaceport and control center for GISTDA's THEOS (Thailand Earth Observation Satellite) program, officially serving as the GISTDA THEOS Control &amp; Receiving Station [SRC-0068]. Recently, the Space Krenovation Park was visited by delegations from Thailand's Ministry of Higher Education, Science, Research and Innovation (MHESI) and Japan's Ministry of Economy, Trade and Industry (METI) [SRC-0198, SRC-0198]. This visit was part of a strategic partnership aiming to establish a domestic spaceport and a national satellite constellation in the Eastern Economic Corridor (EEC) [SRC-0198, SRC-0198]. This international collaboration highlights the park's critical role in advancing Thailand's national space industry, attracting investment, and stimulating the New S-Curve economy through knowledge transfer and high-skilled employment [SRC-0198].</t>
+          <t>An advanced hub in Si Racha housing the National Assembly Integrated and Test Centre for satellite development.</t>
         </is>
       </c>
       <c r="T95" t="inlineStr">
@@ -7534,11 +7352,6 @@
       <c r="V95" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC-0198, SRC-0068</t>
         </is>
       </c>
     </row>
@@ -7594,9 +7407,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>The Abu Dhabi Testing Ground, situated in a desert area of Abu Dhabi, United Arab Emirates, serves as a launch location for the nation's expanding aerospace and space exploration programs [SRC-0207, SRC-0221]. While specific details regarding the exact coordinates, founding year, and permanent radar or support facilities of the testing ground are not detailed in the provided sources, the site is notably utilized by the Technology Innovation Institute (TII), which operates as the applied research division of the Advanced Technology Research Council (ATRC) [SRC-0207].
-The testing ground gained historical prominence in February 2026 when it hosted the successful launch of the UAE's first locally designed and manufactured hybrid rocket [SRC-0207, SRC-0221]. This landmark mission was conducted by a team of researchers led by Dr. Najwa Aaraj and Dr. Elias Tsotsanis to test cutting-edge propulsion systems [SRC-0221, SRC-0207]. The rocket launched from this desert site utilized a hybrid propulsion system, combining a solid fuel component with nitrous oxide acting as the oxidizer, which is considered safer and more cost-effective than fully liquid-fueled engines [SRC-0207].
-During its flight from the Abu Dhabi site, the hybrid sounding rocket reached an altitude of approximately three kilometers before safely descending using a parachute recovery system [SRC-0207, SRC-0221]. The mission successfully validated the rocket's structural durability, flight stability, and propulsion efficiency [SRC-0207]. Engineers at the site collected extensive performance data during the flight to improve future designs [SRC-0207]. All essential components of the rocket, including avionics, structural frameworks, and control mechanisms, were developed and tested locally, demonstrating the UAE's growing sovereign capabilities in aerospace engineering [SRC-0207, SRC-0207]. The site currently acts as a critical test bed for proving new technologies before they are scaled up for larger launchers and orbital flights, aligning with the UAE's broader national space strategy [SRC-0207, SRC-0207].</t>
+          <t>Testing ground used for the launch of the UAE's first homegrown hybrid rocket.</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
@@ -7612,11 +7423,6 @@
       <c r="V96" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>SRC-0207, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -7672,9 +7478,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>The AN/TPY-2 Radar Site in the United Arab Emirates (UAE) is a forward-based early warning and missile defense installation equipped with the Army/Navy Transportable Radar Surveillance (AN/TPY-2) system [SRC-0183]. While the exact location, founding year, and internal governing structure of the specific UAE site are not fully detailed in the provided sources, it forms a critical node in the broader United States and allied ballistic missile defense architecture deployed across the Middle East [SRC-0183, SRC-0011].
-The key facility at this site is the AN/TPY-2 radar, a highly mobile, high-resolution, X-band active electronically scanned array (AESA) radar originally manufactured by Raytheon [SRC-0183, SRC-0011, SRC-0011]. Operating in the 8.55 to 10 GHz frequency range, the radar utilizes over 25,000 gallium arsenide (and increasingly Gallium Nitride) transmit/receive modules across an approximate 9.2-square-meter aperture [SRC-0183, SRC-0011, SRC-0011, SRC-0190]. The system is capable of electronically steering its radar beams to detect, classify, and track hundreds of ballistic missile threats simultaneously at ranges of 1,000 kilometers or more [SRC-0011, SRC-0011, SRC-0011]. In the UAE, this radar integrates with Terminal High Altitude Area Defense (THAAD) batteries to provide a rapid response capability against regional theater ballistic threats [SRC-0183, SRC-0011, SRC-0190].
-The site has seen notable operational activity during periods of heightened regional tensions. During the 2026 Iran war, the UAE Ministry of Defense reported that national air defenses were actively intercepting missiles and drones launched from Iran [SRC-0078]. Concurrently, satellite imagery and news reports indicated that radar bases housing key U.S. missile interceptors, including locations in the UAE, were targeted and hit during these retaliatory strikes [SRC-0012, SRC-0012, SRC-0184, SRC-0184]. Despite these attacks, the AN/TPY-2 network remains a cornerstone of the layered defense strategy for the UAE and allied forces in the Persian Gulf region [SRC-0183, SRC-0011].</t>
+          <t>Forward-based X-band active electronically scanned array radar deployed for missile warning.</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
@@ -7690,11 +7494,6 @@
       <c r="V97" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W97" t="inlineStr">
-        <is>
-          <t>SRC-0183, SRC-0011, SRC-0190, SRC-0078, SRC-0012, SRC-0184</t>
         </is>
       </c>
     </row>
@@ -7745,9 +7544,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>Ahtopol is a former rocket launch site located in Bulgaria [SRC-0095, SRC-0096]. Geographically situated at coordinates 42°05′09″N 27°57′18″E, the facility was utilized for aerospace and rocket launch activities during the 1980s [SRC-0095, SRC-0096]. The site officially became operational in the year 1984 and maintained active operations until it was closed in 1990 [SRC-0095, SRC-0096]. 
-During its six years of operational history, the Ahtopol launch site was utilized for a total of 28 rocket launches [SRC-0095, SRC-0096]. The aerospace operations conducted at this location involved suborbital flights, with the highest achieved altitude recorded at 90 kilometers, reaching the upper limits of the atmosphere just below the official edge of space [SRC-0095, SRC-0096]. Additionally, the heaviest rocket launched from the Ahtopol facility weighed 475 kilograms [SRC-0095, SRC-0096]. 
-While the fundamental operational statistics and geographical location of the site are documented, the available sources do not provide further detailed information concerning the specific governing organization, military branch, or space agency that managed the facility [SRC-0095, SRC-0096]. Furthermore, the provided texts do not contain details regarding the site's key infrastructure, specific radar systems, or its current status and preservation following the cessation of launch activities in 1990 [SRC-0095, SRC-0096].</t>
+          <t>Former sounding rocket launch site operated from 1984 to 1990.</t>
         </is>
       </c>
       <c r="T98" t="inlineStr">
@@ -7763,11 +7560,6 @@
       <c r="V98" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC-0095, SRC-0096</t>
         </is>
       </c>
     </row>
@@ -7823,8 +7615,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>**Ämari Air Base** is a key military installation located in Estonia, serving as a central hub for both national and international air defense operations. The base operates as the permanent garrison and headquarters for the Air Defence Wing (Õhukaitsedivisjon) of the Estonian Air Force, an active unit established in 2023 [SRC-0014, SRC-0014]. The Air Defence Wing's primary mission at the base is to ensure the integrity of Estonian airspace through the planning and execution of active air defense operations [SRC-0014]. To support this mission, Ämari Air Base is slated to be equipped with newly purchased IRIS-T medium-range air defense systems [SRC-0014].
-Beyond its national significance, Ämari Air Base is a critical component of the North Atlantic Treaty Organization's (NATO) defense architecture on its Eastern Flank [SRC-0119]. Following Russia's illegal annexation of Crimea in 2014, NATO expanded its Baltic Air Policing Mission, deploying allied fighter detachments to Ämari to help secure the region's airspace [SRC-0119]. The base has since become integral to NATO's evolving Rotational Air Defense Model, which aims to provide continuous protection against airborne threats by deploying ground-based long-range air defenses alongside traditional air patrols [SRC-0119, SRC-0119]. Estonia provides crucial host nation support for the various allied air defense contingents that operate out of Ämari Air Base [SRC-0119]. Through these joint and multinational efforts, the base actively facilitates the strengthening of NATO's Integrated Air and Missile Defense System (IAMD), effectively contributing to the collective security, military mobility, and deterrence measures of the Baltic region [SRC-0119, SRC-0119].</t>
+          <t>Permanent location for the Estonian Air Defence Wing and its IRIS-T medium-range air defense systems.</t>
         </is>
       </c>
       <c r="T99" t="inlineStr">
@@ -7840,11 +7631,6 @@
       <c r="V99" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC-0014, SRC-0119</t>
         </is>
       </c>
     </row>
@@ -7900,9 +7686,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>The **Lohtaja Firing Range and Training Area** is a prominent military installation located in Finland, noted by geopolitical analyses to be associated with the Lapland region [SRC-0221], and specifically encompassing the coastal areas around Lohtaja and Houraati [SRC-0017]. As a central hub for the Finnish Defence Forces, the range is utilized jointly by the Finnish Army, Navy, Air Force, and the Border Guard to maintain and enhance national and regional security [SRC-0017, SRC-0191]. 
-The facility is best known for hosting "Mallet Strike," a major biannual ground-based air defence exercise that stands as the most critical live-firing training event for Finnish conscripts, reservists, and active personnel [SRC-0017, SRC-0007]. Since 2023, the site has regularly integrated allied NATO forces into its operations, featuring troops and equipment from countries such as the United Kingdom, Sweden, Norway, and Germany [SRC-0221, SRC-0017, SRC-0007, SRC-0007]. Exercises at the site frequently involve up to 1,900 personnel [SRC-0017, SRC-0191].
-Lohtaja provides a highly challenging and realistic training environment, further enhanced by harsh Finnish weather conditions and complex aerial threat simulations [SRC-0007, SRC-0191]. The range supports live-fire operations for a diverse array of anti-aircraft weaponry, including 35ITK88 and 23ITK61/95 anti-aircraft guns, as well as numerous surface-to-air missile systems like the ITO90M, ITO05, ITO05M, NASAMS, British Starstreak, and German Patriot batteries [SRC-0221, SRC-0007]. Recent exercises at the site have also introduced Counter-Unmanned Aerial System (C-UAS) measures and force protection equipment to address modern battlefield threats [SRC-0191, SRC-0017]. The airspace and grounds routinely accommodate large-scale maneuvers involving hundreds of vehicles, drones, helicopters, and fighter aircraft, maintaining Lohtaja's status as a critical asset for both Finnish and NATO integrated air and missile defence capabilities [SRC-0017, SRC-0191, SRC-0007].</t>
+          <t>Major firing range used for national and multinational ground-based air defense and live-fire exercises.</t>
         </is>
       </c>
       <c r="T100" t="inlineStr">
@@ -7918,11 +7702,6 @@
       <c r="V100" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>SRC-0221, SRC-0017, SRC-0191, SRC-0007</t>
         </is>
       </c>
     </row>
@@ -9066,9 +8845,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>The Sēlija Military Training Range is a new, large-scale military testing and training zone located in Latvia, governed by the Latvian Ministry of Defence and utilized by the National Armed Forces and its allies [SRC-0063, SRC-0221]. The development of the facility was significantly accelerated following the 2022 NATO summit in Madrid, which called for an increased presence of allied forces in the Baltic States in response to regional security threats stemming from Russia's invasion of Ukraine [SRC-0063, SRC-0221]. The range covers a vast total area of 15,590 hectares, acquired through the combination of 15,430 hectares of state-owned properties and the expropriation of 160 hectares of private land [SRC-0221, SRC-0063].
-The project's first phase was developed between 2022 and 2025 with an estimated cost of 36.5 million euros, establishing its initial operational capabilities [SRC-0063, SRC-0063]. The live-fire training area was officially opened in February 2026, with key Latvian officials, including President Edgars Rinkēvičs and Minister of Defence Andris Sprūds, in attendance [SRC-0063, SRC-0063, SRC-0221]. Key facilities at the site currently include a logistics support area for company-level units, an ammunition storage area, a 300-metre shooting range, a tactical shooting range for infantry platoons, specialized ranges for machine guns and snipers, and an unexploded ordnance zone [SRC-0063]. 
-Currently active, the range hosts a variety of training operations, including tactical and engineering drills, armored vehicle maneuvers, aircraft overflights, and unmanned aerial vehicle (UAV) training [SRC-0221, SRC-0063]. Soldiers from the Latvian National Armed Forces, the National Guard, the State Defence Service, and allied NATO countries regularly utilize the facility [SRC-0063]. A second phase of development is planned for 2026 to 2029, aiming to expand the site's collective training infrastructure to accommodate larger-scale, brigade-level exercises [SRC-0221, SRC-0063].</t>
+          <t>New military training range spanning over 15,000 hectares for brigade-level exercises and firing.</t>
         </is>
       </c>
       <c r="T116" t="inlineStr">
@@ -9084,11 +8861,6 @@
       <c r="V116" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>SRC-0063, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -9144,9 +8916,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>Šķēde is a veteran air defense military training range located on the Baltic coast of Latvia [SRC-0221]. Serving as a key operational site for both the Latvian National Armed Forces and allied international troops, the active facility plays a critical role in regional defense integration and military readiness [SRC-0221, SRC-0221, SRC-0109]. Unlike the newly developed Sēlija range, Šķēde has functioned as an established air defense range for years, hosting various live-fire exercises and providing essential training infrastructure for Baltic security [SRC-0221]. Furthermore, because neighboring Lithuania currently lacks its own active rocket firing range, Lithuanian military forces regularly utilize the Šķēde facility to conduct their training exercises [SRC-0221].
-The site is notable for accommodating advanced weapon systems and large-scale international military drills. During the "Defender 23" exercise in May 2023, the Michigan National Guard’s 1st Battalion, 182nd Field Artillery Regiment deployed to the Šķēde range to conduct a "Baltic Raid" drill [SRC-0109, SRC-0109]. This event marked a significant regional milestone, as it was the first time an M142 High Mobility Artillery Rocket System (HIMARS) was fired from Latvia into the Baltic Sea, successfully targeting simulated naval threats [SRC-0221, SRC-0109]. This exercise aimed to enhance interoperability between United States, NATO, and partner forces [SRC-0109]. 
-In addition to HIMARS rocket tests, Šķēde has hosted live-fire tests for the Avenger air defense system [SRC-0221]. Today, the range remains highly active and continues to serve as a strategic location for military training, air defense operations, and maritime target engagements along the Baltic coastline [SRC-0221].</t>
+          <t>Coastal military drill site where HIMARS live-fire exercises were conducted against simulated naval targets.</t>
         </is>
       </c>
       <c r="T117" t="inlineStr">
@@ -9162,11 +8932,6 @@
       <c r="V117" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W117" t="inlineStr">
-        <is>
-          <t>SRC-0221, SRC-0109</t>
         </is>
       </c>
     </row>
@@ -9597,7 +9362,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>**Leba in Pommern** is a former rocket launch facility situated at geographical coordinates 54°46′09″N 17°35′37″E [SRC-0095]. Historically located in the region of Pommern (Pomerania), the site was under the jurisdiction of Nazi Germany during its operational years [SRC-0095]. The facility was active during World War II, specifically functioning between 1941 and 1945 [SRC-0095]. During this period, the governing military organization utilized the Leba installation primarily for the testing and launching of Nazi-German rockets [SRC-0095]. Following the end of the Second World War and the subsequent redrawing of national borders in 1945, the territory encompassing the Leba in Pommern launch site was incorporated into Poland [SRC-0095]. Today, the site remains a historical footnote of wartime rocket development. Detailed information regarding specific facilities, radars, or other notable activities at this location is not available in the provided sources.</t>
+          <t>A World War II era rocket launch site used by Nazi Germany.</t>
         </is>
       </c>
       <c r="T123" t="inlineStr">
@@ -9613,11 +9378,6 @@
       <c r="V123" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W123" t="inlineStr">
-        <is>
-          <t>SRC-0095</t>
         </is>
       </c>
     </row>
@@ -9668,7 +9428,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>**Łeba-Rąbka** is a deactivated rocket launch site located at coordinates 54°45′16″N 17°31′05″E in Poland [SRC-0095, SRC-0221]. Established during the Cold War era, the facility was operational for a decade, spanning from 1963 to 1973 [SRC-0095, SRC-0221]. Unlike the military-focused installations from earlier periods in the region, Łeba-Rąbka was governed by Polish authorities and dedicated strictly to scientific research [SRC-0221, SRC-0221]. The site's primary activity involved the launching of Polish meteorological research rockets into the atmosphere [SRC-0221, SRC-0221]. Over the course of its ten-year operational history, a total of 36 rocket launches were successfully conducted from this location [SRC-0095]. The site does not currently host any active aerospace or military operations and is officially classified as inactive [SRC-0221]. Detailed information regarding the specific types of radar, infrastructure, or technical facilities present at Łeba-Rąbka is not available in the provided sources.</t>
+          <t>A former site used for launching Polish rockets in the 1960s and 1970s.</t>
         </is>
       </c>
       <c r="T124" t="inlineStr">
@@ -9684,11 +9444,6 @@
       <c r="V124" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W124" t="inlineStr">
-        <is>
-          <t>SRC-0095, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -9744,8 +9499,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>**SS-Proving Ground Westpreussen** (also known as SS-Proving Ground Westpreußen) is a historical World War II military reservation and rocket launch facility located in the Tuchola Forest [SRC-0095]. The site is positioned at geographical coordinates 53°37′11″N 17°59′06″E [SRC-0095]. While the Tuchola Forest is located in present-day Poland, during the facility's active period in 1944 and 1945, it was part of Nazi-occupied Poland and governed directly by Nazi Germany's military apparatus [SRC-0095]. 
-The proving ground gained strategic prominence in the latter stages of the war. In late July 1944, the rapid advance of the Soviet Red Army forced German forces to evacuate their primary missile testing base at Blizna [SRC-0025]. Consequently, launch activities and testing personnel were immediately relocated to the Tuchola Forest [SRC-0025]. At this new location, the SS-Proving Ground Westpreussen was utilized heavily for the deployment and testing of Nazi-German V-2 ballistic missiles [SRC-0095, SRC-0025, SRC-0031]. The site operated briefly before the war's conclusion in 1945 [SRC-0095]. Detailed specifications concerning the internal facilities, radars, or physical remnants of the site are not provided in the sources.</t>
+          <t>A Nazi German V-2 rocket testing site established in the Tuchola Forest.</t>
         </is>
       </c>
       <c r="T125" t="inlineStr">
@@ -9761,11 +9515,6 @@
       <c r="V125" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W125" t="inlineStr">
-        <is>
-          <t>SRC-0095, SRC-0025, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -9821,8 +9570,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>**Ustka Training Range** is an active military testing and exercise facility located in Ustka, Poland [SRC-0124, SRC-0221]. Governed by Polish defense authorities, the site is extensively utilized by the North Atlantic Treaty Organization (NATO) and allied partner nations for multinational defense drills [SRC-0124, SRC-0221]. The training range serves as a critical hub for conducting live-fire exercises specifically focused on surface-to-air defense systems, ensuring allied interoperability and operational readiness [SRC-0124, SRC-0221]. 
-One of the most notable activities hosted at the Ustka Training Range was its participation in Ramstein Legacy 22, a large-scale NATO live-fire air and missile defense exercise [SRC-0221, SRC-0124]. During this event, military personnel from several allied nations—including the Czech Republic, France, Poland, Slovakia, and the United Kingdom—converged at the site to integrate and test a variety of advanced weapon systems in live-fire scenarios [SRC-0124]. The demonstrations prominently featured systems such as the British Starstreak air defense system [SRC-0124]. The site continues to play a vital role in maintaining the strategic defense posture of European airspace [SRC-0124, SRC-0221].</t>
+          <t>A firing range in Poland used for NATO live-fire air defense exercises such as Ramstein Legacy.</t>
         </is>
       </c>
       <c r="T126" t="inlineStr">
@@ -9838,11 +9586,6 @@
       <c r="V126" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W126" t="inlineStr">
-        <is>
-          <t>SRC-0124, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -9898,11 +9641,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>The **Field Firing Range of Alcochete** is a military proving ground and training facility located in the Lisbon and Tagus Valley region, approximately 30 kilometers east of Lisbon, Portugal [SRC-0149]. Covering an expansive surface area of 7,539 hectares, the installation has historically served as a critical testing and training area for the nation's armed forces [SRC-0149].
-**History and Operations**
-The facility was originally established and opened in 1904, functioning primarily as an artillery and bombing range [SRC-0149]. Over the decades, it has supported various military operations, tests, and exercises. In 1993, the control and administration of the proving ground were officially transferred to the Portuguese Air Force [SRC-0149]. Despite being under Air Force jurisdiction, the firing range remains a joint-use facility. It is actively utilized by other branches of the Portuguese military, as well as various law enforcement agencies, to conduct vital training exercises and weapons testing [SRC-0149]. 
-**Current Status and Future Relocation**
-The current status of the Field Firing Range of Alcochete is transitional. The historic proving ground is scheduled to be closed and relocated to accommodate major civilian infrastructure development in the region [SRC-0149]. Specifically, the site is slated to be replaced by the new Luís de Camões Airport, a major aviation project that is currently projected to open in 2034 [SRC-0149]. As a result of this development, the Portuguese Air Force is planning to relocate the military proving ground operations, with the municipality of Mértola in the Alentejo region being considered as a possible new location for the facility [SRC-0149, SRC-0149].</t>
+          <t>An artillery and bombing range facility operating since 1904.</t>
         </is>
       </c>
       <c r="T127" t="inlineStr">
@@ -9918,11 +9657,6 @@
       <c r="V127" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>SRC-0149</t>
         </is>
       </c>
     </row>
@@ -10123,9 +9857,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>Aegis Ashore Romania is an operational land-based missile defense installation deployed in Romania to support the integrated defense of NATO’s European territory and allied military forces [SRC-0093, SRC-0134]. The facility serves as a critical strategic component aimed at countering ballistic missile threats that originate from outside the Euro-Atlantic region [SRC-0093]. The establishment and operationalization of this site represent a key milestone and contribution by the United States Missile Defense Agency (MDA) to Phase 3 of the European Phased Adaptive Approach (EPAA) [SRC-0093]. 
-Technologically, the Aegis Ashore system in Romania is specifically designed and equipped to launch advanced Standard Missile-3 (SM-3) interceptors, which notably includes both the SM-3 Block IBTU and the SM-3 Block IIA missile variants [SRC-0093]. The development of the Aegis Ashore architecture leverages decades of United States investment in advanced radar technologies and missile defense systems, building heavily upon the proven capabilities of the maritime Aegis Combat System [SRC-0101]. 
-To ensure the operational success, safety, and reliability of the Romanian deployment, extensive research, development, and live-fire testing were conducted at the Aegis Ashore Missile Defense Test Complex (AAMDTC) [SRC-0134]. This test complex is located at the Pacific Missile Range Facility (PMRF) in Kauai, Hawaii [SRC-0134]. The PMRF testing facility, which was established specifically for research and evaluation purposes, has been instrumental in rigorously evaluating the Aegis Ashore systems before their active operational deployment in Romania and other international locations [SRC-0134]. Currently, the Aegis Ashore Romania site remains fully operational, functioning as a cornerstone of NATO's ballistic missile defense shield in Europe [SRC-0093, SRC-0134].</t>
+          <t>A strategic ballistic missile defense installation supporting NATO's European Phased Adaptive Approach.</t>
         </is>
       </c>
       <c r="T130" t="inlineStr">
@@ -10141,11 +9873,6 @@
       <c r="V130" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W130" t="inlineStr">
-        <is>
-          <t>SRC-0093, SRC-0134, SRC-0101</t>
         </is>
       </c>
     </row>
@@ -10904,9 +10631,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>The Aberporth Range is a rocket launch and aerospace testing facility located in Wales, near the town of Aberystwyth [SRC-0162]. Situated at the geographical coordinates of 52.1°N, 4.3°W, the site is operated and governed by the Defence Evaluation and Research Agency (DERA) [SRC-0162]. 
-Historically, the Aberporth Range has functioned as a suborbital launch site, contributing to regional aerospace testing and evaluation efforts [SRC-0162]. The range is most notably associated with the launch of the Skylark, a British sounding rocket utilized heavily during the mid-to-late 20th century for various scientific, atmospheric, and technological missions [SRC-0162]. 
-While the site is recognized in global registries of rocket launch facilities, the provided sources do not contain further detailed information regarding its exact founding year, an extensive operational history, specific radar and tracking infrastructure, or its current active status. Due to this limitation of available source data, a more comprehensive description of the facility's day-to-day operations and modern capabilities cannot be generated.</t>
+          <t>A missile testing and rocket range in Wales historically used for Skylark rockets.</t>
         </is>
       </c>
       <c r="T141" t="inlineStr">
@@ -10922,11 +10647,6 @@
       <c r="V141" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W141" t="inlineStr">
-        <is>
-          <t>SRC-0162</t>
         </is>
       </c>
     </row>
@@ -11060,8 +10780,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>Spaceport Cornwall is an aerospace facility located in Newquay, Cornwall, England, UK, and operates in association with the United Kingdom Space Agency (UKSA) [SRC-0031, SRC-0096]. The site was developed as a key component of the UK government's LaunchUK programme, which aimed to establish a domestic network of spaceports to capture a share of the growing commercial spaceflight market [SRC-0096, SRC-0174, SRC-0174]. Capitalizing on the UK's geography for accessing low Earth orbit, Spaceport Cornwall was distinctively designed to support horizontal launch operations rather than traditional vertical rocket launches [SRC-0174, SRC-0221].
-The spaceport's most notable operational activity occurred when it hosted its first and only attempted space launch [SRC-0174, SRC-0221]. This historic mission was conducted by Virgin Orbit, a private aerospace company that utilized a modified Boeing 747 aircraft to air-launch small satellites into orbit [SRC-0174, SRC-0221]. However, the highly anticipated horizontal launch attempt ultimately ended in failure [SRC-0221]. Following this unsuccessful mission, Virgin Orbit suffered severe financial difficulties and eventually declared bankruptcy [SRC-0174, SRC-0221]. Due to the complete collapse of its primary commercial launch partner, Spaceport Cornwall is currently inactive for space launch operations [SRC-0221]. The provided sources do not detail the spaceport's specific radar facilities, precise founding date, or internal administrative structure beyond its UKSA affiliation [SRC-0031, SRC-0221].</t>
+          <t>A spaceport in England intended for horizontal rocket launches.</t>
         </is>
       </c>
       <c r="T143" t="inlineStr">
@@ -11077,11 +10796,6 @@
       <c r="V143" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>SRC-0031, SRC-0096, SRC-0174, SRC-0221</t>
         </is>
       </c>
     </row>
@@ -11132,9 +10846,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>Sutherland Spaceport is a proposed rocket launch facility located on the Scottish mainland in the Scottish Highlands, near the settlement of Tongue [SRC-0221, SRC-0161, SRC-0176]. The site was initially conceived as part of the UK government's strategic initiative to establish a domestic commercial space industry, specifically targeting the launch of small satellites into polar and sun-synchronous orbits [SRC-0174, SRC-0161]. The ambitious project officially received formal planning approval from the Scotland Highland Council in August 2020 [SRC-0096].
-The primary commercial operator slated to use the Sutherland facility was the UK-based rocket manufacturer Orbex [SRC-0221, SRC-0176]. However, the development of the spaceport encountered critical and ultimately fatal obstacles. In October 2024, Orbex announced a major strategic shift, declaring its intention to completely mothball the proposed Sutherland spaceport project [SRC-0176]. The company decided to relocate its planned launch operations to the SaxaVord Spaceport on the Shetland Islands, citing that SaxaVord was in a significantly more advanced state of development and operational readiness [SRC-0176]. 
-The viability of the Sutherland project collapsed completely shortly thereafter. Orbex faced severe financial difficulties, ultimately becoming insolvent and permanently ceasing all operations in February 2026 [SRC-0221, SRC-0176]. Consequently, following the bankruptcy of its anchor tenant and main launch provider, the Sutherland Spaceport project remains frozen and mothballed, with no active space launches occurring at the site [SRC-0221, SRC-0176].</t>
+          <t>A planned vertical launch spaceport in the Scottish Highlands.</t>
         </is>
       </c>
       <c r="T144" t="inlineStr">
@@ -11150,11 +10862,6 @@
       <c r="V144" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC-0221, SRC-0161, SRC-0176, SRC-0174, SRC-0096</t>
         </is>
       </c>
     </row>
@@ -11271,9 +10978,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>Ascension Island is a remote Atlantic island located at geographical coordinates 7°58′29″S 14°24′53″W [SRC-0096]. Although it is a British territory, the island plays a highly strategic role as a major down-range tracking station for the United States' Eastern Range (ER), a vast space and missile tracking network managed by the 45th Space Wing stationed at Patrick Air Force Base [SRC-0118, SRC-0189]. The Eastern Range infrastructure extends from Newfoundland across the Atlantic, terminating at Ascension Island [SRC-0189].
-The island is outfitted with an array of sophisticated tracking, radar, and telemetry facilities to monitor ballistic missiles and orbital space launches continuously from liftoff [SRC-0069, SRC-0106]. Its key infrastructure includes precision metric tracking radars that use both beacon and echo tracking to supply real-time flight data to central command computers [SRC-0106]. Ascension also features advanced metric optics capabilities, housing precision theodolites, ballistic cameras, and long-range large-aperture telescopes [SRC-0106].
-To support crucial data acquisition, Ascension Island relies on post-detect telemetry systems and land-based stations that transmit real-time telemetry back to the mainland via satellite communications (SATCOM) [SRC-0189, SRC-0106, SRC-0118]. However, unlike several other down-range stations, Ascension Island does not possess telemetry doppler data capabilities for metric measurements [SRC-0106]. Additionally, the site supports the Missile Impact Location System (MILS), utilizing a target array of bottom-mounted hydrophones located near the island to record impact data from reentry vehicles [SRC-0106]. Historically, during the late 1950s, the U.S. military deployed modified radar and telemetry ships between Antigua and Ascension Island to recover launch reentry vehicles and collect vital weather data [SRC-0192]. Today, Ascension Island remains a critical node in global space domain tracking.</t>
+          <t>A British overseas territory utilized as a tracking station and historical launch site for the Eastern Range.</t>
         </is>
       </c>
       <c r="T146" t="inlineStr">
@@ -11289,11 +10994,6 @@
       <c r="V146" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>SRC-0096, SRC-0118, SRC-0189, SRC-0069, SRC-0106, SRC-0192</t>
         </is>
       </c>
     </row>
@@ -11943,9 +11643,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>Utingu, commonly known as Punsand Bay, is a geographical location in Australia that has been associated with the development of aerospace and rocket launch infrastructure [SRC-0096]. Situated in Bamaga, the area operates under the local government jurisdiction of the council of the Torres Strait Island Region [SRC-0096]. 
-Historically, the site was identified as a secondary launch facility for Space Centre Australia, intended to complement the organization's primary site facilities located further south near RAAF Scherger on the Cape York Peninsula [SRC-0096]. A key strategic and geographical advantage of Utingu Punsand Bay is its extreme northern latitude. It is noted as being one of the closest facilities to equatorial launch access in the entire Asia Pacific region [SRC-0096]. Proximity to the equator is a highly desirable trait for spaceports, as it provides launch vehicles with an equatorial velocity boost, increasing payload capacity and launch efficiency.
-Despite these geographic benefits and its formal designation as a secondary site for Space Centre Australia, the facility is currently categorized strictly under "past and/or planned only" spaceports [SRC-0096]. While the overarching Space Centre Australia project has been active in securing land for its main site, the provided sources do not detail a specific founding year, the presence of key facilities, tracking radars, or any notable launch activities that have actually taken place at the Utingu Punsand Bay site [SRC-0096]. Its current status remains that of a planned or historical concept rather than an active, operational orbital spaceport [SRC-0096].</t>
+          <t>Secondary launch site known for its close equatorial launch access in the Asia Pacific region.</t>
         </is>
       </c>
       <c r="T155" t="inlineStr">
@@ -11961,11 +11659,6 @@
       <c r="V155" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W155" t="inlineStr">
-        <is>
-          <t>SRC-0096</t>
         </is>
       </c>
     </row>
@@ -12021,9 +11714,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>Christmas Island is an Australian external territory located in the Indian Ocean that has a notable history of planned and executed aerospace testing and rocket launch activities [SRC-0096]. The island's formal involvement in the space industry began taking shape in the late 1990s. In 1997, a major commercial project was planned by the Asia Pacific Space Centre to establish a dedicated launch site on the island [SRC-0096]. This proposed spaceport was part of a collaborative aerospace plan involving both Australia and Japan [SRC-0094]. However, despite the initial planning and international interest, the spaceport project ultimately did not proceed due to insufficient financial backing [SRC-0096].
-Although the 1997 commercial spaceport did not materialize into a permanent governing organization, Christmas Island later served as a successful testing ground for international aerospace research. In 2002, the Japan Aerospace Exploration Agency (JAXA) successfully utilized the island for Phase I of its High Speed Flight Demonstration (HSFD) program [SRC-0096]. These notable flight tests and demonstrations were conducted at Aeon Field, an existing airfield located on Christmas Island [SRC-0096].
-Today, Christmas Island is classified among past and/or planned rocket launch sites [SRC-0096]. The provided sources do not contain further detailed information regarding a specific founding year for a permanent spaceport, the installation of permanent tracking radars, or any subsequent spaceflight activities beyond the 2002 JAXA demonstration [SRC-0096]. Its current status is inactive regarding ongoing orbital rocket launches.</t>
+          <t>Planned launch site and location of a 2002 High Speed Flight Demonstration by Japan.</t>
         </is>
       </c>
       <c r="T156" t="inlineStr">
@@ -12039,11 +11730,6 @@
       <c r="V156" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
-        <is>
-          <t>SRC-0096, SRC-0094</t>
         </is>
       </c>
     </row>
@@ -12246,7 +11932,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>The ARPA Long-Range Tracking and Instrumentation Radar (ALTAIR) is a highly sensitive tracking radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island in the Kwajalein Atoll, Marshall Islands [SRC-0071, SRC-0071, SRC-0150]. Conceived in the early 1960s to study U.S. strategic weapon performance against large Soviet radars, ALTAIR became operational in 1970 [SRC-0071, SRC-0071]. The facility is governed under the Ronald Reagan Ballistic Missile Defense Test Site by the U.S. Army Space and Missile Defense Command [SRC-0150, SRC-0151]. ALTAIR operates at both VHF and UHF frequencies and features a massive 150-foot diameter antenna that rotates on a 110-foot circular track [SRC-0071, SRC-0071]. Despite its rotating portion weighing almost a million pounds, the system is exceptionally agile and capable of tracking deep reentry vehicles [SRC-0071]. ALTAIR is notable for its immense power-aperture product, which allows it to consistently acquire ballistic missile targets launched from Vandenberg Space Force Base over 3500 kilometers away [SRC-0071, SRC-0071]. In 1977, ALTAIR's mission expanded into space surveillance; it now serves as a central node for detecting new foreign space launches and tracking deep-space satellites for the U.S. Space Command [SRC-0071, SRC-0071]. Additionally, ALTAIR supports complex scientific research, such as NASA's sounding rocket tests and the generation of highly precise, GPS-driven vertical ionospheric models [SRC-0071, SRC-0151]. ALTAIR remains an actively modernized, heavily utilized asset at the range [SRC-0071, SRC-0071].</t>
+          <t>ARPA Long-Range Tracking and Instrumentation Radar utilized for deep-space tracking and tracking space launches.</t>
         </is>
       </c>
       <c r="T159" t="inlineStr">
@@ -12262,11 +11948,6 @@
       <c r="V159" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W159" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12322,7 +12003,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>The Target Resolution and Discrimination Experiment (TRADEX) is a precision instrumentation radar situated at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, Kwajalein Atoll, within the Marshall Islands [SRC-0071, SRC-0071]. It holds the distinction of being the first radar fielded at KREMS, becoming fully operational and accepted by the Advanced Research Projects Agency in December 1962 [SRC-0071, SRC-0071]. The facility falls under the governance of the U.S. Army Space and Missile Defense Command as part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0150, SRC-0151]. Initially designed with an 84-foot antenna operating as a UHF tracker and L-band illuminator, TRADEX was an early pioneer of pulse compression waveforms for high sensitivity and precise range resolution [SRC-0071, SRC-0071]. In 1970, the radar was shut down for a major redesign that removed its UHF tracking capability and replaced it with a dual-frequency L-band and S-band system [SRC-0071]. TRADEX has played a pivotal role in ballistic missile defense development, acting as the primary testbed for discrimination techniques and algorithms for systems like Nike-X, Safeguard, and Site Defense [SRC-0071, SRC-0071]. In its current status, TRADEX operates as a dedicated contributing sensor for the Space Surveillance Network, providing deep-space tracking while also continuing its mission of gathering signature data on ballistic missiles and validating modern naval Aegis BMD waveforms [SRC-0071, SRC-0071].</t>
+          <t>Target Resolution and Discrimination Experiment radar used for missile tracking.</t>
         </is>
       </c>
       <c r="T160" t="inlineStr">
@@ -12338,11 +12019,6 @@
       <c r="V160" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12074,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>The ARPA-Lincoln C-band Observables Radar (ALCOR) is a high-power tracking and imaging radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island in the Kwajalein Atoll [SRC-0071, SRC-0071]. Managed by the U.S. Army Space and Missile Defense Command under the Reagan Test Site, ALCOR was authorized for development in 1965 and became operational in January 1970 [SRC-0150, SRC-0071, SRC-0071]. ALCOR operates in the C-band and is enclosed within a prominent radome [SRC-0071, SRC-0071]. It was historically significant as the United States' first high-power, long-range, wideband radar [SRC-0071]. ALCOR originally utilized 500 MHz chirped pulses to achieve extraordinary range resolution, allowing researchers to measure the exact length of threat objects and discern individual scattering centers on reentry vehicles [SRC-0071, SRC-0071]. This capability was instrumental in proving the value of wideband radars for ballistic missile discrimination [SRC-0071]. Furthermore, ALCOR achieved a major technological milestone in 1971 when it became the first radar to successfully apply inverse synthetic aperture radar (ISAR) imaging techniques to orbiting satellites, profoundly advancing the field of space-object identification [SRC-0071]. Today, ALCOR maintains an active and critical operational status at the Reagan Test Site [SRC-0071, SRC-0071]. Following a 1999 modernization to the Radar Open System Architecture, it continues to track main rocket bodies, identify space debris, and capture real-time wideband signatures [SRC-0071, SRC-0071, SRC-0151].</t>
+          <t>ARPA Lincoln C-Band Observables Radar providing high-resolution imaging capabilities.</t>
         </is>
       </c>
       <c r="T161" t="inlineStr">
@@ -12414,11 +12090,6 @@
       <c r="V161" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12145,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>The Millimeter-Wave (MMW) radar is a highly advanced imaging and tracking system located on Roi-Namur island in the Kwajalein Atoll, Marshall Islands [SRC-0071, SRC-0071]. Operated under the Ronald Reagan Ballistic Missile Defense Test Site by the U.S. Army Space and Missile Defense Command, the MMW radar was developed to meet the growing need for high-resolution target data and became operational in 1983 [SRC-0150, SRC-0071, SRC-0071]. Operating in the Ka-band, the MMW radar is enclosed in a protective radome and features a specialized optical beam waveguide system designed to reduce microwave losses [SRC-0071, SRC-0071]. The radar's very short wavelength significantly increases the number of visible scattering centers on a target, allowing it to produce incredibly detailed images [SRC-0071]. Because of this, it quickly became the premier imaging system at the Kiernan Reentry Measurements Site (KREMS) for space-object identification [SRC-0071]. MMW's precision also makes it an essential asset for Ballistic Missile Defense testing, as it can accurately measure the miss distance and impact point of kinetic interceptors [SRC-0071]. In 1987, it was integrated with the Kwajalein Discrimination System to provide real-time imaging of reentry vehicles [SRC-0071]. Upgraded in 2000 under the Radar Open System Architecture program, the MMW radar remains fully operational today, continuously supporting U.S. Strategic Command space missions and missile test operations [SRC-0150, SRC-0071].</t>
+          <t>Millimeter-Wave imaging radar used for space surveillance and detailed intelligence data collection.</t>
         </is>
       </c>
       <c r="T162" t="inlineStr">
@@ -12490,11 +12161,6 @@
       <c r="V162" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W162" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0150</t>
         </is>
       </c>
     </row>
@@ -12682,9 +12348,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>Bikini Atoll is a geographic feature and former weapons testing site located in the Ralik (Sunset) Chain of the Marshall Islands in the Pacific Ocean [SRC-0163]. The atoll is situated at the coordinates 11°36′54″N 165°33′11″E [SRC-0096]. Historically, Bikini Atoll served as a primary location for the Pacific Proving Grounds, an extensive reservation established by the United States Atomic Energy Commission in the year 1946 [SRC-0149]. The governing organization for these proving grounds was the United States Department of Energy [SRC-0149].
-The most notable activities conducted at Bikini Atoll centered around the United States' nuclear weapons testing program [SRC-0149, SRC-0163]. In addition to nuclear detonations, the atoll was utilized as a rocket launch site; these rocket launches were conducted specifically in conjunction with the nuclear bomb tests to support the testing program's objectives [SRC-0096]. While detailed information on specific key facilities or radars at the atoll is not provided in the available sources, its primary function was fully dedicated to these explosive and rocket testing operations.
-Operating alongside Enewetak Atoll and the surrounding areas, Bikini Atoll played a significant role in the testing of advanced weapons technologies until the Pacific Proving Grounds were officially deactivated in 1963 [SRC-0149]. Regarding its current status, the testing facilities at Bikini Atoll are inactive, and the site remains an inactive U.S. Department of Energy area [SRC-0149].</t>
+          <t>Pacific Proving Grounds site formerly used for launches in conjunction with nuclear bomb tests.</t>
         </is>
       </c>
       <c r="T165" t="inlineStr">
@@ -12700,11 +12364,6 @@
       <c r="V165" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC-0163, SRC-0096, SRC-0149</t>
         </is>
       </c>
     </row>
@@ -12755,9 +12414,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>Eniwetok (also spelled Enewetak) is an atoll located in the western Ralik (Sunset) Chain of the Marshall Islands in the Pacific Ocean [SRC-0163]. Positioned at the exact coordinates of 11°20′24″N 162°19′30″E, it served as a significant site for mid-twentieth-century military experimentation [SRC-0096]. Along with Bikini Atoll, Eniwetok was one of the primary components of the Pacific Proving Grounds, a designated testing area established in 1946 by the United States Atomic Energy Commission [SRC-0149]. The site fell under the jurisdiction and governing organization of the United States Department of Energy [SRC-0149].
-During its operational years, Eniwetok was primarily utilized for nuclear weapons testing [SRC-0149]. As part of these operations, the atoll functioned as a rocket launch site, with various rocket launches executed in direct conjunction with the nuclear bomb tests taking place at the facility [SRC-0096]. While the sources do not detail specific key facilities, buildings, or radar installations located on the atoll, its infrastructure was fully dedicated to supporting these nuclear and rocket test missions.
-The testing installations at Eniwetok were heavily utilized until the broader Pacific Proving Grounds were deactivated in 1963 [SRC-0149]. Regarding its current status, the Eniwetok testing site is classified as an inactive U.S. Department of Energy area [SRC-0149].</t>
+          <t>Pacific Proving Grounds site formerly used for launches in conjunction with nuclear bomb tests.</t>
         </is>
       </c>
       <c r="T166" t="inlineStr">
@@ -12773,11 +12430,6 @@
       <c r="V166" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W166" t="inlineStr">
-        <is>
-          <t>SRC-0163, SRC-0096, SRC-0149</t>
         </is>
       </c>
     </row>
@@ -13059,9 +12711,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>The Eastern Range (ER) is a massive United States launch range extending from Argentia in Newfoundland to Ascension Island in the South Atlantic Ocean [SRC-0189]. The range operates primarily out of the Cape Canaveral Space Force Station and the Kennedy Space Center in Florida [SRC-0189, SRC-0118]. Constructed in the 1950s and early 1960s to serve as research and development facilities for early missile programs [SRC-0189], the ER is currently governed by the United States Space Force (USSF) and managed by Space Launch Delta 45 (formerly the 45th Space Wing), headquartered at Patrick Space Force Base [SRC-0189, SRC-0202].
-The primary mission of the Eastern Range is to support safe and secure space and ballistic missile launches, aeronautical operations, and space surveillance for the Department of Defense, NASA, and commercial entities [SRC-0202, SRC-0189]. To accomplish this, the range utilizes a vast array of key facilities and instrumentation, including precision tracking radars, telemetry processing systems, optic tracking systems, and the Flight Termination System (FTS) [SRC-0118, SRC-0202]. The ER incorporates the Network CORE communication backbone and downrange tracking sites in Antigua and Ascension Island [SRC-0118, SRC-0118]. Furthermore, support ships such as the USNS Howard O. Lorenzen and USNS Invincible provide critical radar tracking data in broad ocean areas where ground stations cannot reach [SRC-0192, SRC-0192, SRC-0192].
-In recent years, the Eastern Range has experienced a massive increase in operations. After a "Drive for 48" initiative aimed at supporting 48 launches a year [SRC-0203], the range supported a record-breaking 109 orbital flights in 2025 [SRC-0203, SRC-0202]. Currently active and expanding under a "Spaceport of the Future" infrastructure initiative, the ER aims to accommodate 500 or more launches annually by 2030, remaining the dominant space launch hub in the United States [SRC-0203].</t>
+          <t>Florida space launch range for polar and geostationary orbits.</t>
         </is>
       </c>
       <c r="T170" t="inlineStr">
@@ -13077,11 +12727,6 @@
       <c r="V170" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W170" t="inlineStr">
-        <is>
-          <t>SRC-0189, SRC-0118, SRC-0202, SRC-0192, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -13137,9 +12782,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>Cape Canaveral Space Force Station (CCSFS) is a premier military space launch facility located on Cape Canaveral in Brevard County, Florida, situated south-southeast of NASA's Kennedy Space Center on Merritt Island [SRC-0031]. The site was established in 1949 by President Harry S. Truman as the Joint Long Range Proving Ground [SRC-0031]. Following a transfer of land from the Navy to the Air Force, it was designated the Long Range Proving Ground Base in 1950 [SRC-0031]. Over the decades, the site underwent several name changes, including Cape Kennedy Air Force Station, before officially becoming Cape Canaveral Space Force Station in December 2020 [SRC-0031].
-Governed by the United States Space Force and operated by Space Launch Delta 45, CCSFS acts as the primary launch site for the Eastern Range [SRC-0031]. The station’s key facilities include four highly active space launch complexes (SLC-36, SLC-40, SLC-41, and SLC-46), Landing Zone 40, and a 10,000-foot Skid Strip runway used by heavy military airlift aircraft to transport satellite payloads [SRC-0031, SRC-0031, SRC-0031]. Additionally, the site hosts the Naval Ordnance Test Unit (NOTU), which tests sea-based weapons and Fleet Ballistic Missiles [SRC-0031, SRC-0031].
-Cape Canaveral has an exceptionally notable history in spaceflight. It was the launch site for the first U.S. Earth satellite in 1958, the first U.S. astronaut in orbit in 1962, and early spacecraft to orbit Mars, Saturn, and Mercury [SRC-0031]. During the Cold War, the facility tested major missile systems including the Redstone, Jupiter, Polaris, Atlas, and Titan [SRC-0031]. Today, the station remains highly active, partnering heavily with commercial space industry leaders. Private companies such as SpaceX, United Launch Alliance, and Blue Origin lease and operate launch pads at the site, launching Falcon 9, Vulcan Centaur, and New Glenn rockets into orbit [SRC-0031].</t>
+          <t>Launch and testing site located on the Eastern Range.</t>
         </is>
       </c>
       <c r="T171" t="inlineStr">
@@ -13155,11 +12798,6 @@
       <c r="V171" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC-0031</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13005,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>The Ronald Reagan Ballistic Missile Defense Test Site (RTS), formerly known as Kwajalein Missile Range, is located in the Kwajalein Atoll of the Republic of the Marshall Islands, situated in the central Pacific Ocean [SRC-0071, SRC-0150]. Established in 1959 when the atoll was chosen to test the Nike-Zeus antiballistic missile system, the site has grown into a premier Department of Defense Major Range and Test Facility Base [SRC-0071, SRC-0071, SRC-0150]. It is governed by the U.S. Army Space and Missile Defense Command (USASMDC) [SRC-0150]. Operations are controlled remotely from the RTS Operation Center in Huntsville, Alabama (ROC-H) [SRC-0150]. The installation's key facilities include the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, which hosts four world-class instrumentation radars: ALTAIR, TRADEX, ALCOR, and MMW [SRC-0071, SRC-0071]. RTS also features extensive telemetry sites, optical tracking mounts like the Super RADOT, and a ship-based mobile range safety system [SRC-0071, SRC-0071, SRC-0071]. Notable activities at the site include developmental and operational flight tests for Air Force Minuteman III intercontinental ballistic missiles (Glory Trip missions), Army and Navy hypersonic boost-glide tests, and intercept demonstrations for Missile Defense Agency systems like THAAD, Patriot, and Aegis [SRC-0150, SRC-0150, SRC-0164]. Furthermore, RTS provides vital space domain awareness for U.S. Strategic Command and supports NASA scientific research, such as the SEED sounding rocket mission for ionospheric studies [SRC-0164, SRC-0151]. Today, RTS remains in active operational status, continuously modernized through distributed net-centric architecture [SRC-0071, SRC-0164].</t>
+          <t>The Ronald Reagan Ballistic Missile Defense Test Site (RTS), historically known as the Kwajalein Missile Range, is a premier United States military test range located on the Kwajalein Atoll in the Republic of the Marshall Islands, approximately 2,200 miles southwest of Hawaii [SRC-0106, SRC-0159]. Founded over 50 years ago, the site's technical operations began around 1962 when the TRADEX radar became operational, with the facility being officially renamed the Reagan Test Site in 1999 [SRC-0071, SRC-0071, SRC-0071]. The RTS is governed by the U.S. Army Space and Missile Defense Command (USASMDC), with technical leadership and scientific advisement provided by MIT Lincoln Laboratory [SRC-0159, SRC-0071, SRC-0164]. The site's primary mission includes testing intercontinental ballistic missiles (ICBMs), evaluating ballistic missile defense systems, and conducting space domain awareness [SRC-0164]. Key facilities are largely centered at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur island, which hosts four of the world's most sophisticated high-power instrumentation radars: ALTAIR (VHF/UHF), TRADEX (L/S band), ALCOR (C-band), and MMW (Ka-band) [SRC-0071, SRC-0071]. These systems provide unparalleled radar measurements, space-object tracking, and deep-space intelligence collection [SRC-0164, SRC-0106]. Additionally, the range relies on extensive telemetry sites, optical tracking systems like SRADOT, and underwater acoustic impact location systems [SRC-0164]. Currently, RTS operates as a government-managed, contractor-operated (GMCO) installation, with operations run remotely from the RTS Operation Center in Huntsville, Alabama (ROC-H) [SRC-0164, SRC-0150]. The facility routinely supports high-profile Department of Defense operations, such as the Air Force's "Glory Trip" Minuteman III tests, hypersonic boost-glide developmental tests, and NASA scientific missions, cementing its status as a critical node in U.S. national security and space surveillance networks [SRC-0164, SRC-0150, SRC-0151].</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
@@ -13387,7 +13025,7 @@
       </c>
       <c r="W174" t="inlineStr">
         <is>
-          <t>SRC-0071, SRC-0150, SRC-0164, SRC-0151</t>
+          <t>SRC-0106, SRC-0159, SRC-0071, SRC-0164, SRC-0150, SRC-0151</t>
         </is>
       </c>
     </row>
@@ -13519,9 +13157,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>White Sands Missile Range (WSMR) is a vast military testing area and firing range located in the Tularosa Basin of southern New Mexico [SRC-0218]. Covering approximately 3,200 square miles across Doña Ana, Otero, Socorro, Sierra, and Lincoln counties, it is the largest military installation in the United States [SRC-0218]. The installation was originally established in 1941 as the Alamogordo Bombing and Gunnery Range [SRC-0218]. It was officially designated as the White Sands Proving Ground on July 9, 1945, and later renamed White Sands Missile Range in May 1958 [SRC-0218, SRC-0218].
-Governed by the United States Army Test and Evaluation Command (ATEC), WSMR provides an overland range to support research and development testing for the Army, Navy, Air Force, NASA, and commercial partners [SRC-0218, SRC-0106]. Key facilities include multiple launch complexes (such as LC-33, LC-36, and LC-38), the White Sands Test Center, the High-Energy Laser Test Facility (HELSTF), and the Radar Target Backscatter Facility (RATSCAT) [SRC-0106, SRC-0106, SRC-0218, SRC-0218]. The range is also equipped with over 2,000 monumented instrumentation points and rare Multiple Object Tracking Radars (MOTR) used for flight safety operations [SRC-0106, SRC-0157].
-WSMR is famous for several historically significant events, most notably the Trinity test on July 16, 1945, the world's first atomic bomb detonation [SRC-0218]. Following World War II, the range hosted the testing of 67 captured German V-2 rockets [SRC-0218]. It was also the site of the only space shuttle landing outside of California or Florida, when Columbia landed on the Northrop Strip in 1982 [SRC-0218]. Currently active, WSMR conducts ongoing developmental testing of air defense systems, ballistic missiles, and electromagnetic countermeasures, while also housing protected natural areas like White Sands National Park [SRC-0106, SRC-0218, SRC-0218].</t>
+          <t>Vast overland military testing area and proving ground in New Mexico.</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
@@ -13537,11 +13173,6 @@
       <c r="V176" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W176" t="inlineStr">
-        <is>
-          <t>SRC-0218, SRC-0106, SRC-0157</t>
         </is>
       </c>
     </row>
@@ -13673,9 +13304,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>Dugway Proving Ground is an active and specialized military installation situated in the Great Salt Lake Desert of Utah [SRC-0149]. While its exact founding year is not specified in the provided records, the facility operates as a critical component of the Department of Defense's Major Range and Test Facility Base (MRTFB), which is a national asset maintained to support the DoD acquisition system [SRC-0085, SRC-0105]. The proving ground is governed and managed by the United States Army Test and Evaluation Command [SRC-0149].
-The primary mission and notable activities at Dugway Proving Ground revolve around the testing and evaluation of United States and Allied biological and chemical weapon defense systems [SRC-0149]. Unlike ranges focused heavily on ballistic missile or space launches, Dugway specializes in environmental testing, evaluating chemical and biological defense systems, and validating passive defense systems [SRC-0222]. The remote and harsh geography of the Utah desert provides a secure, isolated, and controlled environment necessary for these highly sensitive and hazardous evaluations. 
-As a core testing site, the proving ground relies on specific infrastructure to safely test these defensive capabilities, though exact radar or launch complex specifications are not heavily detailed in the sources [SRC-0149, SRC-0105]. Currently, Dugway Proving Ground remains an active and vital military testing location. Historically, the Department of Defense has recognized its ongoing importance by allocating millions of dollars in future infrastructure and range improvements to ensure its capabilities can meet the future needs of the military and the Army Test and Evaluation Command [SRC-0105, SRC-0105].</t>
+          <t>Army proving ground in Utah for biological and chemical defense testing.</t>
         </is>
       </c>
       <c r="T178" t="inlineStr">
@@ -13691,11 +13320,6 @@
       <c r="V178" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W178" t="inlineStr">
-        <is>
-          <t>SRC-0149, SRC-0085, SRC-0105, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -13827,9 +13451,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>Aberdeen Test Center is located at the Aberdeen Proving Ground on the western shore of the Chesapeake Bay, approximately 30 miles northeast of Baltimore, Maryland [SRC-0149, SRC-0106]. Established on October 20, 1917, just six months after the United States entered World War I, it holds the distinction of being the United States Army's oldest active proving ground [SRC-0149]. It was originally constructed to ensure that the design and testing of ordnance materiel could be conducted in close proximity to the nation's industrial and shipping hubs [SRC-0149]. The facility is governed and operated by the United States Army [SRC-0149, SRC-0222].
-The testing center boasts expansive facilities, including 79,000 acres of land and water dedicated to firing and explosive testing, as well as 3,000 acres strictly for automotive system evaluations [SRC-0106]. Key facilities include ten major automotive test areas covering 39 miles of severe terrain courses, such as the Munson Test Course, Perryman Test Course, and Churchville Test Area, which feature steep hills, mud, and staggered bumps to test vehicle endurance [SRC-0106]. For weaponry, the Main Front Area provides 28 firing positions and restricted airspace for range firings out to 34,000 meters [SRC-0106].
-Notable activities at the Aberdeen Test Center involve the developmental testing of artillery weapon systems, mortars, recoilless rifles, armored vehicles, and air defense systems [SRC-0106]. The site also conducts rigorous environmental and vulnerability tests, assessing live ammunition and warheads against vibration, temperature extremes, fungus, salt fog, and electromagnetic interference [SRC-0222, SRC-0106]. Today, the Aberdeen Test Center remains a fully active proving ground, continuing its century-long legacy of evaluating the durability, ballistic vulnerability, and overall performance of military vehicles and ordnance for the U.S. Armed Forces [SRC-0149, SRC-0222, SRC-0106].</t>
+          <t>Army proving ground and testing center in Maryland.</t>
         </is>
       </c>
       <c r="T180" t="inlineStr">
@@ -13845,11 +13467,6 @@
       <c r="V180" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W180" t="inlineStr">
-        <is>
-          <t>SRC-0149, SRC-0106, SRC-0222</t>
         </is>
       </c>
     </row>
@@ -13905,9 +13522,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>The Nevada Test and Training Range (NTTR) is a massive military testing and training installation located within the Nellis Air Force Base Complex in southern Nevada [SRC-0149, SRC-0222]. Originally associated with the adjacent Nevada National Security Site (formerly the Nevada Proving Grounds) [SRC-0149], the NTTR is governed and operated by the United States Air Force [SRC-0222]. It serves as a major component of the Department of Defense's Major Range and Test Facility Base (MRTFB) [SRC-0085].
-The NTTR encompasses specialized air and ground sectors designed for rigorous combat simulations. Key facilities include the North Ranges, which feature the Tonopah and Tolicha Peak Electronic Combat (EC) areas [SRC-0106]. These areas provide highly realistic enemy radar environments for aircrew training [SRC-0106]. The tactical ranges, such as Range 71, are equipped with simulated missile sites, airfields, convoys, and nuclear bombing circles where live and inert ordnance can be deployed [SRC-0106]. The South Ranges similarly offer realistic ground target simulations, including ICBM sites and targets in and around Dogbone Lake [SRC-0106]. 
-Notable activities at the NTTR focus on advanced tactical warfare training, including air-to-air and air-to-ground munitions delivery, and air combat maneuvering [SRC-0222, SRC-0106]. The range is essential for conducting Operational Test and Evaluation (OT&amp;E) and hosting major large-force exercises like Red Flag and Gallant Eagle [SRC-0106]. Currently, the Nevada Test and Training Range remains a fully active and premier training hub for the Air Force. Recognizing its critical role in national security and pilot readiness, the military has planned significant investments for the NTTR, including over $450 million in infrastructure and test asset improvements to support future weapon systems testing and advanced electronic warfare simulations [SRC-0222, SRC-0105].</t>
+          <t>Air Force training and testing range in Nevada.</t>
         </is>
       </c>
       <c r="T181" t="inlineStr">
@@ -13923,11 +13538,6 @@
       <c r="V181" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W181" t="inlineStr">
-        <is>
-          <t>SRC-0149, SRC-0222, SRC-0085, SRC-0106, SRC-0105</t>
         </is>
       </c>
     </row>
@@ -13983,7 +13593,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>The Utah Test and Training Range (UTTR) is located in the Great Salt Lake Desert, approximately 70 miles west of Salt Lake City, Utah [SRC-0106]. The range encompasses 2,136 square nautical miles of Department of Defense-owned landspace [SRC-0106], split into two primary restricted areas: the North Range and the South Range, bounded by military operating areas with restricted airspace extending from the surface up to 58,000 feet [SRC-0106]. UTTR is managed by the 6501st Range Squadron out of Hill Air Force Base, which operates under the 6545th Test Group and the Air Force Flight Test Center (AFFTC) [SRC-0106]. The installation provides extensive range facilities for the test and evaluation of manned and unmanned aircraft systems, as well as tactical training for air-to-air and air-to-ground weapon delivery [SRC-0106]. Its sophisticated instrumentation network includes the High Accuracy Multiple Object Tracking System (HAMOTS), which collects time-space-position information, alongside precision tracking radars, surveillance radars, and cinetheodolites [SRC-0106], [SRC-0106]. Operations are overseen from the Mission Control Center at Hill AFB, which is equipped for real-time data collection and display [SRC-0106]. UTTR houses numerous specialized target facilities, such as the Eagle Range for air-to-ground scoring, the Kitty Cat Range for live ordnance drops, and the Wildcat and Baker's Strongpoint Ranges, which feature simulated industrial complexes, convoys, and surface-to-air missile sites [SRC-0106]. Notable activities conducted at the range include the testing of cruise missiles (such as the ALCM and GLCM), Maverick missiles, conventional munitions shelf-life testing, and full-spectrum joint training exercises [SRC-0106].</t>
+          <t>Air Force range in Utah supporting missile and guided weapons testing.</t>
         </is>
       </c>
       <c r="T182" t="inlineStr">
@@ -13999,11 +13609,6 @@
       <c r="V182" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W182" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
         </is>
       </c>
     </row>
@@ -14059,7 +13664,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>The Arnold Engineering Development Complex (AEDC), historically referred to as the Arnold Engineering Development Center, is situated in middle Tennessee, roughly 72 miles southeast of Nashville and 61 miles northwest of Chattanooga [SRC-0106]. It occupies a 40,000-acre reservation, allowing it to operate with minimal environmental impact while accommodating advanced test facilities [SRC-0106]. AEDC manages, develops, and operates critical ground environmental test facilities dedicated to the research and development of aerospace systems [SRC-0106]. The complex simulates aerodynamic, propulsion, and space flight environments to support a wide range of government and commercial users [SRC-0106]. AEDC is equipped with uniquely advanced testing infrastructure. It houses nine wind tunnels covering Mach 0.2 to 10, including the nation's only 16-foot transonic and supersonic wind tunnels capable of airframe and propulsion integration testing under controlled altitude conditions [SRC-0106]. Other key facilities include arc heater test units like the Dust Erosion Tunnel and High Enthalpy Ablation Test Facility, aeroballistic and impact ranges capable of accelerating models to 23,500 feet per second, and multiple turbojet and turbofan test cells [SRC-0106]. These robust capabilities enable AEDC to support testing for an extensive array of notable military programs. Historical and ongoing projects supported at the complex include the B-1 and F-15/16 aircraft, various air-launched cruise missiles, the Peacekeeper and Minuteman ICBMs, the Trident missile, and the Space Shuttle [SRC-0106].</t>
+          <t>Air Force complex in Tennessee focused on aerodynamic and propulsion testing.</t>
         </is>
       </c>
       <c r="T183" t="inlineStr">
@@ -14075,11 +13680,6 @@
       <c r="V183" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W183" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
         </is>
       </c>
     </row>
@@ -14211,7 +13811,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>The Naval Air Warfare Center Weapons Division (NAWCWD) operates extensive test and evaluation facilities at China Lake, located in the upper Mojave Desert about 150 miles northeast of Los Angeles, California [SRC-0106]. As a premier military proving ground and testing facility [SRC-0149], [SRC-0195], the China Lake complex spans 1.1 million acres of land and incorporates 17,000 square miles of the R-2508 restricted military airspace [SRC-0195]. NAWCWD China Lake is responsible for the development, testing, and evaluation of air- and surface-launched weapons, electronic warfare systems, missiles, and parachute systems [SRC-0106]. The installation features specialized testing zones, including Air Operation Ranges (Air Weapons Range, Air Tactics Range, and Military Target Range) for evaluating fire-control systems and guided weapons against fixed and moving targets [SRC-0106]. It also houses Guided Missile Ranges for testing tactical air-defense systems, heavily instrumented Supersonic Test Tracks, and Explosive and Propulsion Test Ranges [SRC-0106], [SRC-0106]. The Electronic Warfare Threat Environment Simulation (EWTES) Facility, also known as the Electronic Combat Range, provides a simulated hostile defense environment for electronic countermeasures testing and tactics development [SRC-0106], [SRC-0195]. China Lake has supported a vast array of high-profile defense projects, including the integration and testing of TOMAHAWK and cruise missiles, HARM, SPARROW, SIDEWINDER, MAVERICK, and various Navy conventional ordnance systems [SRC-0106].</t>
+          <t>Major naval testing facility in California's Mojave Desert.</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
@@ -14227,11 +13827,6 @@
       <c r="V185" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W185" t="inlineStr">
-        <is>
-          <t>SRC-0106, SRC-0149, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -14365,7 +13960,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>The Naval Air Warfare Center Aircraft Division (NAWCAD) Patuxent River, historically known as the Naval Air Test Center, is situated in Lexington Park, Maryland, on the shores of the Chesapeake Bay approximately 45 miles southeast of Washington, D.C. [SRC-0106]. As a major component of the Department of Defense's test infrastructure, NAWCAD provides comprehensive technical and engineering support for the life cycle testing and evaluation of aircraft weapon systems [SRC-0106], [SRC-0195]. The installation features extensive airfield and flight test ranges, controlling 50,000 square miles of airspace, 39,375 square miles of sea space, and 7,950 acres of land space to support its research and development missions [SRC-0195]. NAWCAD Patuxent River encompasses state-of-the-art infrastructure, including the Air Combat Environment Test and Evaluation Facility (ACETEF) and Electromagnetic Environmental Effects Facilities, which allow for the thorough evaluation of electromagnetic interference, radiation hazards, and vulnerability [SRC-0106], [SRC-0195]. Its capabilities also include full-scale aircraft testing with operating engines and systems under normal power [SRC-0106], as well as air-breathing propulsion system test facilities [SRC-0195]. The site primarily performs developmental and operational testing of both manned and unmanned air vehicles, covering mission systems, carrier suitability certification, modeling, and simulation support [SRC-0195]. It supports over 160 aircraft representing all Navy and Marine Corps platforms, functioning as a critical hub for evaluating aircraft flight characteristics, maintenance logistics, and weapon separation envelopes [SRC-0106], [SRC-0106].</t>
+          <t>Naval test center in Maryland for aircraft and integrated systems.</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
@@ -14381,11 +13976,6 @@
       <c r="V187" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W187" t="inlineStr">
-        <is>
-          <t>SRC-0106, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -14441,7 +14031,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>The Atlantic Undersea Test and Evaluation Center (AUTEC) is a detachment of the Naval Undersea Warfare Center (NUWC) Division Newport, with its primary deep-water test facilities located on Andros Island and the Berry Islands in the Bahamas [SRC-0106], [SRC-0195]. AUTEC’s administrative and flight operations are headquartered in West Palm Beach, Florida [SRC-0195]. Located in the Tongue of the Ocean—a sheltered, 800-fathom-deep, and quiet body of water—AUTEC provides the U.S. Navy with full-spectrum test and evaluation capabilities for undersea warfare systems, sonar calibration, and fleet readiness [SRC-0106], [SRC-0195]. The center is composed of three main ranges: the AUTEC Weapons Range, an instrumented tracking range for assessing sensors, weapons, and platforms; the Acoustic Measurement Range, the East Coast's only permanent underwater noise-measuring facility for recording hydroacoustic emissions from submarines and surface ships; and the Fleet Operational Readiness Accuracy Check Site (FORACS V), which measures the accuracy of ASW and navigational sensors [SRC-0106]. The main base at Andros Island's Site 1 hosts the Command Control Building for real-time tracking and data processing, a precision machine shop, dive lockers, and torpedo Intermediate Maintenance Activities (IMA) for both lightweight and heavyweight torpedoes [SRC-0195]. AUTEC supports high-profile Navy projects, including Mk 46 and Mk 48 torpedo certifications, DD-963 and FFG-7 ship acceptance trials, advanced magnetics silencing, and various anti-submarine warfare tactics development [SRC-0106], [SRC-0195].</t>
+          <t>Navy acoustic and underwater test facility.</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
@@ -14457,11 +14047,6 @@
       <c r="V188" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W188" t="inlineStr">
-        <is>
-          <t>SRC-0106, SRC-0195</t>
         </is>
       </c>
     </row>
@@ -14517,7 +14102,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>The Upgraded Early Warning Radar (UEWR) at Beale Air Force Base in California is a critical ground-based strategic radar site operated by the United States Space Force [SRC-0190], [SRC-0212]. Managed by the 7th Space Warning Squadron (7 SWS) under the Space Operations Command, the installation forms a vital node in the United States' early warning and space domain awareness network [SRC-0190]. The Beale radar operates using an AN/FPS-132 Solid-State Phased Array system transmitting in the UHF band [SRC-0190]. Designed with two active array faces, the facility provides 240-degree azimuth coverage [SRC-0190], [SRC-0212]. The Beale radar was originally built in 1979 as a PAVE PAWS (Perimeter Acquisition Vehicle Entry Phased-Array Weapons System) installation [SRC-0190]. It underwent a significant upgrade to the UEWR configuration in 2005 and received further system enhancements in 2019 [SRC-0190]. Today, the radar feeds directly into the Missile Defense Agency's Ground-based Midcourse Defense (GMD) system, alongside sister UEWR sites in Thule, Greenland, and Fylingdales, United Kingdom [SRC-0187], [SRC-0212]. It provides essential detection, tracking, and classification data to identify incoming ballistic missile threats [SRC-0212]. The Beale UEWR is currently slated for the Ground Based Radar Digitization (GBRD) program's Phase 1 prototyping, with an Initial Operational Capability (IOC) targeted for Fiscal Year 2030, ensuring the continued modernization of its strategic missile warning and space surveillance missions [SRC-0190].</t>
+          <t>Upgraded Early Warning Radar in California supporting missile defense.</t>
         </is>
       </c>
       <c r="T189" t="inlineStr">
@@ -14533,11 +14118,6 @@
       <c r="V189" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W189" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0212, SRC-0187</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14173,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>Cape Cod Space Force Station, located atop Flat Rock Hill within the Massachusetts Military Reservation, hosts a vital strategic radar installation [SRC-0133]. The site was established and activated in 1980 as a PAVE Phased Array Warning System (PAVE PAWS) installation, originally using the AN/FPS-115 radar to guard the East Coast against sea-launched and intercontinental ballistic missiles [SRC-0190]. The facility is currently operated by the 6th Space Warning Squadron (6 SWS), a unit functioning under the United States Space Force's Space Operations Command [SRC-0190]. The key facility at this station is the AN/FPS-132 Upgraded Early Warning Radar (UEWR) [SRC-0190]. Upgraded from its original configuration under a 2013 contract, the current solid-state phased-array radar operates in the UHF frequency band and features two active faces [SRC-0190]. Each radar face provides 120 degrees of azimuth coverage, yielding a combined 240-degree coverage arc across the Atlantic Ocean [SRC-0190]. Using electronic beam steering instead of a rotating mechanical dish, the system can rapidly scan the horizon [SRC-0133]. The radar's primary mission includes missile warning and space surveillance [SRC-0133]. It actively tracks low-Earth orbit satellites, space debris, and other objects deviating from known orbits [SRC-0190]. Notably, the Cape Cod UEWR is the only radar in the United States capable of confirming a detected missile launch directed toward the US or Canada from the east [SRC-0133]. The radar completed its UEWR modernization between 2016 and 2017, successfully integrating into the Ballistic Missile Defense System [SRC-0190]. Currently, the radar is fully operational and is scheduled for front-end digitization under the Space Force's accelerated Ground Based Radar Digitization (GBRD) program [SRC-0190].</t>
+          <t>Upgraded Early Warning Radar in Massachusetts supporting missile defense.</t>
         </is>
       </c>
       <c r="T190" t="inlineStr">
@@ -14609,11 +14189,6 @@
       <c r="V190" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W190" t="inlineStr">
-        <is>
-          <t>SRC-0133, SRC-0190</t>
         </is>
       </c>
     </row>
@@ -14669,7 +14244,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>Clear Space Force Station, located in central Alaska, operates as a critical sensor hub for the Pacific theater [SRC-0190]. The site was originally established in September 1961 as one of the three original Ballistic Missile Early Warning System (BMEWS) installations, which initially relied on mechanical radars [SRC-0190]. Today, the early warning mission at the site is governed and executed by the 13th Space Warning Squadron (13 SWS) under the United States Space Force Space Operations Command [SRC-0190]. The primary facility at the site is the AN/FPS-132 Upgraded Early Warning Radar (UEWR) [SRC-0190]. The system was upgraded from its 1981 AN/FPS-123 Solid-State Phased Array Radar System (SSPARS) configuration by Raytheon under a $125.3 million contract awarded in 2012 [SRC-0190]. Housed within the original scanner building, the modern UEWR features a two-panel solid-state phased array operating in the UHF band [SRC-0190], [SRC-0190]. This dual-face design provides a 240-degree coverage arc across the Arctic and Pacific regions [SRC-0190]. Clear SFS serves a vital role by conducting overlapping early warning, precision tracking, and space surveillance missions [SRC-0190]. The UEWR upgrade was officially completed in Fiscal Year 2016, adding crucial Ground-based Midcourse Defense communication capabilities to the site [SRC-0190]. Currently, the UEWR radar is fully operational and continues its continuous missile warning mission [SRC-0190]. To ensure its long-term viability, the Clear UEWR has been selected for phase one prototyping under the Space Force's Ground Based Radar Digitization (GBRD) program, an initiative designed to transition legacy radar infrastructure from analog to digital operations by upgrading both front-end antennas and back-end data processors by 2030 [SRC-0186], [SRC-0190].</t>
+          <t>Upgraded Early Warning Radar located in Alaska.</t>
         </is>
       </c>
       <c r="T191" t="inlineStr">
@@ -14685,11 +14260,6 @@
       <c r="V191" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W191" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0186</t>
         </is>
       </c>
     </row>
@@ -14745,7 +14315,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>Located at Clear Space Force Station in Alaska, the Long Range Discrimination Radar (LRDR) is a cutting-edge sensor designed to defend the US homeland against complex ballistic missile threats [SRC-0190]. The Missile Defense Agency (MDA) initiated the LRDR program in March 2014, driven by a congressional mandate to deploy a radar optimized against threats from North Korea [SRC-0190]. Lockheed Martin was awarded the $784 million development contract in October 2015, and the radar achieved initial fielding on December 6, 2021 [SRC-0190]. The LRDR is jointly managed by the MDA and the United States Space Force Combat Forces Command [SRC-0190]. It is maintained locally by the 13th Space Warning Squadron, while daily operations are executed remotely by the 7th Space Warning Squadron [SRC-0190]. The key facility, the AN/FPS-138 LRDR, is a multi-face active electronically scanned array (AESA) radar utilizing Gallium Nitride (GaN) solid-state semiconductor technology [SRC-0190]. It features dual monostatic arrays operating in the S-band, with each radar face measuring 60 feet high and 60 feet wide [SRC-0190]. The radar is specifically designed for high-resolution midcourse target discrimination [SRC-0190]. It can simultaneously track and distinguish lethal ballistic missile warheads from decoys, spent rocket bodies, and space debris, preserving the limited inventory of Ground-Based Interceptors [SRC-0045], [SRC-0190]. The system is capable of continuous threat monitoring, ensuring operational readiness even during maintenance cycles [SRC-0045]. Lockheed Martin completed final acceptance and handed the radar over to the MDA in April 2024 [SRC-0190]. The system transitioned to fully operational status under the Combat Forces Command on December 8, 2025, and was declared fully operational for homeland defense in early 2026 [SRC-0190].</t>
+          <t>Long Range Discrimination Radar located in Alaska for missile defense.</t>
         </is>
       </c>
       <c r="T192" t="inlineStr">
@@ -14761,11 +14331,6 @@
       <c r="V192" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W192" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0045</t>
         </is>
       </c>
     </row>
@@ -14821,7 +14386,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>Cavalier Space Force Station is situated in North Dakota, approximately 15 miles south of the Canadian border [SRC-0143]. The radar facility was originally designed and built by General Electric in the early 1970s as the Perimeter Acquisition Radar (PAR), serving as a central component of the US Army's Safeguard anti-ballistic missile system [SRC-0190]. After the Safeguard system was decommissioned in 1976 shortly after activation, the radar was transferred to the Air Force [SRC-0190]. The base was renamed Cavalier Air Force Station in 1983 and officially became Cavalier Space Force Station in 2021 [SRC-0190]. The site is currently governed by the 10th Space Warning Squadron (10 SWS) under the Space Force's Space Operations Command, with maintenance and sustainment support provided by contractors such as InDyne [SRC-0190], [SRC-0210]. The station houses the AN/FPQ-16 Perimeter Acquisition Radar Attack Characterization System (PARCS) [SRC-0190]. PARCS is a massive, single-faced passive electronically scanned array (PESA) radar housed in a reinforced concrete structure [SRC-0190]. Operating in the UHF band between 420 and 450 MHz, the radar utilizes an output of approximately 14.3 megawatts of peak power [SRC-0190]. The radar's single face provides 140 degrees of azimuth coverage with a detection range extending up to 2,000 miles [SRC-0190]. PARCS provides early warning detection of sea-launched and intercontinental ballistic missiles targeting North America [SRC-0190]. Operating as a collateral sensor for the Space Surveillance Network, it continuously monitors and tracks more than half of all Earth-orbiting space objects [SRC-0190]. PARCS remains fully operational today and is scheduled for a comprehensive overhaul to digitize its 1970s-era front-end antenna under the Ground Based Radar Digitization (GBRD) program [SRC-0190].</t>
+          <t>Perimeter Acquisition Radar Attack Characterization System in North Dakota.</t>
         </is>
       </c>
       <c r="T193" t="inlineStr">
@@ -14837,11 +14402,6 @@
       <c r="V193" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W193" t="inlineStr">
-        <is>
-          <t>SRC-0143, SRC-0190, SRC-0210</t>
         </is>
       </c>
     </row>
@@ -15054,7 +14614,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>The Sea-Based X-Band Radar (SBX-1) is a mobile, ocean-going early warning and tracking radar platform typically deployed in the Pacific Ocean [SRC-0129], [SRC-0190]. Introduced in 2006, the radar was uniquely developed to serve as a highly relocatable, precision midcourse sensor for the US ballistic missile defense system [SRC-0093], [SRC-0190]. The platform is operated and governed jointly by the Military Sealift Command (MSC) and the Missile Defense Agency (MDA) [SRC-0190]. The SBX consists of an advanced X-band phased-array radar mounted on a modified semi-submersible oil rig platform [SRC-0129], [SRC-0190]. The massive radar array is protected from the maritime environment by a pressurized white radome measuring 103 feet high and 120 feet in diameter [SRC-0190]. The system utilizes approximately 45,000 active transmit/receive modules and 69,632 multi-sectional circuits to electronically shape, steer, and amplify the radar beam [SRC-0190]. The radar provides high-precision tracking, object classification, and midcourse discrimination of threat missiles and countermeasures [SRC-0093], [SRC-0129]. It is incredibly sensitive, capable of identifying baseball-sized objects at a range of up to 2,500 miles [SRC-0190]. In 2012, the SBX was placed in a limited test and operations status, allowing it to be recalled to active duty for contingency operations and testing [SRC-0181]. The platform remains an active and critical defense asset today. After 20 years of maritime service, the vessel recently underwent major maintenance to replace its distinctive golf ball-like radome dome in December 2025 [SRC-0129], [SRC-0190]. The recent deployment of new ground-based radars in Alaska may provide the MDA with the geographic flexibility to permanently relocate the SBX to the East Coast or Hawaii [SRC-0181].</t>
+          <t>Mobile semi-submersible early warning and discrimination radar system.</t>
         </is>
       </c>
       <c r="T196" t="inlineStr">
@@ -15070,11 +14630,6 @@
       <c r="V196" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W196" t="inlineStr">
-        <is>
-          <t>SRC-0129, SRC-0190, SRC-0093, SRC-0181</t>
         </is>
       </c>
     </row>
@@ -15130,7 +14685,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>The Army/Navy Transportable Radar Surveillance (AN/TPY-2) system is a mobile, high-resolution radar platform designed for rapid global deployment [SRC-0183]. Introduced in 2007, these transportable systems have been forward-deployed to strategic locations worldwide, including Japan, South Korea, Turkey, and the United Arab Emirates, to counter regional ballistic missile threats [SRC-0183], [SRC-0190]. The radar system is operated and governed jointly by the US Army and the Missile Defense Agency (MDA) [SRC-0190]. The primary facility is the AN/TPY-2 trailer-mounted, single-faced active electronically scanned array (AESA) radar operating in the X-band, specifically between 8.55 and 10 GHz [SRC-0190]. It utilizes over 25,000 transmit/receive modules across a 9.2-square-meter aperture to provide 120 degrees of sector coverage with a detection range exceeding 1,000 kilometers [SRC-0183], [SRC-0190]. The radar can operate in two distinct modes: a forward-based mode for long-range surveillance and early warning, or a terminal mode where it serves as the fire control element for the Terminal High Altitude Area Defense (THAAD) system [SRC-0183]. Currently, five forward-based AN/TPY-2 sites augment US homeland defense by detecting, tracking, and discriminating inbound targets much earlier in their flight paths [SRC-0093], [SRC-0093]. The radar can be transported by C-17 aircraft to austere locations, enabling highly responsive sensor coverage [SRC-0183]. The system remains fully operational globally. The radar fleet recently completed a comprehensive modernization program between 2024 and 2025 to transition its modules to advanced Gallium Nitride (GaN) solid-state technology, significantly enhancing its reliability and performance [SRC-0190]. Additionally, defense contractor Raytheon was recently awarded a $966 million contract modification to continue supporting the radar [SRC-0086].</t>
+          <t>Trailer-mounted X-band radar system used for missile defense.</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
@@ -15146,11 +14701,6 @@
       <c r="V197" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W197" t="inlineStr">
-        <is>
-          <t>SRC-0183, SRC-0190, SRC-0093, SRC-0086</t>
         </is>
       </c>
     </row>
@@ -15333,9 +14883,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>Located in **Jacksonville, Florida**, **Cecil Airport Spaceport** (also referred to as Cecil Spaceport or Cecil Field Spaceport) is a commercial horizontal launch site co-located at Cecil Airport, a public joint civil-military aviation facility [SRC-0110, SRC-0110, SRC-0154]. Formerly known as Naval Air Station Cecil Field, the site transitioned to commercial and civilian use and is now governed and operated by the **Jackson Aviation Authority** [SRC-0110, SRC-0031]. The facility achieved a significant historical milestone when it was officially licensed in **January 2010**, becoming the **first commercial Air and Space Port on the East Coast of the United States** [SRC-0110]. Because of its unique capabilities, the State of Florida legally considers the facility a designated "spaceport territory" [SRC-0110].
-The spaceport's primary launch infrastructure centers around its massive **horizontal launch runway, which measures 12,503 feet in length and 200 feet in width** [SRC-0110]. Currently, Cecil Spaceport is licensed by the FAA strictly to support **suborbital commercial space launches**; however, its close proximity to the Atlantic Ocean makes it highly suitable to potentially support orbital launch operations in the future [SRC-0110]. 
-Beyond its spaceflight launch capabilities, Cecil Airport remains a highly active multi-purpose aviation hub that regularly supports general aviation (GA) and ongoing military operations [SRC-0110]. Additionally, the site functions as a major **Maintenance, Repair, and Overhaul (MRO) facility**, providing critical services for large aerospace entities and defense contractors, including Boeing, Flightstar, Pratt &amp; Whitney, and the United States Navy [SRC-0110]. By successfully combining commercial space operations with traditional aviation and MRO services, Cecil Spaceport maintains a highly active current status within the United States' expanding horizontal spaceport network [SRC-0110, SRC-0110].</t>
+          <t>FAA-licensed commercial spaceport in Florida.</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
@@ -15351,11 +14899,6 @@
       <c r="V200" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W200" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0154, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -16554,9 +16097,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>The Tonopah Test Range, located in Nevada, United States (coordinates 37°47′47″N 116°46′46″W), is a significant military testing, training, and launch facility [SRC-0096, SRC-0095]. Historically, the site at Tonopah functioned as a Continental United States (CONUS) radar station under the Aerospace Defense Command's Semi-Automatic Ground Environment (SAGE) network [SRC-0016].
-Today, Tonopah is deeply integrated into the operations of the Tactical Fighter Weapons Center (TFWC), which is headquartered at Nellis Air Force Base [SRC-0106]. The TFWC manages approximately 6,000 square miles of desert terrain, characterized by valleys, dry lakebeds, and mountain ranges with elevations between 2,500 and 10,000 feet above sea level [SRC-0106]. Within this vast restricted airspace, the Tonopah Electronic Combat (EC) Range serves as one of the two primary "North Ranges" (the other being Tolicha Peak) [SRC-0106].
-The primary operational purpose of the Tonopah EC Range is to simulate a realistic enemy radar and threat environment for tactical aircrew training [SRC-0106]. The facility provides an operationally oriented, combat-like setting where multiple air and ground units can conduct integrated air-to-air and air-to-ground training, as well as test and evaluation (T&amp;E) missions [SRC-0106]. The region's dry climate ensures excellent flight conditions year-round, allowing the facility to accommodate everything from single-aircraft sorties to massive joint exercises involving hundreds of military aircraft [SRC-0106]. Additionally, Tonopah is formally classified as a rocket launch site within the United States [SRC-0096, SRC-0095].</t>
+          <t>Military testing area in Nevada.</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
@@ -16572,11 +16113,6 @@
       <c r="V217" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W217" t="inlineStr">
-        <is>
-          <t>SRC-0096, SRC-0095, SRC-0016, SRC-0106</t>
         </is>
       </c>
     </row>
@@ -16769,9 +16305,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>The former Mount Horace Greeley Calumet Air Force Station (AFS) is a deactivated military installation located in Keweenaw County, Michigan [SRC-0110]. The property encompasses a total of approximately 2,964 acres of land, composed of five separate but contiguous parcels that include both the footprint of the historical military facility and surrounding forested wilderness [SRC-0110].
-Historically, the site was established and utilized as a United States Air Force radar tracking and surveillance facility [SRC-0016, SRC-0110]. As part of the Continental United States (CONUS) air defense network, the Calumet station operated under the Aerospace Defense Command [SRC-0016]. The military continued to operate the radar facility until its official closure in 1988 [SRC-0110]. A decade after its decommission as a military installation, the infrastructure was repurposed as a youth correctional facility, which remained active from 1998 until 2004 [SRC-0110]. Since 2004, the property has been entirely vacant and inactive [SRC-0110].
-Environmental assessments of the former Calumet Air Force Station indicate that portions of the site were previously used as a landfill, resulting in documented contamination issues across the premises [SRC-0110]. Recently, the former Calumet AFS was evaluated as "Site 1" in a site selection and feasibility study conducted by the Michigan Aerospace Manufacturing Association [SRC-0110]. The Michigan Launch Initiative assessed the location to determine its viability for hosting a commercial vertical launch complex to support small-class orbital rockets [SRC-0110, SRC-0110]. However, the existing environmental contamination and past usage as a landfill present significant development challenges for future aerospace infrastructure [SRC-0110].</t>
+          <t>Proposed spaceport site in Michigan previously used as an Air Force radar facility.</t>
         </is>
       </c>
       <c r="T220" t="inlineStr">
@@ -16787,11 +16321,6 @@
       <c r="V220" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W220" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0016</t>
         </is>
       </c>
     </row>
@@ -16842,9 +16371,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>The former Keweenaw Rocket Range is located in Keweenaw County, Michigan, situated along the shore of Lake Superior at the easternmost point of the Keweenaw Peninsula [SRC-0110]. The site spans approximately 474 acres and comprises four contiguous parcels of state-owned land [SRC-0110]. While a designated portion of this property was historically developed as the Keweenaw Rocket Range, the remainder of the site consists of pristine forested wilderness that is currently utilized for outdoor recreation [SRC-0110].
-Historically, the site operated as an active sounding rocket launch facility between 1964 and 1971 [SRC-0096, SRC-0095]. During this operational period, the launch complex was primarily utilized by NASA and the University of Michigan to conduct suborbital sounding rocket missions [SRC-0110]. Records show that more than 50 rocket launches were successfully executed at the Keweenaw site [SRC-0096, SRC-0095]. These suborbital flights supported payload capacities of up to 770 kilograms and reached maximum altitudes of less than 160 kilometers [SRC-0096, SRC-0095].
-Following the conclusion of its launch programs in 1971, the Keweenaw Rocket Range was deactivated and remains inactive today [SRC-0096, SRC-0095]. Recently, the historic launch site was evaluated as "Site 2" under the Michigan Launch Initiative's site selection and feasibility study for a new commercial spaceport [SRC-0110]. An assessment of the property's environmental conditions noted that, unlike some other candidate sites, there is no known contamination present at the former rocket range [SRC-0110]. The study considered the area's strategic geographic benefits, particularly its coastal Lake Superior location, for potentially supporting future small-class vertical launch vehicles and modern spaceport operations [SRC-0110, SRC-0110].</t>
+          <t>Former NASA sounding rocket launch site in Michigan proposed as a spaceport.</t>
         </is>
       </c>
       <c r="T221" t="inlineStr">
@@ -16860,11 +16387,6 @@
       <c r="V221" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W221" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0096, SRC-0095</t>
         </is>
       </c>
     </row>
@@ -16987,8 +16509,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>The Raco Army Airfield, currently known as the Smithers Winter Test Center, is a facility located in the state of Michigan [SRC-0110]. The site encompasses approximately 800 acres and consists of a single contiguous parcel of land that is presently owned and governed by the United States Forest Service [SRC-0110]. Historically, the installation was designated as the Raco Army Airfield (AAF), during which time it served primarily as a refueling stop for military aircraft [SRC-0110]. The airfield's structural layout is distinct, featuring three runways of equal length that are arranged in a geometric triangular pattern [SRC-0110].
-In its current status, the facility has been repurposed from its original military aviation mission. It is now officially known as the Smithers Winter Test Center and is utilized primarily as a specialized testing location for evaluating vehicles under harsh winter conditions [SRC-0110]. Environmental assessments of the property indicate that there is no known contamination present at the site, which distinguishes it from other historical military facilities in the region [SRC-0110]. The site was recently evaluated as a potential candidate (designated as Site 6) for a vertical launch complex under the Michigan Spaceport Site Selection and Feasibility Study, owing to its extensive acreage and existing runway footprint [SRC-0110]. While its primary current use remains vehicular winter testing, its legacy infrastructure continues to make it a point of interest for future aerospace or testing developments [SRC-0110].</t>
+          <t>Former Army airfield in Michigan proposed as a launch site.</t>
         </is>
       </c>
       <c r="T223" t="inlineStr">
@@ -17004,11 +16525,6 @@
       <c r="V223" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W223" t="inlineStr">
-        <is>
-          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -17059,9 +16575,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>The Oscoda-Wurtsmith Alert Apron is a designated parcel of land located at the Oscoda-Wurtsmith Airport (OSC) in Michigan [SRC-0110, SRC-0110]. Encompassing approximately 125 acres, this specific site includes the historical Alert Apron and its immediate surrounding areas [SRC-0110]. The property is governed by the Oscoda-Wurtsmith Airport Authority, which assumed control of the broader airport facility after it transitioned to public use in December 1993 [SRC-0110, SRC-0110].
-Historically, the site was an integral component of the Wurtsmith Air Force Base, a military installation that was originally established in 1923 as a soft-surface landing site for the Army Air Corps and later operated by the United States Air Force [SRC-0110]. Following the end of the Cold War and the fall of the Soviet Union, the base was deemed no longer necessary and officially closed in 1993 [SRC-0110]. Since the base's closure, the Alert Apron site has remained largely vacant [SRC-0110].
-In recent years, the Alert Apron was evaluated as "Site 11" during the Michigan Spaceport Site Selection and Feasibility Study for potential development as a vertical launch complex [SRC-0110]. However, development at this site faces several notable constraints. Because it is located directly on an active airfield, any new facilities or structures built on the apron are strictly subject to height restrictions governed by Federal Aviation Administration Part 77 imaginary surfaces, which ensure that new constructions do not interfere with aircraft operations [SRC-0110, SRC-0110]. Furthermore, environmental assessments indicate that the site has known contamination issues, as it was previously utilized by the military for the use and storage of hazardous substances and waste materials [SRC-0110].</t>
+          <t>Proposed spaceport launch location on a former Air Force base in Michigan.</t>
         </is>
       </c>
       <c r="T224" t="inlineStr">
@@ -17077,11 +16591,6 @@
       <c r="V224" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W224" t="inlineStr">
-        <is>
-          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -24779,8 +24288,7 @@
       </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>Licensed in June 2015, the Houston Spaceport is a horizontal commercial spaceport co-located at Ellington Airport, an airport owned by the City of Houston and operated by the Houston Airport System [SRC-0110, SRC-0110]. Located approximately 5.5 miles northwest of the National Aeronautics and Space Administration's (NASA) Johnson Space Center, the facility accommodates general aviation, military, NASA, and suborbital commercial space operations [SRC-0110]. Notably, the Houston Spaceport was the very first commercial spaceport in the United States to construct a new control tower equipped with dedicated mission-control facilities designed specifically for commercial space operations [SRC-0110].
-The spaceport features a primary runway measuring 9,001 feet long by 150 feet wide, well above the 8,000-foot recommendation for Horizontal Takeoff Horizontal Landing (HTHL) operations [SRC-0110, SRC-0110]. Like other air and space ports, it uses conventional runway infrastructure to support these HTHL vehicles, which rely on aerodynamic control through a combination of jet-power, rocket power, or controlled glide [SRC-0110, SRC-0110]. As an active hub for aerospace activity, the spaceport had secured commitments from tenants including Intuitive Machines, San Jacinto College, and FlightSafety International as of January 2020 [SRC-0110]. The spaceport's development and planning involved conceptual terminal designs focused on integrating aerospace commercial activities into the existing airfield [SRC-0110]. Overall, it functions not only as a licensed launch and reentry site but also as an emerging center for aerospace testing, development, manufacturing, and research opportunities [SRC-0110].</t>
+          <t>Commercial spaceport located in Texas.</t>
         </is>
       </c>
       <c r="T325" t="inlineStr">
@@ -24796,11 +24304,6 @@
       <c r="V325" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W325" t="inlineStr">
-        <is>
-          <t>SRC-0110</t>
         </is>
       </c>
     </row>
@@ -24851,9 +24354,7 @@
       </c>
       <c r="S326" t="inlineStr">
         <is>
-          <t>Licensed in June 2004, the Mojave Air and Space Port holds the distinction of being the first commercially licensed spaceport in the United States [SRC-0110, SRC-0110]. Operated by the East Kern Airport District, the facility is located in the Mojave Desert of California [SRC-0110]. As a prominent horizontal air and space port, it is equipped with a massive primary runway measuring 12,503 feet long by 200 feet wide, making it highly capable of supporting various Horizontal Takeoff Horizontal Landing (HTHL) vehicles [SRC-0110, SRC-0110].
-The spaceport is a leading air launch facility for private spaceflight and aerospace research [SRC-0161]. It is licensed to support suborbital commercial launches while concurrently functioning as a general aviation airport [SRC-0110]. The site has attracted significant aerospace investment and is home to over 60 tenants [SRC-0110]. Prominent companies operating out of the facility include Interorbital Systems, Masten Space Systems, Northrop Grumman, Stratolaunch Systems, The Spaceship Company, and Virgin Orbit [SRC-0110]. Prior to moving its operations to Spaceport America in 2019, Virgin Galactic also based its spaceflight activities at Mojave [SRC-0188].
-Beyond serving as a launch site, the spaceport operates as a dynamic hub for aerospace business. The diverse companies stationed at the Mojave Air and Space Port conduct a wide range of activities, including advanced vehicle development, cutting-edge aerospace design, and extensive flight testing and research [SRC-0110, SRC-0110]. This blend of capabilities allows the spaceport to generate revenue from testing, manufacturing, and research that often exceeds the revenue tied strictly to licensed launches [SRC-0110].</t>
+          <t>Commercial spaceport located in California.</t>
         </is>
       </c>
       <c r="T326" t="inlineStr">
@@ -24869,11 +24370,6 @@
       <c r="V326" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W326" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0161, SRC-0188</t>
         </is>
       </c>
     </row>
@@ -24924,9 +24420,7 @@
       </c>
       <c r="S327" t="inlineStr">
         <is>
-          <t>Licensed by the FAA in June 2006, the Oklahoma Air and Space Port holds the unique distinction of being the first licensed commercial spaceport located in a land-locked state in the United States [SRC-0110]. Situated in Burns Flat, Oklahoma, the spaceport is co-located with the Clinton-Sherman Industrial Airpark and is managed by the Oklahoma Industry Development Authority (OSIDA) [SRC-0110, SRC-0096]. It features a massive primary runway measuring 13,503 feet long by 150 feet wide, which provides substantial infrastructure for Horizontal Takeoff Horizontal Landing (HTHL) spaceplanes [SRC-0110].
-The facility is currently licensed to support suborbital commercial space launches and simultaneously serves as an active airport accommodating both military and general aviation operations [SRC-0110]. Uniquely, the Oklahoma Air and Space Port was the first commercially licensed spaceport in the country to establish an FAA-approved spaceflight corridor that was not situated within Special Use Airspace (SUA) [SRC-0110].
-In addition to its launch capabilities, the spaceport features existing infrastructure dedicated to aerospace testing, research and development, and flight operations [SRC-0110]. These facilities position the site to attract emerging aerospace ventures. For example, it was announced that Dawn Aerospace's Aurora Mark 2 suborbital spaceplane would begin flying from the Burns Flat spaceport [SRC-0203]. By utilizing its existing runway and aerospace infrastructure, the Oklahoma Spaceport continues to function as a vital hub for commercial spaceflight research and horizontal launch operations [SRC-0110, SRC-0203].</t>
+          <t>Commercial spaceport located in Oklahoma.</t>
         </is>
       </c>
       <c r="T327" t="inlineStr">
@@ -24942,11 +24436,6 @@
       <c r="V327" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0096, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -25002,9 +24491,7 @@
       </c>
       <c r="S328" t="inlineStr">
         <is>
-          <t>The Pacific Spaceport Complex – Alaska, formerly known as the Kodiak Launch Complex, is a commercial and military spaceport located on Kodiak Island, Alaska [SRC-0161, SRC-0110]. Owned and operated by the Alaska Aerospace Corporation, the facility was officially awarded its commercial spaceport license in September 2003 [SRC-0110]. Notably, the Pacific Spaceport Complex – Alaska became the first commercial spaceport in the United States that was not co-located on a preexisting federal range [SRC-0110].
-Operating as a vertical launch site, the complex is capable of supporting launch azimuths ranging from 110 degrees to 220 degrees, making it highly suitable for missions requiring high inclination and polar orbits [SRC-0110]. Since 1998, the facility has supported various orbital and sub-orbital launch operations for both commercial and military customers [SRC-0161]. Historical records indicate that the spaceport has hosted at least 9 launches over its operational history [SRC-0161].
-The site’s remote location in Alaska provides a unique geographic advantage for vertical rocket launches, ensuring safe trajectories over the Pacific Ocean [SRC-0110]. By providing access to specialized launch corridors, the Pacific Spaceport Complex – Alaska remains an important asset within the United States' vertical commercial spaceport network, directly supporting the testing and deployment of advanced aerospace technologies away from traditional mainland federal ranges [SRC-0110, SRC-0110].</t>
+          <t>Commercial spaceport located in Kodiak Island, Alaska.</t>
         </is>
       </c>
       <c r="T328" t="inlineStr">
@@ -25020,11 +24507,6 @@
       <c r="V328" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W328" t="inlineStr">
-        <is>
-          <t>SRC-0161, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25075,9 +24557,7 @@
       </c>
       <c r="S329" t="inlineStr">
         <is>
-          <t>Spaceport America, formerly known as the Southwest Regional Spaceport, is an FAA-licensed commercial spaceport located on 18,000 acres of State Trust Land in the Jornada del Muerto desert basin, 45 miles north of Las Cruces, New Mexico [SRC-0188]. Owned and operated by the State of New Mexico through the New Mexico Spaceport Authority, it bills itself as the world's first purpose-built commercial spaceport [SRC-0188]. Unlike many other sites, Spaceport America was constructed to accommodate both vertical and horizontal launch aerospace vehicles, featuring a 12,000-foot concrete runway [SRC-0188, SRC-0188].
-The spaceport's inception dates back to 1990, with initial funding secured via congressional earmarks [SRC-0188]. The site broke ground in 2009 and was officially declared open on October 18, 2011 [SRC-0188, SRC-0188]. Virgin Galactic signed a 20-year lease as the anchor tenant, and on May 22, 2021, launched the VSS Unity with three people aboard, making New Mexico the third US state to launch humans into space [SRC-0188, SRC-0188]. The terminal hangar facility, designed by Foster+Partners, achieved LEED-Gold certification and incorporates sustainable features like "Earth Tubes" for cooling [SRC-0188, SRC-0188].
-Spaceport America hosts several tenants and operators, including UP Aerospace, SpinLaunch, HAPSMobile Aerovironment, EXOS Aerospace, and Boeing [SRC-0188, SRC-0188]. UP Aerospace has launched numerous SpaceLoft XL sounding rockets from the site since its first rocket launch on September 25, 2006 [SRC-0188, SRC-0188]. The spaceport also serves as an educational and non-aerospace hub, hosting the Spaceport America Cup for intercollegiate rocket engineering (from 2017 to 2024) and providing test tracks for automotive companies like Infiniti [SRC-0188, SRC-0188].</t>
+          <t>Commercial spaceport located in New Mexico.</t>
         </is>
       </c>
       <c r="T329" t="inlineStr">
@@ -25093,11 +24573,6 @@
       <c r="V329" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W329" t="inlineStr">
-        <is>
-          <t>SRC-0188</t>
         </is>
       </c>
     </row>
@@ -25148,9 +24623,7 @@
       </c>
       <c r="S330" t="inlineStr">
         <is>
-          <t>The Mid-Atlantic Regional Spaceport (MARS) is an FAA-licensed vertical launch commercial spaceport located at Wallops Island, Virginia [SRC-0110, SRC-0161]. The facility is owned and operated by the Virginia Commercial Space Flight Authority (VCSFA) and was officially awarded a Launch Site Operator License in December 2002 [SRC-0110]. As a critical component of the United States' vertical launch network, MARS shares geography with NASA's Wallops Flight Facility, leveraging the location's extensive history in rocket launches and scientific exploration [SRC-0110, SRC-0161].
-The spaceport maintains multiple active launch complexes to accommodate a variety of rocket classes. Launch Pad 0A has historically supported medium-to-large lift launch vehicles, most notably the Antares rocket used for resupply missions to the International Space Station [SRC-0110, SRC-0110]. Launch Pad 0B is designated for small lift launch vehicles, such as the Minotaur I [SRC-0110]. Additionally, commercial aerospace company Rocket Lab USA constructed a new launch facility at MARS, known as Launch Pad 2, which was designed to support its launch operations beginning in 2020 [SRC-0110].
-By 2025, the Mid-Atlantic Regional Spaceport stood out as a significant contributor to orbital spaceflight. Outside of the traditional federal ranges at Cape Canaveral and Vandenberg, MARS was the only other spaceport in the United States to host an orbital launch that year, specifically a Rocket Lab Electron mission [SRC-0203]. The site provides crucial infrastructure and launch capabilities for commercial, government, and military payloads [SRC-0110].</t>
+          <t>Commercial spaceport located in Virginia.</t>
         </is>
       </c>
       <c r="T330" t="inlineStr">
@@ -25166,11 +24639,6 @@
       <c r="V330" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W330" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0161, SRC-0203</t>
         </is>
       </c>
     </row>
@@ -25226,7 +24694,7 @@
       </c>
       <c r="S331" t="inlineStr">
         <is>
-          <t>The Kodiak Launch Complex, currently known as the Pacific Spaceport Complex – Alaska (PSCA), is a commercial and military spaceport located on Kodiak Island, Alaska [SRC-0092, SRC-0096, SRC-0110]. Owned and operated by the Alaska Aerospace Corporation (formerly the Alaska Aerospace Development Corporation), the facility was created by the State of Alaska to develop aerospace-related economic and technical opportunities [SRC-0110, SRC-0092]. It officially became a commercially licensed spaceport in September 2003, making it the first commercial spaceport in the United States that was not co-located on a preexisting federal range [SRC-0110]. Operational since 1991, the complex has supported a mix of orbital and suborbital missions [SRC-0096, SRC-0161]. The site's geographic location is highly advantageous, capable of supporting launch azimuths ranging from 110° to 220°, which is ideal for placing payloads into high-inclination and polar orbits [SRC-0110]. Over its history, the facility has hosted at least 26 launches, accommodating launch vehicles with a lift-off mass of up to 86,000 kilograms [SRC-0096]. Its launch operations encompass ballistic missile interceptor tests as well as commercial and government satellite launches [SRC-0096]. Among the launch vehicles supported at the complex are the Athena and Minuteman/AIT rockets [SRC-0162]. Today, the spaceport remains an active asset for sub-orbital and orbital launches, catering to both military and civilian aerospace customers [SRC-0096, SRC-0161].</t>
+          <t>Rocket launch site in Alaska.</t>
         </is>
       </c>
       <c r="T331" t="inlineStr">
@@ -25242,11 +24710,6 @@
       <c r="V331" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W331" t="inlineStr">
-        <is>
-          <t>SRC-0092, SRC-0096, SRC-0110, SRC-0161, SRC-0162</t>
         </is>
       </c>
     </row>
@@ -25302,7 +24765,7 @@
       </c>
       <c r="S332" t="inlineStr">
         <is>
-          <t>The SpaceX Launch Site, formally known as the SpaceX Starbase Spaceport, is a private rocket production facility, test site, and spaceport located at Boca Chica, Texas [SRC-0096, SRC-0094]. Situated near the Gulf of Mexico, the site was originally planned to accommodate commercial launches of the Falcon family of rockets [SRC-0096]. However, it has since evolved to be used exclusively by SpaceX for the development, testing, and launching of the massive Starship spacecraft and its Super Heavy booster [SRC-0096]. Operations at the Texas facility began around 2018, and it has since supported numerous prototype test flights and orbital launch attempts [SRC-0096]. Starbase has accommodated rockets with a lift-off mass of approximately 5,000,000 kilograms, making it the primary hub for the company's interplanetary ambitions [SRC-0096]. The launch site has hosted around 21 launches as of recent tracking data [SRC-0161]. In addition to its dedicated Starbase facility, SpaceX conducts the vast majority of its commercial, civil, and military launches from leased pads at federal and military ranges. This includes Space Launch Complex 40 (SLC-40) and Launch Complex 39A (LC-39A) at the Kennedy Space Center and Cape Canaveral Space Force Station in Florida, as well as Space Launch Complex 4E (SLC-4E) and Space Launch Complex 6 (SLC-6) at Vandenberg Space Force Base in California [SRC-0031, SRC-0031, SRC-0214, SRC-0214]. These distributed sites allow SpaceX to maintain a high launch cadence across the country.</t>
+          <t>Private launch site located in Texas.</t>
         </is>
       </c>
       <c r="T332" t="inlineStr">
@@ -25318,11 +24781,6 @@
       <c r="V332" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W332" t="inlineStr">
-        <is>
-          <t>SRC-0096, SRC-0094, SRC-0161, SRC-0031, SRC-0214</t>
         </is>
       </c>
     </row>
@@ -25378,7 +24836,7 @@
       </c>
       <c r="S333" t="inlineStr">
         <is>
-          <t>The Blue Origin Launch Site, known operationally as Corn Ranch, is a private spaceport and rocket testing facility located near Van Horn, Texas [SRC-0096]. Operational since 2006, the West Texas facility is owned and operated entirely by Blue Origin, the aerospace manufacturer founded by Jeff Bezos [SRC-0096]. Corn Ranch is predominantly utilized for suborbital spaceflight launches and rocket engine testing, specifically serving as the exclusive launch site for the company's New Shepard reusable suborbital launch vehicle [SRC-0096, SRC-0161]. The site has hosted numerous uncrewed and crewed flights, with historical launch counts reported between 20 and 38 missions depending on the operational timeframe [SRC-0096, SRC-0161]. Rockets launched from this Texas facility have achieved altitudes of approximately 105 kilometers, successfully crossing the Kármán line into space before vertically landing [SRC-0096]. Beyond its private Texas launch site, Blue Origin has significantly expanded its orbital launch capabilities by leasing Launch Complex 36 (LC-36) at the Cape Canaveral Space Force Station in Florida [SRC-0031]. In September 2015, NASA announced that Blue Origin had leased LC-36 and would modify the historic pad as a launch site for their next-generation launch vehicles [SRC-0031]. At LC-36, the company is actively developing facilities to support its heavy-lift New Glenn rocket, marking a transition from purely suborbital operations in Texas to heavy-lift orbital missions from the Florida coast [SRC-0031, SRC-0031].</t>
+          <t>Private launch site located in Texas.</t>
         </is>
       </c>
       <c r="T333" t="inlineStr">
@@ -25394,11 +24852,6 @@
       <c r="V333" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W333" t="inlineStr">
-        <is>
-          <t>SRC-0096, SRC-0161, SRC-0031</t>
         </is>
       </c>
     </row>
@@ -25520,7 +24973,7 @@
       </c>
       <c r="S335" t="inlineStr">
         <is>
-          <t>The California Spaceport is a commercial space launch facility located within the boundaries of Vandenberg Space Force Base (formerly Vandenberg Air Force Base) on the central coast of California [SRC-0092, SRC-0110]. It holds a significant historical distinction as the first commercially licensed spaceport in the United States, having received its Launch Site Operator License from the Federal Aviation Administration (FAA) on September 19, 1996 [SRC-0092, SRC-0110]. The spaceport's launch infrastructure is situated at Space Launch Complex 8 (SLC-8) [SRC-0110]. Initially, the site was operated and managed by Spaceport Systems International, L.P. (SSI) in a strategic partnership with ITT Federal Services Corporation (ITT FSC), a major technical and support services contractor [SRC-0092]. Today, the site is operated by L3Harris Spaceport Systems [SRC-0110]. The facility was established to provide flexible and cost-effective commercial launch operations by directly leveraging the existing launch infrastructure, airspace coordination, and range safety services of the federal Western Range [SRC-0092, SRC-0092]. California Spaceport has supported commercial vertical launch activities, with early reports noting at least two launches from the facility [SRC-0092]. While the 2018 Annual Compendium of Commercial Space Transportation indicated that its active license was set to expire in September 2021 [SRC-0110], the spaceport represents a critical early milestone in the development of the commercial spaceflight industry in the United States, demonstrating the viability of hosting commercial spaceports on existing federal military ranges [SRC-0092].</t>
+          <t>Commercial spaceport located in California.</t>
         </is>
       </c>
       <c r="T335" t="inlineStr">
@@ -25536,11 +24989,6 @@
       <c r="V335" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W335" t="inlineStr">
-        <is>
-          <t>SRC-0092, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25591,7 +25039,7 @@
       </c>
       <c r="S336" t="inlineStr">
         <is>
-          <t>Spaceport Florida is a commercial space launch facility located within the federal Eastern Range at Cape Canaveral Space Force Station (formerly Cape Canaveral Air Station) in Florida [SRC-0092, SRC-0092]. The site was initially established and managed by the Spaceport Florida Authority (SFA), an entity created by the Governor and Legislature of Florida as the United States' first state government space agency [SRC-0092]. The SFA was designed to foster space-related enterprises, commercial launch activities, and educational projects to stimulate the state's economy [SRC-0092]. To facilitate these launches, the spaceport operates Launch Complex 46 (LC-46), for which it originally received a Launch Site Operator License from the Federal Aviation Administration (FAA) [SRC-0092]. Operations at the site directly benefit from the existing tracking infrastructure and robust range safety services provided by the Department of Defense at the federal launch range [SRC-0092]. Currently, the facility is part of the broader Cape Canaveral Spaceport (CCS) network operated by Space Florida, which encompasses multiple launch facilities including the Shuttle Landing Facility, SLC-36, SLC-37, SLC-40, SLC-41, and SLC-46 [SRC-0110]. LC-46 was officially licensed for vertical launches in July 2010 and remains the only licensed spaceport on CCS that supports vertical launch [SRC-0110]. The facility has successfully supported both commercial and government vertical launch operations over its history, including at least two early launches [SRC-0092, SRC-0110].</t>
+          <t>Commercial spaceport located in Florida.</t>
         </is>
       </c>
       <c r="T336" t="inlineStr">
@@ -25607,11 +25055,6 @@
       <c r="V336" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W336" t="inlineStr">
-        <is>
-          <t>SRC-0092, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -25667,9 +25110,7 @@
       </c>
       <c r="S337" t="inlineStr">
         <is>
-          <t>The John F. Kennedy Space Center (KSC) is a major United States spaceport located on Merritt Island, Florida, situated west and north of Cape Canaveral and linked to it by bridges and causeways [SRC-0031, SRC-0031]. Governed and operated by the National Aeronautics and Space Administration (NASA), KSC was originally established to support the Apollo program. The sheer size of the Saturn V rocket, which was necessary to achieve the goal of landing a man on the Moon, required a much larger launch facility than the adjacent Cape Canaveral could provide [SRC-0031]. Following the assassination of President John F. Kennedy, his successor, President Lyndon B. Johnson, issued Executive Order 11129 on November 29, 1963, officially renaming the Merritt Island Launch Operations Center to the John F. Kennedy Space Center [SRC-0031].
-KSC boasts extensive infrastructure to support human and robotic spaceflight. Key facilities include Launch Complex 39 (specifically pads LC-39A and LC-39B), the iconic Vehicle Assembly Building, the Launch Control Center, the Crawlerway, and multiple Orbiter Processing Facilities [SRC-0031, SRC-0031, SRC-0031]. Additionally, the site hosts the Shuttle Landing Facility (SLF), a runway historically used for Space Shuttle Orbiter landings [SRC-0110]. Today, the SLF is operated by Space Florida under a property agreement with NASA and supports horizontal suborbital and orbital commercial launches [SRC-0110].
-Historically notable for launching the Apollo Saturn V rockets and the Space Shuttle fleet [SRC-0031, SRC-0110], KSC currently operates in conjunction with the adjacent Cape Canaveral Space Force Station as part of the Eastern Range [SRC-0054, SRC-0202]. The Eastern Range, overseen by the U.S. Space Force's Space Launch Delta 45, provides essential safety, tracking, and control infrastructure for all KSC launches [SRC-0202, SRC-0202]. KSC continues to be a bustling hub for NASA, military, and commercial aerospace endeavors [SRC-0202, SRC-0202].</t>
+          <t>Major NASA space launch facility in Florida.</t>
         </is>
       </c>
       <c r="T337" t="inlineStr">
@@ -25685,11 +25126,6 @@
       <c r="V337" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W337" t="inlineStr">
-        <is>
-          <t>SRC-0031, SRC-0110, SRC-0054, SRC-0202</t>
         </is>
       </c>
     </row>
@@ -25745,9 +25181,7 @@
       </c>
       <c r="S338" t="inlineStr">
         <is>
-          <t>Wallops Flight Facility is a United States spaceport and rocket launch site located on Wallops Island, Virginia [SRC-0154, SRC-0162]. Governed and operated by the National Aeronautics and Space Administration (NASA), the site has historically grown from a small test range for guided missile research into the agency's premier location for suborbital and small orbital activities [SRC-0185].
-The facility supports NASA's Science Mission Directorate, with its strategic vision and goals encompassing Earth Science, Heliophysics, and Astrophysics [SRC-0185]. To achieve these goals, Wallops is heavily utilized for launching sounding rockets, scientific balloons, and small orbital aerospace vehicles that aid in worldwide science exploration and technology development [SRC-0185]. Wallops is equipped with a tracking radar that integrates with broader monitoring networks, such as the Eastern Test Range [SRC-0106]. Furthermore, launches from Wallops Island have been used to test and demonstrate the tracking capabilities of other advanced military systems, such as the Long Range Discrimination Radar (LRDR) [SRC-0100].
-In addition to NASA's own operations, Wallops Flight Facility hosts the Mid-Atlantic Regional Spaceport (MARS), facilitating commercial and military spaceflight [SRC-0031]. As commercial space industry capabilities have expanded, Wallops has accommodated private aerospace companies. Notably, Rocket Lab constructed its Launch Complex 2 at the facility, which was slated to debut with a mission for the U.S. Air Force [SRC-0110, SRC-0110, SRC-0110]. By providing robust infrastructure for both government research and commercial enterprises, Wallops Flight Facility remains a critical component of the United States' national space launch architecture and scientific testing capabilities [SRC-0185, SRC-0154].</t>
+          <t>NASA launch and testing site in Virginia.</t>
         </is>
       </c>
       <c r="T338" t="inlineStr">
@@ -25763,11 +25197,6 @@
       <c r="V338" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W338" t="inlineStr">
-        <is>
-          <t>SRC-0154, SRC-0162, SRC-0185, SRC-0106, SRC-0100, SRC-0031, SRC-0110</t>
         </is>
       </c>
     </row>
@@ -26092,9 +25521,7 @@
       </c>
       <c r="S343" t="inlineStr">
         <is>
-          <t>The Green River Launch Complex is a United States military rocket launch site and weapons test facility located in the state of Utah [SRC-0036, SRC-0037, SRC-0095, SRC-0218]. Classified as a proving ground and launch complex, the site was utilized by the United States Air Force to support suborbital sounding rocket flights and experimental missile testing during the Cold War era [SRC-0037, SRC-0218].
-One of the most notable activities associated with the Green River Launch Complex occurred on July 11, 1970 [SRC-0218]. On this date, the U.S. Air Force launched an Athena sounding rocket equipped with a V-123-D re-entry vehicle [SRC-0218]. The test's intended target was located within the White Sands Missile Range (WSMR) in New Mexico [SRC-0218]. However, the rocket suffered a significant anomaly and veered off its planned trajectory [SRC-0218]. Instead of landing in New Mexico, the Athena rocket flew over the international border and impacted approximately 180 to 200 miles south of the United States-Mexico border, crashing in the Mapimi Desert in the northeastern corner of the Mexican state of Durango [SRC-0218]. 
-Beyond its use for the Athena program and its categorization alongside other national aerospace test facilities, detailed operational history, establishing dates, and current status of the Green River Launch Complex are not extensively documented in the available records [SRC-0036, SRC-0037, SRC-0218].</t>
+          <t>Former military launch complex in Utah.</t>
         </is>
       </c>
       <c r="T343" t="inlineStr">
@@ -26110,11 +25537,6 @@
       <c r="V343" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W343" t="inlineStr">
-        <is>
-          <t>SRC-0036, SRC-0037, SRC-0095, SRC-0218</t>
         </is>
       </c>
     </row>
@@ -26781,8 +26203,7 @@
       </c>
       <c r="S352" t="inlineStr">
         <is>
-          <t>**Aegis Ashore Poland**, located in Redzikowo, is a modern missile defense installation that represents a critical contribution by the United States Missile Defense Agency (MDA) to Phase 3 of the European Phased Adaptive Approach [SRC-0093]. The site is specifically designed to launch advanced interceptors, including the SM-3 Block IBTU and Block IIA missiles, providing a defensive shield for NATO's European territory and forces against ballistic missile threats originating from outside the Euro-Atlantic region [SRC-0093, SRC-0093]. 
-The facility reached a significant milestone in December 2023 when it was officially accepted by the U.S. Chief of Naval Operations [SRC-0093]. Currently, Aegis Ashore Poland is funded, maintained, and operated by the United States Navy [SRC-0093]. As part of its integration process, the installation was scheduled for a planned maintenance period focused on upgrading its computer networks and communications systems [SRC-0093]. Upon completion of these technical upgrades, the facility will be formally accepted by the U.S. European Command [SRC-0093, SRC-0093]. Following this acceptance, the governing authority and operational control of the Redzikowo site will be transferred from the U.S. European Command directly to NATO [SRC-0093, SRC-0093].</t>
+          <t>Aegis Ashore missile defense site in northern Poland with SPY-1D radar and SM-3 interceptors.</t>
         </is>
       </c>
       <c r="T352" t="inlineStr">
@@ -26798,11 +26219,6 @@
       <c r="V352" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W352" t="inlineStr">
-        <is>
-          <t>SRC-0093</t>
         </is>
       </c>
     </row>
@@ -26929,9 +26345,7 @@
       </c>
       <c r="S354" t="inlineStr">
         <is>
-          <t>Adak Island, located in the Aleutian Islands of Alaska, serves as a nominal strategic location for the United States Department of Defense's Ballistic Missile Defense System [SRC-0178, SRC-0178, SRC-0179, SRC-0179]. Although often referred to as a base of operations, its most prominent modern role is designated as the homeport for the Sea-Based X-Band Radar (SBX-1) [SRC-0178, SRC-0178, SRC-0179].
-The SBX-1 is a massive, floating active electronically scanned array radar mounted on a fifth-generation CS-50 twin-hulled semi-submersible platform [SRC-0178, SRC-0179]. Developed by the Missile Defense Agency (MDA), the radar is designed to operate in severe weather and heavy seas to detect, track, and discriminate incoming ballistic missiles targeting the United States from adversaries like North Korea and China [SRC-0178, SRC-0178, SRC-0179]. To accommodate this specialized vessel, the military invested $26 million in 2007 to construct a custom eight-point mooring chain system in Adak's Kuluk Bay [SRC-0178, SRC-0179].
-Despite being officially slated to be based at Adak Island, the SBX-1 has never actually moored there or put into port at the facility [SRC-0178, SRC-0178, SRC-0179, SRC-0179]. Instead, the radar station has spent its operational life either roaming the Pacific Ocean, including the waters off the coast of Alaska, or returning to Pearl Harbor, Hawaii, for extensive maintenance, repairs, and testing [SRC-0178, SRC-0179, SRC-0178, SRC-0179]. As a result, while Adak Island features the dedicated infrastructure to support the SBX-1, it remains an unused deployment site for the vessel [SRC-0178, SRC-0179, SRC-0179]. Additional details regarding the site's other historical uses or facilities are not provided in the source material.</t>
+          <t>Aleutian Island station historically supporting Cobra Judy and now Sea-Based X-band Radar (SBX-1) home port.</t>
         </is>
       </c>
       <c r="T354" t="inlineStr">
@@ -26947,11 +26361,6 @@
       <c r="V354" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W354" t="inlineStr">
-        <is>
-          <t>SRC-0178, SRC-0179</t>
         </is>
       </c>
     </row>
@@ -27007,9 +26416,7 @@
       </c>
       <c r="S355" t="inlineStr">
         <is>
-          <t>Pearl Harbor Naval Base, part of Joint Base Pearl Harbor-Hickam, is a premier United States Navy installation located on the island of Oahu, Hawaii [SRC-0074, SRC-0136]. Managed under the Commander, Navy Region Hawaii, the base hosts the Pearl Harbor Naval Shipyard and provides critical operational, maintenance, and logistics support for the U.S. Pacific Fleet [SRC-0136, SRC-0134].
-In the 21st century, Pearl Harbor has become a vital hub for the Missile Defense Agency's (MDA) Ballistic Missile Defense System, primarily due to its ongoing support of the Sea-Based X-band Radar (SBX-1) [SRC-0178, SRC-0179, SRC-0178]. The SBX-1 is a self-propelled, floating radar station mounted on a semi-submersible platform, designed to track and discriminate incoming ballistic missile threats [SRC-0178, SRC-0179]. Although nominally assigned to a homeport in Adak, Alaska, the SBX-1 spends a significant portion of its time moored at Pearl Harbor for testing, maintenance, and upgrades [SRC-0179, SRC-0178, SRC-0179].
-Historical records indicate the SBX-1 was stationed at Pearl Harbor for repairs for 170 days in 2006, 63 days in 2007, 63 days in 2008, 177 days in 2009, and 51 days in 2010 [SRC-0178, SRC-0179]. The vessel also returned in late 2015 for testing and underwent a $24 million upgrade before departing again in 2017 [SRC-0179, SRC-0179]. After 20 years of service, the SBX-1 recently received a new protective radome while undergoing maintenance at the base [SRC-0129]. Because of the radar's distinct, spherical white dome and its frequent, highly visible presence at the installation, local residents have colloquially dubbed the vessel the "Golf Ball" or the "Pearl of Pearl Harbor" [SRC-0179].</t>
+          <t>Major Hawaiian naval base; home port for Aegis BMD-capable ships and Sea-Based X-band Radar (SBX-1).</t>
         </is>
       </c>
       <c r="T355" t="inlineStr">
@@ -27025,11 +26432,6 @@
       <c r="V355" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W355" t="inlineStr">
-        <is>
-          <t>SRC-0074, SRC-0136, SRC-0134, SRC-0178, SRC-0179, SRC-0129</t>
         </is>
       </c>
     </row>
@@ -27625,9 +27027,7 @@
       </c>
       <c r="S363" t="inlineStr">
         <is>
-          <t>The Shariki Communications Site is a military installation located in the Shariki region of Japan [SRC-0012]. It functions as a critical forward-deployed sensor node for the United States Department of Defense's layered ballistic missile defense architecture in the Pacific theater [SRC-0012].
-The primary asset at the Shariki site is the AN/TPY-2 radar system [SRC-0012]. The AN/TPY-2 is a transportable, high-resolution X-band active electronically scanned array (AESA) radar designed to detect, track, and discriminate short-, medium-, and intermediate-range ballistic missiles [SRC-0012, SRC-0011]. At the Shariki installation, the radar's specific operational mandate is to collect strategic-level intelligence and metric data on North Korean missile developments [SRC-0012]. Additionally, due to its geographic position and high-powered sensors, the AN/TPY-2 radar at Shariki is capable of scanning into Russian territory situated near Japan [SRC-0012].
-The intelligence and tracking data generated by the Shariki site provide vital early warning of incoming warheads for Japan [SRC-0012]. This capability seamlessly integrates with and complements the broader Japanese missile defense network, which utilizes Patriot PAC-3 systems for terminal point defense and Aegis-equipped Kongo-class destroyers armed with RIM-161 Standard Missile 3 (SM-3) interceptors for theater-wide ballistic missile defense [SRC-0012]. While the site is a critical component of regional security and U.S.-Japanese military cooperation, further extensive details regarding its establishment date, facility footprint, or managing personnel are not covered in the available source material.</t>
+          <t>Forward-based AN/TPY-2 X-band radar in Aomori, Japan for missile defense.</t>
         </is>
       </c>
       <c r="T363" t="inlineStr">
@@ -27643,11 +27043,6 @@
       <c r="V363" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="W363" t="inlineStr">
-        <is>
-          <t>SRC-0012, SRC-0011</t>
         </is>
       </c>
     </row>
@@ -28096,7 +27491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T186"/>
+  <dimension ref="A1:T131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -28328,7 +27723,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>The Dashuli Tracking Station, originally constructed in 1968 to support missile testing, currently serves as the nerve center for the telemetry, tracking, and command network at the Jiuquan Satellite Launch Centre [SRC-0084]. Among its primary instrumentation is a tracking radar system, which operates in conjunction with optical tracking telescopes to monitor launch vehicles [SRC-0084]. While the specific manufacturer, frequency band, and exact year of the radar's construction are not explicitly detailed in the provided sources, the radar's core purpose is to track launch vehicles from lift-off until approximately 500 seconds into the flight [SRC-0084]. The radar system is part of a broader tracking network that includes optical, communication, computer, and meteorology sub-systems [SRC-0084]. The data gathered by this tracking radar, along with telemetry measurements, is fed into the station's control hall [SRC-0084, SRC-0084]. This hall features over 30 control consoles that display 120 sets of real-time data regarding the trajectory of the launch vehicle and the live status of the rocket and its payload [SRC-0084]. This tracking information is then transmitted in real-time to the Mission Command and Control Centre at the headquarters to facilitate crucial decision-making during the launch process [SRC-0084]. Currently, the radar remains an operational and integral component of China's space launch infrastructure at Jiuquan [SRC-0084, SRC-0084].</t>
+          <t>Nerve center for the telemetry, tracking, and command network at Jiuquan. Transmits real-time trajectory data to the control headquarters.</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -28349,11 +27744,6 @@
       <c r="S3" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>SRC-0084</t>
         </is>
       </c>
     </row>
@@ -28651,8 +28041,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>The AN/TPY-2 is a highly advanced, trailer-mounted active electronically scanned array (AESA) missile defense radar [SRC-0011, SRC-0012]. Manufactured by Raytheon Technologies and introduced in 2007, this ruggedized, all-weather system operates in the X-band frequency range (8.55–10 GHz) [SRC-0011, SRC-0011, SRC-0011, SRC-0012]. Operating in the X-band, combined with electronic beam steering, provides exceptional target resolution, allowing the radar to precisely track small objects and accurately discriminate between actual ballistic missile warheads and decoys [SRC-0012, SRC-0011, SRC-0012].
-The AN/TPY-2 boasts a detection range exceeding 1,000 kilometers, reaching up to 3,000 kilometers depending on the target and operating mode [SRC-0011, SRC-0012, SRC-0011]. It is capable of tracking hundreds of targets simultaneously and integrates seamlessly with defense networks like THAAD, Aegis BMD, and C2BMC [SRC-0011, SRC-0011, SRC-0011, SRC-0011]. The system's primary purpose is long-range detection, tracking, and discrimination of ballistic missile threats, serving as both a forward-based early warning radar and a terminal defense radar [SRC-0012, SRC-0011, SRC-0011]. Currently operational and in active deployment globally, the radar stationed in the Shariki region of Japan is specifically tasked with collecting strategic intelligence on North Korean missile developments and providing early warning of incoming warheads [SRC-0011, SRC-0012]. Additionally, from its position at Shariki, the AN/TPY-2 has the capability to scan Russian territory near Japan [SRC-0012].</t>
+          <t>Scans neighboring territories to monitor missile developments. Integrates with existing missile defense architectures.</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -28673,11 +28062,6 @@
       <c r="S7" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>SRC-0011, SRC-0012</t>
         </is>
       </c>
     </row>
@@ -30543,7 +29927,7 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>The Multiple Object Tracking Radar (MOTR) is an extremely rare, phased-array tracking radar utilized at the White Sands Missile Range (WSMR) [SRC-0114, SRC-0157]. Built in the mid-1980s, the original procurement cost for each MOTR unit was approximately $36 million [SRC-0114]. While the specific manufacturer and frequency band are not explicitly named in the provided sources, the MOTR operates by transmitting a pulse of energy through phase-shifting elements, delaying the pulse by a fraction of a wavelength to steer the beam off boresight [SRC-0114]. This advanced technology enables the radar to cover a 60-degree area and provides the capability to track the exact location of up to 40 airborne objects simultaneously with extreme precision [SRC-0157, SRC-0114]. The energy is received and processed by any of three channel receivers [SRC-0114]. The primary purpose of the radar is to support flight safety operations, carefully tracking airborne systems under test to ensure they remain on their designated paths [SRC-0157]. As for its current status, WSMR owns three of the five MOTR systems ever produced worldwide (MOTR-1, MOTR-3, and MOTR-4) [SRC-0114, SRC-0114]. MOTR-4 was recently saved from an Air Force scrap yard at Vandenberg Air Force Base and transferred to WSMR to replace aging infrastructure [SRC-0157, SRC-0157]. Recreating such a system today would cost upward of $70 billion [SRC-0114].</t>
+          <t>Capable of tracking up to 40 airborne objects simultaneously, ensuring systems under test fly safely.</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -30564,11 +29948,6 @@
       <c r="S33" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="T33" t="inlineStr">
-        <is>
-          <t>SRC-0114, SRC-0157</t>
         </is>
       </c>
     </row>
@@ -30615,7 +29994,7 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>The AN/FPS-16 is a precision instrumentation tracking radar manufactured by RCA that has been historically utilized at the White Sands Missile Range (WSMR) for trajectory tracking and data collection [SRC-0217]. The exact frequency band is not specified in the sources, but the radar was integrated into the range well before 1972, a time when WSMR maintained three AN/FPS-16 units in active operation [SRC-0217]. During the 1963 to 1964 testing season, the AN/FPS-16 was employed to track superpressure balloons carrying spherical targets, successfully recording position data in X, Y, and Z coordinates on magnetic tape at a rate of one data point per second [SRC-0103]. Unlike newer phased-array systems, the AN/FPS-16 operates on a single-track basis and lacks the capability to provide precision measurements for multiple objects simultaneously [SRC-0114, SRC-0114]. On average, the radar's purpose supports about 25 tracks during a single mission [SRC-0114]. Regarding its current status, the AN/FPS-16 system at WSMR is being phased out of service due to aging technology and high maintenance costs. Upgrading the existing AN/FPS-16 radars to modern standards would have cost the installation approximately $7.5 million, while purchasing new equivalents would cost $9 million [SRC-0114]. To improve data quality and reduce associated costs by 70 percent, WSMR is replacing two of its AN/FPS-16 radars with the newly acquired Multiple Object Tracking Radar 4 (MOTR-4) [SRC-0114, SRC-0114].</t>
+          <t>Used to track targets and missiles, though being partially supplemented by newer MOTR systems.</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -30636,11 +30015,6 @@
       <c r="S34" t="inlineStr">
         <is>
           <t>Published</t>
-        </is>
-      </c>
-      <c r="T34" t="inlineStr">
-        <is>
-          <t>SRC-0217, SRC-0103, SRC-0114</t>
         </is>
       </c>
     </row>
@@ -31236,7 +30610,7 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled, mobile active electronically scanned array (AESA) early-warning radar system [SRC-0179, SRC-0178, SRC-0179]. Operating in the X-band, it provides finer target resolution than lower-frequency radars [SRC-0178, SRC-0179]. The radar was developed by Raytheon, with Boeing serving as the prime contractor, and was deployed in 2006 as a critical midcourse sensor for the U.S. Ballistic Missile Defense System [SRC-0178, SRC-0178, SRC-0178]. The radar antenna itself spans 384 square meters and is protected by a flexible, positively pressurized central dome [SRC-0178, SRC-0179, SRC-0178]. The array is built to accommodate 45,000 solid-state transmit-receive modules, and currently operates with approximately 22,000 installed modules focused toward the center to minimize grating lobes [SRC-0179, SRC-0179]. The primary purpose of the SBX-1 is to detect, precision-track, and discriminate enemy ballistic missile warheads from decoys, boasting the capability to track an object the size of a baseball from 2,900 miles away [SRC-0179, SRC-0178, SRC-0178]. While the vessel is nominally homeported at Adak Island in Alaska, it has never actually been moored there [SRC-0179, SRC-0179, SRC-0179, SRC-0178]. Instead, the SBX-1 has spent significant time at Pearl Harbor, Hawaii, for extensive maintenance, testing, and repairs—such as a 170-day stay in 2006—and actively deploys from there into the Pacific Ocean to monitor foreign missile launches [SRC-0179, SRC-0179, SRC-0178].</t>
+          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled, mobile active electronically scanned array radar station that operates as a critical part of the Ground-Based Midcourse Defense (GMD) system [SRC-0178, SRC-0179, SRC-0179]. While nominally based at Adak Island, Alaska, it has spent significant time in Pearl Harbor for maintenance and upgrades [SRC-0178, SRC-0179]. Designed by Raytheon for Boeing and deployed in 2006, the $900 million system operates in the X-band to provide high-resolution target discrimination, differentiating enemy warheads from decoys and conducting precision tracking [SRC-0179, SRC-0178, SRC-0178, SRC-0178]. The radar is mounted on a converted fifth-generation CS-50 twin-hulled semi-submersible platform that displaces 50,000 tons and measures 389 feet in length [SRC-0178, SRC-0179, SRC-0179]. The 4,130-square-foot phased-array antenna weighs 4,000,000 pounds and utilizes tens of thousands of solid-state transmit-receive modules mounted on an octagonal base capable of moving ±270 degrees in azimuth [SRC-0178, SRC-0178, SRC-0179]. The radar is protected by a flexible, positive-air-pressure central dome [SRC-0178, SRC-0179]. Capable of detecting baseball-sized objects from 2,500 to 2,900 miles away, the SBX-1 has undergone numerous maintenance periods at Pearl Harbor, most notably replacing its massive protective radome in December 2025 to ensure its continued viability for decades of future homeland missile defense missions [SRC-0178, SRC-0179, SRC-0190, SRC-0190].</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -31261,7 +30635,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>SRC-0179, SRC-0178</t>
+          <t>SRC-0178, SRC-0179, SRC-0190</t>
         </is>
       </c>
     </row>
@@ -38283,3147 +37657,6 @@
       <c r="T131" t="inlineStr">
         <is>
           <t>SRC-0086, SRC-0013, SRC-0016</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>RAD-0131</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>SITE-0138</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Tracking, Telemetry And Flight Termination System</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>The tracking radar infrastructure at SaxaVord Spaceport is a newly established, bespoke rocket tracking, telemetry, and flight termination system located on the Lamba Ness peninsula on the island of Unst in Shetland, Scotland [SRC-0130, SRC-0176]. While specific technical parameters such as the system's exact frequency band, manufacturer, power output, and physical dimensions are not explicitly detailed in the provided sources, the radar network is an essential part of the first fully licensed vertical launch spaceport in Western Europe [SRC-0175, SRC-0176]. 
-The primary purpose of this tracking equipment is to monitor the ascent of rockets launching small satellites into polar and sun-synchronous orbits [SRC-0175]. In modern spaceflight operations, such tracking systems are mandated by range authorities to follow the vehicle's flight path continuously and relay data to a Range Control Centre, which is proposed to be located at the former RAF SaxaVord radar complex [SRC-0176, SRC-0202]. If a rocket veers off its designated trajectory, the integrated flight termination system can be activated to safely destroy the vehicle [SRC-0202]. The tracking and telemetry systems have already been installed on the site to support the first operational launch complex [SRC-0130]. Following the UK Civil Aviation Authority's issuance of a range licence in April 2024, which allows the spaceport to control the sea and airspace along its launch trajectories, this tracking infrastructure is primed to eventually support up to 30 launches per year [SRC-0176, SRC-0130, SRC-0176].</t>
-        </is>
-      </c>
-      <c r="P132" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>SRC-0130</t>
-        </is>
-      </c>
-      <c r="S132" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
-        <is>
-          <t>SRC-0130, SRC-0176, SRC-0175, SRC-0202</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>RAD-0132</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>SITE-0352</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Aegis Ashore</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>The Aegis Ashore system in Romania is a critical land-based ballistic missile defense (BMD) installation designed to defeat short- to intermediate-range ballistic missile threats [SRC-0134]. While the exact dimensions, power output, year built, and specific site manufacturing details of the Romanian facility are not explicitly detailed in the provided sources, the Aegis system fundamentally relies on S-band radar frequencies for its operations [SRC-0178]. The primary purpose of this system is to provide robust defense for NATO's European territories and deployed forces against ballistic missile threats originating from outside the Euro-Atlantic region [SRC-0093]. To achieve this defensive mission, the Aegis Ashore site is highly capable and specifically equipped to launch advanced Standard Missile-3 (SM-3) Block IBTU and Block IIA interceptors [SRC-0093]. Regarding its current status, the Aegis Ashore system in Romania is fully operational [SRC-0134, SRC-0093]. It currently serves as a cornerstone of the Missile Defense Agency's contribution to Phase 3 of the European Phased Adaptive Approach (EPAA) [SRC-0093]. Notable operational development and rigorous testing for the Aegis Ashore architecture were extensively conducted at the Pacific Missile Range Facility in Hawaii beginning in 2002; these tests were critical to ensuring the reliability and success of the active operational system that is now deployed in Romania [SRC-0134].</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>SRC-0134</t>
-        </is>
-      </c>
-      <c r="S133" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
-        <is>
-          <t>SRC-0134, SRC-0178, SRC-0093</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>RAD-0133</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>SITE-0357</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Early Warning Radar</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N134" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>The provided sources contain very limited technical information regarding the surveillance radar at Rovaniemi Air Base. Specific details such as the radar's exact type, frequency band, manufacturer, year of construction, physical dimensions, power output, current operational status, and any recent modernizations or upgrades are not mentioned in the available documents. What is known from the sources is that an early warning radar was active at Rovaniemi in the mid-1980s. Its capabilities were notably demonstrated during the Lake Inari incident on December 28, 1984 [SRC-0165]. During this event, a Soviet Navy SS-N-3 missile, which had been modified with MiG avionics for use as a remote-controlled target, lost radio contact with its operator, strayed across the Finnish border, and eventually crashed through the ice into Lake Inari [SRC-0165]. The early warning radar at Rovaniemi successfully detected the incoming missile, which prompted the dispatch of two Saab 35 Draken fighter jets to investigate the airspace incursion [SRC-0165]. Although the fighters were unable to locate the missile in the air before it crashed, the radar's early warning detection successfully fulfilled its purpose of monitoring Finnish airspace for unauthorized border crossings during a tense period [SRC-0165].</t>
-        </is>
-      </c>
-      <c r="P134" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>SRC-0165</t>
-        </is>
-      </c>
-      <c r="S134" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>SRC-0165</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>RAD-0134</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>SITE-0356</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Close-Range Radar</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N135" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>Similar to the Rovaniemi system, the provided sources lack detailed technical specifications for the surveillance radar located at the Kaamanen Radar Site. There is no information available in the text regarding the system's frequency band, manufacturer, exact year it was built, power capabilities, physical dimensions, or current operational status. However, the sources describe it as a close-range radar system [SRC-0165]. The primary notable operation involving this radar also occurred during the December 1984 Lake Inari incident [SRC-0165]. While the Rovaniemi early warning radar provided the initial warning, the close-range radar at Kaamanen also successfully picked up the unauthorized entry of the Soviet SS-N-3 cruise missile into Finnish airspace [SRC-0165]. The missile, which was being used as a target drone by the Soviet Navy, had strayed off course due to a presumed loss of radio contact with its operator [SRC-0165]. The combined tracking data from the Kaamanen close-range radar and the Rovaniemi early warning radar alerted the Finnish military to the threat [SRC-0165]. While the specific technical parameters of the Kaamanen radar remain unstated in the provided documents, its capability to detect and track stray cruise missiles over the remote northern territories of Finland was clearly demonstrated during this historical event [SRC-0165].</t>
-        </is>
-      </c>
-      <c r="P135" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>SRC-0165</t>
-        </is>
-      </c>
-      <c r="S135" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
-        <is>
-          <t>SRC-0165</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>RAD-0135</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>SITE-0113</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Air And Sea Surveillance Radar System</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>The NATO Missile Firing Installation (NAMFI), located at Souda Bay on the island of Crete, Greece, relies on an Air and Sea surveillance radar system to safely support its extensive operations [SRC-0122, SRC-0122, SRC-0122]. Established in 1967 as a premier NATO training facility for air defense systems, the range takes advantage of the region's clear atmospheric conditions year-round [SRC-0122]. Because the firing range's operational trajectories frequently intersect with busy commercial and military air and maritime traffic routes, the primary purpose of the surveillance radar system is to monitor the surrounding environment and resolve any possible tracking conflicts to ensure safety during live-fire exercises [SRC-0122]. The radar provides critical situational awareness for a variety of complex missile tests, most notably supporting launches of the MIM-104 Patriot and MIM-23 Hawk surface-to-air missile systems, as well as occasionally tracking other air-to-surface weapons [SRC-0122]. While specific technical specifications—such as the radar's exact designation, frequency band, manufacturer, dimensions, peak power output, and precise year of installation—are not detailed in the provided sources, the radar system remains in highly active operational status [SRC-0122]. It currently supports the armed forces of Greece, Germany, the Netherlands, and the United States during regular, multinational integrated air and missile defense training operations [SRC-0122, SRC-0122].</t>
-        </is>
-      </c>
-      <c r="P136" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R136" t="inlineStr">
-        <is>
-          <t>SRC-0122</t>
-        </is>
-      </c>
-      <c r="S136" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T136" t="inlineStr">
-        <is>
-          <t>SRC-0122</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>RAD-0136</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>SITE-0194</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Cobra Dane (An/Fps-108)</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>The COBRA DANE (AN/FPS-108) is a single-faced, ground-based, L-band (1175–1375 MHz) large phased-array radar (LPAR) located at Eareckson Air Station on Shemya Island, Alaska [SRC-0001, SRC-0043, SRC-0190]. Developed in the mid-1970s and achieving operational status in 1977, the radar was initially built for the United States Air Force to collect intelligence data on Soviet ballistic missile tests and verify the SALT II arms limitation treaty [SRC-0043, SRC-0001, SRC-0190]. Today, it is operated by the U.S. Space Force [SRC-0043, SRC-0190]. COBRA DANE features a massive 95-foot diameter array face containing 15,360 active radiating elements and generates a peak RF power of approximately 15.4 megawatts using 96 Traveling Wave Tube (TWT) amplifiers [SRC-0190, SRC-0001, SRC-0043]. Its primary capabilities include providing midcourse coverage for the Ballistic Missile Defense System (detecting and classifying ICBMs and SLBMs to cue interceptors) and conducting space domain awareness by tracking satellites and orbital debris [SRC-0043, SRC-0027, SRC-0044]. It can detect objects as small as a basketball at distances of 2,000 miles [SRC-0043, SRC-0043]. Having undergone significant modernizations, such as the 1990 System Modernization and recent TWT redesigns, COBRA DANE is currently slated for comprehensive back-end digitization under the Ground Based Radar Digitization (GBRD) program [SRC-0001, SRC-0186, SRC-0190, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P137" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R137" t="inlineStr">
-        <is>
-          <t>SRC-0001</t>
-        </is>
-      </c>
-      <c r="S137" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T137" t="inlineStr">
-        <is>
-          <t>SRC-0001, SRC-0043, SRC-0190, SRC-0027, SRC-0044, SRC-0186</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>RAD-0137</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>SITE-0344</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Long Range Discrimination Radar (Lrdr) (An/Fps-138)</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N138" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O138" t="inlineStr">
-        <is>
-          <t>The Long Range Discrimination Radar (LRDR), designated as AN/FPS-138, is a state-of-the-art solid-state Active Electronically Scanned Array (AESA) radar located at Clear Space Force Station in Alaska [SRC-0045, SRC-0045, SRC-0190]. Developed by Lockheed Martin, the contract was awarded in 2015, leading to its initial fielding in December 2021 [SRC-0100, SRC-0190]. The LRDR operates in the S-band and utilizes highly efficient Gallium Nitride (GaN) semiconductor technology [SRC-0100, SRC-0190]. Physically, it features dual monostatic arrays, each measuring 60 feet high by 60 feet wide, providing an extensive field of view for its multi-mission requirements [SRC-0100, SRC-0190, SRC-0003]. The radar's primary purpose is homeland missile defense, specifically designed to simultaneously search, track, and discriminate multiple long-range ballistic missile threats [SRC-0045, SRC-0045]. Its high-resolution S-band capabilities allow it to distinguish lethal warheads from non-lethal decoys and debris, preserving the inventory of Ground-Based Interceptors [SRC-0190, SRC-0045, SRC-0100]. Additionally, it supports space domain awareness by monitoring active and inactive satellites [SRC-0100, SRC-0190]. The system achieved operational acceptance by the USSF Combat Forces Command in December 2025 and is fully operational for homeland defense, featuring an adaptable open architecture designed to counter emerging hypersonic threats [SRC-0045, SRC-0190, SRC-0045].</t>
-        </is>
-      </c>
-      <c r="P138" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>SRC-0045</t>
-        </is>
-      </c>
-      <c r="S138" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T138" t="inlineStr">
-        <is>
-          <t>SRC-0045, SRC-0190, SRC-0100, SRC-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>RAD-0138</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>SITE-0345</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Perimeter Acquisition Radar Attack Characterization System (Parcs) (An/Fpq-16)</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N139" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>The Perimeter Acquisition Radar Attack Characterization System (PARCS), designated AN/FPQ-16, is a massive, single-faced passive electronically scanned array (PESA) radar situated at Cavalier Space Force Station in North Dakota [SRC-0008, SRC-0143, SRC-0190]. Built by General Electric in the early 1970s, it originally served as the Perimeter Acquisition Radar (PAR) for the U.S. Army's Safeguard anti-ballistic missile program before being transferred to the Air Force in 1976 and 1977 [SRC-0190, SRC-0008, SRC-0008]. Operating in the UHF band (420–450 MHz), the radar boasts a peak power output of roughly 14.3 megawatts [SRC-0132, SRC-0190]. Its single fixed antenna face provides a 140-degree azimuth and 93-degree elevation coverage, capable of detecting and tracking targets up to 2,000 miles away [SRC-0132, SRC-0190]. The primary mission of PARCS is early warning, keeping watch for sea-launched and intercontinental ballistic missiles aimed at North America, while its secondary role involves monitoring over half of all Earth-orbiting objects for the Space Surveillance Network [SRC-0143, SRC-0190, SRC-0008]. Maintained by the 10th Space Warning Squadron and sustained by contractors such as InDyne, this legacy Cold War asset remains operational today [SRC-0190, SRC-0190]. To address hardware obsolescence, PARCS is scheduled to receive a modernized, digitized front-end antenna array under the Space Force's Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P139" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>SRC-0008</t>
-        </is>
-      </c>
-      <c r="S139" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T139" t="inlineStr">
-        <is>
-          <t>SRC-0008, SRC-0143, SRC-0190, SRC-0132, SRC-0186</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>RAD-0139</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>SITE-0366</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Multiple Object Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O140" t="inlineStr">
-        <is>
-          <t>The Multiple Object Tracking Radar (MOTR) is a highly specialized phased-array tracking system located at White Sands Missile Range (WSMR) [SRC-0114, SRC-0157]. Built in the mid-1980s at an original cost of $36 million each, the MOTR is an exceptionally rare asset, with only five units ever constructed worldwide [SRC-0114, SRC-0157]. The radar transmits pulses of energy through phase-shifting elements, allowing it to electronically steer its beam off-boresight to cover a 60-degree area and simultaneously track up to 40 airborne objects [SRC-0157, SRC-0114]. Its primary purpose at WSMR is to support flight safety operations and test evaluations by providing precise Time-Space-Position-Information (TSPI) data, ensuring that airborne systems follow their intended flight paths safely [SRC-0157, SRC-0114]. 
-Currently, WSMR is the only installation globally to house three MOTR systems [SRC-0114]. Most notably, MOTR-4 was rescued from an Air Force scrap yard at Vandenberg Air Force Base in 2011 [SRC-0157, SRC-0157]. An internal team at WSMR successfully disassembled, transported, and reassembled the radar, achieving operational status in 2015 [SRC-0157, SRC-0114]. This acquisition replaced older AN/FPS-16 radars, delivering vastly improved data quality and realizing significant cost savings for the installation [SRC-0114, SRC-0114, SRC-0114].</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>SRC-0114</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T140" t="inlineStr">
-        <is>
-          <t>SRC-0114, SRC-0157</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>RAD-0140</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>SITE-0366</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>An/Fps-16 (An/Fps-16)</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O141" t="inlineStr">
-        <is>
-          <t>Historically, White Sands Missile Range (WSMR) operated multiple RCA-manufactured AN/FPS-16 instrumentation radars to provide precise metric tracking and flight safety data [SRC-0008], [SRC-0217]. These single-object tracking radar systems were crucial for observing test vehicles, sounding rockets, and tracking superpressure weather balloons while recording position data at a rate of one point per second [SRC-0103], [SRC-0153]. Over the decades, WSMR utilized at least three of these legacy tracking systems across its expansive range [SRC-0217]. While highly accurate, the AN/FPS-16 radars were limited by their ability to track only a single object at a time and required significant personnel and financial resources to maintain [SRC-0114]. Rather than spending approximately $7.5 million to upgrade the aging FPS-16s to modern standards, or $9 million for new equivalent units, WSMR strategically replaced them with a rare Multiple Object Tracking Radar (MOTR-4) acquired from Vandenberg [SRC-0114], [SRC-0114], [SRC-0114]. The transportable MOTR system maintained the high tracking accuracy of the AN/FPS-16 while offering multiple-track capabilities, effectively replacing two FPS-16 units and saving the equivalent of eight employees' annual workloads [SRC-0114], [SRC-0114].</t>
-        </is>
-      </c>
-      <c r="P141" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R141" t="inlineStr">
-        <is>
-          <t>SRC-0008</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T141" t="inlineStr">
-        <is>
-          <t>SRC-0008, SRC-0217, SRC-0103, SRC-0153, SRC-0114</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>RAD-0141</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SITE-0347</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Upgraded Early Warning Radar (Uewr) (An/Fps-132)</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N142" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O142" t="inlineStr">
-        <is>
-          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Cape Cod Space Force Station, Massachusetts, provides critical early warning coverage over the United States East Coast and the Atlantic Ocean [SRC-0133], [SRC-0190]. Operated by the 6th Space Warning Squadron, the radar is the only facility in the nation capable of confirming a detected intercontinental or sea-launched ballistic missile attack from the east [SRC-0133]. Housed in a 32-meter (105-foot) high building, the solid-state phased-array radar utilizes two flat faces tilted back 20 degrees, each measuring 31 meters (102 feet) wide [SRC-0133]. The system operates in the UHF band (420 to 450 MHz) and features 1,792 active antenna elements per face, capable of producing approximately 582.4 kW of peak power and 152.5 kW of average power [SRC-0133], [SRC-0133]. The radar electronically steers a narrow 2.2-degree main beam to provide a 240-degree sweep [SRC-0133], [SRC-0133]. Originally activated in 1980 as a PAVE PAWS installation, it was upgraded to the AN/FPS-132 UEWR configuration by Raytheon between 2013 and 2017 [SRC-0190], [SRC-0190]. This modification integrated the radar into the Ballistic Missile Defense System without requiring major structural changes [SRC-0190]. It also continues its secondary mission of space surveillance and is targeted for the Space Force's upcoming GBRD modernization by 2030 [SRC-0186], [SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P142" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>SRC-0133</t>
-        </is>
-      </c>
-      <c r="S142" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
-        <is>
-          <t>SRC-0133, SRC-0190, SRC-0186</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>RAD-0142</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>SITE-0344</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Upgraded Early Warning Radar (Uewr) (An/Fps-132)</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Clear Space Force Station, Alaska, is a vital strategic sensor hub in the Pacific theater, operated by the 13th Space Warning Squadron [SRC-0190], [SRC-0190]. Originally established in September 1961 as a mechanical Ballistic Missile Early Warning System (BMEWS) site, the facility was upgraded in 1981 to an AN/FPS-123 Solid-State Phased Array Radar System (SSPARS) [SRC-0190]. To meet modern threats, the Air Force and the Missile Defense Agency awarded Raytheon a $125.3 million contract in 2012 to upgrade the system to the AN/FPS-132 UEWR configuration [SRC-0190]. Completed in Fiscal Year 2016 within the existing scanner building, this upgrade integrated critical Ground-based Midcourse Defense (GMD) communication capabilities [SRC-0190]. Operating in the UHF band, the radar’s two-panel phased-array configuration provides a 240-degree coverage arc stretching across the Arctic and Pacific regions [SRC-0190], [SRC-0190]. Its primary purpose is to provide early warning of ballistic missile attacks and overlapping space domain awareness alongside the newly constructed Long Range Discrimination Radar (LRDR) also located at Clear [SRC-0190], [SRC-0190]. To counter future advanced digital threats, the Clear UEWR is scheduled for front-end antenna digitization and integration into a common virtual software stack under the Space Force's Ground Based Radar Digitization (GBRD) Phase 1 prototyping program, expected to achieve initial operational capability by FY 2030 [SRC-0190], [SRC-0190], [SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P143" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>SRC-0190</t>
-        </is>
-      </c>
-      <c r="S143" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
-        <is>
-          <t>SRC-0190</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>RAD-0143</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>SITE-0290</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Arsr-4 (Arsr-4) At Gibbsboro J-51 Jss</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O144" t="inlineStr">
-        <is>
-          <t>The ARSR-4 (Air Route Surveillance Radar-4) at the Gibbsboro J-51 Joint Surveillance System (JSS) site is a three-dimensional, long-range surveillance radar located at 39°49′29″N 074°57′15″W in New Jersey [SRC-0086, SRC-0086]. Manufactured by the Northrop Grumman Corporation in the 1990s, the ARSR-4 was designed to replace obsolete 1960s-vintage AN/FPS-20 and ARSR-1/2 radars [SRC-0086, SRC-0086, SRC-0086]. It operates in the L-band frequency range of 1.215 to 1.4 GHz, utilizing dual-channel frequency hopping technology to provide robust long-range detection and anti-jamming defense [SRC-0086, SRC-0086]. This solid-state radar system features an impressive effective detection range of 250 nautical miles and can detect small, low-flying objects by minimizing clutter and weather effects through its "look down" capability [SRC-0086, SRC-0086]. The ARSR-4 emits a peak power of 65 kW and an average power of 3.5 kW [SRC-0086]. The Gibbsboro site, formerly known as the Aerospace Defense Command (ADCOM) Gibbsboro Air Force Station (Z-63), saw its USAF operations close in 1984 before it transitioned into a joint-use FAA/USAF JSS facility [SRC-0086]. During the change-out to the new ARSR-4 system, the nearby Trevose J-61 site served as a temporary data-tie to maintain coverage until Gibbsboro officially reopened with its upgraded ARSR-4 [SRC-0086]. Today, it functions as a critical, largely unattended asset for both national airspace defense and civil air traffic control [SRC-0086, SRC-0086].</t>
-        </is>
-      </c>
-      <c r="P144" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R144" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S144" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T144" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>RAD-0144</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>SITE-0291</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Arsr-2 (Arsr-2) At Gallup Gal Jss</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N145" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>The ARSR-2 at the Gallup GAL JSS site is a long-range Air Route Surveillance Radar located at 36°04′33″N 108°51′37″W, above Washington Pass, north of Gallup, New Mexico [SRC-0086]. It is also historically known as the Farmington site and the former Aerospace Defense Command (ADCOM) SAGE site Z-221 [SRC-0086]. Opened by the Federal Aviation Administration (FAA) in 1963, the system forms a vital part of the Joint Surveillance System (JSS), providing atmospheric air defense and air traffic control data for both the FAA and the United States Air Force [SRC-0086, SRC-0086]. The ARSR-2 was originally developed by Raytheon in the 1960s to operate in the L-band frequency range of 1215 to 1350 MHz, functioning identically to its ARSR-1 predecessor but with redesigned components for improved reliability [SRC-0086, SRC-0086]. Initially, the radar provided a detection range of approximately 200 nautical miles and relied on nationwide vacuum tube technology [SRC-0086, SRC-0086]. However, to maintain its operational viability and extend its service life, the Gallup ARSR-2, alongside all other ARSR-1 and ARSR-2 systems, was upgraded to the modern Common ARSR (CARSR) configuration by the end of 2015 [SRC-0086, SRC-0086]. This substantial upgrade replaced legacy parts with completely solid-state transmitter components and software shared with the FAA's newer ASR-11 airport surveillance radars, maintaining its 200-nautical-mile range while vastly improving its operational efficiency [SRC-0086].</t>
-        </is>
-      </c>
-      <c r="P145" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R145" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T145" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>RAD-0145</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SITE-0292</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Arsr-1E (Arsr-1E) At Mesa Rica Qwc Jss</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N146" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>The ARSR-1E at the Mesa Rica QWC JSS site is a long-range Air Route Surveillance Radar situated at 35°14′15″N 104°12′16″W in New Mexico [SRC-0086]. Originally part of the Semi Automatic Ground Environment (SAGE) network, it operated as the former Aerospace Defense Command (ADCOM) SAGE site Z-234 [SRC-0086, SRC-0086]. Manufactured by Raytheon and initially introduced in 1958, the ARSR-1 series operates in the adjacent L-band frequency range between 1215 and 1350 MHz [SRC-0086, SRC-0086]. Built to support both civilian air traffic control and military air defense, the system originally achieved a maximum detection range of around 170 to 200 nautical miles [SRC-0086, SRC-0086]. Like many older radar installations in the Joint Surveillance System, the Mesa Rica facility initially relied on outdated vacuum tube technology [SRC-0086]. Over time, these legacy systems required significant overhauls to remain reliable and effective for the Federal Aviation Administration (FAA) and the U.S. Air Force [SRC-0086, SRC-0086]. By the end of 2015, the Mesa Rica ARSR-1E was fully modernized under the Common ARSR (CARSR) upgrade program [SRC-0086]. This crucial retrofit replaced the aging hardware with a completely solid-state architecture, integrating new transmitter components and modern software shared with the FAA's ASR-11 radars [SRC-0086]. Through this modernization, the Mesa Rica site continues its dual-purpose mission, sustaining a reliable 200-nautical-mile surveillance range to monitor internal and border airspace [SRC-0086, SRC-0086].</t>
-        </is>
-      </c>
-      <c r="P146" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>RAD-0146</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>SITE-0293</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Surveillance Radar At Silver City J-28 Jss</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>The surveillance radar at the Silver City J-28 JSS site was a long-range radar installation located atop Brushy Mountain at 32°59′21″N 108°57′38″W in New Mexico [SRC-0086]. Originally established as part of the 1972 Southern Air Defense System, the Silver City facility operated as the former Aerospace Defense Command (ADCOM) site Z-245 [SRC-0086]. Like other legacy radar facilities integrated into the Joint Surveillance System (JSS), it was designed to provide crucial atmospheric air defense tracking and civil air traffic control data for both the Federal Aviation Administration and the United States Air Force [SRC-0086]. While specific dimensions and power outputs for the original Silver City radar are not explicitly detailed in the provided sources, the site historically utilized legacy long-range search radar equipment characteristic of the early Cold War and SAGE network eras [SRC-0086, SRC-0086]. Ultimately, the Silver City J-28 site was closed in the 1990s as the U.S. military and the FAA sought to modernize the JSS network with more advanced, reliable, and standardized radar technology [SRC-0086]. The surveillance coverage formerly provided by the Silver City facility was subsequently replaced by the newly constructed J-28A site in Deming, New Mexico [SRC-0086]. The Deming site took over the sector's operational responsibilities by utilizing the highly capable ARSR-4 three-dimensional solid-state radar system, effectively ending the operational history of the Silver City J-28 site [SRC-0086, SRC-0086].</t>
-        </is>
-      </c>
-      <c r="P147" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>RAD-0147</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>SITE-0225</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Arsr-4 (Arsr-4) At Deming Tars</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>The Deming area in New Mexico hosts two distinct yet complementary radar surveillance capabilities: the ARSR-4 at the J-28A Joint Surveillance System (JSS) site and the Tethered Aerostat Radar System (TARS). The ARSR-4 radar, located at 32°29′30″N 107°09′59″W, is a state-of-the-art, three-dimensional, solid-state long-range surveillance radar manufactured by Northrop Grumman [SRC-0086, SRC-0086]. Operating in the L-band (1.215–1.4 GHz), the ARSR-4 outputs 65 kW of peak power and provides a 250-nautical-mile detection range [SRC-0086]. It features a "look down" capability and frequency-hopping technology to track low-flying targets while minimizing clutter [SRC-0086, SRC-0086]. The J-28A site was established to replace the older Silver City J-28 installation, providing enhanced air defense and air traffic control data [SRC-0086]. In addition to the fixed ARSR-4, Deming operates a TARS site at 32°01′36″N 107°51′51″W [SRC-0197]. The TARS platform uses a 420,000-cubic-foot helium-filled aerostat that ascends to 15,000 feet, carrying a Lockheed Martin L-88(V)3 L-band radar [SRC-0098, SRC-0197]. The TARS radar features a 29-foot rotating antenna inside a fabric windscreen, providing 360-degree, downward-looking coverage out to 200 nautical miles [SRC-0098, SRC-0197]. Modernized in 1999 to the standard 420K/L-88 configuration, the Deming TARS plays a critical role in supporting U.S. Customs and Border Protection by detecting low-flying drug smugglers and airborne incursions along the southern border [SRC-0098, SRC-0098].</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R148" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S148" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T148" t="inlineStr">
-        <is>
-          <t>SRC-0086, SRC-0197, SRC-0098</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>RAD-0148</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>SITE-0295</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Arsr-2 (Arsr-2) At Battle Mountain Btm Jss</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N149" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O149" t="inlineStr">
-        <is>
-          <t>The ARSR-2 at the Battle Mountain BTM JSS site is a long-range Air Route Surveillance Radar positioned on top of Mount Lewis, south of Battle Mountain, Nevada, at coordinates 40°24′11″N 116°52′04″W [SRC-0086]. Historically referred to as the Elko site and designated as the former Aerospace Defense Command (ADCOM) site Z-214, the facility is a key component of the Joint Surveillance System (JSS) [SRC-0086]. Operating in the L-band frequency range (1215–1350 MHz), the ARSR-2 was developed by Raytheon in the 1960s to serve the dual purposes of North American atmospheric air defense and civilian air traffic control [SRC-0086, SRC-0086, SRC-0086]. Originally reliant on vacuum tube electronics, the system provided reliable detection out to a range of 200 nautical miles [SRC-0086, SRC-0086]. Over the decades, maintaining these legacy components became increasingly difficult [SRC-0086]. To ensure continued operational viability, the Federal Aviation Administration and the U.S. Air Force upgraded the Battle Mountain installation under the Common ARSR (CARSR) program, which was completed for all ARSR-1/2 systems by the end of 2015 [SRC-0086]. This critical modernization replaced the outdated hardware with a completely solid-state architecture, sharing modern software and transmitter components with the newer ASR-11 airport surveillance radars [SRC-0086]. Today, the upgraded Battle Mountain radar remains an essential, unmanned asset that provides continuous, highly reliable airspace monitoring capabilities for the western United States [SRC-0086, SRC-0086].</t>
-        </is>
-      </c>
-      <c r="P149" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R149" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T149" t="inlineStr">
-        <is>
-          <t>SRC-0086</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>RAD-0149</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>SITE-0045</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>C-Band Monopulse Precision Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O150" t="inlineStr">
-        <is>
-          <t>Changchun Station is part of China's network of five fixed near-Earth satellite control stations, deployed to perform daily tracking and control over medium and low-orbiting satellites [SRC-0040, SRC-0040]. To fulfill its tracking and control responsibilities, the station is equipped with a C-band monopulse precision tracking radar [SRC-0040, SRC-0040]. Although the sources do not specify the manufacturer or the exact year this radar was built, they detail its capabilities and operational purpose. The radar operates in the C-band frequency and is specifically designed for the precise measurement of a satellite's perigee period and its reentry orbit [SRC-0040, SRC-0040]. It possesses a high capability for locating orbits with data, which is attributed to its large number of measurement elements and overall high measurement precision [SRC-0040, SRC-0040]. In conjunction with other station facilities like VHF/UHF control systems, station computers, and monitoring display equipment, the radar's data undergoes preprocessing to support digital guidance, acquisition, and remote control instruction delivery [SRC-0040, SRC-0040, SRC-0040]. The station exchanges this processed radar data with the Xi'an Satellite Control Center to conserve communication voice channels and integrate into the broader China Aerospace Control Network [SRC-0040, SRC-0040]. The current status of the radar system involves active participation in China's near-Earth satellite tracking, telemetry, control, and recovery operations [SRC-0040, SRC-0040].</t>
-        </is>
-      </c>
-      <c r="P150" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R150" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-      <c r="S150" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T150" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>RAD-0150</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>SITE-0046</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>C-Band Monopulse Precision Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O151" t="inlineStr">
-        <is>
-          <t>Xiamen Station is a critical node in the China Aerospace Control Network, functioning both as one of the five fixed near-Earth satellite control stations and as a key facility for geostationary orbital satellite launches [SRC-0040, SRC-0040]. Among its primary tracking instrumentation is a C-band monopulse precision tracking radar [SRC-0040, SRC-0040]. While the specific manufacturer and exact year of construction are not provided in the sources, the radar operates within the C-band frequency [SRC-0040, SRC-0040]. This radar system is utilized for highly precise measurements of satellite perigee periods and reentry orbits, a capability made possible by its large number of measurement elements and high overall measurement precision [SRC-0040, SRC-0040]. Alongside the station's unified C-band carrier wave control systems, the radar provides vital data for tracking orbit measurements, including distance, azimuth, and pitch angle [SRC-0040]. Data from the radar is processed by the station's dual computers and exchanged with the Xi'an Satellite Control Center, ensuring robust attitude and orbit control during long-term satellite supervision and geostationary satellite launches [SRC-0040, SRC-0040, SRC-0040]. Today, the radar remains in an active operational status, continuing to support the daily tracking, control, and launch missions of China's expanding aerospace and satellite network [SRC-0040, SRC-0040].</t>
-        </is>
-      </c>
-      <c r="P151" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R151" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-      <c r="S151" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T151" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>RAD-0151</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>SITE-0047</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>C-Band Monopulse Precision Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O152" t="inlineStr">
-        <is>
-          <t>The Nanning Station operates as one of China's five fixed near-earth satellite control stations within the national aerospace network [SRC-0040], [SRC-0040]. As part of this network, several control stations are outfitted with a C-band monopulse precision tracking radar, which serves as a core component of the site's telemetry and tracking capabilities [SRC-0040], [SRC-0040]. The provided sources do not disclose the manufacturer or the exact year this radar was built, but they highlight its operational characteristics and strategic importance [SRC-0040], [SRC-0040]. Operating within the C-band frequency range, the radar is designed with a large number of measurement elements that provide high measurement precision [SRC-0040], [SRC-0040]. Its primary purpose is to locate orbits using recorded data, making it particularly suitable for measuring a satellite's perigee period and its reentry orbit [SRC-0040], [SRC-0040]. The Nanning Station itself leverages these tracking radar capabilities to perform daily control over medium- and low-orbiting satellites [SRC-0040]. Additionally, the station conducts carrier rocket flight coverage tracking measurements during geostationary satellite launches and perigee control missions for near-earth orbital satellites [SRC-0040]. The radar system remains operational as an integral part of China's tracking and control network, which effectively manages both domestic and overseas satellite missions [SRC-0040], [SRC-0040].</t>
-        </is>
-      </c>
-      <c r="P152" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R152" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T152" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>RAD-0152</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>SITE-0048</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Unified C-Band Carrier Wave Control System</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O153" t="inlineStr">
-        <is>
-          <t>The Weinan Station is a critical dual-purpose facility within China's aerospace control network, supporting both near-earth and geostationary orbital satellite operations [SRC-0040], [SRC-0040], [SRC-0040]. A primary system at this site is the unified C-band carrier wave control system, which acts as a tracking radar and telemetry unit [SRC-0040]. Operating in the C-band frequency range, this system functions cooperatively with in-satellite transponders to execute precise tracking orbit measurements, telemetry reception, and remote control for high-orbiting satellites up to 40,000 kilometers in altitude [SRC-0040]. Its tracking radar capabilities specifically cover distance, azimuth, and pitch angle measurements [SRC-0040]. The sources do not document the system's manufacturer or the year it was built, but its operational purpose is clearly defined: it is essential for the launch and daily control of geostationary satellites [SRC-0040], [SRC-0040]. The Weinan Station utilizes a duplex computer architecture to process the radar's station data, exchange data with the Xi'an Control Center, and manage satellite attitude and long-term orbit control [SRC-0040]. Additionally, the system supports simulated maneuver tests for satellite-to-earth reentry routes [SRC-0040]. The system is currently operational, playing a foundational role in managing China's geostationary communication satellites and broader space domain activities [SRC-0040], [SRC-0040].</t>
-        </is>
-      </c>
-      <c r="P153" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R153" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-      <c r="S153" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T153" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>RAD-0153</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>SITE-0049</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>C-Band Monopulse Precision Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>The Kashgar Station (referred to as Kash Station in the sources) is deployed in the western part of China as one of the five fixed near-earth satellite control stations [SRC-0040], [SRC-0040]. Like other stations in this network, it is supported by a C-band monopulse precision tracking radar, although the specific manufacturer and year of construction are not provided in the source documents [SRC-0040], [SRC-0040]. Operating on the C-band frequency, this radar system is engineered with a high number of measurement elements, which ensures exceptionally high measurement precision [SRC-0040], [SRC-0040]. The primary purpose of this radar is the accurate measurement of a satellite's perigee period and its reentry orbit, leveraging its strong capability to locate orbits using precise tracking data [SRC-0040], [SRC-0040]. At the Kashgar Station, this radar facilitates the cooperative daily tracking and control of medium- and low-orbiting satellites [SRC-0040]. Working in tandem with other regional stations, the facility ensures continuous orbital monitoring and trajectory tracking, which are critical for both satellite maintenance and the safe recovery of reentry compartments [SRC-0040], [SRC-0040], [SRC-0040]. The radar remains an operational asset within China's broader aerospace control network, actively contributing to the nation's space surveillance and satellite tracking missions [SRC-0040], [SRC-0040].</t>
-        </is>
-      </c>
-      <c r="P154" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R154" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-      <c r="S154" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T154" t="inlineStr">
-        <is>
-          <t>SRC-0040</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>RAD-0154</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>SITE-0054</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Radar System</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N155" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O155" t="inlineStr">
-        <is>
-          <t>The Integrated Test Range (ITR) located at Chandipur in the Balasore district of Odisha, India, operates a variety of high-performance range instrumentation systems, which prominently include tracking radars [SRC-0073, SRC-0073, SRC-0076]. These local radar arrays are specifically deployed to track the flight trajectories of rockets, ballistic missiles, and airborne weapon systems from their initial take-off through to the point of impact [SRC-0076, SRC-0222]. The primary purpose of this radar system is to precisely locate flying objects, capture real-time flight data, and work in conjunction with Electro-Optical Tracking Systems (EOTS), telemetry stations, and central computer systems to evaluate overall weapon performance [SRC-0076, SRC-0050]. 
-Recently, these radars have been actively utilized in major strategic tests, such as the successful flight-trials of the Very Short-Range Air Defence System (VSHORADS) and the Agni-1 short-range ballistic missile, where they successfully monitored the missiles' flight paths and validated their effectiveness against aerial targets [SRC-0073, SRC-0073, SRC-0050]. The systems remain in active operational status under the management of the Defence Research and Development Organisation (DRDO) [SRC-0076, SRC-0050]. While the sources confirm their critical operational role, they do not disclose specific technical details regarding the radars' exact type, frequency bands, manufacturers, or the years they were built [SRC-0073, SRC-0076, SRC-0222, SRC-0050].</t>
-        </is>
-      </c>
-      <c r="P155" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R155" t="inlineStr">
-        <is>
-          <t>SRC-0073</t>
-        </is>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T155" t="inlineStr">
-        <is>
-          <t>SRC-0073, SRC-0076, SRC-0222, SRC-0050</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>RAD-0155</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>SITE-0065</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>An/Tpy-2</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N156" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr">
-        <is>
-          <t>The AN/TPY-2 (Army Navy/Transportable Radar Surveillance) is an advanced, transportable Active Electronically Scanned Array (AESA) radar system manufactured by Raytheon Technologies [SRC-0011], [SRC-0011], [SRC-0012]. Introduced to the military in 2007, the radar operates in the high-frequency X-band (8.55–10 GHz), which provides exceptional target resolution, precise discrimination between warheads and non-threats like decoys, and highly accurate target tracking [SRC-0011], [SRC-0011], [SRC-0012]. The radar features an antenna aperture of approximately 9.2 square meters and utilizes fully electronic beam steering [SRC-0011], [SRC-0011]. Built for a strategic missile-defense purpose, the system is designed to detect, track, and classify ballistic missile threats during their midcourse and terminal phases at ranges exceeding 1,000 kilometers [SRC-0011], [SRC-0011], [SRC-0012]. The AN/TPY-2 boasts the capability to track hundreds of targets simultaneously with rapid, sub-second update rates, integrating seamlessly with allied and U.S. missile-defense architectures such as THAAD, Aegis BMD, and the Command and Control, Battle Management, and Communications (C2BMC) network [SRC-0011], [SRC-0011], [SRC-0011]. The radar is currently fully operational and actively deployed across the globe [SRC-0011]. In Israel, the system was provided by the United States to act as a critical early warning sensor, complementing the country's existing Arrow 2 and Patriot PAC-3 air defense systems [SRC-0012]. The Israeli deployment of the AN/TPY-2 radar is supervised by the U.S. Army's 1st Space Brigade, specifically operating as the 13th Missile Defence Battery [SRC-0012].</t>
-        </is>
-      </c>
-      <c r="P156" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>SRC-0011</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>SRC-0011, SRC-0012</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>RAD-0156</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>SITE-0077</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Saturn-Ms</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>The Saturn-MS measuring complex is a strategic tracking and telemetry radar system located at the Baikonur Cosmodrome in Kazakhstan [SRC-0173]. The facility is visually defined by its two massive parabolic antennas, each measuring 25 meters in diameter and weighing 200 tons, situated atop Murguduk hill [SRC-0173]. Construction of the Saturn-MS complex began on January 25, 1967, and following initial communication tests with the Luna-16 interplanetary station in November 1970, the system entered full-scale operational service on November 3, 1971 [SRC-0173]. While the specific manufacturer and frequency bands are not detailed in the available sources, its capabilities are extensive. The complex is designed to monitor rocket trajectories, gather telemetry, manage space communications, and execute satellite control during the critical phases of a launch [SRC-0173]. Historically operated as an exclusively military facility, the complex tracked various high-profile missions, including the Soyuz-Apollo program, the Buran shuttle, and interplanetary probes to the Moon, Mars, and Venus [SRC-0173, SRC-0173]. In 2006, the military unit managing the site was disbanded, and Saturn-MS transitioned into a fully civilian tracking facility [SRC-0173]. Today, it continues to undergo gradual modernization to serve as the primary monitoring "eyes" for Baikonur Cosmodrome launches well into the future [SRC-0173].</t>
-        </is>
-      </c>
-      <c r="P157" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R157" t="inlineStr">
-        <is>
-          <t>SRC-0173</t>
-        </is>
-      </c>
-      <c r="S157" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T157" t="inlineStr">
-        <is>
-          <t>SRC-0173</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>RAD-0157</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>SITE-0096</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>An/Tpy-2</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O158" t="inlineStr">
-        <is>
-          <t>The AN/TPY-2 (Army Navy/Transportable Radar Surveillance) is a highly mobile, transportable active electronically scanned array (AESA) radar system developed and manufactured by Raytheon Technologies [SRC-0011, SRC-0012, SRC-0012, SRC-0183]. Introduced into service in 2007, this advanced sensor operates in the X-band frequency range (8.55–10 GHz), which provides exceptional target resolution and tracking fidelity [SRC-0012, SRC-0183, SRC-0011, SRC-0190]. The system is designed to detect, classify, track, and discriminate between ballistic missiles, lethal warheads, and non-threats such as decoys at extraordinary ranges exceeding 1,000 kilometers [SRC-0011, SRC-0011, SRC-0011, SRC-0012]. It is capable of tracking hundreds of high-speed targets simultaneously and uses electronic beam steering for near-instantaneous updates [SRC-0011, SRC-0011]. Recently, Raytheon upgraded the AN/TPY-2 with gallium nitride (GaN) semiconductor components, significantly improving its overall sensitivity, search volume, and detection range over legacy models [SRC-0190, SRC-0012, SRC-0158]. The primary purpose of the AN/TPY-2 is to serve as the cornerstone sensor for the Terminal High Altitude Area Defense (THAAD) system, while also cueing other defense networks such as the MIM-104 Patriot PAC-3, Aegis BMD, and C2BMC systems [SRC-0012, SRC-0190, SRC-0011, SRC-0011, SRC-0011]. It can be deployed in a forward-based mode for strategic early warning or a terminal mode for fire control [SRC-0183]. Currently, the AN/TPY-2 remains fully operational and is actively deployed in the United Arab Emirates (UAE), where it is integrated with THAAD batteries to provide regional missile defense and rapid response capabilities against theater ballistic threats [SRC-0183, SRC-0183].</t>
-        </is>
-      </c>
-      <c r="P158" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R158" t="inlineStr">
-        <is>
-          <t>SRC-0012</t>
-        </is>
-      </c>
-      <c r="S158" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T158" t="inlineStr">
-        <is>
-          <t>SRC-0011, SRC-0012, SRC-0183, SRC-0190, SRC-0158</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>RAD-0158</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>SITE-0098</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Iris-T Radar</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N159" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O159" t="inlineStr">
-        <is>
-          <t>The IRIS-T radar is an integral component of the IRIS-T SLM medium-range air defense system, which is slated to be permanently stationed at the Ämari Air Base in Estonia [SRC-0014, SRC-0014]. Originating from Germany, the system was part of a joint procurement decision made by Estonia and Latvia in May 2023 to significantly enhance their ground-based air defense capabilities [SRC-0014]. Currently, the radar and its associated systems are on order, with three batteries expected to become fully operational within the Estonian Air Force's newly established Air Defence Wing by the year 2026 [SRC-0014, SRC-0014]. The radar is highly mobile and is designed to be mounted on the German-manufactured MAN SX44 platform truck, which also serves as the transport vehicle for the system's operations center and missile launcher [SRC-0014]. The primary purpose of the IRIS-T radar is to support active air defense operations and ensure the integrity of Estonia's airspace [SRC-0014]. While specific technical specifications such as the exact frequency band and the original year built are not detailed in the provided sources, the radar will function as the primary sensor for the IRIS-T SLM batteries [SRC-0014, SRC-0014]. Once fielded, it will work in tandem with NATO allied fighter detachments that are also deployed to Ämari Air Base for the Baltic Air Policing Mission, thereby providing a critical medium-range tracking and targeting capability against regional aerial threats [SRC-0119].</t>
-        </is>
-      </c>
-      <c r="P159" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R159" t="inlineStr">
-        <is>
-          <t>SRC-0014</t>
-        </is>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
-          <t>SRC-0014, SRC-0119</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>RAD-0159</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>SITE-0125</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Czech Radar Systems</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O160" t="inlineStr">
-        <is>
-          <t>During the NATO large-scale live-fire air defense exercise Ramstein Legacy 22, which took place from June 6 to 10, 2022, Czech radar systems were deployed on a beach at the Ustka Training Range in Poland [SRC-0124], [SRC-0124]. While specific details regarding the exact radar type, frequency band, manufacturer, and year built are not provided in the available sources, these radar systems were part of a broader integration of 17 surface-based air and missile defense systems tested in live-fire scenarios [SRC-0124]. The primary purpose of deploying these systems at Ustka was to participate in multinational demonstrations alongside French, Polish, Slovak, and United Kingdom troops, focusing on enhancing allied interoperability and demonstrating various weapons platforms, including the Starstreak air defense system [SRC-0124], [SRC-0124]. The exercise aimed to strengthen the NATO alliance's defensive posture in response to conventional threats, highlighting a unified coalition effort across the European theater [SRC-0124]. The current status of these Czech radar systems at the Ustka site is not active, as they were deployed temporarily as part of a rotational exercise involving around 50 aircraft and multiple international contingents [SRC-0124], [SRC-0124]. This event served to reinforce the integrated air defense capabilities and the cooperative bond among NATO allies [SRC-0124].</t>
-        </is>
-      </c>
-      <c r="P160" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>SRC-0124</t>
-        </is>
-      </c>
-      <c r="S160" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
-          <t>SRC-0124</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>RAD-0160</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>SITE-0351</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>An/Spy-1</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N161" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O161" t="inlineStr">
-        <is>
-          <t>The AN/SPY-1 radar is a critical sensor component integrated into the Aegis Ashore Poland installation, representing a key element of the United States Missile Defense Agency’s (MDA) Phase 3 contribution to the European Phased Adaptive Approach [SRC-0093]. Accepted by the Chief of Naval Operations in December 2023, this site is funded and operated by the U.S. Navy to protect NATO's European territory against ballistic missile threats [SRC-0093]. While the exact manufacturer and year built are not detailed in the provided sources, the AN/SPY-1 serves as a primary sensor for the Aegis Combat System and the broader Aegis Ballistic Missile Defense System [SRC-0055], [SRC-0055], [SRC-0179], [SRC-0179]. The Aegis system is known to operate in the S-band frequency, differentiating it from X-band and C-band defense radars [SRC-0178]. The AN/SPY-1 radar's capabilities are vast, supporting full Aegis missile defense warfighting operations while also participating in the Space Force Space Domain Awareness (SDA) mission [SRC-0093]. Following its operational acceptance, the Poland site entered a maintenance period to upgrade its computer networks and communications systems [SRC-0093]. The radar's SDA capability has been fully transitioned to the Navy, maintaining complete compatibility with deployed naval operations and incorporating appropriate safeguards for its dual-mission profile [SRC-0093]. The system remains in active operational status, continuously supporting defense requirements and future capability demonstrations in the region [SRC-0093], [SRC-0093].</t>
-        </is>
-      </c>
-      <c r="P161" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R161" t="inlineStr">
-        <is>
-          <t>SRC-0093</t>
-        </is>
-      </c>
-      <c r="S161" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T161" t="inlineStr">
-        <is>
-          <t>SRC-0093, SRC-0055, SRC-0179, SRC-0178</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>RAD-0161</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>SITE-0145</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Precision Tracking Radar</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N162" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O162" t="inlineStr">
-        <is>
-          <t>Ascension Island, situated in the Atlantic Ocean, serves as a crucial downrange station within the Eastern Test Range (ETR) network, hosting precision tracking radars to support space and missile operations [SRC-0095, SRC-0106]. While the provided sources do not specify the radar's exact manufacturer, operating frequency band, or the year it was originally built, they identify the system as a metric radar capable of performing both beacon and echo tracking [SRC-0106, SRC-0106]. The primary purpose of this radar installation is to provide comprehensive launch, midcourse, and terminal phase coverage for ballistic missiles [SRC-0106]. In terms of capabilities, the precision tracking radar acquires and transmits real-time trajectory data directly to the computer center at Cape Canaveral Air Force Station (CCAFS) [SRC-0106]. The radar operates alongside a broader suite of instrumentation on the island, including target arrays of bottom-mounted hydrophones for the Missile Impact Location System (MILS) and terrestrial telemetry stations [SRC-0106, SRC-0106, SRC-0106]. Notably, while other ETR downrange sites possess telemetry doppler data capabilities for metric measurements, Ascension Island does not [SRC-0106]. In its current status, Ascension Island remains an active and vital post-detect telemetry site for the ETR, utilizing advanced digital satellite communication (SATCOM) links to transport telemetry and radar management data back to the Range Operations Control Center [SRC-0118, SRC-0118].</t>
-        </is>
-      </c>
-      <c r="P162" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R162" t="inlineStr">
-        <is>
-          <t>SRC-0095</t>
-        </is>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T162" t="inlineStr">
-        <is>
-          <t>SRC-0095, SRC-0106, SRC-0118</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>RAD-0162</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>SITE-0173</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Altair</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N163" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O163" t="inlineStr">
-        <is>
-          <t>The ARPA Long-Range Tracking and Instrumentation Radar (ALTAIR) is a highly agile tracking and instrumentation radar located at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur, part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Designed and developed under the direction of ARPA and Lincoln Laboratory, it began operations in 1970 [SRC-0071], [SRC-0071], [SRC-0071]. ALTAIR operates in the VHF (0.162 GHz) and UHF (0.422 GHz) frequency bands and is equipped with a massive 150-foot diameter antenna that rotates on a 110-foot circular track [SRC-0071], [SRC-0071], [SRC-0071]. It produces a peak transmit power of 6 megawatts at both frequencies, with a range resolution of 32 meters at VHF and 15 meters at UHF [SRC-0071], [SRC-0071], [SRC-0071]. Originally built to evaluate U.S. strategic weapons against Soviet-style large VHF and UHF radars, ALTAIR is capable of acquiring targets over 3500 kilometers away [SRC-0071], [SRC-0071]. Over time, its purpose expanded to include tracking new foreign space launches, conducting space surveillance, performing deep-space tracking, and supporting ionospheric modeling [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0151]. ALTAIR was upgraded in 1984 with an array of traveling-wave tubes to double its UHF average power, and further upgraded in 1995 to 300 kW, greatly enhancing its deep-space capabilities [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. In 2002, the radar's electronics were modernized under the Radar Open System Architecture (ROSA) project, allowing remote operations [SRC-0071], [SRC-0071], [SRC-0071]. Today, ALTAIR remains an active and heavily utilized sensor, supporting space activities for 128 hours per week while serving as a critical asset for the U.S. Space Surveillance Network [SRC-0071], [SRC-0071], [SRC-0071].</t>
-        </is>
-      </c>
-      <c r="P163" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R163" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-      <c r="S163" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T163" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0151</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>RAD-0163</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>SITE-0173</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Tradex</t>
-        </is>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N164" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O164" t="inlineStr">
-        <is>
-          <t>The Target Resolution and Discrimination Experiment (TRADEX) is a high-power instrumentation and tracking radar situated at the Kiernan Reentry Measurements Site (KREMS) on Roi-Namur within the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0071]. Built by the RCA Corporation under the direction of ARPA, TRADEX was the first radar installed at the site and began operations in 1962 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. It originally operated as a UHF tracker and L-band illuminator, but in 1970, the radar was extensively modified to operate in the L-band (1.320 GHz) and S-band (2.95 GHz) [SRC-0071], [SRC-0071], [SRC-0071]. The radar features an 84-foot diameter antenna and utilizes pulse compression to achieve a range resolution of approximately 15 meters [SRC-0071], [SRC-0071], [SRC-0071]. It delivers a peak transmit power of 2.0 megawatts in both its L-band and S-band frequencies [SRC-0071]. TRADEX was historically a workhorse for developing ballistic missile discrimination techniques, evaluating reentry vehicle wakes, and collecting signature data for systems like Safeguard [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Its capabilities were steadily upgraded with features like multi-static measurements, S-band pseudo-random noise waveforms to emulate Soviet radars, and a real-time multi-target tracker [SRC-0071], [SRC-0071], [SRC-0071]. In 2002, the radar received a Radar Open System Architecture (ROSA) modernization, equipping it with commercial off-the-shelf hardware and enabling remote operations [SRC-0071], [SRC-0071], [SRC-0071]. Currently, TRADEX remains fully operational, serving as an official contributing sensor to the Air Force Space Surveillance Network and dedicating at least 10 hours a week to deep-space tracking [SRC-0071], [SRC-0071].</t>
-        </is>
-      </c>
-      <c r="P164" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T164" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>RAD-0164</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>SITE-0173</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Alcor</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>The ARPA-Lincoln C-band Observables Radar (ALCOR) is a wideband instrumentation and imaging radar located at the Reagan Test Site on Roi-Namur [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Lincoln Laboratory served as the prime contractor for the radar, with assistance from RCA, Westinghouse, Hughes, and Honeywell [SRC-0071], [SRC-0071]. ALCOR became operational in January 1970, marking a milestone as the United States' first high-power, long-range, wideband radar [SRC-0071], [SRC-0071], [SRC-0071]. The system operates in the C-band (5.664 GHz narrowband and 5.672 GHz wideband) utilizing a 40-foot diameter antenna with a peak transmit power of 2.25 megawatts and a very narrow 0.3-degree beamwidth [SRC-0071]. ALCOR's extremely wide 500 MHz bandwidth allows it to provide fine range resolution, which is essential for measuring the length of objects and examining individual scattering centers [SRC-0071], [SRC-0071], [SRC-0071]. Because of this, its primary purpose involves ballistic missile discrimination and space-object identification [SRC-0071], [SRC-0071]. Notably, in 1971, ALCOR became the first radar to successfully use inverse synthetic aperture radar (ISAR) imaging techniques on orbiting satellites [SRC-0071], [SRC-0071]. The radar has seen multiple upgrades over its lifetime, including the installation of an extended-interaction klystron high-power amplifier in 1994, which increased its pulse-repetition frequency and enabled real-time coherent integration [SRC-0071], [SRC-0071]. In 1999, ALCOR was the first radar at the site to receive the Radar Open System Architecture (ROSA) modernization, which replaced legacy components with modern modular systems [SRC-0071]. ALCOR remains an active, state-of-the-art sensor today [SRC-0071].</t>
-        </is>
-      </c>
-      <c r="P165" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-      <c r="S165" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T165" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>RAD-0165</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>SITE-0173</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Mmw</t>
-        </is>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O166" t="inlineStr">
-        <is>
-          <t>The Millimeter-Wave (MMW) radar is an extremely high-resolution imaging radar located at the Reagan Test Site on Roi-Namur [SRC-0071], [SRC-0071], [SRC-0071]. Developed with Lincoln Laboratory acting as the prime contractor, the MMW radar began operations in 1983 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Originally designed as a dual-frequency system operating at 35 GHz (Ka-band) and 95.5 GHz (W-band), the 95.5 GHz capability was removed in the 1990s due to high atmospheric absorption and transmission losses [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. Today, it operates strictly in the Ka-band using a 45-foot diameter antenna and generates 0.060 megawatts of peak transmit power [SRC-0071]. A standout feature is its exceptionally narrow beamwidth of 0.0435 degrees and its wide 4 GHz bandwidth, which provides a highly precise range resolution of approximately six centimeters [SRC-0071], [SRC-0113], [SRC-0113]. The primary purpose of the MMW radar is to collect high-fidelity signature databases on ballistic missiles, measure interceptor miss distances, and conduct detailed space-object identification [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. It is currently the highest-resolution imaging radar in the Space Surveillance Network and serves as the primary satellite-imaging sensor at the Reagan Test Site [SRC-0071], [SRC-0071], [SRC-0113]. The radar has undergone continuous technological improvements, including the adoption of an advanced quasi-optical beam-waveguide system, a new radome, and the Radar Open System Architecture (ROSA) upgrade in October 2000 [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071], [SRC-0071]. In 2011, it became the first radar to utilize the new ROSA II technology, and it remains fully operational today [SRC-0071], [SRC-0071], [SRC-0071].</t>
-        </is>
-      </c>
-      <c r="P166" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T166" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0113</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>RAD-0166</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>SITE-0173</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Mps-36</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N167" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O167" t="inlineStr">
-        <is>
-          <t>The MPS-36 radars are a pair of skin and beacon-tracking radars located on Kwajalein Island, which is part of the Ronald Reagan Ballistic Missile Defense Test Site [SRC-0071], [SRC-0151]. While the provided sources do not explicitly detail their original manufacturer, exact frequency band, or initial year built, they have long played a vital supporting role during test launches and space missions at the site [SRC-0071], [SRC-0151], [SRC-0151]. Their primary purpose is to provide highly accurate trajectory tracking of test vehicles, main rocket bodies, and scientific payloads [SRC-0071], [SRC-0151]. During missions such as the NASA Sporadic-E Electro Dynamics (SEED) sounding rocket launch, the two MPS-36 radars are utilized to track the rocket body and payload to measure and predict their trajectory from launch to impact in the broad ocean area, which is especially critical in the event of a loss of downlinked telemetry data [SRC-0151], [SRC-0151]. Like the larger KREMS radars located on Roi-Namur, the MPS-36 systems have undergone significant modernization to maintain their effectiveness and integration with the rest of the range. In 2004, the two MPS-36 radars received an upgrade utilizing the Radar Open System Architecture (ROSA) back-end technology, which automated the systems and integrated them into the centralized Kwajalein Mission Control Center [SRC-0071], [SRC-0071], [SRC-0071]. Today, both MPS-36 radars remain operational and continue to support critical data collection for Department of Defense and NASA missions [SRC-0071], [SRC-0151].</t>
-        </is>
-      </c>
-      <c r="P167" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R167" t="inlineStr">
-        <is>
-          <t>SRC-0071</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T167" t="inlineStr">
-        <is>
-          <t>SRC-0071, SRC-0151</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>RAD-0167</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>SITE-0170</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Multiple Object Tracking Radar 2 (Motr-2)</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N168" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O168" t="inlineStr">
-        <is>
-          <t>The Multiple Object Tracking Radar 2 (MOTR-2) is a highly sophisticated phased-array tracking radar stationed at Cape Canaveral Space Force Station [SRC-0157, SRC-0114]. Manufactured in the mid-1980s at an initial cost of $36 million per unit, the MOTR system is exceedingly rare, with only five units ever built globally [SRC-0114, SRC-0114]. While the exact frequency band and manufacturer are not detailed in the sources, the system's design is well documented. Initially, the White Sands Missile Range was slated to receive the first three systems; however, following the tragic accident that claimed the Space Shuttle Challenger, the MOTR-2 unit was permanently diverted to Cape Canaveral [SRC-0157, SRC-0114]. The radar is engineered to transmit energy pulses through phase-shifting elements, using fractional wavelength delays to steer its beam off boresight [SRC-0114]. This allows the radar to effectively scan a 60-degree area and track the precise location of up to 40 airborne objects simultaneously, a significant capability upgrade over single-track legacy systems [SRC-0157, SRC-0114]. Returning signals are processed via a three-channel receiver architecture to produce highly accurate measurement data [SRC-0114]. The primary purpose of the MOTR-2 is to provide critical tracking and flight safety operations for launch vehicles and airborne systems on the range [SRC-0157, SRC-0114]. In its current status, it remains an active and invaluable tracking asset, with estimates suggesting that recreating a radar of this caliber today would cost $70 billion [SRC-0114].</t>
-        </is>
-      </c>
-      <c r="P168" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R168" t="inlineStr">
-        <is>
-          <t>SRC-0157</t>
-        </is>
-      </c>
-      <c r="S168" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T168" t="inlineStr">
-        <is>
-          <t>SRC-0157, SRC-0114</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>RAD-0168</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>SITE-0181</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>An-Gpn12 Surveillance Radar</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N169" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O169" t="inlineStr">
-        <is>
-          <t>At the Utah Test and Training Range (UTTR), the radar network includes the AN-GPN12 surveillance radar system, which is a critical component for monitoring the expansive airspace over the Great Salt Lake Desert [SRC-0106, SRC-0106]. The UTTR itself provides major range facilities for the test and evaluation of manned and unmanned aircraft systems, as well as tactical training for air-to-air and air-to-ground weapon delivery [SRC-0106]. The AN-GPN12 is integrated into the range's broader tracking network and is operated alongside two precision tracking radars [SRC-0106]. This surveillance radar is specifically provided, maintained, and operated by the 299th Communication Squadron, also known as Clover Control, which is a unit of the Utah Air National Guard [SRC-0106]. Radar information and time-space-position information from the UTTR network are linked via microwave to the Mission Control Center located at Hill Air Force Base, where the data is displayed on plotboards in real-time for test managers [SRC-0106, SRC-0106]. Additionally, the radar tracking data can be transmitted by microwave through the data acquisition and transmission system directly to Edwards Air Force Base to support joint testing and evaluation efforts [SRC-0106]. While the specific manufacturer, installation year, and frequency band of the AN-GPN12 are not detailed in the available sources, its primary capability and purpose are to provide robust airspace surveillance to ensure range safety and coordinate complex operational testing within the UTTR's restricted airspace [SRC-0106, SRC-0106]. The system is currently operational [SRC-0106].</t>
-        </is>
-      </c>
-      <c r="P169" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R169" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T169" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>RAD-0169</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>SITE-0181</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Precision Tracking Radars</t>
-        </is>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O170" t="inlineStr">
-        <is>
-          <t>In addition to surveillance capabilities, the Utah Test and Training Range (UTTR) operates a network featuring two precision tracking radars [SRC-0106]. These radars are essential for supporting the primary mission of the UTTR, which involves the comprehensive test and evaluation of manned and unmanned aerospace systems, cruise missiles, and conventional munitions [SRC-0106, SRC-0106]. Positioned to cover the vast airspace of the North and South Ranges, these tracking radars capture critical time-space-position information (TSPI) during flight tests [SRC-0106, SRC-0106]. The data collected by both precision tracking radars is transmitted in real-time via a dedicated microwave link to the Mission Control Center (MCC) situated at Hill Air Force Base [SRC-0106, SRC-0106]. At the MCC, the radar telemetry and TSPI data are displayed on large plotboards to allow range control personnel to monitor test vehicles dynamically [SRC-0106, SRC-0106]. Furthermore, the radar network is integrated with the broader Department of Defense test infrastructure, possessing the capability to send radar tracking information by microwave through a data acquisition and transmission system to Edwards Air Force Base [SRC-0106]. The available sources do not specify the exact manufacturer, operating frequency band, or year of installation for these two precision tracking radars [SRC-0106]. However, their current status is operational, and their main purpose is to function alongside the High Accuracy Multiple Object Tracking System (HAMOTS), cinetheodolites, and the AN-GPN12 surveillance radar to deliver highly accurate, real-time tracking data for tactical training and weapon delivery evaluations [SRC-0106, SRC-0106, SRC-0106].</t>
-        </is>
-      </c>
-      <c r="P170" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R170" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T170" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>RAD-0170</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>SITE-0188</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>An/Fps-132 Upgraded Early Warning Radar (Uewr)</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N171" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Beale Air Force Base in California is a solid-state phased-array radar system operating in the Ultra High Frequency (UHF) band [SRC-0183, SRC-0190, SRC-0212]. Originally established in 1979 as an AN/FPS-115 PAVE Phased Array Warning System (PAVE PAWS), the radar was subsequently upgraded to the AN/FPS-123 Early Warning Radar, and finally modernized to the Raytheon-manufactured AN/FPS-132 UEWR configuration in 2005 [SRC-0190, SRC-0184, SRC-0184, SRC-0190, SRC-0212]. The radar features a two-panel configuration housed in a 10-story scanner building, with each fixed-orientation face providing 120 degrees of azimuth coverage, yielding a total 240-degree coverage arc oriented toward the Pacific Ocean [SRC-0190, SRC-0212, SRC-0190, SRC-0190]. The primary purpose of the Beale UEWR is to provide early warning of land-launched and sea-launched ballistic missile attacks, conduct target classification, and supply midcourse missile tracking data to cue other sensors and interceptors within the Ground-based Midcourse Defense (GMD) system [SRC-0190, SRC-0212]. It also performs a secondary space domain awareness mission, tracking satellites and space debris for the Space Surveillance Network [SRC-0183, SRC-0190, SRC-0212]. Because of its proximity to the Vandenberg Space Force Base interceptor site, the Beale UEWR serves as a primary demonstration platform for GMD test events [SRC-0212, SRC-0190]. Currently, the radar is fully operational under the 7th Space Warning Squadron of the U.S. Space Force and is scheduled for front-end and back-end digitization under the Ground Based Radar Digitization (GBRD) program, with Initial Operational Capability targeted for fiscal year 2030 [SRC-0190, SRC-0190, SRC-0190, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R171" t="inlineStr">
-        <is>
-          <t>SRC-0183</t>
-        </is>
-      </c>
-      <c r="S171" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T171" t="inlineStr">
-        <is>
-          <t>SRC-0183, SRC-0190, SRC-0212, SRC-0184</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>RAD-0171</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>SITE-0347</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>An/Fps-132 Uewr</t>
-        </is>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O172" t="inlineStr">
-        <is>
-          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) at Cape Cod Space Force Station, Massachusetts, is a solid-state phased array radar system operating in the UHF band (420 to 450 MHz) [SRC-0133, SRC-0133, SRC-0190]. Originally built by Raytheon and activated in 1980 as a PAVE PAWS installation (AN/FPS-115), it received significant electronics and signal processor upgrades from Raytheon between 2013 and 2016 to reach its current UEWR configuration [SRC-0190, SRC-0184, SRC-0190]. The radar consists of two active array faces tilted at a 20-degree angle, with each face containing 1,792 active antenna elements out of a total 5,354 [SRC-0133, SRC-0133]. Together, the panels provide a 240-degree azimuth coverage across the Atlantic Ocean [SRC-0190, SRC-0133]. It operates at an average power of 152.5 kW and a peak output of 340 watts per active element [SRC-0133, SRC-0133]. The radar’s purpose is to provide early warning of intercontinental and sea-launched ballistic missile (ICBM and SLBM) attacks against North America, while its secondary mission involves tracking low-Earth orbit satellites and space debris for space domain awareness [SRC-0190, SRC-0133, SRC-0190]. Currently, the radar is fully operational under the 6th Space Warning Squadron and is scheduled to undergo front-end digitization as part of the Ground Based Radar Digitization (GBRD) program’s initial prototyping phase [SRC-0190, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P172" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R172" t="inlineStr">
-        <is>
-          <t>SRC-0133</t>
-        </is>
-      </c>
-      <c r="S172" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T172" t="inlineStr">
-        <is>
-          <t>SRC-0133, SRC-0190, SRC-0184</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>RAD-0172</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>SITE-0344</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>An/Fps-132 Uewr</t>
-        </is>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N173" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O173" t="inlineStr">
-        <is>
-          <t>The AN/FPS-132 Upgraded Early Warning Radar (UEWR) located at Clear Space Force Station in Alaska is a solid-state phased array radar operating in the UHF frequency band [SRC-0001, SRC-0190, SRC-0190]. The site was originally established in 1961 as a Ballistic Missile Early Warning System (BMEWS) facility with mechanical radars before transitioning to a solid-state system in 1981 [SRC-0001, SRC-0190]. In 2012, Raytheon was contracted to upgrade the system to the AN/FPS-132 UEWR configuration, a modernization effort completed in Fiscal Year 2016 [SRC-0001, SRC-0190]. The system utilizes a two-panel array configuration housed in a specialized scanner building, providing a 240-degree coverage arc across the Arctic and Pacific regions [SRC-0190, SRC-0190, SRC-0008]. Its primary purpose is to deliver long-range early warning, precision tracking, and target classification of ballistic missile threats, as well as to support space surveillance operations for the Space Surveillance Network [SRC-0190, SRC-0093, SRC-0093]. Currently, the UEWR is fully operational and maintained by the 13th Space Warning Squadron [SRC-0190]. Looking forward, the radar is slated to receive comprehensive hardware and software upgrades, including aperture digitization, under the Space Force's Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P173" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R173" t="inlineStr">
-        <is>
-          <t>SRC-0001</t>
-        </is>
-      </c>
-      <c r="S173" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T173" t="inlineStr">
-        <is>
-          <t>SRC-0001, SRC-0190, SRC-0008, SRC-0093, SRC-0186</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>RAD-0173</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>SITE-0344</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Long Range Discrimination Radar (Lrdr / An/Fps-138)</t>
-        </is>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N174" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>The Long Range Discrimination Radar (LRDR), designated AN/FPS-138, at Clear Space Force Station is an advanced multi-face Active Electronically Scanned Array (AESA) radar operating in the S-band [SRC-0190, SRC-0005, SRC-0100, SRC-0190]. Manufactured by Lockheed Martin under a $784 million contract awarded in 2015, the radar achieved initial fielding in late 2021 and was officially accepted for operational use in December 2025 [SRC-0045, SRC-0181, SRC-0190]. The LRDR incorporates scalable Gallium Nitride (GaN) solid-state technology, featuring dual monostatic arrays that each measure 60 feet high by 60 feet wide [SRC-0190, SRC-0003, SRC-0100]. It was specifically designed to provide persistent, long-range midcourse discrimination, capable of simultaneously tracking multiple small objects and distinguishing lethal ballistic missile warheads from decoys, spent rocket bodies, and debris [SRC-0190, SRC-0045, SRC-0100]. By accurately filtering out non-lethal objects, it conserves the inventory of Ground-Based Interceptors [SRC-0190, SRC-0100]. The radar features an open systems architecture and a unique "maintain-while-operate" capability ensuring continuous 24/7 coverage [SRC-0100, SRC-0045]. Currently, the LRDR is fully operational for homeland defense and space domain awareness missions under the command of the U.S. Space Force Combat Forces Command, integrated directly with the Command and Control, Battle Management and Communications (C2BMC) network [SRC-0100, SRC-0190, SRC-0045, SRC-0045].</t>
-        </is>
-      </c>
-      <c r="P174" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R174" t="inlineStr">
-        <is>
-          <t>SRC-0190</t>
-        </is>
-      </c>
-      <c r="S174" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T174" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0005, SRC-0100, SRC-0045, SRC-0181, SRC-0003</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>RAD-0174</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>SITE-0345</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>An/Fpq-16 Parcs</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N175" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O175" t="inlineStr">
-        <is>
-          <t>The AN/FPQ-16 Perimeter Acquisition Radar Attack Characterization System (PARCS) is a massive, single-faced, passive electronically scanned array (PESA) radar located at Cavalier Space Force Station in North Dakota [SRC-0008, SRC-0143, SRC-0190]. Operating in the UHF band (420–450 MHz), PARCS was manufactured by General Electric in the early 1970s as part of the U.S. Army's Safeguard anti-ballistic missile system [SRC-0008, SRC-0190, SRC-0132]. Following the decommissioning of the Safeguard program, the radar was transferred to the Air Force in 1976 [SRC-0008, SRC-0190]. The massive concrete installation generates a peak output of approximately 14.3 megawatts, directing a single north-facing beam that provides 140 degrees of azimuth coverage and 93 degrees of elevation coverage [SRC-0132, SRC-0190]. With a detection range of roughly 2,000 miles, its primary purpose is to detect and track incoming intercontinental and sea-launched ballistic missiles targeting North America [SRC-0008, SRC-0190, SRC-0132]. Its secondary mission is space surveillance, where it tracks more than half of all Earth-orbiting objects for the Space Surveillance Network [SRC-0143, SRC-0190, SRC-0008]. Currently, PARCS is fully operational under the 10th Space Warning Squadron, sustained by a multi-year contract with InDyne Inc., and is scheduled for a comprehensive front-end digitization overhaul under the Ground Based Radar Digitization (GBRD) program [SRC-0186, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P175" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R175" t="inlineStr">
-        <is>
-          <t>SRC-0008</t>
-        </is>
-      </c>
-      <c r="S175" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T175" t="inlineStr">
-        <is>
-          <t>SRC-0008, SRC-0143, SRC-0190, SRC-0132, SRC-0186</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>RAD-0175</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>SITE-0195</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Sea-Based X-Band Radar (Sbx-1)</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N176" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O176" t="inlineStr">
-        <is>
-          <t>The Sea-Based X-Band Radar (SBX-1) is a floating, self-propelled Active Electronically Scanned Array (AESA) radar platform operating in the X-band frequency [SRC-0178, SRC-0178, SRC-0178]. Developed by Raytheon (radar) and Boeing (prime contractor) and deployed in 2006, the radar is mounted on a heavily modified fifth-generation CS-50 twin-hulled semi-submersible drilling rig [SRC-0178, SRC-0178, SRC-0178, SRC-0190]. The radar antenna weighs 1,800 tonnes and is protected by a flexible, positive-air-pressure radome measuring 103 feet high and 120 feet in diameter [SRC-0178, SRC-0179, SRC-0190]. It contains approximately 45,000 solid-state transmit-receive modules that can mechanically move ±270 degrees in azimuth and up to 85 degrees in elevation [SRC-0190, SRC-0178, SRC-0179]. The system's primary purpose is ballistic missile defense, specifically midcourse discrimination—identifying lethal enemy warheads from decoys—and providing precision tracking data to the Ground-Based Midcourse Defense (GMD) system [SRC-0190, SRC-0178, SRC-0179]. Its X-band wavelength provides extreme resolution, capable of tracking an object the size of a baseball from 2,500 to 2,900 miles away [SRC-0178, SRC-0190, SRC-0179]. Currently, SBX-1 is an active, operational asset managed by the Military Sealift Command; it received a new radome in December 2025 and routinely deploys in the Pacific Ocean to monitor missile threats [SRC-0129, SRC-0129, SRC-0190].</t>
-        </is>
-      </c>
-      <c r="P176" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R176" t="inlineStr">
-        <is>
-          <t>SRC-0178</t>
-        </is>
-      </c>
-      <c r="S176" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T176" t="inlineStr">
-        <is>
-          <t>SRC-0178, SRC-0190, SRC-0179, SRC-0129</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>RAD-0176</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>SITE-0196</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>An/Tpy-2</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N177" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O177" t="inlineStr">
-        <is>
-          <t>The AN/TPY-2 is a high-resolution, mobile Active Electronically Scanned Array (AESA) radar operating in the X-band (8.55–10 GHz) [SRC-0190, SRC-0011, SRC-0012]. Manufactured by Raytheon and initially introduced in 2007, the system consists of a trailer-mounted 9.2-square-meter antenna array utilizing thousands of solid-state transmit/receive modules [SRC-0011, SRC-0011, SRC-0183, SRC-0190]. Recently, Raytheon completed upgrades equipping the radar with Gallium Nitride (GaN) semiconductor technology, which significantly enhanced its search volume, sensitivity, and detection range [SRC-0190, SRC-0012, SRC-0158]. The AN/TPY-2 has a detection range exceeding 1,000 kilometers and provides 120-degree sector coverage while tracking hundreds of targets simultaneously [SRC-0190, SRC-0011, SRC-0011]. The radar serves a dual-purpose mission: in "Terminal Mode," it acts as the primary fire control radar for the Terminal High Altitude Area Defense (THAAD) system, guiding interceptors against descending warheads; in "Forward-Based Mode," it acts as a strategic early warning sensor deployed globally to detect ballistic missiles in their boost and early ascent phases [SRC-0190, SRC-0012]. Currently, the system is fully operational with deployments in regions such as Japan, South Korea, Israel, and the Middle East, and receives ongoing modernization and sustainment support under a recent $966 million contract modification [SRC-0011, SRC-0183, SRC-0190, SRC-0158].</t>
-        </is>
-      </c>
-      <c r="P177" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R177" t="inlineStr">
-        <is>
-          <t>SRC-0190</t>
-        </is>
-      </c>
-      <c r="S177" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T177" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0011, SRC-0012, SRC-0183, SRC-0158</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>RAD-0177</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>SITE-0219</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Air Route Surveillance Radar (Arsr)</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N178" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O178" t="inlineStr">
-        <is>
-          <t>The former Calumet Air Force Station, located in Michigan, was historically utilized as a United States Air Force radar facility until its closure in 1988 [SRC-0110]. During its operational tenure, the facility served as a Continental United States (CONUS) station for the Air Route Surveillance Radar (ARSR) network, a system jointly operated by the Air Force and the Federal Aviation Administration to monitor internal and border airspace [SRC-0016], [SRC-0016]. While the exact ARSR variant stationed at Calumet is not detailed in the sources, the ARSR family consists of long-range 3D surveillance radars that operate in the L-band frequency (1.215–1.4 GHz) [SRC-0013], [SRC-0016]. These systems were manufactured by defense contractors such as Raytheon, Westinghouse, and Northrop Grumman, with the earliest models introduced in 1958 [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. They were designed with a look-down capability to detect low-flying aircraft attempting to elude detection, advanced clutter reduction processing, and an effective tracking range of 200 to 250 nautical miles [SRC-0013], [SRC-0016], [SRC-0016]. Following the end of its mission as a military radar facility, the Calumet site was repurposed as a youth correctional facility from 1998 to 2004, and the land has remained vacant and unused since 2004 [SRC-0110].</t>
-        </is>
-      </c>
-      <c r="P178" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R178" t="inlineStr">
-        <is>
-          <t>SRC-0110</t>
-        </is>
-      </c>
-      <c r="S178" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
-          <t>SRC-0110, SRC-0016, SRC-0013</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>RAD-0178</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>SITE-0216</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Air Route Surveillance Radar (Arsr)</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N179" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O179" t="inlineStr">
-        <is>
-          <t>The Tonopah Test Range in Nevada operates as a Continental United States (CONUS) station within the Air Route Surveillance Radar (ARSR) network, a long-range radar system utilized jointly by the United States Air Force and the Federal Aviation Administration to control and monitor airspace within and around U.S. borders [SRC-0016], [SRC-0016]. Although the exact ARSR model installed at Tonopah is unspecified in the provided documentation, ARSR systems universally operate in the L-band frequency range (1.215–1.4 GHz) as long-range, three-dimensional air surveillance radars [SRC-0013], [SRC-0016]. Primary manufacturers of the ARSR series include Raytheon, Westinghouse, and Northrop Grumman, with the system's first generation introduced in 1958 [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. The radars generally provide an effective target detection range between 200 and 250 nautical miles, utilizing hardware and software post-processing to reduce clutter and detect low-flying targets [SRC-0013], [SRC-0016], [SRC-0016], [SRC-0016]. In addition to its role in the ARSR network, the Tonopah Test Range features a dedicated Electronic Combat (EC) Range [SRC-0106]. This EC range is specifically designed to provide a realistic, simulated enemy radar environment to support the training of aircrews in electronic warfare, although the exact designations of the hostile threat radars simulated at this location are not detailed [SRC-0106].</t>
-        </is>
-      </c>
-      <c r="P179" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R179" t="inlineStr">
-        <is>
-          <t>SRC-0016</t>
-        </is>
-      </c>
-      <c r="S179" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
-          <t>SRC-0016, SRC-0013, SRC-0106</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>RAD-0179</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>SITE-0224</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>L-88(V)3 Radar</t>
-        </is>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N180" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O180" t="inlineStr">
-        <is>
-          <t>The L-88(V)3 radar is an airborne ground surveillance radar operating as the primary payload for the Tethered Aerostat Radar System (TARS) at Cudjoe Key, Florida [SRC-0190, SRC-0197]. Manufactured by Lockheed Martin, the L-88(V)3 is a lightweight derivative of the standard L-88 radar, specifically operating in the L-band frequency [SRC-0190, SRC-0197]. The first aerostats were assigned to the United States Air Force at Cudjoe Key in December 1980, though Lockheed Martin was awarded subsequent contracts (such as in 2002) to provide the upgraded L-88(V)3 radar systems for the TARS network [SRC-0197, SRC-0098]. The radar is mounted beneath a 275,000-cubic-foot (275K) Lockheed Martin blimp tethered at high altitudes (up to 15,000 feet) and enclosed by a fabric windscreen [SRC-0197, SRC-0197]. The radar utilizes a rotating antenna to provide 360-degree coverage at maximum detection ranges of up to 200 nautical miles (370 kilometers) [SRC-0190, SRC-0098, SRC-0197]. The primary purpose of the radar is to conduct low-level surveillance across the Straits of Florida and the Caribbean, functioning as an anti-drug smuggling and air sovereignty asset capable of tracking low-flying aircraft and surface vessels [SRC-0196, SRC-0197]. Currently, the system remains in active service and is operated by the U.S. Customs and Border Protection (CBP) agency, continuously feeding track data to the Air and Marine Operations Center [SRC-0197, SRC-0196, SRC-0197].</t>
-        </is>
-      </c>
-      <c r="P180" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R180" t="inlineStr">
-        <is>
-          <t>SRC-0190</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
-          <t>SRC-0190, SRC-0197, SRC-0098, SRC-0196</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>RAD-0180</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>SITE-0225</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>L-88 Radar</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N181" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O181" t="inlineStr">
-        <is>
-          <t>The L-88 radar is a downward-looking, airborne ground surveillance system deployed at the Tethered Aerostat Radar System (TARS) site in Deming, New Mexico [SRC-0197, SRC-0098, SRC-0197]. Built and integrated by Lockheed Martin, the radar operates in the L-band frequency and features a 29-foot rotating antenna enclosed in a protective aerodynamic radome windscreen [SRC-0190, SRC-0098]. Following a 1999 modernization contract from the U.S. Air Force, the Deming TARS installation was successfully upgraded and transitioned to the standard 420K/L-88 configuration [SRC-0098]. Designed to be lofted to an operational altitude of 15,000 feet by a massive 420,000-cubic-foot helium-filled aerostat, the radar provides uninterrupted, 360-degree coverage over a 200-nautical-mile radius [SRC-0190, SRC-0197, SRC-0098]. The L-88's core purpose is to support North American Aerospace Defense Command (NORAD) and federal law enforcement by detecting and tracking low-altitude, low-observable threats such as drug-smuggling aircraft, ultra-lights, and drones crossing the United States-Mexico border [SRC-0196, SRC-0197]. Despite its robust design and capability to withstand severe weather, the current operational status of the Deming aerostat radar site is listed as "Not Flying" [SRC-0197]. The broader TARS program, however, remains actively funded and operated under the jurisdiction of U.S. Customs and Border Protection (CBP) [SRC-0197].</t>
-        </is>
-      </c>
-      <c r="P181" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R181" t="inlineStr">
-        <is>
-          <t>SRC-0197</t>
-        </is>
-      </c>
-      <c r="S181" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T181" t="inlineStr">
-        <is>
-          <t>SRC-0197, SRC-0098, SRC-0190, SRC-0196</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>RAD-0181</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>SITE-0336</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Metric Tracking Radars</t>
-        </is>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N182" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O182" t="inlineStr">
-        <is>
-          <t>The Kennedy Space Center (KSC) in Florida, operating in conjunction with the Cape Canaveral Air Force Station and Patrick Air Force Base as part of the Eastern Space and Missile Center, utilizes a network of metric tracking radars [SRC-0106], [SRC-0106], [SRC-0189]. While the exact manufacturer, operating frequency bands, and specific years of construction for the individual radar units physically situated at KSC are not fully detailed in the provided sources, these precision tracking systems are fundamental to the Eastern Range's launch operations [SRC-0106], [SRC-0106]. The primary purpose of these metric radars is to provide highly accurate, real-time trajectory and positioning data to central computer systems during the prelaunch, launch, and postlaunch phases of test vehicles [SRC-0106], [SRC-0106].
-These radar systems are highly capable, configured for either beacon tracking or echo tracking, which allows them to reliably monitor rockets, space boosters, and space shuttles as they ascend [SRC-0106], [SRC-0162]. The data generated by these radars is critical for range safety, enabling flight safety officers to monitor the vehicle's flight path, predict impact points, and ensure the launch remains within safe operational corridors [SRC-0118], [SRC-0118]. Currently, these metric tracking radars remain an active, integral component of the Eastern Range's instrumentation, working alongside telemetry and optical systems to support military, civilian, and commercial missions [SRC-0106], [SRC-0189], [SRC-0189].</t>
-        </is>
-      </c>
-      <c r="P182" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R182" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-      <c r="S182" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T182" t="inlineStr">
-        <is>
-          <t>SRC-0106, SRC-0189, SRC-0162, SRC-0118</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>RAD-0182</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>SITE-0337</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>Wallops Island (Nasa) Radar</t>
-        </is>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N183" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O183" t="inlineStr">
-        <is>
-          <t>The Wallops Flight Facility, operated by NASA in Virginia, features an on-site radar system dedicated to supporting the facility's aerospace testing missions [SRC-0106], [SRC-0154], [SRC-0154]. While the specific technical parameters of this radar—such as its exact hardware type, frequency band, manufacturer, and year of construction—are not detailed in the provided sources, its presence is documented as part of the Eastern Test Range's broader tracking and instrumentation network [SRC-0106]. The primary purpose of the radar infrastructure at Wallops Island is to provide crucial flight tracking and range safety data for the rockets, sounding rockets, and suborbital missions launched from the site [SRC-0106]. 
-Although the on-site radar's specific capabilities are not exhaustively described, the launch activities at Wallops Flight Facility are frequently supported and monitored by highly advanced external radar systems. For instance, the Long Range Discrimination Radar (LRDR) and its scaled Solid State Radar Integration Site (SSRIS) prototype in Moorestown, New Jersey, have actively tracked space launches originating from NASA's Wallops Island to test and verify their own tracking software [SRC-0003], [SRC-0100]. During these exercises, the external phased-array systems successfully demonstrated their ability to acquire and track Wallops-launched rockets, highlighting the facility's active, ongoing status as a key launch site within the United States' space testing infrastructure [SRC-0100].</t>
-        </is>
-      </c>
-      <c r="P183" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R183" t="inlineStr">
-        <is>
-          <t>SRC-0106</t>
-        </is>
-      </c>
-      <c r="S183" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T183" t="inlineStr">
-        <is>
-          <t>SRC-0106, SRC-0154, SRC-0003, SRC-0100</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>RAD-0183</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>SITE-0340</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Mobile Multi-Sensor Tspi System (Mmts) Radar</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N184" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O184" t="inlineStr">
-        <is>
-          <t>The Mobile Multi-Sensor Time-Space-Position-Information-System (MMTS) is a specialized tracking system delivered to and integrated into Redstone Arsenal via the TENA network architecture [SRC-0085]. Manufactured by Photo-Sonics, Inc., under a contract awarded by the U.S. Army Program Executive Office for Simulation, Training, and Instrumentation (PEO STRI), this mobile platform incorporates both high-performance optical tracking pedestals and a radar unit that functions as a comprehensive single-station solution [SRC-0085]. While the specific frequency band and exact year of construction for the radar component are not detailed in the sources, the system's primary purpose is to track and provide highly accurate Time-Space-Position-Information (TSPI) for high-speed weapons, including hyper-velocity projectiles [SRC-0085].
-The MMTS radar system boasts advanced capabilities such as a high-speed auto tracker capable of capturing 250 frames per second, high dynamics, and fully integrated pedestal and sensor control software [SRC-0085]. It also features automated stellar and turn-and-dump calibration, alongside a simulation system and a range interface computer designed to calculate real-time three-dimensional data [SRC-0085]. Integrated data-reduction software further enables six degrees of freedom calculations [SRC-0085]. Before its final delivery to the Redstone facility, the MMTS successfully completed functional testing and its Final Site Acceptance Test at the White Sands Missile Range, proving its current operational readiness [SRC-0085].</t>
-        </is>
-      </c>
-      <c r="P184" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R184" t="inlineStr">
-        <is>
-          <t>SRC-0085</t>
-        </is>
-      </c>
-      <c r="S184" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>SRC-0085</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>RAD-0184</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>SITE-0353</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Sea-Based X-Band Radar (Sbx-1)</t>
-        </is>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N185" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O185" t="inlineStr">
-        <is>
-          <t>The Sea-Based X-Band Radar (SBX-1) is nominally assigned to Adak Island, Alaska, as its official homeport, although the radar has never actually moored or deployed there despite the installation of a $26 million mooring chain system [SRC-0179, SRC-0179, SRC-0179, SRC-0179]. Developed by Raytheon and Boeing, the SBX-1 was deployed in 2006 as a floating, mobile active electronically scanned array (AESA) early-warning radar [SRC-0179, SRC-0178, SRC-0178]. It operates in the X-band, providing high-resolution tracking capabilities that allow it to differentiate lethal warheads from decoys during the midcourse phase of a ballistic missile's flight [SRC-0178, SRC-0179]. The massive 384-square-meter antenna is mounted on a semi-submersible platform and currently houses 22,000 solid-state transmit-receive modules, though it has the capacity for 45,000 [SRC-0179, SRC-0179, SRC-0179]. The radar is incredibly powerful, with the ability to track baseball-sized objects from 2,900 miles away [SRC-0179]. Its primary purpose at its intended Adak base was to track missile threats launched toward the United States from North Korea and China [SRC-0179]. However, in practice, the SBX-1 roams the Pacific Ocean to monitor missile tests and relies on Pearl Harbor, Hawaii, for its maintenance and port stays [SRC-0179, SRC-0179, SRC-0179].</t>
-        </is>
-      </c>
-      <c r="P185" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R185" t="inlineStr">
-        <is>
-          <t>SRC-0179</t>
-        </is>
-      </c>
-      <c r="S185" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T185" t="inlineStr">
-        <is>
-          <t>SRC-0179, SRC-0178</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>RAD-0185</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>SITE-0362</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>An/Tpy-2</t>
-        </is>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>See description</t>
-        </is>
-      </c>
-      <c r="N186" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="O186" t="inlineStr">
-        <is>
-          <t>The AN/TPY-2 is a transportable, high-resolution, X-band active electronically scanned array (AESA) radar manufactured by Raytheon [SRC-0011, SRC-0012]. Introduced in 2007, this system is a primary component of the U.S. military's layered ballistic missile defense network, notably serving as the radar for the THAAD system [SRC-0012, SRC-0011, SRC-0011]. It operates in the X-band frequency (8.55–10 GHz), which provides a shorter wavelength and finer resolution necessary to differentiate between hostile warheads, clutter, and decoys during the midcourse and terminal phases of a ballistic missile's flight [SRC-0011, SRC-0012]. The radar has a detection range of over 1,000 kilometers and is capable of simultaneously tracking hundreds of targets [SRC-0011, SRC-0011, SRC-0011]. Featuring electronic beam steering, the AN/TPY-2 provides exceptional target discrimination and near-instantaneous updates [SRC-0011, SRC-0011]. The system is highly mobile and trailer-mounted, requiring only a small crew to operate [SRC-0011]. An AN/TPY-2 radar has been deployed to the Shariki region in Japan. Its primary purpose at this forward-based location is to collect strategic-level early warning information on North Korean missile developments, warn Japan of incoming warheads, and scan Russian territory near Japan [SRC-0012]. The radar seamlessly integrates with U.S. and allied missile defense networks, passing critical trajectory data to downstream fire control systems [SRC-0011, SRC-0012].</t>
-        </is>
-      </c>
-      <c r="P186" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="R186" t="inlineStr">
-        <is>
-          <t>SRC-0011</t>
-        </is>
-      </c>
-      <c r="S186" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="T186" t="inlineStr">
-        <is>
-          <t>SRC-0011, SRC-0012</t>
         </is>
       </c>
     </row>
